--- a/data/leaves.xlsx
+++ b/data/leaves.xlsx
@@ -5,22 +5,35 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="B:\1MY-PROJECT\1MY-PROJECT\attendance_report\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mohamed.subhy\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE076E94-0F3E-4F5A-9C9C-06575BE42821}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D74AFE6-B1A9-40BE-A610-87486A6CC1A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="673" uniqueCount="215">
   <si>
     <t>leave_id</t>
   </si>
@@ -68,20 +81,630 @@
   </si>
   <si>
     <t>created_by</t>
+  </si>
+  <si>
+    <t>LV-1</t>
+  </si>
+  <si>
+    <t>معتمدة</t>
+  </si>
+  <si>
+    <t>LV-2</t>
+  </si>
+  <si>
+    <t>مرضية</t>
+  </si>
+  <si>
+    <t>تقرير طبي</t>
+  </si>
+  <si>
+    <t>26883</t>
+  </si>
+  <si>
+    <t>27164</t>
+  </si>
+  <si>
+    <t>29933</t>
+  </si>
+  <si>
+    <t>29995</t>
+  </si>
+  <si>
+    <t>30630</t>
+  </si>
+  <si>
+    <t>32348</t>
+  </si>
+  <si>
+    <t>32391</t>
+  </si>
+  <si>
+    <t>24135</t>
+  </si>
+  <si>
+    <t>26752</t>
+  </si>
+  <si>
+    <t>27313</t>
+  </si>
+  <si>
+    <t>27510</t>
+  </si>
+  <si>
+    <t>27943</t>
+  </si>
+  <si>
+    <t>28217</t>
+  </si>
+  <si>
+    <t>29446</t>
+  </si>
+  <si>
+    <t>29977</t>
+  </si>
+  <si>
+    <t>30361</t>
+  </si>
+  <si>
+    <t>30492</t>
+  </si>
+  <si>
+    <t>30536</t>
+  </si>
+  <si>
+    <t>30541</t>
+  </si>
+  <si>
+    <t>30562</t>
+  </si>
+  <si>
+    <t>31282</t>
+  </si>
+  <si>
+    <t>31286</t>
+  </si>
+  <si>
+    <t>31384</t>
+  </si>
+  <si>
+    <t>31731</t>
+  </si>
+  <si>
+    <t>31976</t>
+  </si>
+  <si>
+    <t>25298</t>
+  </si>
+  <si>
+    <t>26691</t>
+  </si>
+  <si>
+    <t>26787</t>
+  </si>
+  <si>
+    <t>28331</t>
+  </si>
+  <si>
+    <t>30584</t>
+  </si>
+  <si>
+    <t>30882</t>
+  </si>
+  <si>
+    <t>31039</t>
+  </si>
+  <si>
+    <t>31739</t>
+  </si>
+  <si>
+    <t>32083</t>
+  </si>
+  <si>
+    <t>admin</t>
+  </si>
+  <si>
+    <t>LV-3</t>
+  </si>
+  <si>
+    <t>LV-4</t>
+  </si>
+  <si>
+    <t>LV-5</t>
+  </si>
+  <si>
+    <t>LV-6</t>
+  </si>
+  <si>
+    <t>LV-7</t>
+  </si>
+  <si>
+    <t>LV-8</t>
+  </si>
+  <si>
+    <t>LV-9</t>
+  </si>
+  <si>
+    <t>LV-10</t>
+  </si>
+  <si>
+    <t>LV-11</t>
+  </si>
+  <si>
+    <t>LV-12</t>
+  </si>
+  <si>
+    <t>LV-13</t>
+  </si>
+  <si>
+    <t>LV-14</t>
+  </si>
+  <si>
+    <t>LV-15</t>
+  </si>
+  <si>
+    <t>LV-16</t>
+  </si>
+  <si>
+    <t>LV-17</t>
+  </si>
+  <si>
+    <t>LV-18</t>
+  </si>
+  <si>
+    <t>LV-19</t>
+  </si>
+  <si>
+    <t>LV-20</t>
+  </si>
+  <si>
+    <t>LV-21</t>
+  </si>
+  <si>
+    <t>LV-22</t>
+  </si>
+  <si>
+    <t>LV-23</t>
+  </si>
+  <si>
+    <t>LV-24</t>
+  </si>
+  <si>
+    <t>LV-25</t>
+  </si>
+  <si>
+    <t>LV-26</t>
+  </si>
+  <si>
+    <t>LV-27</t>
+  </si>
+  <si>
+    <t>LV-28</t>
+  </si>
+  <si>
+    <t>LV-29</t>
+  </si>
+  <si>
+    <t>LV-30</t>
+  </si>
+  <si>
+    <t>LV-31</t>
+  </si>
+  <si>
+    <t>LV-32</t>
+  </si>
+  <si>
+    <t>LV-33</t>
+  </si>
+  <si>
+    <t>LV-34</t>
+  </si>
+  <si>
+    <t>LV-35</t>
+  </si>
+  <si>
+    <t>LV-36</t>
+  </si>
+  <si>
+    <t>LV-37</t>
+  </si>
+  <si>
+    <t>LV-38</t>
+  </si>
+  <si>
+    <t>LV-39</t>
+  </si>
+  <si>
+    <t>LV-40</t>
+  </si>
+  <si>
+    <t>LV-41</t>
+  </si>
+  <si>
+    <t>LV-42</t>
+  </si>
+  <si>
+    <t>LV-43</t>
+  </si>
+  <si>
+    <t>LV-44</t>
+  </si>
+  <si>
+    <t>LV-45</t>
+  </si>
+  <si>
+    <t>LV-46</t>
+  </si>
+  <si>
+    <t>LV-47</t>
+  </si>
+  <si>
+    <t>LV-48</t>
+  </si>
+  <si>
+    <t>LV-49</t>
+  </si>
+  <si>
+    <t>LV-50</t>
+  </si>
+  <si>
+    <t>LV-51</t>
+  </si>
+  <si>
+    <t>LV-52</t>
+  </si>
+  <si>
+    <t>LV-53</t>
+  </si>
+  <si>
+    <t>LV-54</t>
+  </si>
+  <si>
+    <t>LV-55</t>
+  </si>
+  <si>
+    <t>LV-56</t>
+  </si>
+  <si>
+    <t>LV-57</t>
+  </si>
+  <si>
+    <t>LV-58</t>
+  </si>
+  <si>
+    <t>LV-59</t>
+  </si>
+  <si>
+    <t>LV-60</t>
+  </si>
+  <si>
+    <t>محمد امينو لاباران</t>
+  </si>
+  <si>
+    <t>MOHAMMAD  AMINU LABA</t>
+  </si>
+  <si>
+    <t>TS | Others</t>
+  </si>
+  <si>
+    <t>اخصائي مشتريات</t>
+  </si>
+  <si>
+    <t>راكان وليد محمد النداف</t>
+  </si>
+  <si>
+    <t>RAKAN WALEED  MOHAMM</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> | Others</t>
+  </si>
+  <si>
+    <t>محاسب</t>
+  </si>
+  <si>
+    <t>ماجد عبدالله عبدالعزيز الخميس</t>
+  </si>
+  <si>
+    <t>MAJED ABDULLAH ABDUL</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> | Security</t>
+  </si>
+  <si>
+    <t>حارس امن</t>
+  </si>
+  <si>
+    <t>محمد أيمن غيث</t>
+  </si>
+  <si>
+    <t>MOHAMMAD AYMAN GHAIT</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> | Accounting</t>
+  </si>
+  <si>
+    <t>محمد احمد الحميد</t>
+  </si>
+  <si>
+    <t>AHMED MOHAMED ALHMED</t>
+  </si>
+  <si>
+    <t>اسماعيل عيسى عبدالله المتروك</t>
+  </si>
+  <si>
+    <t>ISMAIEL EISSA ABDULL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PROD | </t>
+  </si>
+  <si>
+    <t>مهندس جودة كهربائي</t>
+  </si>
+  <si>
+    <t>سالم مشعل صويحي نخيلان</t>
+  </si>
+  <si>
+    <t>salem meshall suwayh</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> | Sales</t>
+  </si>
+  <si>
+    <t>مهندس تطوير أعمال</t>
+  </si>
+  <si>
+    <t>معاذ  عبدالرحيم  سليمان  ابداح</t>
+  </si>
+  <si>
+    <t>MUATH ABDURAHEEM SUL</t>
+  </si>
+  <si>
+    <t>ADMN | Others</t>
+  </si>
+  <si>
+    <t>نور صالح سامح الدوسري</t>
+  </si>
+  <si>
+    <t>NOOR  SALEH SAMEH AL</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> | Production</t>
+  </si>
+  <si>
+    <t>عامل انتاج</t>
+  </si>
+  <si>
+    <t>زياد مرزوق سالم ال سبيهين</t>
+  </si>
+  <si>
+    <t>ZIYAD MARZOUK SALIM</t>
+  </si>
+  <si>
+    <t>Prod_Area | Others</t>
+  </si>
+  <si>
+    <t>منسق مواد</t>
+  </si>
+  <si>
+    <t>ايهاب فهد المرمش</t>
+  </si>
+  <si>
+    <t>EHAB FAHAD ALMARMASH</t>
+  </si>
+  <si>
+    <t>فني امن وسلامة</t>
+  </si>
+  <si>
+    <t>مشعل عبيدان علي الشهيل</t>
+  </si>
+  <si>
+    <t>MISHAAL OBAIDAN ALI</t>
+  </si>
+  <si>
+    <t>فني سلامة</t>
+  </si>
+  <si>
+    <t>نواف رشيد  البقعاوي</t>
+  </si>
+  <si>
+    <t>NAWAF RASHEED  ALBAQ</t>
+  </si>
+  <si>
+    <t>محلل نظم المعلومات</t>
+  </si>
+  <si>
+    <t>مشعل راضي الشمري</t>
+  </si>
+  <si>
+    <t>MESHAL RADHI ALSHAMM</t>
+  </si>
+  <si>
+    <t>فني انتاج</t>
+  </si>
+  <si>
+    <t>علي خالد علي السعدون</t>
+  </si>
+  <si>
+    <t>ALI KHALID ALI ALSAD</t>
+  </si>
+  <si>
+    <t>مهندس انتاج</t>
+  </si>
+  <si>
+    <t>سالم جارالله التميمي</t>
+  </si>
+  <si>
+    <t>SALEM JARALLAH ALTAM</t>
+  </si>
+  <si>
+    <t>عبدالله عبيدالله الشمري</t>
+  </si>
+  <si>
+    <t>ABDULLAH OBAIDULLAH</t>
+  </si>
+  <si>
+    <t>عمر سعود الحربي</t>
+  </si>
+  <si>
+    <t>OMR SAUD ALHARBI</t>
+  </si>
+  <si>
+    <t>عبدالاله خالد محمد الشمري</t>
+  </si>
+  <si>
+    <t>ABDULLAH KHALID MOHA</t>
+  </si>
+  <si>
+    <t>ناصر حضيري الشمري</t>
+  </si>
+  <si>
+    <t>NASSER HUDHAIRI ALSH</t>
+  </si>
+  <si>
+    <t>ريان بركة الشمري</t>
+  </si>
+  <si>
+    <t>RAYAN BRUKAH ALSHAMM</t>
+  </si>
+  <si>
+    <t>محمد خالد المنيعي</t>
+  </si>
+  <si>
+    <t>MOHAMMED KHALED ALME</t>
+  </si>
+  <si>
+    <t>مهند سعود الخطيب</t>
+  </si>
+  <si>
+    <t>AUHAND SAUD ALKHATIB</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> | Procurement</t>
+  </si>
+  <si>
+    <t>أخصائي مشتريات</t>
+  </si>
+  <si>
+    <t>مشاري راجح محمد الشمري</t>
+  </si>
+  <si>
+    <t>MESHARI RAJEH M ALSH</t>
+  </si>
+  <si>
+    <t>ماجد عامر هجان العنزي</t>
+  </si>
+  <si>
+    <t>MAJED AMER HAJAN ALA</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> | </t>
+  </si>
+  <si>
+    <t>عبدالله رشيد سعد المجحد</t>
+  </si>
+  <si>
+    <t>ABDULLAH RASHEED SAA</t>
+  </si>
+  <si>
+    <t>GN | Admin</t>
+  </si>
+  <si>
+    <t>استقبال</t>
+  </si>
+  <si>
+    <t>ابراهيم سعود ابراهيم العليط</t>
+  </si>
+  <si>
+    <t>IBRAHIM SAUD  IBRAHI</t>
+  </si>
+  <si>
+    <t>ملاحظ متابعة مواد</t>
+  </si>
+  <si>
+    <t>محمد مرزوق فهد الشمري</t>
+  </si>
+  <si>
+    <t>MOHAMMED  MARZOUQ  F</t>
+  </si>
+  <si>
+    <t>BU | Production</t>
+  </si>
+  <si>
+    <t>اخصائي جودة</t>
+  </si>
+  <si>
+    <t>ابراهيم محمد علي عبدالقوي</t>
+  </si>
+  <si>
+    <t>EBRAHIM MOHAMMED ALI</t>
+  </si>
+  <si>
+    <t>عامل</t>
+  </si>
+  <si>
+    <t>قبلان بن غانم الشمري</t>
+  </si>
+  <si>
+    <t>QUBLAN GHANEM ALSHAM</t>
+  </si>
+  <si>
+    <t>سلطان منصور التميمي</t>
+  </si>
+  <si>
+    <t>SULTAN MANSOUR ALTAM</t>
+  </si>
+  <si>
+    <t>مهندس شبكات</t>
+  </si>
+  <si>
+    <t>يوسف محمد الميناوي</t>
+  </si>
+  <si>
+    <t>YOUSEF MOHAMMED ALMA</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> | Admin</t>
+  </si>
+  <si>
+    <t>مشرف حركة</t>
+  </si>
+  <si>
+    <t>سليمان عبدالله سليمان البور</t>
+  </si>
+  <si>
+    <t>SULAIMAN ABDULLAH S</t>
+  </si>
+  <si>
+    <t>الجوهره عثمان العبلان</t>
+  </si>
+  <si>
+    <t>ALJAWHARAH OTHMAN AL</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="166" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+  <numFmts count="1">
+    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -107,15 +730,50 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="2">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -413,10 +1071,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P4"/>
+  <dimension ref="A1:Y76"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="7.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.75" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="25.375" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="23.125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="5.875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.75" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7.375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="17.875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="9.875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -466,22 +1140,2741 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="O2" s="2"/>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="I3" s="1"/>
-      <c r="J3" s="1"/>
-      <c r="O3" s="2"/>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
-      <c r="O4" s="2"/>
+    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" t="s">
+        <v>114</v>
+      </c>
+      <c r="E2" t="s">
+        <v>115</v>
+      </c>
+      <c r="F2" t="s">
+        <v>116</v>
+      </c>
+      <c r="G2" t="s">
+        <v>117</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I2" s="6">
+        <v>46069</v>
+      </c>
+      <c r="J2" s="6">
+        <v>46126</v>
+      </c>
+      <c r="K2" t="s">
+        <v>17</v>
+      </c>
+      <c r="N2" t="s">
+        <v>20</v>
+      </c>
+      <c r="O2" s="1">
+        <v>46154</v>
+      </c>
+      <c r="P2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="3" spans="1:25" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3" t="s">
+        <v>118</v>
+      </c>
+      <c r="E3" t="s">
+        <v>119</v>
+      </c>
+      <c r="F3" t="s">
+        <v>120</v>
+      </c>
+      <c r="G3" t="s">
+        <v>121</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I3" s="6">
+        <v>46127</v>
+      </c>
+      <c r="J3" s="6">
+        <v>46127</v>
+      </c>
+      <c r="K3" t="s">
+        <v>17</v>
+      </c>
+      <c r="N3" t="s">
+        <v>20</v>
+      </c>
+      <c r="O3" s="1">
+        <v>46154</v>
+      </c>
+      <c r="P3" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q3" s="2"/>
+      <c r="R3" s="2"/>
+      <c r="S3" s="2"/>
+      <c r="T3" s="2"/>
+      <c r="U3" s="2"/>
+      <c r="V3" s="2"/>
+      <c r="W3" s="2"/>
+      <c r="X3" s="2"/>
+      <c r="Y3" s="2"/>
+    </row>
+    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" t="s">
+        <v>122</v>
+      </c>
+      <c r="E4" t="s">
+        <v>123</v>
+      </c>
+      <c r="F4" t="s">
+        <v>124</v>
+      </c>
+      <c r="G4" t="s">
+        <v>125</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I4" s="6">
+        <v>46140</v>
+      </c>
+      <c r="J4" s="6">
+        <v>46140</v>
+      </c>
+      <c r="K4" t="s">
+        <v>17</v>
+      </c>
+      <c r="N4" t="s">
+        <v>20</v>
+      </c>
+      <c r="O4" s="1">
+        <v>46154</v>
+      </c>
+      <c r="P4" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q4" s="3"/>
+      <c r="R4" s="3"/>
+      <c r="S4" s="3"/>
+      <c r="T4" s="3"/>
+      <c r="U4" s="3"/>
+      <c r="V4" s="4"/>
+      <c r="W4" s="4"/>
+      <c r="X4" s="3"/>
+      <c r="Y4" s="3"/>
+    </row>
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>57</v>
+      </c>
+      <c r="B5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" t="s">
+        <v>126</v>
+      </c>
+      <c r="E5" t="s">
+        <v>127</v>
+      </c>
+      <c r="F5" t="s">
+        <v>128</v>
+      </c>
+      <c r="G5" t="s">
+        <v>121</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I5" s="6">
+        <v>46140</v>
+      </c>
+      <c r="J5" s="6">
+        <v>46143</v>
+      </c>
+      <c r="K5" t="s">
+        <v>17</v>
+      </c>
+      <c r="N5" t="s">
+        <v>20</v>
+      </c>
+      <c r="O5" s="1">
+        <v>46154</v>
+      </c>
+      <c r="P5" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q5" s="3"/>
+      <c r="R5" s="3"/>
+      <c r="S5" s="3"/>
+      <c r="T5" s="3"/>
+      <c r="U5" s="3"/>
+      <c r="V5" s="4"/>
+      <c r="W5" s="4"/>
+      <c r="X5" s="3"/>
+      <c r="Y5" s="3"/>
+    </row>
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>58</v>
+      </c>
+      <c r="B6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" t="s">
+        <v>129</v>
+      </c>
+      <c r="E6" t="s">
+        <v>130</v>
+      </c>
+      <c r="F6" t="s">
+        <v>128</v>
+      </c>
+      <c r="G6" t="s">
+        <v>121</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I6" s="6">
+        <v>46140</v>
+      </c>
+      <c r="J6" s="6">
+        <v>46140</v>
+      </c>
+      <c r="K6" t="s">
+        <v>17</v>
+      </c>
+      <c r="N6" t="s">
+        <v>20</v>
+      </c>
+      <c r="O6" s="1">
+        <v>46154</v>
+      </c>
+      <c r="P6" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>59</v>
+      </c>
+      <c r="B7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" t="s">
+        <v>129</v>
+      </c>
+      <c r="E7" t="s">
+        <v>130</v>
+      </c>
+      <c r="F7" t="s">
+        <v>128</v>
+      </c>
+      <c r="G7" t="s">
+        <v>121</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I7" s="6">
+        <v>46131</v>
+      </c>
+      <c r="J7" s="6">
+        <v>46131</v>
+      </c>
+      <c r="K7" t="s">
+        <v>17</v>
+      </c>
+      <c r="N7" t="s">
+        <v>20</v>
+      </c>
+      <c r="O7" s="1">
+        <v>46154</v>
+      </c>
+      <c r="P7" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>60</v>
+      </c>
+      <c r="B8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" t="s">
+        <v>25</v>
+      </c>
+      <c r="D8" t="s">
+        <v>129</v>
+      </c>
+      <c r="E8" t="s">
+        <v>130</v>
+      </c>
+      <c r="F8" t="s">
+        <v>128</v>
+      </c>
+      <c r="G8" t="s">
+        <v>121</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I8" s="6">
+        <v>46134</v>
+      </c>
+      <c r="J8" s="6">
+        <v>46134</v>
+      </c>
+      <c r="K8" t="s">
+        <v>17</v>
+      </c>
+      <c r="N8" t="s">
+        <v>20</v>
+      </c>
+      <c r="O8" s="1">
+        <v>46154</v>
+      </c>
+      <c r="P8" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>61</v>
+      </c>
+      <c r="B9" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" t="s">
+        <v>26</v>
+      </c>
+      <c r="D9" t="s">
+        <v>131</v>
+      </c>
+      <c r="E9" t="s">
+        <v>132</v>
+      </c>
+      <c r="F9" t="s">
+        <v>133</v>
+      </c>
+      <c r="G9" t="s">
+        <v>134</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I9" s="6">
+        <v>46120</v>
+      </c>
+      <c r="J9" s="6">
+        <v>46120</v>
+      </c>
+      <c r="K9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N9" t="s">
+        <v>20</v>
+      </c>
+      <c r="O9" s="1">
+        <v>46154</v>
+      </c>
+      <c r="P9" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>62</v>
+      </c>
+      <c r="B10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" t="s">
+        <v>27</v>
+      </c>
+      <c r="D10" t="s">
+        <v>135</v>
+      </c>
+      <c r="E10" t="s">
+        <v>136</v>
+      </c>
+      <c r="F10" t="s">
+        <v>137</v>
+      </c>
+      <c r="G10" t="s">
+        <v>138</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I10" s="6">
+        <v>46124</v>
+      </c>
+      <c r="J10" s="6">
+        <v>46124</v>
+      </c>
+      <c r="K10" t="s">
+        <v>17</v>
+      </c>
+      <c r="N10" t="s">
+        <v>20</v>
+      </c>
+      <c r="O10" s="1">
+        <v>46154</v>
+      </c>
+      <c r="P10" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>63</v>
+      </c>
+      <c r="B11" t="s">
+        <v>28</v>
+      </c>
+      <c r="C11" t="s">
+        <v>28</v>
+      </c>
+      <c r="D11" t="s">
+        <v>139</v>
+      </c>
+      <c r="E11" t="s">
+        <v>140</v>
+      </c>
+      <c r="F11" t="s">
+        <v>141</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I11" s="6">
+        <v>46111</v>
+      </c>
+      <c r="J11" s="6">
+        <v>46111</v>
+      </c>
+      <c r="K11" t="s">
+        <v>17</v>
+      </c>
+      <c r="N11" t="s">
+        <v>20</v>
+      </c>
+      <c r="O11" s="1">
+        <v>46154</v>
+      </c>
+      <c r="P11" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>64</v>
+      </c>
+      <c r="B12" t="s">
+        <v>29</v>
+      </c>
+      <c r="C12" t="s">
+        <v>29</v>
+      </c>
+      <c r="D12" t="s">
+        <v>142</v>
+      </c>
+      <c r="E12" t="s">
+        <v>143</v>
+      </c>
+      <c r="F12" t="s">
+        <v>144</v>
+      </c>
+      <c r="G12" t="s">
+        <v>145</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I12" s="6">
+        <v>46106</v>
+      </c>
+      <c r="J12" s="6">
+        <v>46108</v>
+      </c>
+      <c r="K12" t="s">
+        <v>17</v>
+      </c>
+      <c r="N12" t="s">
+        <v>20</v>
+      </c>
+      <c r="O12" s="1">
+        <v>46154</v>
+      </c>
+      <c r="P12" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>65</v>
+      </c>
+      <c r="B13" t="s">
+        <v>30</v>
+      </c>
+      <c r="C13" t="s">
+        <v>30</v>
+      </c>
+      <c r="D13" t="s">
+        <v>146</v>
+      </c>
+      <c r="E13" t="s">
+        <v>147</v>
+      </c>
+      <c r="F13" t="s">
+        <v>148</v>
+      </c>
+      <c r="G13" t="s">
+        <v>149</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I13" s="6">
+        <v>46112</v>
+      </c>
+      <c r="J13" s="6">
+        <v>46112</v>
+      </c>
+      <c r="K13" t="s">
+        <v>17</v>
+      </c>
+      <c r="N13" t="s">
+        <v>20</v>
+      </c>
+      <c r="O13" s="1">
+        <v>46154</v>
+      </c>
+      <c r="P13" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>66</v>
+      </c>
+      <c r="B14" t="s">
+        <v>31</v>
+      </c>
+      <c r="C14" t="s">
+        <v>31</v>
+      </c>
+      <c r="D14" t="s">
+        <v>150</v>
+      </c>
+      <c r="E14" t="s">
+        <v>151</v>
+      </c>
+      <c r="F14" t="s">
+        <v>148</v>
+      </c>
+      <c r="G14" t="s">
+        <v>152</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I14" s="6">
+        <v>46106</v>
+      </c>
+      <c r="J14" s="6">
+        <v>46106</v>
+      </c>
+      <c r="K14" t="s">
+        <v>17</v>
+      </c>
+      <c r="N14" t="s">
+        <v>20</v>
+      </c>
+      <c r="O14" s="1">
+        <v>46154</v>
+      </c>
+      <c r="P14" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>67</v>
+      </c>
+      <c r="B15" t="s">
+        <v>32</v>
+      </c>
+      <c r="C15" t="s">
+        <v>32</v>
+      </c>
+      <c r="D15" t="s">
+        <v>153</v>
+      </c>
+      <c r="E15" t="s">
+        <v>154</v>
+      </c>
+      <c r="F15" t="s">
+        <v>148</v>
+      </c>
+      <c r="G15" t="s">
+        <v>155</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I15" s="6">
+        <v>46114</v>
+      </c>
+      <c r="J15" s="6">
+        <v>46114</v>
+      </c>
+      <c r="K15" t="s">
+        <v>17</v>
+      </c>
+      <c r="N15" t="s">
+        <v>20</v>
+      </c>
+      <c r="O15" s="1">
+        <v>46154</v>
+      </c>
+      <c r="P15" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>68</v>
+      </c>
+      <c r="B16" t="s">
+        <v>33</v>
+      </c>
+      <c r="C16" t="s">
+        <v>33</v>
+      </c>
+      <c r="D16" t="s">
+        <v>156</v>
+      </c>
+      <c r="E16" t="s">
+        <v>157</v>
+      </c>
+      <c r="F16" t="s">
+        <v>120</v>
+      </c>
+      <c r="G16" t="s">
+        <v>158</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I16" s="6">
+        <v>46091</v>
+      </c>
+      <c r="J16" s="6">
+        <v>46091</v>
+      </c>
+      <c r="K16" t="s">
+        <v>17</v>
+      </c>
+      <c r="N16" t="s">
+        <v>20</v>
+      </c>
+      <c r="O16" s="1">
+        <v>46154</v>
+      </c>
+      <c r="P16" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>69</v>
+      </c>
+      <c r="B17" t="s">
+        <v>34</v>
+      </c>
+      <c r="C17" t="s">
+        <v>34</v>
+      </c>
+      <c r="D17" t="s">
+        <v>159</v>
+      </c>
+      <c r="E17" t="s">
+        <v>160</v>
+      </c>
+      <c r="F17" t="s">
+        <v>144</v>
+      </c>
+      <c r="G17" t="s">
+        <v>161</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I17" s="6">
+        <v>46110</v>
+      </c>
+      <c r="J17" s="6">
+        <v>46110</v>
+      </c>
+      <c r="K17" t="s">
+        <v>17</v>
+      </c>
+      <c r="N17" t="s">
+        <v>20</v>
+      </c>
+      <c r="O17" s="1">
+        <v>46154</v>
+      </c>
+      <c r="P17" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>70</v>
+      </c>
+      <c r="B18" t="s">
+        <v>35</v>
+      </c>
+      <c r="C18" t="s">
+        <v>35</v>
+      </c>
+      <c r="D18" t="s">
+        <v>162</v>
+      </c>
+      <c r="E18" t="s">
+        <v>163</v>
+      </c>
+      <c r="F18" t="s">
+        <v>144</v>
+      </c>
+      <c r="G18" t="s">
+        <v>164</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I18" s="6">
+        <v>46113</v>
+      </c>
+      <c r="J18" s="6">
+        <v>46113</v>
+      </c>
+      <c r="K18" t="s">
+        <v>17</v>
+      </c>
+      <c r="N18" t="s">
+        <v>20</v>
+      </c>
+      <c r="O18" s="1">
+        <v>46154</v>
+      </c>
+      <c r="P18" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>71</v>
+      </c>
+      <c r="B19" t="s">
+        <v>24</v>
+      </c>
+      <c r="C19" t="s">
+        <v>24</v>
+      </c>
+      <c r="D19" t="s">
+        <v>126</v>
+      </c>
+      <c r="E19" t="s">
+        <v>127</v>
+      </c>
+      <c r="F19" t="s">
+        <v>128</v>
+      </c>
+      <c r="G19" t="s">
+        <v>121</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I19" s="6">
+        <v>46092</v>
+      </c>
+      <c r="J19" s="6">
+        <v>46092</v>
+      </c>
+      <c r="K19" t="s">
+        <v>17</v>
+      </c>
+      <c r="N19" t="s">
+        <v>20</v>
+      </c>
+      <c r="O19" s="1">
+        <v>46154</v>
+      </c>
+      <c r="P19" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>72</v>
+      </c>
+      <c r="B20" t="s">
+        <v>36</v>
+      </c>
+      <c r="C20" t="s">
+        <v>36</v>
+      </c>
+      <c r="D20" t="s">
+        <v>165</v>
+      </c>
+      <c r="E20" t="s">
+        <v>166</v>
+      </c>
+      <c r="F20" t="s">
+        <v>144</v>
+      </c>
+      <c r="G20" t="s">
+        <v>164</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I20" s="6">
+        <v>46093</v>
+      </c>
+      <c r="J20" s="6">
+        <v>46093</v>
+      </c>
+      <c r="K20" t="s">
+        <v>17</v>
+      </c>
+      <c r="N20" t="s">
+        <v>20</v>
+      </c>
+      <c r="O20" s="1">
+        <v>46154</v>
+      </c>
+      <c r="P20" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>73</v>
+      </c>
+      <c r="B21" t="s">
+        <v>36</v>
+      </c>
+      <c r="C21" t="s">
+        <v>36</v>
+      </c>
+      <c r="D21" t="s">
+        <v>165</v>
+      </c>
+      <c r="E21" t="s">
+        <v>166</v>
+      </c>
+      <c r="F21" t="s">
+        <v>144</v>
+      </c>
+      <c r="G21" t="s">
+        <v>164</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I21" s="6">
+        <v>46105</v>
+      </c>
+      <c r="J21" s="6">
+        <v>46107</v>
+      </c>
+      <c r="K21" t="s">
+        <v>17</v>
+      </c>
+      <c r="N21" t="s">
+        <v>20</v>
+      </c>
+      <c r="O21" s="1">
+        <v>46154</v>
+      </c>
+      <c r="P21" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>74</v>
+      </c>
+      <c r="B22" t="s">
+        <v>37</v>
+      </c>
+      <c r="C22" t="s">
+        <v>37</v>
+      </c>
+      <c r="D22" t="s">
+        <v>167</v>
+      </c>
+      <c r="E22" t="s">
+        <v>168</v>
+      </c>
+      <c r="F22" t="s">
+        <v>144</v>
+      </c>
+      <c r="G22" t="s">
+        <v>161</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I22" s="6">
+        <v>46098</v>
+      </c>
+      <c r="J22" s="6">
+        <v>46099</v>
+      </c>
+      <c r="K22" t="s">
+        <v>17</v>
+      </c>
+      <c r="N22" t="s">
+        <v>20</v>
+      </c>
+      <c r="O22" s="1">
+        <v>46154</v>
+      </c>
+      <c r="P22" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>75</v>
+      </c>
+      <c r="B23" t="s">
+        <v>38</v>
+      </c>
+      <c r="C23" t="s">
+        <v>38</v>
+      </c>
+      <c r="D23" t="s">
+        <v>169</v>
+      </c>
+      <c r="E23" t="s">
+        <v>170</v>
+      </c>
+      <c r="F23" t="s">
+        <v>144</v>
+      </c>
+      <c r="G23" t="s">
+        <v>161</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I23" s="6">
+        <v>46110</v>
+      </c>
+      <c r="J23" s="6">
+        <v>46110</v>
+      </c>
+      <c r="K23" t="s">
+        <v>17</v>
+      </c>
+      <c r="N23" t="s">
+        <v>20</v>
+      </c>
+      <c r="O23" s="1">
+        <v>46154</v>
+      </c>
+      <c r="P23" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>76</v>
+      </c>
+      <c r="B24" t="s">
+        <v>39</v>
+      </c>
+      <c r="C24" t="s">
+        <v>39</v>
+      </c>
+      <c r="D24" t="s">
+        <v>171</v>
+      </c>
+      <c r="E24" t="s">
+        <v>172</v>
+      </c>
+      <c r="F24" t="s">
+        <v>144</v>
+      </c>
+      <c r="G24" t="s">
+        <v>161</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I24" s="6">
+        <v>46109</v>
+      </c>
+      <c r="J24" s="6">
+        <v>46109</v>
+      </c>
+      <c r="K24" t="s">
+        <v>17</v>
+      </c>
+      <c r="N24" t="s">
+        <v>20</v>
+      </c>
+      <c r="O24" s="1">
+        <v>46154</v>
+      </c>
+      <c r="P24" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>77</v>
+      </c>
+      <c r="B25" t="s">
+        <v>40</v>
+      </c>
+      <c r="C25" t="s">
+        <v>40</v>
+      </c>
+      <c r="D25" t="s">
+        <v>173</v>
+      </c>
+      <c r="E25" t="s">
+        <v>174</v>
+      </c>
+      <c r="F25" t="s">
+        <v>144</v>
+      </c>
+      <c r="G25" t="s">
+        <v>161</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I25" s="6">
+        <v>46099</v>
+      </c>
+      <c r="J25" s="6">
+        <v>46099</v>
+      </c>
+      <c r="K25" t="s">
+        <v>17</v>
+      </c>
+      <c r="N25" t="s">
+        <v>20</v>
+      </c>
+      <c r="O25" s="1">
+        <v>46154</v>
+      </c>
+      <c r="P25" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>78</v>
+      </c>
+      <c r="B26" t="s">
+        <v>41</v>
+      </c>
+      <c r="C26" t="s">
+        <v>41</v>
+      </c>
+      <c r="D26" t="s">
+        <v>175</v>
+      </c>
+      <c r="E26" t="s">
+        <v>176</v>
+      </c>
+      <c r="F26" t="s">
+        <v>144</v>
+      </c>
+      <c r="G26" t="s">
+        <v>161</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I26" s="6">
+        <v>46105</v>
+      </c>
+      <c r="J26" s="6">
+        <v>46106</v>
+      </c>
+      <c r="K26" t="s">
+        <v>17</v>
+      </c>
+      <c r="N26" t="s">
+        <v>20</v>
+      </c>
+      <c r="O26" s="1">
+        <v>46154</v>
+      </c>
+      <c r="P26" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>79</v>
+      </c>
+      <c r="B27" t="s">
+        <v>42</v>
+      </c>
+      <c r="C27" t="s">
+        <v>42</v>
+      </c>
+      <c r="D27" t="s">
+        <v>177</v>
+      </c>
+      <c r="E27" t="s">
+        <v>178</v>
+      </c>
+      <c r="F27" t="s">
+        <v>128</v>
+      </c>
+      <c r="G27" t="s">
+        <v>121</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I27" s="6">
+        <v>46091</v>
+      </c>
+      <c r="J27" s="6">
+        <v>46091</v>
+      </c>
+      <c r="K27" t="s">
+        <v>17</v>
+      </c>
+      <c r="N27" t="s">
+        <v>20</v>
+      </c>
+      <c r="O27" s="1">
+        <v>46154</v>
+      </c>
+      <c r="P27" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>80</v>
+      </c>
+      <c r="B28" t="s">
+        <v>43</v>
+      </c>
+      <c r="C28" t="s">
+        <v>43</v>
+      </c>
+      <c r="D28" t="s">
+        <v>179</v>
+      </c>
+      <c r="E28" t="s">
+        <v>180</v>
+      </c>
+      <c r="F28" t="s">
+        <v>181</v>
+      </c>
+      <c r="G28" t="s">
+        <v>182</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I28" s="6">
+        <v>46113</v>
+      </c>
+      <c r="J28" s="6">
+        <v>46113</v>
+      </c>
+      <c r="K28" t="s">
+        <v>17</v>
+      </c>
+      <c r="N28" t="s">
+        <v>20</v>
+      </c>
+      <c r="O28" s="1">
+        <v>46154</v>
+      </c>
+      <c r="P28" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>81</v>
+      </c>
+      <c r="B29" t="s">
+        <v>44</v>
+      </c>
+      <c r="C29" t="s">
+        <v>44</v>
+      </c>
+      <c r="D29" t="s">
+        <v>183</v>
+      </c>
+      <c r="E29" t="s">
+        <v>184</v>
+      </c>
+      <c r="F29" t="s">
+        <v>144</v>
+      </c>
+      <c r="G29" t="s">
+        <v>161</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I29" s="6">
+        <v>46095</v>
+      </c>
+      <c r="J29" s="6">
+        <v>46095</v>
+      </c>
+      <c r="K29" t="s">
+        <v>17</v>
+      </c>
+      <c r="N29" t="s">
+        <v>20</v>
+      </c>
+      <c r="O29" s="1">
+        <v>46154</v>
+      </c>
+      <c r="P29" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>82</v>
+      </c>
+      <c r="B30" t="s">
+        <v>44</v>
+      </c>
+      <c r="C30" t="s">
+        <v>44</v>
+      </c>
+      <c r="D30" t="s">
+        <v>183</v>
+      </c>
+      <c r="E30" t="s">
+        <v>184</v>
+      </c>
+      <c r="F30" t="s">
+        <v>144</v>
+      </c>
+      <c r="G30" t="s">
+        <v>161</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I30" s="6">
+        <v>46105</v>
+      </c>
+      <c r="J30" s="6">
+        <v>46105</v>
+      </c>
+      <c r="K30" t="s">
+        <v>17</v>
+      </c>
+      <c r="N30" t="s">
+        <v>20</v>
+      </c>
+      <c r="O30" s="1">
+        <v>46154</v>
+      </c>
+      <c r="P30" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>83</v>
+      </c>
+      <c r="B31" t="s">
+        <v>44</v>
+      </c>
+      <c r="C31" t="s">
+        <v>44</v>
+      </c>
+      <c r="D31" t="s">
+        <v>183</v>
+      </c>
+      <c r="E31" t="s">
+        <v>184</v>
+      </c>
+      <c r="F31" t="s">
+        <v>144</v>
+      </c>
+      <c r="G31" t="s">
+        <v>161</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I31" s="6">
+        <v>46106</v>
+      </c>
+      <c r="J31" s="6">
+        <v>46106</v>
+      </c>
+      <c r="K31" t="s">
+        <v>17</v>
+      </c>
+      <c r="N31" t="s">
+        <v>20</v>
+      </c>
+      <c r="O31" s="1">
+        <v>46154</v>
+      </c>
+      <c r="P31" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>84</v>
+      </c>
+      <c r="B32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C32" t="s">
+        <v>45</v>
+      </c>
+      <c r="D32" t="s">
+        <v>185</v>
+      </c>
+      <c r="E32" t="s">
+        <v>186</v>
+      </c>
+      <c r="F32" t="s">
+        <v>187</v>
+      </c>
+      <c r="G32" t="s">
+        <v>121</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I32" s="6">
+        <v>46093</v>
+      </c>
+      <c r="J32" s="6">
+        <v>46093</v>
+      </c>
+      <c r="K32" t="s">
+        <v>17</v>
+      </c>
+      <c r="N32" t="s">
+        <v>20</v>
+      </c>
+      <c r="O32" s="1">
+        <v>46154</v>
+      </c>
+      <c r="P32" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>85</v>
+      </c>
+      <c r="B33" t="s">
+        <v>42</v>
+      </c>
+      <c r="C33" t="s">
+        <v>42</v>
+      </c>
+      <c r="D33" t="s">
+        <v>177</v>
+      </c>
+      <c r="E33" t="s">
+        <v>178</v>
+      </c>
+      <c r="F33" t="s">
+        <v>128</v>
+      </c>
+      <c r="G33" t="s">
+        <v>121</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I33" s="6">
+        <v>46099</v>
+      </c>
+      <c r="J33" s="6">
+        <v>46099</v>
+      </c>
+      <c r="K33" t="s">
+        <v>17</v>
+      </c>
+      <c r="N33" t="s">
+        <v>20</v>
+      </c>
+      <c r="O33" s="1">
+        <v>46154</v>
+      </c>
+      <c r="P33" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
+        <v>86</v>
+      </c>
+      <c r="B34" t="s">
+        <v>42</v>
+      </c>
+      <c r="C34" t="s">
+        <v>42</v>
+      </c>
+      <c r="D34" t="s">
+        <v>177</v>
+      </c>
+      <c r="E34" t="s">
+        <v>178</v>
+      </c>
+      <c r="F34" t="s">
+        <v>128</v>
+      </c>
+      <c r="G34" t="s">
+        <v>121</v>
+      </c>
+      <c r="H34" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I34" s="6">
+        <v>46098</v>
+      </c>
+      <c r="J34" s="6">
+        <v>46098</v>
+      </c>
+      <c r="K34" t="s">
+        <v>17</v>
+      </c>
+      <c r="N34" t="s">
+        <v>20</v>
+      </c>
+      <c r="O34" s="1">
+        <v>46154</v>
+      </c>
+      <c r="P34" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
+        <v>87</v>
+      </c>
+      <c r="B35" t="s">
+        <v>35</v>
+      </c>
+      <c r="C35" t="s">
+        <v>35</v>
+      </c>
+      <c r="D35" t="s">
+        <v>162</v>
+      </c>
+      <c r="E35" t="s">
+        <v>163</v>
+      </c>
+      <c r="F35" t="s">
+        <v>144</v>
+      </c>
+      <c r="G35" t="s">
+        <v>164</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I35" s="6">
+        <v>46099</v>
+      </c>
+      <c r="J35" s="6">
+        <v>46099</v>
+      </c>
+      <c r="K35" t="s">
+        <v>17</v>
+      </c>
+      <c r="N35" t="s">
+        <v>20</v>
+      </c>
+      <c r="O35" s="1">
+        <v>46154</v>
+      </c>
+      <c r="P35" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
+        <v>88</v>
+      </c>
+      <c r="B36" t="s">
+        <v>34</v>
+      </c>
+      <c r="C36" t="s">
+        <v>34</v>
+      </c>
+      <c r="D36" t="s">
+        <v>159</v>
+      </c>
+      <c r="E36" t="s">
+        <v>160</v>
+      </c>
+      <c r="F36" t="s">
+        <v>144</v>
+      </c>
+      <c r="G36" t="s">
+        <v>161</v>
+      </c>
+      <c r="H36" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I36" s="6">
+        <v>46099</v>
+      </c>
+      <c r="J36" s="6">
+        <v>46099</v>
+      </c>
+      <c r="K36" t="s">
+        <v>17</v>
+      </c>
+      <c r="N36" t="s">
+        <v>20</v>
+      </c>
+      <c r="O36" s="1">
+        <v>46154</v>
+      </c>
+      <c r="P36" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
+        <v>89</v>
+      </c>
+      <c r="B37" t="s">
+        <v>34</v>
+      </c>
+      <c r="C37" t="s">
+        <v>34</v>
+      </c>
+      <c r="D37" t="s">
+        <v>159</v>
+      </c>
+      <c r="E37" t="s">
+        <v>160</v>
+      </c>
+      <c r="F37" t="s">
+        <v>144</v>
+      </c>
+      <c r="G37" t="s">
+        <v>161</v>
+      </c>
+      <c r="H37" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I37" s="6">
+        <v>46116</v>
+      </c>
+      <c r="J37" s="6">
+        <v>46116</v>
+      </c>
+      <c r="K37" t="s">
+        <v>17</v>
+      </c>
+      <c r="N37" t="s">
+        <v>20</v>
+      </c>
+      <c r="O37" s="1">
+        <v>46154</v>
+      </c>
+      <c r="P37" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
+        <v>90</v>
+      </c>
+      <c r="B38" t="s">
+        <v>28</v>
+      </c>
+      <c r="C38" t="s">
+        <v>28</v>
+      </c>
+      <c r="D38" t="s">
+        <v>139</v>
+      </c>
+      <c r="E38" t="s">
+        <v>140</v>
+      </c>
+      <c r="F38" t="s">
+        <v>141</v>
+      </c>
+      <c r="G38">
+        <v>0</v>
+      </c>
+      <c r="H38" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I38" s="6">
+        <v>46082</v>
+      </c>
+      <c r="J38" s="6">
+        <v>46082</v>
+      </c>
+      <c r="K38" t="s">
+        <v>17</v>
+      </c>
+      <c r="N38" t="s">
+        <v>20</v>
+      </c>
+      <c r="O38" s="1">
+        <v>46154</v>
+      </c>
+      <c r="P38" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
+        <v>91</v>
+      </c>
+      <c r="B39" t="s">
+        <v>46</v>
+      </c>
+      <c r="C39" t="s">
+        <v>46</v>
+      </c>
+      <c r="D39" t="s">
+        <v>188</v>
+      </c>
+      <c r="E39" t="s">
+        <v>189</v>
+      </c>
+      <c r="F39" t="s">
+        <v>190</v>
+      </c>
+      <c r="G39" t="s">
+        <v>191</v>
+      </c>
+      <c r="H39" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I39" s="6">
+        <v>46082</v>
+      </c>
+      <c r="J39" s="6">
+        <v>46082</v>
+      </c>
+      <c r="K39" t="s">
+        <v>17</v>
+      </c>
+      <c r="N39" t="s">
+        <v>20</v>
+      </c>
+      <c r="O39" s="1">
+        <v>46154</v>
+      </c>
+      <c r="P39" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A40" t="s">
+        <v>92</v>
+      </c>
+      <c r="B40" t="s">
+        <v>47</v>
+      </c>
+      <c r="C40" t="s">
+        <v>47</v>
+      </c>
+      <c r="D40" t="s">
+        <v>192</v>
+      </c>
+      <c r="E40" t="s">
+        <v>193</v>
+      </c>
+      <c r="F40" t="s">
+        <v>148</v>
+      </c>
+      <c r="G40" t="s">
+        <v>194</v>
+      </c>
+      <c r="H40" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I40" s="6">
+        <v>46088</v>
+      </c>
+      <c r="J40" s="6">
+        <v>46088</v>
+      </c>
+      <c r="K40" t="s">
+        <v>17</v>
+      </c>
+      <c r="N40" t="s">
+        <v>20</v>
+      </c>
+      <c r="O40" s="1">
+        <v>46154</v>
+      </c>
+      <c r="P40" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A41" t="s">
+        <v>93</v>
+      </c>
+      <c r="B41" t="s">
+        <v>48</v>
+      </c>
+      <c r="C41" t="s">
+        <v>48</v>
+      </c>
+      <c r="D41" t="s">
+        <v>195</v>
+      </c>
+      <c r="E41" t="s">
+        <v>196</v>
+      </c>
+      <c r="F41" t="s">
+        <v>197</v>
+      </c>
+      <c r="G41" t="s">
+        <v>198</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I41" s="6">
+        <v>46077</v>
+      </c>
+      <c r="J41" s="6">
+        <v>46077</v>
+      </c>
+      <c r="K41" t="s">
+        <v>17</v>
+      </c>
+      <c r="N41" t="s">
+        <v>20</v>
+      </c>
+      <c r="O41" s="1">
+        <v>46154</v>
+      </c>
+      <c r="P41" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A42" t="s">
+        <v>94</v>
+      </c>
+      <c r="B42" t="s">
+        <v>22</v>
+      </c>
+      <c r="C42" t="s">
+        <v>22</v>
+      </c>
+      <c r="D42" t="s">
+        <v>118</v>
+      </c>
+      <c r="E42" t="s">
+        <v>119</v>
+      </c>
+      <c r="F42" t="s">
+        <v>120</v>
+      </c>
+      <c r="G42" t="s">
+        <v>121</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I42" s="6">
+        <v>46063</v>
+      </c>
+      <c r="J42" s="6">
+        <v>46063</v>
+      </c>
+      <c r="K42" t="s">
+        <v>17</v>
+      </c>
+      <c r="N42" t="s">
+        <v>20</v>
+      </c>
+      <c r="O42" s="1">
+        <v>46154</v>
+      </c>
+      <c r="P42" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A43" t="s">
+        <v>95</v>
+      </c>
+      <c r="B43" t="s">
+        <v>49</v>
+      </c>
+      <c r="C43" t="s">
+        <v>49</v>
+      </c>
+      <c r="D43" t="s">
+        <v>199</v>
+      </c>
+      <c r="E43" t="s">
+        <v>200</v>
+      </c>
+      <c r="F43" t="s">
+        <v>120</v>
+      </c>
+      <c r="G43" t="s">
+        <v>201</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I43" s="6">
+        <v>46061</v>
+      </c>
+      <c r="J43" s="6">
+        <v>46067</v>
+      </c>
+      <c r="K43" t="s">
+        <v>17</v>
+      </c>
+      <c r="N43" t="s">
+        <v>20</v>
+      </c>
+      <c r="O43" s="1">
+        <v>46154</v>
+      </c>
+      <c r="P43" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A44" t="s">
+        <v>96</v>
+      </c>
+      <c r="B44" t="s">
+        <v>49</v>
+      </c>
+      <c r="C44" t="s">
+        <v>49</v>
+      </c>
+      <c r="D44" t="s">
+        <v>199</v>
+      </c>
+      <c r="E44" t="s">
+        <v>200</v>
+      </c>
+      <c r="F44" t="s">
+        <v>120</v>
+      </c>
+      <c r="G44" t="s">
+        <v>201</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I44" s="6">
+        <v>46077</v>
+      </c>
+      <c r="J44" s="6">
+        <v>46079</v>
+      </c>
+      <c r="K44" t="s">
+        <v>17</v>
+      </c>
+      <c r="N44" t="s">
+        <v>20</v>
+      </c>
+      <c r="O44" s="1">
+        <v>46154</v>
+      </c>
+      <c r="P44" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A45" t="s">
+        <v>97</v>
+      </c>
+      <c r="B45" t="s">
+        <v>24</v>
+      </c>
+      <c r="C45" t="s">
+        <v>24</v>
+      </c>
+      <c r="D45" t="s">
+        <v>126</v>
+      </c>
+      <c r="E45" t="s">
+        <v>127</v>
+      </c>
+      <c r="F45" t="s">
+        <v>128</v>
+      </c>
+      <c r="G45" t="s">
+        <v>121</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I45" s="6">
+        <v>46070</v>
+      </c>
+      <c r="J45" s="6">
+        <v>46070</v>
+      </c>
+      <c r="K45" t="s">
+        <v>17</v>
+      </c>
+      <c r="N45" t="s">
+        <v>20</v>
+      </c>
+      <c r="O45" s="1">
+        <v>46154</v>
+      </c>
+      <c r="P45" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A46" t="s">
+        <v>98</v>
+      </c>
+      <c r="B46" t="s">
+        <v>50</v>
+      </c>
+      <c r="C46" t="s">
+        <v>50</v>
+      </c>
+      <c r="D46" t="s">
+        <v>202</v>
+      </c>
+      <c r="E46" t="s">
+        <v>203</v>
+      </c>
+      <c r="F46" t="s">
+        <v>144</v>
+      </c>
+      <c r="G46" t="s">
+        <v>161</v>
+      </c>
+      <c r="H46" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I46" s="6">
+        <v>46061</v>
+      </c>
+      <c r="J46" s="6">
+        <v>46061</v>
+      </c>
+      <c r="K46" t="s">
+        <v>17</v>
+      </c>
+      <c r="N46" t="s">
+        <v>20</v>
+      </c>
+      <c r="O46" s="1">
+        <v>46154</v>
+      </c>
+      <c r="P46" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A47" t="s">
+        <v>99</v>
+      </c>
+      <c r="B47" t="s">
+        <v>50</v>
+      </c>
+      <c r="C47" t="s">
+        <v>50</v>
+      </c>
+      <c r="D47" t="s">
+        <v>202</v>
+      </c>
+      <c r="E47" t="s">
+        <v>203</v>
+      </c>
+      <c r="F47" t="s">
+        <v>144</v>
+      </c>
+      <c r="G47" t="s">
+        <v>161</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I47" s="6">
+        <v>46067</v>
+      </c>
+      <c r="J47" s="6">
+        <v>46067</v>
+      </c>
+      <c r="K47" t="s">
+        <v>17</v>
+      </c>
+      <c r="N47" t="s">
+        <v>20</v>
+      </c>
+      <c r="O47" s="1">
+        <v>46154</v>
+      </c>
+      <c r="P47" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="48" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A48" t="s">
+        <v>100</v>
+      </c>
+      <c r="B48" t="s">
+        <v>50</v>
+      </c>
+      <c r="C48" t="s">
+        <v>50</v>
+      </c>
+      <c r="D48" t="s">
+        <v>202</v>
+      </c>
+      <c r="E48" t="s">
+        <v>203</v>
+      </c>
+      <c r="F48" t="s">
+        <v>144</v>
+      </c>
+      <c r="G48" t="s">
+        <v>161</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I48" s="6">
+        <v>46071</v>
+      </c>
+      <c r="J48" s="6">
+        <v>46071</v>
+      </c>
+      <c r="K48" t="s">
+        <v>17</v>
+      </c>
+      <c r="N48" t="s">
+        <v>20</v>
+      </c>
+      <c r="O48" s="1">
+        <v>46154</v>
+      </c>
+      <c r="P48" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="49" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A49" t="s">
+        <v>101</v>
+      </c>
+      <c r="B49" t="s">
+        <v>50</v>
+      </c>
+      <c r="C49" t="s">
+        <v>50</v>
+      </c>
+      <c r="D49" t="s">
+        <v>202</v>
+      </c>
+      <c r="E49" t="s">
+        <v>203</v>
+      </c>
+      <c r="F49" t="s">
+        <v>144</v>
+      </c>
+      <c r="G49" t="s">
+        <v>161</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I49" s="6">
+        <v>46077</v>
+      </c>
+      <c r="J49" s="6">
+        <v>46077</v>
+      </c>
+      <c r="K49" t="s">
+        <v>17</v>
+      </c>
+      <c r="N49" t="s">
+        <v>20</v>
+      </c>
+      <c r="O49" s="1">
+        <v>46154</v>
+      </c>
+      <c r="P49" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="50" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A50" t="s">
+        <v>102</v>
+      </c>
+      <c r="B50" t="s">
+        <v>25</v>
+      </c>
+      <c r="C50" t="s">
+        <v>25</v>
+      </c>
+      <c r="D50" t="s">
+        <v>129</v>
+      </c>
+      <c r="E50" t="s">
+        <v>130</v>
+      </c>
+      <c r="F50" t="s">
+        <v>128</v>
+      </c>
+      <c r="G50" t="s">
+        <v>121</v>
+      </c>
+      <c r="H50" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I50" s="6">
+        <v>46070</v>
+      </c>
+      <c r="J50" s="6">
+        <v>46070</v>
+      </c>
+      <c r="K50" t="s">
+        <v>17</v>
+      </c>
+      <c r="N50" t="s">
+        <v>20</v>
+      </c>
+      <c r="O50" s="1">
+        <v>46154</v>
+      </c>
+      <c r="P50" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="51" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A51" t="s">
+        <v>103</v>
+      </c>
+      <c r="B51" t="s">
+        <v>25</v>
+      </c>
+      <c r="C51" t="s">
+        <v>25</v>
+      </c>
+      <c r="D51" t="s">
+        <v>129</v>
+      </c>
+      <c r="E51" t="s">
+        <v>130</v>
+      </c>
+      <c r="F51" t="s">
+        <v>128</v>
+      </c>
+      <c r="G51" t="s">
+        <v>121</v>
+      </c>
+      <c r="H51" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I51" s="6">
+        <v>46078</v>
+      </c>
+      <c r="J51" s="6">
+        <v>46078</v>
+      </c>
+      <c r="K51" t="s">
+        <v>17</v>
+      </c>
+      <c r="N51" t="s">
+        <v>20</v>
+      </c>
+      <c r="O51" s="1">
+        <v>46154</v>
+      </c>
+      <c r="P51" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="52" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A52" t="s">
+        <v>104</v>
+      </c>
+      <c r="B52" t="s">
+        <v>25</v>
+      </c>
+      <c r="C52" t="s">
+        <v>25</v>
+      </c>
+      <c r="D52" t="s">
+        <v>129</v>
+      </c>
+      <c r="E52" t="s">
+        <v>130</v>
+      </c>
+      <c r="F52" t="s">
+        <v>128</v>
+      </c>
+      <c r="G52" t="s">
+        <v>121</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I52" s="6">
+        <v>46079</v>
+      </c>
+      <c r="J52" s="6">
+        <v>46079</v>
+      </c>
+      <c r="K52" t="s">
+        <v>17</v>
+      </c>
+      <c r="N52" t="s">
+        <v>20</v>
+      </c>
+      <c r="O52" s="1">
+        <v>46154</v>
+      </c>
+      <c r="P52" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="53" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A53" t="s">
+        <v>105</v>
+      </c>
+      <c r="B53" t="s">
+        <v>51</v>
+      </c>
+      <c r="C53" t="s">
+        <v>51</v>
+      </c>
+      <c r="D53" t="s">
+        <v>204</v>
+      </c>
+      <c r="E53" t="s">
+        <v>205</v>
+      </c>
+      <c r="F53" t="s">
+        <v>144</v>
+      </c>
+      <c r="G53" t="s">
+        <v>206</v>
+      </c>
+      <c r="H53" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I53" s="6">
+        <v>46086</v>
+      </c>
+      <c r="J53" s="6">
+        <v>46086</v>
+      </c>
+      <c r="K53" t="s">
+        <v>17</v>
+      </c>
+      <c r="N53" t="s">
+        <v>20</v>
+      </c>
+      <c r="O53" s="1">
+        <v>46154</v>
+      </c>
+      <c r="P53" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="54" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A54" t="s">
+        <v>106</v>
+      </c>
+      <c r="B54" t="s">
+        <v>51</v>
+      </c>
+      <c r="C54" t="s">
+        <v>51</v>
+      </c>
+      <c r="D54" t="s">
+        <v>204</v>
+      </c>
+      <c r="E54" t="s">
+        <v>205</v>
+      </c>
+      <c r="F54" t="s">
+        <v>144</v>
+      </c>
+      <c r="G54" t="s">
+        <v>206</v>
+      </c>
+      <c r="H54" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I54" s="6">
+        <v>46067</v>
+      </c>
+      <c r="J54" s="6">
+        <v>46067</v>
+      </c>
+      <c r="K54" t="s">
+        <v>17</v>
+      </c>
+      <c r="N54" t="s">
+        <v>20</v>
+      </c>
+      <c r="O54" s="1">
+        <v>46154</v>
+      </c>
+      <c r="P54" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="55" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A55" t="s">
+        <v>107</v>
+      </c>
+      <c r="B55" t="s">
+        <v>51</v>
+      </c>
+      <c r="C55" t="s">
+        <v>51</v>
+      </c>
+      <c r="D55" t="s">
+        <v>204</v>
+      </c>
+      <c r="E55" t="s">
+        <v>205</v>
+      </c>
+      <c r="F55" t="s">
+        <v>144</v>
+      </c>
+      <c r="G55" t="s">
+        <v>206</v>
+      </c>
+      <c r="H55" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I55" s="6">
+        <v>46068</v>
+      </c>
+      <c r="J55" s="6">
+        <v>46068</v>
+      </c>
+      <c r="K55" t="s">
+        <v>17</v>
+      </c>
+      <c r="N55" t="s">
+        <v>20</v>
+      </c>
+      <c r="O55" s="1">
+        <v>46154</v>
+      </c>
+      <c r="P55" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="56" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A56" t="s">
+        <v>108</v>
+      </c>
+      <c r="B56" t="s">
+        <v>52</v>
+      </c>
+      <c r="C56" t="s">
+        <v>52</v>
+      </c>
+      <c r="D56" t="s">
+        <v>207</v>
+      </c>
+      <c r="E56" t="s">
+        <v>208</v>
+      </c>
+      <c r="F56" t="s">
+        <v>209</v>
+      </c>
+      <c r="G56" t="s">
+        <v>210</v>
+      </c>
+      <c r="H56" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I56" s="6">
+        <v>46082</v>
+      </c>
+      <c r="J56" s="6">
+        <v>46082</v>
+      </c>
+      <c r="K56" t="s">
+        <v>17</v>
+      </c>
+      <c r="N56" t="s">
+        <v>20</v>
+      </c>
+      <c r="O56" s="1">
+        <v>46154</v>
+      </c>
+      <c r="P56" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="57" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A57" t="s">
+        <v>109</v>
+      </c>
+      <c r="B57" t="s">
+        <v>42</v>
+      </c>
+      <c r="C57" t="s">
+        <v>42</v>
+      </c>
+      <c r="D57" t="s">
+        <v>177</v>
+      </c>
+      <c r="E57" t="s">
+        <v>178</v>
+      </c>
+      <c r="F57" t="s">
+        <v>128</v>
+      </c>
+      <c r="G57" t="s">
+        <v>121</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I57" s="6">
+        <v>46072</v>
+      </c>
+      <c r="J57" s="6">
+        <v>46072</v>
+      </c>
+      <c r="K57" t="s">
+        <v>17</v>
+      </c>
+      <c r="N57" t="s">
+        <v>20</v>
+      </c>
+      <c r="O57" s="1">
+        <v>46154</v>
+      </c>
+      <c r="P57" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="58" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A58" t="s">
+        <v>110</v>
+      </c>
+      <c r="B58" t="s">
+        <v>53</v>
+      </c>
+      <c r="C58" t="s">
+        <v>53</v>
+      </c>
+      <c r="D58" t="s">
+        <v>211</v>
+      </c>
+      <c r="E58" t="s">
+        <v>212</v>
+      </c>
+      <c r="F58" t="s">
+        <v>144</v>
+      </c>
+      <c r="G58" t="s">
+        <v>161</v>
+      </c>
+      <c r="H58" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I58" s="6">
+        <v>46070</v>
+      </c>
+      <c r="J58" s="6">
+        <v>46070</v>
+      </c>
+      <c r="K58" t="s">
+        <v>17</v>
+      </c>
+      <c r="N58" t="s">
+        <v>20</v>
+      </c>
+      <c r="O58" s="1">
+        <v>46154</v>
+      </c>
+      <c r="P58" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="59" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A59" t="s">
+        <v>111</v>
+      </c>
+      <c r="B59" t="s">
+        <v>53</v>
+      </c>
+      <c r="C59" t="s">
+        <v>53</v>
+      </c>
+      <c r="D59" t="s">
+        <v>211</v>
+      </c>
+      <c r="E59" t="s">
+        <v>212</v>
+      </c>
+      <c r="F59" t="s">
+        <v>144</v>
+      </c>
+      <c r="G59" t="s">
+        <v>161</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I59" s="6">
+        <v>46079</v>
+      </c>
+      <c r="J59" s="6">
+        <v>46079</v>
+      </c>
+      <c r="K59" t="s">
+        <v>17</v>
+      </c>
+      <c r="N59" t="s">
+        <v>20</v>
+      </c>
+      <c r="O59" s="1">
+        <v>46154</v>
+      </c>
+      <c r="P59" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="60" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A60" t="s">
+        <v>112</v>
+      </c>
+      <c r="B60" t="s">
+        <v>54</v>
+      </c>
+      <c r="C60" t="s">
+        <v>54</v>
+      </c>
+      <c r="D60" t="s">
+        <v>213</v>
+      </c>
+      <c r="E60" t="s">
+        <v>214</v>
+      </c>
+      <c r="F60" t="s">
+        <v>187</v>
+      </c>
+      <c r="G60">
+        <v>0</v>
+      </c>
+      <c r="H60" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I60" s="6">
+        <v>46077</v>
+      </c>
+      <c r="J60" s="6">
+        <v>46077</v>
+      </c>
+      <c r="K60" t="s">
+        <v>17</v>
+      </c>
+      <c r="N60" t="s">
+        <v>20</v>
+      </c>
+      <c r="O60" s="1">
+        <v>46154</v>
+      </c>
+      <c r="P60" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="61" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A61" t="s">
+        <v>113</v>
+      </c>
+      <c r="B61" t="s">
+        <v>45</v>
+      </c>
+      <c r="C61" t="s">
+        <v>45</v>
+      </c>
+      <c r="D61" t="s">
+        <v>185</v>
+      </c>
+      <c r="E61" t="s">
+        <v>186</v>
+      </c>
+      <c r="F61" t="s">
+        <v>187</v>
+      </c>
+      <c r="G61" t="s">
+        <v>121</v>
+      </c>
+      <c r="H61" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I61" s="6">
+        <v>46085</v>
+      </c>
+      <c r="J61" s="6">
+        <v>46085</v>
+      </c>
+      <c r="K61" t="s">
+        <v>17</v>
+      </c>
+      <c r="N61" t="s">
+        <v>20</v>
+      </c>
+      <c r="O61" s="1">
+        <v>46154</v>
+      </c>
+      <c r="P61" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="62" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="C62" s="5"/>
+      <c r="F62" s="5"/>
+    </row>
+    <row r="63" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="C63" s="5"/>
+      <c r="F63" s="5"/>
+    </row>
+    <row r="64" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="C64" s="5"/>
+      <c r="F64" s="5"/>
+    </row>
+    <row r="65" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C65" s="5"/>
+      <c r="F65" s="5"/>
+    </row>
+    <row r="66" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C66" s="5"/>
+      <c r="F66" s="5"/>
+    </row>
+    <row r="67" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C67" s="5"/>
+      <c r="F67" s="5"/>
+    </row>
+    <row r="68" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C68" s="5"/>
+      <c r="F68" s="5"/>
+    </row>
+    <row r="69" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C69" s="5"/>
+      <c r="F69" s="5"/>
+    </row>
+    <row r="70" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C70" s="5"/>
+      <c r="F70" s="5"/>
+    </row>
+    <row r="71" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C71" s="5"/>
+      <c r="F71" s="5"/>
+    </row>
+    <row r="72" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C72" s="5"/>
+      <c r="F72" s="5"/>
+    </row>
+    <row r="73" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C73" s="5"/>
+      <c r="F73" s="5"/>
+    </row>
+    <row r="74" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C74" s="5"/>
+      <c r="F74" s="5"/>
+    </row>
+    <row r="75" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C75" s="5"/>
+      <c r="F75" s="5"/>
+    </row>
+    <row r="76" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C76" s="5"/>
+      <c r="F76" s="5"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <conditionalFormatting sqref="B2:B61">
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C2:C61">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/leaves.xlsx
+++ b/data/leaves.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6344" uniqueCount="1206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6346" uniqueCount="1208">
   <si>
     <t>leave_id</t>
   </si>
@@ -3631,6 +3631,12 @@
   </si>
   <si>
     <t>LV-685</t>
+  </si>
+  <si>
+    <t>LV-686</t>
+  </si>
+  <si>
+    <t>محمد صبحي محمد احمد</t>
   </si>
 </sst>
 </file>
@@ -29201,7 +29207,7 @@
       <c r="F665" s="1" t="s">
         <v>428</v>
       </c>
-      <c r="G665" s="1">
+      <c r="G665" s="4">
         <v>0.0</v>
       </c>
       <c r="H665" s="4" t="s">
@@ -29829,64 +29835,184 @@
       </c>
     </row>
     <row r="682" ht="14.25" customHeight="1">
-      <c r="C682" s="11"/>
-      <c r="I682" s="12"/>
-      <c r="J682" s="12"/>
+      <c r="A682" s="1" t="s">
+        <v>1206</v>
+      </c>
+      <c r="B682" s="7">
+        <v>28798.0</v>
+      </c>
+      <c r="C682" s="8">
+        <v>28798.0</v>
+      </c>
+      <c r="D682" s="4" t="s">
+        <v>1207</v>
+      </c>
+      <c r="E682" s="1"/>
+      <c r="F682" s="1"/>
+      <c r="G682" s="4"/>
+      <c r="H682" s="4"/>
+      <c r="I682" s="9">
+        <v>46301.0</v>
+      </c>
+      <c r="J682" s="9">
+        <v>46332.0</v>
+      </c>
+      <c r="K682" s="4"/>
+      <c r="N682" s="4"/>
     </row>
     <row r="683" ht="14.25" customHeight="1">
-      <c r="C683" s="11"/>
-      <c r="I683" s="12"/>
-      <c r="J683" s="12"/>
+      <c r="A683" s="1"/>
+      <c r="B683" s="7"/>
+      <c r="C683" s="8"/>
+      <c r="D683" s="4"/>
+      <c r="E683" s="1"/>
+      <c r="F683" s="1"/>
+      <c r="G683" s="4"/>
+      <c r="H683" s="4"/>
+      <c r="I683" s="9"/>
+      <c r="J683" s="9"/>
+      <c r="K683" s="4"/>
+      <c r="N683" s="4"/>
     </row>
     <row r="684" ht="14.25" customHeight="1">
-      <c r="C684" s="11"/>
-      <c r="I684" s="12"/>
-      <c r="J684" s="12"/>
+      <c r="A684" s="1"/>
+      <c r="B684" s="7"/>
+      <c r="C684" s="8"/>
+      <c r="D684" s="4"/>
+      <c r="E684" s="1"/>
+      <c r="F684" s="1"/>
+      <c r="G684" s="4"/>
+      <c r="H684" s="4"/>
+      <c r="I684" s="9"/>
+      <c r="J684" s="9"/>
+      <c r="K684" s="4"/>
+      <c r="N684" s="4"/>
     </row>
     <row r="685" ht="14.25" customHeight="1">
-      <c r="C685" s="11"/>
-      <c r="I685" s="12"/>
-      <c r="J685" s="12"/>
+      <c r="A685" s="1"/>
+      <c r="B685" s="7"/>
+      <c r="C685" s="8"/>
+      <c r="D685" s="4"/>
+      <c r="E685" s="1"/>
+      <c r="F685" s="1"/>
+      <c r="G685" s="4"/>
+      <c r="H685" s="4"/>
+      <c r="I685" s="9"/>
+      <c r="J685" s="9"/>
+      <c r="K685" s="4"/>
+      <c r="N685" s="4"/>
     </row>
     <row r="686" ht="14.25" customHeight="1">
-      <c r="C686" s="11"/>
-      <c r="I686" s="12"/>
-      <c r="J686" s="12"/>
+      <c r="A686" s="1"/>
+      <c r="B686" s="7"/>
+      <c r="C686" s="8"/>
+      <c r="D686" s="4"/>
+      <c r="E686" s="1"/>
+      <c r="F686" s="1"/>
+      <c r="G686" s="4"/>
+      <c r="H686" s="4"/>
+      <c r="I686" s="9"/>
+      <c r="J686" s="9"/>
+      <c r="K686" s="4"/>
+      <c r="N686" s="4"/>
     </row>
     <row r="687" ht="14.25" customHeight="1">
-      <c r="C687" s="11"/>
-      <c r="I687" s="12"/>
-      <c r="J687" s="12"/>
+      <c r="A687" s="1"/>
+      <c r="B687" s="7"/>
+      <c r="C687" s="8"/>
+      <c r="D687" s="4"/>
+      <c r="E687" s="1"/>
+      <c r="F687" s="1"/>
+      <c r="G687" s="4"/>
+      <c r="H687" s="4"/>
+      <c r="I687" s="9"/>
+      <c r="J687" s="9"/>
+      <c r="K687" s="4"/>
+      <c r="N687" s="4"/>
     </row>
     <row r="688" ht="14.25" customHeight="1">
-      <c r="C688" s="11"/>
-      <c r="I688" s="12"/>
-      <c r="J688" s="12"/>
+      <c r="A688" s="1"/>
+      <c r="B688" s="7"/>
+      <c r="C688" s="8"/>
+      <c r="D688" s="4"/>
+      <c r="E688" s="1"/>
+      <c r="F688" s="1"/>
+      <c r="G688" s="4"/>
+      <c r="H688" s="4"/>
+      <c r="I688" s="9"/>
+      <c r="J688" s="9"/>
+      <c r="K688" s="4"/>
+      <c r="N688" s="4"/>
     </row>
     <row r="689" ht="14.25" customHeight="1">
-      <c r="C689" s="11"/>
-      <c r="I689" s="12"/>
-      <c r="J689" s="12"/>
+      <c r="A689" s="1"/>
+      <c r="B689" s="7"/>
+      <c r="C689" s="8"/>
+      <c r="D689" s="4"/>
+      <c r="E689" s="1"/>
+      <c r="F689" s="1"/>
+      <c r="G689" s="4"/>
+      <c r="H689" s="4"/>
+      <c r="I689" s="9"/>
+      <c r="J689" s="9"/>
+      <c r="K689" s="4"/>
+      <c r="N689" s="4"/>
     </row>
     <row r="690" ht="14.25" customHeight="1">
-      <c r="C690" s="11"/>
-      <c r="I690" s="12"/>
-      <c r="J690" s="12"/>
+      <c r="A690" s="1"/>
+      <c r="B690" s="7"/>
+      <c r="C690" s="8"/>
+      <c r="D690" s="4"/>
+      <c r="E690" s="1"/>
+      <c r="F690" s="1"/>
+      <c r="G690" s="4"/>
+      <c r="H690" s="4"/>
+      <c r="I690" s="9"/>
+      <c r="J690" s="9"/>
+      <c r="K690" s="4"/>
+      <c r="N690" s="4"/>
     </row>
     <row r="691" ht="14.25" customHeight="1">
-      <c r="C691" s="11"/>
-      <c r="I691" s="12"/>
-      <c r="J691" s="12"/>
+      <c r="A691" s="1"/>
+      <c r="B691" s="7"/>
+      <c r="C691" s="8"/>
+      <c r="D691" s="4"/>
+      <c r="E691" s="1"/>
+      <c r="F691" s="1"/>
+      <c r="G691" s="4"/>
+      <c r="H691" s="4"/>
+      <c r="I691" s="9"/>
+      <c r="J691" s="9"/>
+      <c r="K691" s="4"/>
+      <c r="N691" s="4"/>
     </row>
     <row r="692" ht="14.25" customHeight="1">
-      <c r="C692" s="11"/>
-      <c r="I692" s="12"/>
-      <c r="J692" s="12"/>
+      <c r="A692" s="1"/>
+      <c r="B692" s="7"/>
+      <c r="C692" s="8"/>
+      <c r="D692" s="4"/>
+      <c r="E692" s="1"/>
+      <c r="F692" s="1"/>
+      <c r="G692" s="4"/>
+      <c r="H692" s="4"/>
+      <c r="I692" s="9"/>
+      <c r="J692" s="9"/>
+      <c r="K692" s="4"/>
+      <c r="N692" s="4"/>
     </row>
     <row r="693" ht="14.25" customHeight="1">
-      <c r="C693" s="11"/>
-      <c r="I693" s="12"/>
-      <c r="J693" s="12"/>
+      <c r="A693" s="1"/>
+      <c r="B693" s="7"/>
+      <c r="C693" s="8"/>
+      <c r="D693" s="4"/>
+      <c r="E693" s="1"/>
+      <c r="F693" s="1"/>
+      <c r="G693" s="4"/>
+      <c r="H693" s="4"/>
+      <c r="I693" s="9"/>
+      <c r="J693" s="9"/>
+      <c r="K693" s="4"/>
+      <c r="N693" s="4"/>
     </row>
     <row r="694" ht="14.25" customHeight="1">
       <c r="C694" s="11"/>

--- a/data/leaves.xlsx
+++ b/data/leaves.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6346" uniqueCount="1208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6352" uniqueCount="1208">
   <si>
     <t>leave_id</t>
   </si>
@@ -29847,18 +29847,30 @@
       <c r="D682" s="4" t="s">
         <v>1207</v>
       </c>
-      <c r="E682" s="1"/>
-      <c r="F682" s="1"/>
-      <c r="G682" s="4"/>
-      <c r="H682" s="4"/>
+      <c r="E682" s="1" t="s">
+        <v>752</v>
+      </c>
+      <c r="F682" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="G682" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="H682" s="4" t="s">
+        <v>19</v>
+      </c>
       <c r="I682" s="9">
         <v>46301.0</v>
       </c>
       <c r="J682" s="9">
         <v>46332.0</v>
       </c>
-      <c r="K682" s="4"/>
-      <c r="N682" s="4"/>
+      <c r="K682" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="N682" s="4" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="683" ht="14.25" customHeight="1">
       <c r="A683" s="1"/>

--- a/data/leaves.xlsx
+++ b/data/leaves.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6352" uniqueCount="1208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6344" uniqueCount="1206">
   <si>
     <t>leave_id</t>
   </si>
@@ -3631,12 +3631,6 @@
   </si>
   <si>
     <t>LV-685</t>
-  </si>
-  <si>
-    <t>LV-686</t>
-  </si>
-  <si>
-    <t>محمد صبحي محمد احمد</t>
   </si>
 </sst>
 </file>
@@ -29835,42 +29829,15 @@
       </c>
     </row>
     <row r="682" ht="14.25" customHeight="1">
-      <c r="A682" s="1" t="s">
-        <v>1206</v>
-      </c>
-      <c r="B682" s="7">
-        <v>28798.0</v>
-      </c>
-      <c r="C682" s="8">
-        <v>28798.0</v>
-      </c>
-      <c r="D682" s="4" t="s">
-        <v>1207</v>
-      </c>
-      <c r="E682" s="1" t="s">
-        <v>752</v>
-      </c>
-      <c r="F682" s="1" t="s">
-        <v>428</v>
-      </c>
-      <c r="G682" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="H682" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="I682" s="9">
-        <v>46301.0</v>
-      </c>
-      <c r="J682" s="9">
-        <v>46332.0</v>
-      </c>
-      <c r="K682" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="N682" s="4" t="s">
-        <v>21</v>
-      </c>
+      <c r="B682" s="7"/>
+      <c r="C682" s="8"/>
+      <c r="D682" s="4"/>
+      <c r="G682" s="4"/>
+      <c r="H682" s="4"/>
+      <c r="I682" s="9"/>
+      <c r="J682" s="9"/>
+      <c r="K682" s="4"/>
+      <c r="N682" s="4"/>
     </row>
     <row r="683" ht="14.25" customHeight="1">
       <c r="A683" s="1"/>

--- a/data/leaves.xlsx
+++ b/data/leaves.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7304" uniqueCount="1211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7299" uniqueCount="1207">
   <si>
     <t>leave_id</t>
   </si>
@@ -3632,18 +3632,6 @@
   </si>
   <si>
     <t>LV-685</t>
-  </si>
-  <si>
-    <t>LV-686</t>
-  </si>
-  <si>
-    <t>محمد صبحي أحمد</t>
-  </si>
-  <si>
-    <t>MOHAMMED SUBHY AHMED</t>
-  </si>
-  <si>
-    <t>-</t>
   </si>
 </sst>
 </file>
@@ -3720,7 +3708,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="20">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -3766,13 +3754,7 @@
     <xf borderId="0" fillId="0" fontId="4" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -3780,6 +3762,9 @@
     </xf>
     <xf borderId="0" fillId="3" fontId="4" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" readingOrder="1" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
@@ -34154,36 +34139,18 @@
       <c r="R681" s="7"/>
     </row>
     <row r="682" ht="18.0" customHeight="1">
-      <c r="A682" s="6" t="s">
-        <v>1207</v>
-      </c>
-      <c r="B682" s="8">
-        <v>28798.0</v>
-      </c>
-      <c r="C682" s="14">
-        <v>28798.0</v>
-      </c>
-      <c r="D682" s="9" t="s">
-        <v>1208</v>
-      </c>
-      <c r="E682" s="15" t="s">
-        <v>1209</v>
-      </c>
-      <c r="F682" s="15" t="s">
-        <v>35</v>
-      </c>
-      <c r="G682" s="15" t="s">
-        <v>1210</v>
-      </c>
+      <c r="A682" s="6"/>
+      <c r="B682" s="15"/>
+      <c r="C682" s="14"/>
+      <c r="D682" s="9"/>
+      <c r="E682" s="16"/>
+      <c r="F682" s="16"/>
+      <c r="G682" s="16"/>
       <c r="H682" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I682" s="11">
-        <v>46235.0</v>
-      </c>
-      <c r="J682" s="11">
-        <v>46265.0</v>
-      </c>
+      <c r="I682" s="17"/>
+      <c r="J682" s="17"/>
       <c r="K682" s="10" t="s">
         <v>20</v>
       </c>
@@ -34199,17 +34166,17 @@
     </row>
     <row r="683" ht="18.0" customHeight="1">
       <c r="A683" s="6"/>
-      <c r="B683" s="16"/>
+      <c r="B683" s="15"/>
       <c r="C683" s="14"/>
-      <c r="D683" s="17"/>
-      <c r="E683" s="18"/>
-      <c r="F683" s="18"/>
-      <c r="G683" s="18"/>
+      <c r="D683" s="18"/>
+      <c r="E683" s="16"/>
+      <c r="F683" s="16"/>
+      <c r="G683" s="16"/>
       <c r="H683" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I683" s="19"/>
-      <c r="J683" s="19"/>
+      <c r="I683" s="17"/>
+      <c r="J683" s="17"/>
       <c r="K683" s="10" t="s">
         <v>20</v>
       </c>
@@ -34225,17 +34192,17 @@
     </row>
     <row r="684" ht="18.0" customHeight="1">
       <c r="A684" s="6"/>
-      <c r="B684" s="16"/>
+      <c r="B684" s="15"/>
       <c r="C684" s="14"/>
-      <c r="D684" s="17"/>
-      <c r="E684" s="18"/>
-      <c r="F684" s="18"/>
-      <c r="G684" s="18"/>
+      <c r="D684" s="18"/>
+      <c r="E684" s="16"/>
+      <c r="F684" s="16"/>
+      <c r="G684" s="16"/>
       <c r="H684" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I684" s="19"/>
-      <c r="J684" s="19"/>
+      <c r="I684" s="17"/>
+      <c r="J684" s="17"/>
       <c r="K684" s="10" t="s">
         <v>20</v>
       </c>
@@ -34251,17 +34218,17 @@
     </row>
     <row r="685" ht="18.0" customHeight="1">
       <c r="A685" s="6"/>
-      <c r="B685" s="16"/>
+      <c r="B685" s="15"/>
       <c r="C685" s="14"/>
-      <c r="D685" s="17"/>
-      <c r="E685" s="18"/>
-      <c r="F685" s="18"/>
-      <c r="G685" s="18"/>
+      <c r="D685" s="18"/>
+      <c r="E685" s="16"/>
+      <c r="F685" s="16"/>
+      <c r="G685" s="16"/>
       <c r="H685" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I685" s="19"/>
-      <c r="J685" s="19"/>
+      <c r="I685" s="17"/>
+      <c r="J685" s="17"/>
       <c r="K685" s="10" t="s">
         <v>20</v>
       </c>
@@ -34277,17 +34244,17 @@
     </row>
     <row r="686" ht="18.0" customHeight="1">
       <c r="A686" s="6"/>
-      <c r="B686" s="16"/>
+      <c r="B686" s="15"/>
       <c r="C686" s="14"/>
-      <c r="D686" s="17"/>
-      <c r="E686" s="18"/>
-      <c r="F686" s="18"/>
-      <c r="G686" s="18"/>
+      <c r="D686" s="18"/>
+      <c r="E686" s="16"/>
+      <c r="F686" s="16"/>
+      <c r="G686" s="16"/>
       <c r="H686" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I686" s="19"/>
-      <c r="J686" s="19"/>
+      <c r="I686" s="17"/>
+      <c r="J686" s="17"/>
       <c r="K686" s="10" t="s">
         <v>20</v>
       </c>
@@ -34303,17 +34270,17 @@
     </row>
     <row r="687" ht="18.0" customHeight="1">
       <c r="A687" s="6"/>
-      <c r="B687" s="16"/>
+      <c r="B687" s="15"/>
       <c r="C687" s="14"/>
-      <c r="D687" s="17"/>
-      <c r="E687" s="18"/>
-      <c r="F687" s="18"/>
-      <c r="G687" s="18"/>
+      <c r="D687" s="18"/>
+      <c r="E687" s="16"/>
+      <c r="F687" s="16"/>
+      <c r="G687" s="16"/>
       <c r="H687" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I687" s="19"/>
-      <c r="J687" s="19"/>
+      <c r="I687" s="17"/>
+      <c r="J687" s="17"/>
       <c r="K687" s="10" t="s">
         <v>20</v>
       </c>
@@ -34329,17 +34296,17 @@
     </row>
     <row r="688" ht="18.0" customHeight="1">
       <c r="A688" s="6"/>
-      <c r="B688" s="16"/>
+      <c r="B688" s="15"/>
       <c r="C688" s="14"/>
-      <c r="D688" s="17"/>
-      <c r="E688" s="18"/>
-      <c r="F688" s="18"/>
-      <c r="G688" s="18"/>
+      <c r="D688" s="18"/>
+      <c r="E688" s="16"/>
+      <c r="F688" s="16"/>
+      <c r="G688" s="16"/>
       <c r="H688" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I688" s="19"/>
-      <c r="J688" s="19"/>
+      <c r="I688" s="17"/>
+      <c r="J688" s="17"/>
       <c r="K688" s="10" t="s">
         <v>20</v>
       </c>
@@ -34355,17 +34322,17 @@
     </row>
     <row r="689" ht="18.0" customHeight="1">
       <c r="A689" s="6"/>
-      <c r="B689" s="16"/>
+      <c r="B689" s="15"/>
       <c r="C689" s="14"/>
-      <c r="D689" s="17"/>
-      <c r="E689" s="18"/>
-      <c r="F689" s="18"/>
-      <c r="G689" s="18"/>
+      <c r="D689" s="18"/>
+      <c r="E689" s="16"/>
+      <c r="F689" s="16"/>
+      <c r="G689" s="16"/>
       <c r="H689" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I689" s="19"/>
-      <c r="J689" s="19"/>
+      <c r="I689" s="17"/>
+      <c r="J689" s="17"/>
       <c r="K689" s="10" t="s">
         <v>20</v>
       </c>
@@ -34381,17 +34348,17 @@
     </row>
     <row r="690" ht="18.0" customHeight="1">
       <c r="A690" s="6"/>
-      <c r="B690" s="16"/>
+      <c r="B690" s="15"/>
       <c r="C690" s="14"/>
-      <c r="D690" s="17"/>
-      <c r="E690" s="18"/>
-      <c r="F690" s="18"/>
-      <c r="G690" s="18"/>
+      <c r="D690" s="18"/>
+      <c r="E690" s="16"/>
+      <c r="F690" s="16"/>
+      <c r="G690" s="16"/>
       <c r="H690" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I690" s="19"/>
-      <c r="J690" s="19"/>
+      <c r="I690" s="17"/>
+      <c r="J690" s="17"/>
       <c r="K690" s="10" t="s">
         <v>20</v>
       </c>
@@ -34407,17 +34374,17 @@
     </row>
     <row r="691" ht="18.0" customHeight="1">
       <c r="A691" s="6"/>
-      <c r="B691" s="16"/>
+      <c r="B691" s="15"/>
       <c r="C691" s="14"/>
-      <c r="D691" s="17"/>
-      <c r="E691" s="18"/>
-      <c r="F691" s="18"/>
-      <c r="G691" s="18"/>
+      <c r="D691" s="18"/>
+      <c r="E691" s="16"/>
+      <c r="F691" s="16"/>
+      <c r="G691" s="16"/>
       <c r="H691" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I691" s="19"/>
-      <c r="J691" s="19"/>
+      <c r="I691" s="17"/>
+      <c r="J691" s="17"/>
       <c r="K691" s="10" t="s">
         <v>20</v>
       </c>
@@ -34433,17 +34400,17 @@
     </row>
     <row r="692" ht="18.0" customHeight="1">
       <c r="A692" s="6"/>
-      <c r="B692" s="16"/>
+      <c r="B692" s="15"/>
       <c r="C692" s="14"/>
-      <c r="D692" s="17"/>
-      <c r="E692" s="18"/>
-      <c r="F692" s="18"/>
-      <c r="G692" s="18"/>
+      <c r="D692" s="18"/>
+      <c r="E692" s="16"/>
+      <c r="F692" s="16"/>
+      <c r="G692" s="16"/>
       <c r="H692" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I692" s="19"/>
-      <c r="J692" s="19"/>
+      <c r="I692" s="17"/>
+      <c r="J692" s="17"/>
       <c r="K692" s="10" t="s">
         <v>20</v>
       </c>
@@ -34459,17 +34426,17 @@
     </row>
     <row r="693" ht="18.0" customHeight="1">
       <c r="A693" s="6"/>
-      <c r="B693" s="16"/>
+      <c r="B693" s="15"/>
       <c r="C693" s="14"/>
-      <c r="D693" s="17"/>
-      <c r="E693" s="18"/>
-      <c r="F693" s="18"/>
-      <c r="G693" s="18"/>
+      <c r="D693" s="18"/>
+      <c r="E693" s="16"/>
+      <c r="F693" s="16"/>
+      <c r="G693" s="16"/>
       <c r="H693" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I693" s="19"/>
-      <c r="J693" s="19"/>
+      <c r="I693" s="17"/>
+      <c r="J693" s="17"/>
       <c r="K693" s="10" t="s">
         <v>20</v>
       </c>
@@ -34485,17 +34452,17 @@
     </row>
     <row r="694" ht="18.0" customHeight="1">
       <c r="A694" s="6"/>
-      <c r="B694" s="16"/>
+      <c r="B694" s="15"/>
       <c r="C694" s="14"/>
-      <c r="D694" s="20"/>
-      <c r="E694" s="18"/>
-      <c r="F694" s="18"/>
-      <c r="G694" s="18"/>
+      <c r="D694" s="19"/>
+      <c r="E694" s="16"/>
+      <c r="F694" s="16"/>
+      <c r="G694" s="16"/>
       <c r="H694" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I694" s="19"/>
-      <c r="J694" s="19"/>
+      <c r="I694" s="17"/>
+      <c r="J694" s="17"/>
       <c r="K694" s="10" t="s">
         <v>20</v>
       </c>
@@ -34511,17 +34478,17 @@
     </row>
     <row r="695" ht="18.0" customHeight="1">
       <c r="A695" s="6"/>
-      <c r="B695" s="16"/>
+      <c r="B695" s="15"/>
       <c r="C695" s="14"/>
-      <c r="D695" s="20"/>
-      <c r="E695" s="18"/>
-      <c r="F695" s="18"/>
-      <c r="G695" s="18"/>
+      <c r="D695" s="19"/>
+      <c r="E695" s="16"/>
+      <c r="F695" s="16"/>
+      <c r="G695" s="16"/>
       <c r="H695" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I695" s="19"/>
-      <c r="J695" s="19"/>
+      <c r="I695" s="17"/>
+      <c r="J695" s="17"/>
       <c r="K695" s="10" t="s">
         <v>20</v>
       </c>
@@ -34537,17 +34504,17 @@
     </row>
     <row r="696" ht="18.0" customHeight="1">
       <c r="A696" s="6"/>
-      <c r="B696" s="16"/>
+      <c r="B696" s="15"/>
       <c r="C696" s="14"/>
-      <c r="D696" s="20"/>
-      <c r="E696" s="18"/>
-      <c r="F696" s="18"/>
-      <c r="G696" s="18"/>
+      <c r="D696" s="19"/>
+      <c r="E696" s="16"/>
+      <c r="F696" s="16"/>
+      <c r="G696" s="16"/>
       <c r="H696" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I696" s="19"/>
-      <c r="J696" s="19"/>
+      <c r="I696" s="17"/>
+      <c r="J696" s="17"/>
       <c r="K696" s="10" t="s">
         <v>20</v>
       </c>
@@ -34563,17 +34530,17 @@
     </row>
     <row r="697" ht="18.0" customHeight="1">
       <c r="A697" s="6"/>
-      <c r="B697" s="16"/>
+      <c r="B697" s="15"/>
       <c r="C697" s="14"/>
-      <c r="D697" s="20"/>
-      <c r="E697" s="18"/>
-      <c r="F697" s="18"/>
-      <c r="G697" s="18"/>
+      <c r="D697" s="19"/>
+      <c r="E697" s="16"/>
+      <c r="F697" s="16"/>
+      <c r="G697" s="16"/>
       <c r="H697" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I697" s="19"/>
-      <c r="J697" s="19"/>
+      <c r="I697" s="17"/>
+      <c r="J697" s="17"/>
       <c r="K697" s="10" t="s">
         <v>20</v>
       </c>
@@ -34589,17 +34556,17 @@
     </row>
     <row r="698" ht="18.0" customHeight="1">
       <c r="A698" s="6"/>
-      <c r="B698" s="16"/>
+      <c r="B698" s="15"/>
       <c r="C698" s="14"/>
-      <c r="D698" s="20"/>
-      <c r="E698" s="18"/>
-      <c r="F698" s="18"/>
-      <c r="G698" s="18"/>
+      <c r="D698" s="19"/>
+      <c r="E698" s="16"/>
+      <c r="F698" s="16"/>
+      <c r="G698" s="16"/>
       <c r="H698" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I698" s="19"/>
-      <c r="J698" s="19"/>
+      <c r="I698" s="17"/>
+      <c r="J698" s="17"/>
       <c r="K698" s="10" t="s">
         <v>20</v>
       </c>
@@ -34615,17 +34582,17 @@
     </row>
     <row r="699" ht="18.0" customHeight="1">
       <c r="A699" s="6"/>
-      <c r="B699" s="16"/>
+      <c r="B699" s="15"/>
       <c r="C699" s="14"/>
-      <c r="D699" s="20"/>
-      <c r="E699" s="18"/>
-      <c r="F699" s="18"/>
-      <c r="G699" s="18"/>
+      <c r="D699" s="19"/>
+      <c r="E699" s="16"/>
+      <c r="F699" s="16"/>
+      <c r="G699" s="16"/>
       <c r="H699" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I699" s="19"/>
-      <c r="J699" s="19"/>
+      <c r="I699" s="17"/>
+      <c r="J699" s="17"/>
       <c r="K699" s="10" t="s">
         <v>20</v>
       </c>
@@ -34641,17 +34608,17 @@
     </row>
     <row r="700" ht="18.0" customHeight="1">
       <c r="A700" s="6"/>
-      <c r="B700" s="16"/>
+      <c r="B700" s="15"/>
       <c r="C700" s="14"/>
-      <c r="D700" s="20"/>
-      <c r="E700" s="18"/>
-      <c r="F700" s="18"/>
-      <c r="G700" s="18"/>
+      <c r="D700" s="19"/>
+      <c r="E700" s="16"/>
+      <c r="F700" s="16"/>
+      <c r="G700" s="16"/>
       <c r="H700" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I700" s="19"/>
-      <c r="J700" s="19"/>
+      <c r="I700" s="17"/>
+      <c r="J700" s="17"/>
       <c r="K700" s="10" t="s">
         <v>20</v>
       </c>
@@ -34667,17 +34634,17 @@
     </row>
     <row r="701" ht="18.0" customHeight="1">
       <c r="A701" s="6"/>
-      <c r="B701" s="16"/>
+      <c r="B701" s="15"/>
       <c r="C701" s="14"/>
-      <c r="D701" s="20"/>
-      <c r="E701" s="18"/>
-      <c r="F701" s="18"/>
-      <c r="G701" s="18"/>
+      <c r="D701" s="19"/>
+      <c r="E701" s="16"/>
+      <c r="F701" s="16"/>
+      <c r="G701" s="16"/>
       <c r="H701" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I701" s="19"/>
-      <c r="J701" s="19"/>
+      <c r="I701" s="17"/>
+      <c r="J701" s="17"/>
       <c r="K701" s="10" t="s">
         <v>20</v>
       </c>
@@ -34693,17 +34660,17 @@
     </row>
     <row r="702" ht="18.0" customHeight="1">
       <c r="A702" s="6"/>
-      <c r="B702" s="16"/>
+      <c r="B702" s="15"/>
       <c r="C702" s="14"/>
-      <c r="D702" s="20"/>
-      <c r="E702" s="18"/>
-      <c r="F702" s="18"/>
-      <c r="G702" s="18"/>
+      <c r="D702" s="19"/>
+      <c r="E702" s="16"/>
+      <c r="F702" s="16"/>
+      <c r="G702" s="16"/>
       <c r="H702" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I702" s="19"/>
-      <c r="J702" s="19"/>
+      <c r="I702" s="17"/>
+      <c r="J702" s="17"/>
       <c r="K702" s="10" t="s">
         <v>20</v>
       </c>
@@ -34719,17 +34686,17 @@
     </row>
     <row r="703" ht="18.0" customHeight="1">
       <c r="A703" s="6"/>
-      <c r="B703" s="16"/>
+      <c r="B703" s="15"/>
       <c r="C703" s="14"/>
-      <c r="D703" s="20"/>
-      <c r="E703" s="18"/>
-      <c r="F703" s="18"/>
-      <c r="G703" s="18"/>
+      <c r="D703" s="19"/>
+      <c r="E703" s="16"/>
+      <c r="F703" s="16"/>
+      <c r="G703" s="16"/>
       <c r="H703" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I703" s="19"/>
-      <c r="J703" s="19"/>
+      <c r="I703" s="17"/>
+      <c r="J703" s="17"/>
       <c r="K703" s="10" t="s">
         <v>20</v>
       </c>
@@ -34745,17 +34712,17 @@
     </row>
     <row r="704" ht="18.0" customHeight="1">
       <c r="A704" s="6"/>
-      <c r="B704" s="16"/>
+      <c r="B704" s="15"/>
       <c r="C704" s="14"/>
-      <c r="D704" s="20"/>
-      <c r="E704" s="18"/>
-      <c r="F704" s="18"/>
-      <c r="G704" s="18"/>
+      <c r="D704" s="19"/>
+      <c r="E704" s="16"/>
+      <c r="F704" s="16"/>
+      <c r="G704" s="16"/>
       <c r="H704" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I704" s="19"/>
-      <c r="J704" s="19"/>
+      <c r="I704" s="17"/>
+      <c r="J704" s="17"/>
       <c r="K704" s="10" t="s">
         <v>20</v>
       </c>
@@ -34771,17 +34738,17 @@
     </row>
     <row r="705" ht="18.0" customHeight="1">
       <c r="A705" s="6"/>
-      <c r="B705" s="16"/>
+      <c r="B705" s="15"/>
       <c r="C705" s="14"/>
-      <c r="D705" s="20"/>
-      <c r="E705" s="18"/>
-      <c r="F705" s="18"/>
-      <c r="G705" s="18"/>
+      <c r="D705" s="19"/>
+      <c r="E705" s="16"/>
+      <c r="F705" s="16"/>
+      <c r="G705" s="16"/>
       <c r="H705" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I705" s="19"/>
-      <c r="J705" s="19"/>
+      <c r="I705" s="17"/>
+      <c r="J705" s="17"/>
       <c r="K705" s="10" t="s">
         <v>20</v>
       </c>
@@ -34797,17 +34764,17 @@
     </row>
     <row r="706" ht="18.0" customHeight="1">
       <c r="A706" s="6"/>
-      <c r="B706" s="16"/>
+      <c r="B706" s="15"/>
       <c r="C706" s="14"/>
-      <c r="D706" s="20"/>
-      <c r="E706" s="18"/>
-      <c r="F706" s="18"/>
-      <c r="G706" s="18"/>
+      <c r="D706" s="19"/>
+      <c r="E706" s="16"/>
+      <c r="F706" s="16"/>
+      <c r="G706" s="16"/>
       <c r="H706" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I706" s="19"/>
-      <c r="J706" s="19"/>
+      <c r="I706" s="17"/>
+      <c r="J706" s="17"/>
       <c r="K706" s="10" t="s">
         <v>20</v>
       </c>
@@ -34823,17 +34790,17 @@
     </row>
     <row r="707" ht="18.0" customHeight="1">
       <c r="A707" s="6"/>
-      <c r="B707" s="16"/>
+      <c r="B707" s="15"/>
       <c r="C707" s="14"/>
-      <c r="D707" s="20"/>
-      <c r="E707" s="18"/>
-      <c r="F707" s="18"/>
-      <c r="G707" s="18"/>
+      <c r="D707" s="19"/>
+      <c r="E707" s="16"/>
+      <c r="F707" s="16"/>
+      <c r="G707" s="16"/>
       <c r="H707" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I707" s="19"/>
-      <c r="J707" s="19"/>
+      <c r="I707" s="17"/>
+      <c r="J707" s="17"/>
       <c r="K707" s="10" t="s">
         <v>20</v>
       </c>
@@ -34849,17 +34816,17 @@
     </row>
     <row r="708" ht="18.0" customHeight="1">
       <c r="A708" s="6"/>
-      <c r="B708" s="16"/>
+      <c r="B708" s="15"/>
       <c r="C708" s="14"/>
-      <c r="D708" s="20"/>
-      <c r="E708" s="18"/>
-      <c r="F708" s="18"/>
-      <c r="G708" s="18"/>
+      <c r="D708" s="19"/>
+      <c r="E708" s="16"/>
+      <c r="F708" s="16"/>
+      <c r="G708" s="16"/>
       <c r="H708" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I708" s="19"/>
-      <c r="J708" s="19"/>
+      <c r="I708" s="17"/>
+      <c r="J708" s="17"/>
       <c r="K708" s="10" t="s">
         <v>20</v>
       </c>
@@ -34875,17 +34842,17 @@
     </row>
     <row r="709" ht="18.0" customHeight="1">
       <c r="A709" s="6"/>
-      <c r="B709" s="16"/>
+      <c r="B709" s="15"/>
       <c r="C709" s="14"/>
-      <c r="D709" s="20"/>
-      <c r="E709" s="18"/>
-      <c r="F709" s="18"/>
-      <c r="G709" s="18"/>
+      <c r="D709" s="19"/>
+      <c r="E709" s="16"/>
+      <c r="F709" s="16"/>
+      <c r="G709" s="16"/>
       <c r="H709" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I709" s="19"/>
-      <c r="J709" s="19"/>
+      <c r="I709" s="17"/>
+      <c r="J709" s="17"/>
       <c r="K709" s="10" t="s">
         <v>20</v>
       </c>
@@ -34901,17 +34868,17 @@
     </row>
     <row r="710" ht="18.0" customHeight="1">
       <c r="A710" s="6"/>
-      <c r="B710" s="16"/>
+      <c r="B710" s="15"/>
       <c r="C710" s="14"/>
-      <c r="D710" s="20"/>
-      <c r="E710" s="18"/>
-      <c r="F710" s="18"/>
-      <c r="G710" s="18"/>
+      <c r="D710" s="19"/>
+      <c r="E710" s="16"/>
+      <c r="F710" s="16"/>
+      <c r="G710" s="16"/>
       <c r="H710" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I710" s="19"/>
-      <c r="J710" s="19"/>
+      <c r="I710" s="17"/>
+      <c r="J710" s="17"/>
       <c r="K710" s="10" t="s">
         <v>20</v>
       </c>
@@ -34927,17 +34894,17 @@
     </row>
     <row r="711" ht="18.0" customHeight="1">
       <c r="A711" s="6"/>
-      <c r="B711" s="16"/>
+      <c r="B711" s="15"/>
       <c r="C711" s="14"/>
-      <c r="D711" s="20"/>
-      <c r="E711" s="18"/>
-      <c r="F711" s="18"/>
-      <c r="G711" s="18"/>
+      <c r="D711" s="19"/>
+      <c r="E711" s="16"/>
+      <c r="F711" s="16"/>
+      <c r="G711" s="16"/>
       <c r="H711" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I711" s="19"/>
-      <c r="J711" s="19"/>
+      <c r="I711" s="17"/>
+      <c r="J711" s="17"/>
       <c r="K711" s="10" t="s">
         <v>20</v>
       </c>
@@ -34953,17 +34920,17 @@
     </row>
     <row r="712" ht="18.0" customHeight="1">
       <c r="A712" s="6"/>
-      <c r="B712" s="16"/>
+      <c r="B712" s="15"/>
       <c r="C712" s="14"/>
-      <c r="D712" s="20"/>
-      <c r="E712" s="18"/>
-      <c r="F712" s="18"/>
-      <c r="G712" s="18"/>
+      <c r="D712" s="19"/>
+      <c r="E712" s="16"/>
+      <c r="F712" s="16"/>
+      <c r="G712" s="16"/>
       <c r="H712" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I712" s="19"/>
-      <c r="J712" s="19"/>
+      <c r="I712" s="17"/>
+      <c r="J712" s="17"/>
       <c r="K712" s="10" t="s">
         <v>20</v>
       </c>
@@ -34979,17 +34946,17 @@
     </row>
     <row r="713" ht="18.0" customHeight="1">
       <c r="A713" s="6"/>
-      <c r="B713" s="16"/>
+      <c r="B713" s="15"/>
       <c r="C713" s="14"/>
-      <c r="D713" s="20"/>
-      <c r="E713" s="18"/>
-      <c r="F713" s="18"/>
-      <c r="G713" s="18"/>
+      <c r="D713" s="19"/>
+      <c r="E713" s="16"/>
+      <c r="F713" s="16"/>
+      <c r="G713" s="16"/>
       <c r="H713" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I713" s="19"/>
-      <c r="J713" s="19"/>
+      <c r="I713" s="17"/>
+      <c r="J713" s="17"/>
       <c r="K713" s="10" t="s">
         <v>20</v>
       </c>
@@ -35005,17 +34972,17 @@
     </row>
     <row r="714" ht="18.0" customHeight="1">
       <c r="A714" s="6"/>
-      <c r="B714" s="16"/>
+      <c r="B714" s="15"/>
       <c r="C714" s="14"/>
-      <c r="D714" s="20"/>
-      <c r="E714" s="18"/>
-      <c r="F714" s="18"/>
-      <c r="G714" s="18"/>
+      <c r="D714" s="19"/>
+      <c r="E714" s="16"/>
+      <c r="F714" s="16"/>
+      <c r="G714" s="16"/>
       <c r="H714" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I714" s="19"/>
-      <c r="J714" s="19"/>
+      <c r="I714" s="17"/>
+      <c r="J714" s="17"/>
       <c r="K714" s="10" t="s">
         <v>20</v>
       </c>
@@ -35031,17 +34998,17 @@
     </row>
     <row r="715" ht="18.0" customHeight="1">
       <c r="A715" s="6"/>
-      <c r="B715" s="16"/>
+      <c r="B715" s="15"/>
       <c r="C715" s="14"/>
-      <c r="D715" s="20"/>
-      <c r="E715" s="18"/>
-      <c r="F715" s="18"/>
-      <c r="G715" s="18"/>
+      <c r="D715" s="19"/>
+      <c r="E715" s="16"/>
+      <c r="F715" s="16"/>
+      <c r="G715" s="16"/>
       <c r="H715" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I715" s="19"/>
-      <c r="J715" s="19"/>
+      <c r="I715" s="17"/>
+      <c r="J715" s="17"/>
       <c r="K715" s="10" t="s">
         <v>20</v>
       </c>
@@ -35057,17 +35024,17 @@
     </row>
     <row r="716" ht="18.0" customHeight="1">
       <c r="A716" s="6"/>
-      <c r="B716" s="16"/>
+      <c r="B716" s="15"/>
       <c r="C716" s="14"/>
-      <c r="D716" s="20"/>
-      <c r="E716" s="18"/>
-      <c r="F716" s="18"/>
-      <c r="G716" s="18"/>
+      <c r="D716" s="19"/>
+      <c r="E716" s="16"/>
+      <c r="F716" s="16"/>
+      <c r="G716" s="16"/>
       <c r="H716" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I716" s="19"/>
-      <c r="J716" s="19"/>
+      <c r="I716" s="17"/>
+      <c r="J716" s="17"/>
       <c r="K716" s="10" t="s">
         <v>20</v>
       </c>
@@ -35083,17 +35050,17 @@
     </row>
     <row r="717" ht="18.0" customHeight="1">
       <c r="A717" s="6"/>
-      <c r="B717" s="16"/>
+      <c r="B717" s="15"/>
       <c r="C717" s="14"/>
-      <c r="D717" s="20"/>
-      <c r="E717" s="18"/>
-      <c r="F717" s="18"/>
-      <c r="G717" s="18"/>
+      <c r="D717" s="19"/>
+      <c r="E717" s="16"/>
+      <c r="F717" s="16"/>
+      <c r="G717" s="16"/>
       <c r="H717" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I717" s="19"/>
-      <c r="J717" s="19"/>
+      <c r="I717" s="17"/>
+      <c r="J717" s="17"/>
       <c r="K717" s="10" t="s">
         <v>20</v>
       </c>
@@ -35109,17 +35076,17 @@
     </row>
     <row r="718" ht="18.0" customHeight="1">
       <c r="A718" s="6"/>
-      <c r="B718" s="16"/>
+      <c r="B718" s="15"/>
       <c r="C718" s="14"/>
-      <c r="D718" s="20"/>
-      <c r="E718" s="18"/>
-      <c r="F718" s="18"/>
-      <c r="G718" s="18"/>
+      <c r="D718" s="19"/>
+      <c r="E718" s="16"/>
+      <c r="F718" s="16"/>
+      <c r="G718" s="16"/>
       <c r="H718" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I718" s="19"/>
-      <c r="J718" s="19"/>
+      <c r="I718" s="17"/>
+      <c r="J718" s="17"/>
       <c r="K718" s="10" t="s">
         <v>20</v>
       </c>
@@ -35135,17 +35102,17 @@
     </row>
     <row r="719" ht="18.0" customHeight="1">
       <c r="A719" s="6"/>
-      <c r="B719" s="16"/>
+      <c r="B719" s="15"/>
       <c r="C719" s="14"/>
-      <c r="D719" s="20"/>
-      <c r="E719" s="18"/>
-      <c r="F719" s="18"/>
-      <c r="G719" s="18"/>
+      <c r="D719" s="19"/>
+      <c r="E719" s="16"/>
+      <c r="F719" s="16"/>
+      <c r="G719" s="16"/>
       <c r="H719" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I719" s="19"/>
-      <c r="J719" s="19"/>
+      <c r="I719" s="17"/>
+      <c r="J719" s="17"/>
       <c r="K719" s="10" t="s">
         <v>20</v>
       </c>
@@ -35161,17 +35128,17 @@
     </row>
     <row r="720" ht="18.0" customHeight="1">
       <c r="A720" s="6"/>
-      <c r="B720" s="16"/>
+      <c r="B720" s="15"/>
       <c r="C720" s="14"/>
-      <c r="D720" s="20"/>
-      <c r="E720" s="18"/>
-      <c r="F720" s="18"/>
-      <c r="G720" s="18"/>
+      <c r="D720" s="19"/>
+      <c r="E720" s="16"/>
+      <c r="F720" s="16"/>
+      <c r="G720" s="16"/>
       <c r="H720" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I720" s="19"/>
-      <c r="J720" s="19"/>
+      <c r="I720" s="17"/>
+      <c r="J720" s="17"/>
       <c r="K720" s="10" t="s">
         <v>20</v>
       </c>
@@ -35187,17 +35154,17 @@
     </row>
     <row r="721" ht="18.0" customHeight="1">
       <c r="A721" s="6"/>
-      <c r="B721" s="16"/>
+      <c r="B721" s="15"/>
       <c r="C721" s="14"/>
-      <c r="D721" s="20"/>
-      <c r="E721" s="18"/>
-      <c r="F721" s="18"/>
-      <c r="G721" s="18"/>
+      <c r="D721" s="19"/>
+      <c r="E721" s="16"/>
+      <c r="F721" s="16"/>
+      <c r="G721" s="16"/>
       <c r="H721" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I721" s="19"/>
-      <c r="J721" s="19"/>
+      <c r="I721" s="17"/>
+      <c r="J721" s="17"/>
       <c r="K721" s="10" t="s">
         <v>20</v>
       </c>
@@ -35213,17 +35180,17 @@
     </row>
     <row r="722" ht="18.0" customHeight="1">
       <c r="A722" s="6"/>
-      <c r="B722" s="16"/>
+      <c r="B722" s="15"/>
       <c r="C722" s="14"/>
-      <c r="D722" s="20"/>
-      <c r="E722" s="18"/>
-      <c r="F722" s="18"/>
-      <c r="G722" s="18"/>
+      <c r="D722" s="19"/>
+      <c r="E722" s="16"/>
+      <c r="F722" s="16"/>
+      <c r="G722" s="16"/>
       <c r="H722" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I722" s="19"/>
-      <c r="J722" s="19"/>
+      <c r="I722" s="17"/>
+      <c r="J722" s="17"/>
       <c r="K722" s="10" t="s">
         <v>20</v>
       </c>
@@ -35239,17 +35206,17 @@
     </row>
     <row r="723" ht="18.0" customHeight="1">
       <c r="A723" s="6"/>
-      <c r="B723" s="16"/>
+      <c r="B723" s="15"/>
       <c r="C723" s="14"/>
-      <c r="D723" s="20"/>
-      <c r="E723" s="18"/>
-      <c r="F723" s="18"/>
-      <c r="G723" s="18"/>
+      <c r="D723" s="19"/>
+      <c r="E723" s="16"/>
+      <c r="F723" s="16"/>
+      <c r="G723" s="16"/>
       <c r="H723" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I723" s="19"/>
-      <c r="J723" s="19"/>
+      <c r="I723" s="17"/>
+      <c r="J723" s="17"/>
       <c r="K723" s="10" t="s">
         <v>20</v>
       </c>
@@ -35265,17 +35232,17 @@
     </row>
     <row r="724" ht="18.0" customHeight="1">
       <c r="A724" s="6"/>
-      <c r="B724" s="16"/>
+      <c r="B724" s="15"/>
       <c r="C724" s="14"/>
-      <c r="D724" s="20"/>
-      <c r="E724" s="18"/>
-      <c r="F724" s="18"/>
-      <c r="G724" s="18"/>
+      <c r="D724" s="19"/>
+      <c r="E724" s="16"/>
+      <c r="F724" s="16"/>
+      <c r="G724" s="16"/>
       <c r="H724" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I724" s="19"/>
-      <c r="J724" s="19"/>
+      <c r="I724" s="17"/>
+      <c r="J724" s="17"/>
       <c r="K724" s="10" t="s">
         <v>20</v>
       </c>
@@ -35291,17 +35258,17 @@
     </row>
     <row r="725" ht="18.0" customHeight="1">
       <c r="A725" s="6"/>
-      <c r="B725" s="16"/>
+      <c r="B725" s="15"/>
       <c r="C725" s="14"/>
-      <c r="D725" s="20"/>
-      <c r="E725" s="18"/>
-      <c r="F725" s="18"/>
-      <c r="G725" s="18"/>
+      <c r="D725" s="19"/>
+      <c r="E725" s="16"/>
+      <c r="F725" s="16"/>
+      <c r="G725" s="16"/>
       <c r="H725" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I725" s="19"/>
-      <c r="J725" s="19"/>
+      <c r="I725" s="17"/>
+      <c r="J725" s="17"/>
       <c r="K725" s="10" t="s">
         <v>20</v>
       </c>
@@ -35317,17 +35284,17 @@
     </row>
     <row r="726" ht="18.0" customHeight="1">
       <c r="A726" s="6"/>
-      <c r="B726" s="16"/>
+      <c r="B726" s="15"/>
       <c r="C726" s="14"/>
-      <c r="D726" s="20"/>
-      <c r="E726" s="18"/>
-      <c r="F726" s="18"/>
-      <c r="G726" s="18"/>
+      <c r="D726" s="19"/>
+      <c r="E726" s="16"/>
+      <c r="F726" s="16"/>
+      <c r="G726" s="16"/>
       <c r="H726" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I726" s="19"/>
-      <c r="J726" s="19"/>
+      <c r="I726" s="17"/>
+      <c r="J726" s="17"/>
       <c r="K726" s="10" t="s">
         <v>20</v>
       </c>
@@ -35343,17 +35310,17 @@
     </row>
     <row r="727" ht="18.0" customHeight="1">
       <c r="A727" s="6"/>
-      <c r="B727" s="16"/>
+      <c r="B727" s="15"/>
       <c r="C727" s="14"/>
-      <c r="D727" s="20"/>
-      <c r="E727" s="18"/>
-      <c r="F727" s="18"/>
-      <c r="G727" s="18"/>
+      <c r="D727" s="19"/>
+      <c r="E727" s="16"/>
+      <c r="F727" s="16"/>
+      <c r="G727" s="16"/>
       <c r="H727" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I727" s="19"/>
-      <c r="J727" s="19"/>
+      <c r="I727" s="17"/>
+      <c r="J727" s="17"/>
       <c r="K727" s="10" t="s">
         <v>20</v>
       </c>
@@ -35369,17 +35336,17 @@
     </row>
     <row r="728" ht="18.0" customHeight="1">
       <c r="A728" s="6"/>
-      <c r="B728" s="16"/>
+      <c r="B728" s="15"/>
       <c r="C728" s="14"/>
-      <c r="D728" s="20"/>
-      <c r="E728" s="18"/>
-      <c r="F728" s="18"/>
-      <c r="G728" s="18"/>
+      <c r="D728" s="19"/>
+      <c r="E728" s="16"/>
+      <c r="F728" s="16"/>
+      <c r="G728" s="16"/>
       <c r="H728" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I728" s="19"/>
-      <c r="J728" s="19"/>
+      <c r="I728" s="17"/>
+      <c r="J728" s="17"/>
       <c r="K728" s="10" t="s">
         <v>20</v>
       </c>
@@ -35395,17 +35362,17 @@
     </row>
     <row r="729" ht="18.0" customHeight="1">
       <c r="A729" s="6"/>
-      <c r="B729" s="16"/>
+      <c r="B729" s="15"/>
       <c r="C729" s="14"/>
-      <c r="D729" s="20"/>
-      <c r="E729" s="18"/>
-      <c r="F729" s="18"/>
-      <c r="G729" s="18"/>
+      <c r="D729" s="19"/>
+      <c r="E729" s="16"/>
+      <c r="F729" s="16"/>
+      <c r="G729" s="16"/>
       <c r="H729" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I729" s="19"/>
-      <c r="J729" s="19"/>
+      <c r="I729" s="17"/>
+      <c r="J729" s="17"/>
       <c r="K729" s="10" t="s">
         <v>20</v>
       </c>
@@ -35421,17 +35388,17 @@
     </row>
     <row r="730" ht="18.0" customHeight="1">
       <c r="A730" s="6"/>
-      <c r="B730" s="16"/>
+      <c r="B730" s="15"/>
       <c r="C730" s="14"/>
-      <c r="D730" s="20"/>
-      <c r="E730" s="18"/>
-      <c r="F730" s="18"/>
-      <c r="G730" s="18"/>
+      <c r="D730" s="19"/>
+      <c r="E730" s="16"/>
+      <c r="F730" s="16"/>
+      <c r="G730" s="16"/>
       <c r="H730" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I730" s="19"/>
-      <c r="J730" s="19"/>
+      <c r="I730" s="17"/>
+      <c r="J730" s="17"/>
       <c r="K730" s="10" t="s">
         <v>20</v>
       </c>
@@ -35447,17 +35414,17 @@
     </row>
     <row r="731" ht="18.0" customHeight="1">
       <c r="A731" s="6"/>
-      <c r="B731" s="16"/>
+      <c r="B731" s="15"/>
       <c r="C731" s="14"/>
-      <c r="D731" s="20"/>
-      <c r="E731" s="18"/>
-      <c r="F731" s="18"/>
-      <c r="G731" s="18"/>
+      <c r="D731" s="19"/>
+      <c r="E731" s="16"/>
+      <c r="F731" s="16"/>
+      <c r="G731" s="16"/>
       <c r="H731" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I731" s="19"/>
-      <c r="J731" s="19"/>
+      <c r="I731" s="17"/>
+      <c r="J731" s="17"/>
       <c r="K731" s="10" t="s">
         <v>20</v>
       </c>
@@ -35473,17 +35440,17 @@
     </row>
     <row r="732" ht="18.0" customHeight="1">
       <c r="A732" s="6"/>
-      <c r="B732" s="16"/>
+      <c r="B732" s="15"/>
       <c r="C732" s="14"/>
-      <c r="D732" s="20"/>
-      <c r="E732" s="18"/>
-      <c r="F732" s="18"/>
-      <c r="G732" s="18"/>
+      <c r="D732" s="19"/>
+      <c r="E732" s="16"/>
+      <c r="F732" s="16"/>
+      <c r="G732" s="16"/>
       <c r="H732" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I732" s="19"/>
-      <c r="J732" s="19"/>
+      <c r="I732" s="17"/>
+      <c r="J732" s="17"/>
       <c r="K732" s="10" t="s">
         <v>20</v>
       </c>
@@ -35499,17 +35466,17 @@
     </row>
     <row r="733" ht="18.0" customHeight="1">
       <c r="A733" s="6"/>
-      <c r="B733" s="16"/>
+      <c r="B733" s="15"/>
       <c r="C733" s="14"/>
-      <c r="D733" s="20"/>
-      <c r="E733" s="18"/>
-      <c r="F733" s="18"/>
-      <c r="G733" s="18"/>
+      <c r="D733" s="19"/>
+      <c r="E733" s="16"/>
+      <c r="F733" s="16"/>
+      <c r="G733" s="16"/>
       <c r="H733" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I733" s="19"/>
-      <c r="J733" s="19"/>
+      <c r="I733" s="17"/>
+      <c r="J733" s="17"/>
       <c r="K733" s="10" t="s">
         <v>20</v>
       </c>
@@ -35525,17 +35492,17 @@
     </row>
     <row r="734" ht="18.0" customHeight="1">
       <c r="A734" s="6"/>
-      <c r="B734" s="16"/>
+      <c r="B734" s="15"/>
       <c r="C734" s="14"/>
-      <c r="D734" s="20"/>
-      <c r="E734" s="18"/>
-      <c r="F734" s="18"/>
-      <c r="G734" s="18"/>
+      <c r="D734" s="19"/>
+      <c r="E734" s="16"/>
+      <c r="F734" s="16"/>
+      <c r="G734" s="16"/>
       <c r="H734" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I734" s="19"/>
-      <c r="J734" s="19"/>
+      <c r="I734" s="17"/>
+      <c r="J734" s="17"/>
       <c r="K734" s="10" t="s">
         <v>20</v>
       </c>
@@ -35551,17 +35518,17 @@
     </row>
     <row r="735" ht="18.0" customHeight="1">
       <c r="A735" s="6"/>
-      <c r="B735" s="16"/>
+      <c r="B735" s="15"/>
       <c r="C735" s="14"/>
-      <c r="D735" s="20"/>
-      <c r="E735" s="18"/>
-      <c r="F735" s="18"/>
-      <c r="G735" s="18"/>
+      <c r="D735" s="19"/>
+      <c r="E735" s="16"/>
+      <c r="F735" s="16"/>
+      <c r="G735" s="16"/>
       <c r="H735" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I735" s="19"/>
-      <c r="J735" s="19"/>
+      <c r="I735" s="17"/>
+      <c r="J735" s="17"/>
       <c r="K735" s="10" t="s">
         <v>20</v>
       </c>
@@ -35577,17 +35544,17 @@
     </row>
     <row r="736" ht="18.0" customHeight="1">
       <c r="A736" s="6"/>
-      <c r="B736" s="16"/>
+      <c r="B736" s="15"/>
       <c r="C736" s="14"/>
-      <c r="D736" s="20"/>
-      <c r="E736" s="18"/>
-      <c r="F736" s="18"/>
-      <c r="G736" s="18"/>
+      <c r="D736" s="19"/>
+      <c r="E736" s="16"/>
+      <c r="F736" s="16"/>
+      <c r="G736" s="16"/>
       <c r="H736" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I736" s="19"/>
-      <c r="J736" s="19"/>
+      <c r="I736" s="17"/>
+      <c r="J736" s="17"/>
       <c r="K736" s="10" t="s">
         <v>20</v>
       </c>
@@ -35603,17 +35570,17 @@
     </row>
     <row r="737" ht="18.0" customHeight="1">
       <c r="A737" s="6"/>
-      <c r="B737" s="16"/>
+      <c r="B737" s="15"/>
       <c r="C737" s="14"/>
-      <c r="D737" s="20"/>
-      <c r="E737" s="18"/>
-      <c r="F737" s="18"/>
-      <c r="G737" s="18"/>
+      <c r="D737" s="19"/>
+      <c r="E737" s="16"/>
+      <c r="F737" s="16"/>
+      <c r="G737" s="16"/>
       <c r="H737" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I737" s="19"/>
-      <c r="J737" s="19"/>
+      <c r="I737" s="17"/>
+      <c r="J737" s="17"/>
       <c r="K737" s="10" t="s">
         <v>20</v>
       </c>
@@ -35629,17 +35596,17 @@
     </row>
     <row r="738" ht="18.0" customHeight="1">
       <c r="A738" s="6"/>
-      <c r="B738" s="16"/>
+      <c r="B738" s="15"/>
       <c r="C738" s="14"/>
-      <c r="D738" s="20"/>
-      <c r="E738" s="18"/>
-      <c r="F738" s="18"/>
-      <c r="G738" s="18"/>
+      <c r="D738" s="19"/>
+      <c r="E738" s="16"/>
+      <c r="F738" s="16"/>
+      <c r="G738" s="16"/>
       <c r="H738" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I738" s="19"/>
-      <c r="J738" s="19"/>
+      <c r="I738" s="17"/>
+      <c r="J738" s="17"/>
       <c r="K738" s="10" t="s">
         <v>20</v>
       </c>
@@ -35655,17 +35622,17 @@
     </row>
     <row r="739" ht="18.0" customHeight="1">
       <c r="A739" s="6"/>
-      <c r="B739" s="16"/>
+      <c r="B739" s="15"/>
       <c r="C739" s="14"/>
-      <c r="D739" s="20"/>
-      <c r="E739" s="18"/>
-      <c r="F739" s="18"/>
-      <c r="G739" s="18"/>
+      <c r="D739" s="19"/>
+      <c r="E739" s="16"/>
+      <c r="F739" s="16"/>
+      <c r="G739" s="16"/>
       <c r="H739" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I739" s="19"/>
-      <c r="J739" s="19"/>
+      <c r="I739" s="17"/>
+      <c r="J739" s="17"/>
       <c r="K739" s="10" t="s">
         <v>20</v>
       </c>
@@ -35681,17 +35648,17 @@
     </row>
     <row r="740" ht="18.0" customHeight="1">
       <c r="A740" s="6"/>
-      <c r="B740" s="16"/>
+      <c r="B740" s="15"/>
       <c r="C740" s="14"/>
-      <c r="D740" s="20"/>
-      <c r="E740" s="18"/>
-      <c r="F740" s="18"/>
-      <c r="G740" s="18"/>
+      <c r="D740" s="19"/>
+      <c r="E740" s="16"/>
+      <c r="F740" s="16"/>
+      <c r="G740" s="16"/>
       <c r="H740" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I740" s="19"/>
-      <c r="J740" s="19"/>
+      <c r="I740" s="17"/>
+      <c r="J740" s="17"/>
       <c r="K740" s="10" t="s">
         <v>20</v>
       </c>
@@ -35707,17 +35674,17 @@
     </row>
     <row r="741" ht="18.0" customHeight="1">
       <c r="A741" s="6"/>
-      <c r="B741" s="16"/>
+      <c r="B741" s="15"/>
       <c r="C741" s="14"/>
-      <c r="D741" s="20"/>
-      <c r="E741" s="18"/>
-      <c r="F741" s="18"/>
-      <c r="G741" s="18"/>
+      <c r="D741" s="19"/>
+      <c r="E741" s="16"/>
+      <c r="F741" s="16"/>
+      <c r="G741" s="16"/>
       <c r="H741" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I741" s="19"/>
-      <c r="J741" s="19"/>
+      <c r="I741" s="17"/>
+      <c r="J741" s="17"/>
       <c r="K741" s="10" t="s">
         <v>20</v>
       </c>
@@ -35733,17 +35700,17 @@
     </row>
     <row r="742" ht="18.0" customHeight="1">
       <c r="A742" s="6"/>
-      <c r="B742" s="16"/>
+      <c r="B742" s="15"/>
       <c r="C742" s="14"/>
-      <c r="D742" s="20"/>
-      <c r="E742" s="18"/>
-      <c r="F742" s="18"/>
-      <c r="G742" s="18"/>
+      <c r="D742" s="19"/>
+      <c r="E742" s="16"/>
+      <c r="F742" s="16"/>
+      <c r="G742" s="16"/>
       <c r="H742" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I742" s="19"/>
-      <c r="J742" s="19"/>
+      <c r="I742" s="17"/>
+      <c r="J742" s="17"/>
       <c r="K742" s="10" t="s">
         <v>20</v>
       </c>
@@ -35759,17 +35726,17 @@
     </row>
     <row r="743" ht="18.0" customHeight="1">
       <c r="A743" s="6"/>
-      <c r="B743" s="16"/>
+      <c r="B743" s="15"/>
       <c r="C743" s="14"/>
-      <c r="D743" s="20"/>
-      <c r="E743" s="18"/>
-      <c r="F743" s="18"/>
-      <c r="G743" s="18"/>
+      <c r="D743" s="19"/>
+      <c r="E743" s="16"/>
+      <c r="F743" s="16"/>
+      <c r="G743" s="16"/>
       <c r="H743" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I743" s="19"/>
-      <c r="J743" s="19"/>
+      <c r="I743" s="17"/>
+      <c r="J743" s="17"/>
       <c r="K743" s="10" t="s">
         <v>20</v>
       </c>
@@ -35785,17 +35752,17 @@
     </row>
     <row r="744" ht="18.0" customHeight="1">
       <c r="A744" s="6"/>
-      <c r="B744" s="16"/>
+      <c r="B744" s="15"/>
       <c r="C744" s="14"/>
-      <c r="D744" s="20"/>
-      <c r="E744" s="18"/>
-      <c r="F744" s="18"/>
-      <c r="G744" s="18"/>
+      <c r="D744" s="19"/>
+      <c r="E744" s="16"/>
+      <c r="F744" s="16"/>
+      <c r="G744" s="16"/>
       <c r="H744" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I744" s="19"/>
-      <c r="J744" s="19"/>
+      <c r="I744" s="17"/>
+      <c r="J744" s="17"/>
       <c r="K744" s="10" t="s">
         <v>20</v>
       </c>
@@ -35811,17 +35778,17 @@
     </row>
     <row r="745" ht="18.0" customHeight="1">
       <c r="A745" s="6"/>
-      <c r="B745" s="16"/>
+      <c r="B745" s="15"/>
       <c r="C745" s="14"/>
-      <c r="D745" s="20"/>
-      <c r="E745" s="18"/>
-      <c r="F745" s="18"/>
-      <c r="G745" s="18"/>
+      <c r="D745" s="19"/>
+      <c r="E745" s="16"/>
+      <c r="F745" s="16"/>
+      <c r="G745" s="16"/>
       <c r="H745" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I745" s="19"/>
-      <c r="J745" s="19"/>
+      <c r="I745" s="17"/>
+      <c r="J745" s="17"/>
       <c r="K745" s="10" t="s">
         <v>20</v>
       </c>
@@ -35837,17 +35804,17 @@
     </row>
     <row r="746" ht="18.0" customHeight="1">
       <c r="A746" s="6"/>
-      <c r="B746" s="16"/>
+      <c r="B746" s="15"/>
       <c r="C746" s="14"/>
-      <c r="D746" s="20"/>
-      <c r="E746" s="18"/>
-      <c r="F746" s="18"/>
-      <c r="G746" s="18"/>
+      <c r="D746" s="19"/>
+      <c r="E746" s="16"/>
+      <c r="F746" s="16"/>
+      <c r="G746" s="16"/>
       <c r="H746" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I746" s="19"/>
-      <c r="J746" s="19"/>
+      <c r="I746" s="17"/>
+      <c r="J746" s="17"/>
       <c r="K746" s="10" t="s">
         <v>20</v>
       </c>
@@ -35863,17 +35830,17 @@
     </row>
     <row r="747" ht="18.0" customHeight="1">
       <c r="A747" s="6"/>
-      <c r="B747" s="16"/>
+      <c r="B747" s="15"/>
       <c r="C747" s="14"/>
-      <c r="D747" s="20"/>
-      <c r="E747" s="18"/>
-      <c r="F747" s="18"/>
-      <c r="G747" s="18"/>
+      <c r="D747" s="19"/>
+      <c r="E747" s="16"/>
+      <c r="F747" s="16"/>
+      <c r="G747" s="16"/>
       <c r="H747" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I747" s="19"/>
-      <c r="J747" s="19"/>
+      <c r="I747" s="17"/>
+      <c r="J747" s="17"/>
       <c r="K747" s="10" t="s">
         <v>20</v>
       </c>
@@ -35889,17 +35856,17 @@
     </row>
     <row r="748" ht="18.0" customHeight="1">
       <c r="A748" s="6"/>
-      <c r="B748" s="16"/>
+      <c r="B748" s="15"/>
       <c r="C748" s="14"/>
-      <c r="D748" s="20"/>
-      <c r="E748" s="18"/>
-      <c r="F748" s="18"/>
-      <c r="G748" s="18"/>
+      <c r="D748" s="19"/>
+      <c r="E748" s="16"/>
+      <c r="F748" s="16"/>
+      <c r="G748" s="16"/>
       <c r="H748" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I748" s="19"/>
-      <c r="J748" s="19"/>
+      <c r="I748" s="17"/>
+      <c r="J748" s="17"/>
       <c r="K748" s="10" t="s">
         <v>20</v>
       </c>
@@ -35915,17 +35882,17 @@
     </row>
     <row r="749" ht="18.0" customHeight="1">
       <c r="A749" s="6"/>
-      <c r="B749" s="16"/>
+      <c r="B749" s="15"/>
       <c r="C749" s="14"/>
-      <c r="D749" s="20"/>
-      <c r="E749" s="18"/>
-      <c r="F749" s="18"/>
-      <c r="G749" s="18"/>
+      <c r="D749" s="19"/>
+      <c r="E749" s="16"/>
+      <c r="F749" s="16"/>
+      <c r="G749" s="16"/>
       <c r="H749" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I749" s="19"/>
-      <c r="J749" s="19"/>
+      <c r="I749" s="17"/>
+      <c r="J749" s="17"/>
       <c r="K749" s="10" t="s">
         <v>20</v>
       </c>
@@ -35941,17 +35908,17 @@
     </row>
     <row r="750" ht="18.0" customHeight="1">
       <c r="A750" s="6"/>
-      <c r="B750" s="16"/>
+      <c r="B750" s="15"/>
       <c r="C750" s="14"/>
-      <c r="D750" s="20"/>
-      <c r="E750" s="18"/>
-      <c r="F750" s="18"/>
-      <c r="G750" s="18"/>
+      <c r="D750" s="19"/>
+      <c r="E750" s="16"/>
+      <c r="F750" s="16"/>
+      <c r="G750" s="16"/>
       <c r="H750" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I750" s="19"/>
-      <c r="J750" s="19"/>
+      <c r="I750" s="17"/>
+      <c r="J750" s="17"/>
       <c r="K750" s="10" t="s">
         <v>20</v>
       </c>
@@ -35967,17 +35934,17 @@
     </row>
     <row r="751" ht="18.0" customHeight="1">
       <c r="A751" s="6"/>
-      <c r="B751" s="16"/>
+      <c r="B751" s="15"/>
       <c r="C751" s="14"/>
-      <c r="D751" s="20"/>
-      <c r="E751" s="18"/>
-      <c r="F751" s="18"/>
-      <c r="G751" s="18"/>
+      <c r="D751" s="19"/>
+      <c r="E751" s="16"/>
+      <c r="F751" s="16"/>
+      <c r="G751" s="16"/>
       <c r="H751" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I751" s="19"/>
-      <c r="J751" s="19"/>
+      <c r="I751" s="17"/>
+      <c r="J751" s="17"/>
       <c r="K751" s="10" t="s">
         <v>20</v>
       </c>
@@ -35993,17 +35960,17 @@
     </row>
     <row r="752" ht="18.0" customHeight="1">
       <c r="A752" s="6"/>
-      <c r="B752" s="16"/>
+      <c r="B752" s="15"/>
       <c r="C752" s="14"/>
-      <c r="D752" s="20"/>
-      <c r="E752" s="18"/>
-      <c r="F752" s="18"/>
-      <c r="G752" s="18"/>
+      <c r="D752" s="19"/>
+      <c r="E752" s="16"/>
+      <c r="F752" s="16"/>
+      <c r="G752" s="16"/>
       <c r="H752" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I752" s="19"/>
-      <c r="J752" s="19"/>
+      <c r="I752" s="17"/>
+      <c r="J752" s="17"/>
       <c r="K752" s="10" t="s">
         <v>20</v>
       </c>
@@ -36019,17 +35986,17 @@
     </row>
     <row r="753" ht="18.0" customHeight="1">
       <c r="A753" s="6"/>
-      <c r="B753" s="16"/>
+      <c r="B753" s="15"/>
       <c r="C753" s="14"/>
-      <c r="D753" s="20"/>
-      <c r="E753" s="18"/>
-      <c r="F753" s="18"/>
-      <c r="G753" s="18"/>
+      <c r="D753" s="19"/>
+      <c r="E753" s="16"/>
+      <c r="F753" s="16"/>
+      <c r="G753" s="16"/>
       <c r="H753" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I753" s="19"/>
-      <c r="J753" s="19"/>
+      <c r="I753" s="17"/>
+      <c r="J753" s="17"/>
       <c r="K753" s="10" t="s">
         <v>20</v>
       </c>
@@ -36045,17 +36012,17 @@
     </row>
     <row r="754" ht="18.0" customHeight="1">
       <c r="A754" s="6"/>
-      <c r="B754" s="16"/>
+      <c r="B754" s="15"/>
       <c r="C754" s="14"/>
-      <c r="D754" s="20"/>
-      <c r="E754" s="18"/>
-      <c r="F754" s="18"/>
-      <c r="G754" s="18"/>
+      <c r="D754" s="19"/>
+      <c r="E754" s="16"/>
+      <c r="F754" s="16"/>
+      <c r="G754" s="16"/>
       <c r="H754" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I754" s="19"/>
-      <c r="J754" s="19"/>
+      <c r="I754" s="17"/>
+      <c r="J754" s="17"/>
       <c r="K754" s="10" t="s">
         <v>20</v>
       </c>
@@ -36071,17 +36038,17 @@
     </row>
     <row r="755" ht="18.0" customHeight="1">
       <c r="A755" s="6"/>
-      <c r="B755" s="16"/>
+      <c r="B755" s="15"/>
       <c r="C755" s="14"/>
-      <c r="D755" s="20"/>
-      <c r="E755" s="18"/>
-      <c r="F755" s="18"/>
-      <c r="G755" s="18"/>
+      <c r="D755" s="19"/>
+      <c r="E755" s="16"/>
+      <c r="F755" s="16"/>
+      <c r="G755" s="16"/>
       <c r="H755" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I755" s="19"/>
-      <c r="J755" s="19"/>
+      <c r="I755" s="17"/>
+      <c r="J755" s="17"/>
       <c r="K755" s="10" t="s">
         <v>20</v>
       </c>
@@ -36097,17 +36064,17 @@
     </row>
     <row r="756" ht="18.0" customHeight="1">
       <c r="A756" s="6"/>
-      <c r="B756" s="16"/>
+      <c r="B756" s="15"/>
       <c r="C756" s="14"/>
-      <c r="D756" s="20"/>
-      <c r="E756" s="18"/>
-      <c r="F756" s="18"/>
-      <c r="G756" s="18"/>
+      <c r="D756" s="19"/>
+      <c r="E756" s="16"/>
+      <c r="F756" s="16"/>
+      <c r="G756" s="16"/>
       <c r="H756" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I756" s="19"/>
-      <c r="J756" s="19"/>
+      <c r="I756" s="17"/>
+      <c r="J756" s="17"/>
       <c r="K756" s="10" t="s">
         <v>20</v>
       </c>
@@ -36123,17 +36090,17 @@
     </row>
     <row r="757" ht="18.0" customHeight="1">
       <c r="A757" s="6"/>
-      <c r="B757" s="16"/>
+      <c r="B757" s="15"/>
       <c r="C757" s="14"/>
-      <c r="D757" s="20"/>
-      <c r="E757" s="18"/>
-      <c r="F757" s="18"/>
-      <c r="G757" s="18"/>
+      <c r="D757" s="19"/>
+      <c r="E757" s="16"/>
+      <c r="F757" s="16"/>
+      <c r="G757" s="16"/>
       <c r="H757" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I757" s="19"/>
-      <c r="J757" s="19"/>
+      <c r="I757" s="17"/>
+      <c r="J757" s="17"/>
       <c r="K757" s="10" t="s">
         <v>20</v>
       </c>
@@ -36149,17 +36116,17 @@
     </row>
     <row r="758" ht="18.0" customHeight="1">
       <c r="A758" s="6"/>
-      <c r="B758" s="16"/>
+      <c r="B758" s="15"/>
       <c r="C758" s="14"/>
-      <c r="D758" s="20"/>
-      <c r="E758" s="18"/>
-      <c r="F758" s="18"/>
-      <c r="G758" s="18"/>
+      <c r="D758" s="19"/>
+      <c r="E758" s="16"/>
+      <c r="F758" s="16"/>
+      <c r="G758" s="16"/>
       <c r="H758" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I758" s="19"/>
-      <c r="J758" s="19"/>
+      <c r="I758" s="17"/>
+      <c r="J758" s="17"/>
       <c r="K758" s="10" t="s">
         <v>20</v>
       </c>
@@ -36175,17 +36142,17 @@
     </row>
     <row r="759" ht="18.0" customHeight="1">
       <c r="A759" s="6"/>
-      <c r="B759" s="16"/>
+      <c r="B759" s="15"/>
       <c r="C759" s="14"/>
-      <c r="D759" s="20"/>
-      <c r="E759" s="18"/>
-      <c r="F759" s="18"/>
-      <c r="G759" s="18"/>
+      <c r="D759" s="19"/>
+      <c r="E759" s="16"/>
+      <c r="F759" s="16"/>
+      <c r="G759" s="16"/>
       <c r="H759" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I759" s="19"/>
-      <c r="J759" s="19"/>
+      <c r="I759" s="17"/>
+      <c r="J759" s="17"/>
       <c r="K759" s="10" t="s">
         <v>20</v>
       </c>
@@ -36201,17 +36168,17 @@
     </row>
     <row r="760" ht="18.0" customHeight="1">
       <c r="A760" s="6"/>
-      <c r="B760" s="16"/>
+      <c r="B760" s="15"/>
       <c r="C760" s="14"/>
-      <c r="D760" s="20"/>
-      <c r="E760" s="18"/>
-      <c r="F760" s="18"/>
-      <c r="G760" s="18"/>
+      <c r="D760" s="19"/>
+      <c r="E760" s="16"/>
+      <c r="F760" s="16"/>
+      <c r="G760" s="16"/>
       <c r="H760" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I760" s="19"/>
-      <c r="J760" s="19"/>
+      <c r="I760" s="17"/>
+      <c r="J760" s="17"/>
       <c r="K760" s="10" t="s">
         <v>20</v>
       </c>
@@ -36227,17 +36194,17 @@
     </row>
     <row r="761" ht="18.0" customHeight="1">
       <c r="A761" s="6"/>
-      <c r="B761" s="16"/>
+      <c r="B761" s="15"/>
       <c r="C761" s="14"/>
-      <c r="D761" s="20"/>
-      <c r="E761" s="18"/>
-      <c r="F761" s="18"/>
-      <c r="G761" s="18"/>
+      <c r="D761" s="19"/>
+      <c r="E761" s="16"/>
+      <c r="F761" s="16"/>
+      <c r="G761" s="16"/>
       <c r="H761" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I761" s="19"/>
-      <c r="J761" s="19"/>
+      <c r="I761" s="17"/>
+      <c r="J761" s="17"/>
       <c r="K761" s="10" t="s">
         <v>20</v>
       </c>
@@ -36253,17 +36220,17 @@
     </row>
     <row r="762" ht="18.0" customHeight="1">
       <c r="A762" s="6"/>
-      <c r="B762" s="16"/>
+      <c r="B762" s="15"/>
       <c r="C762" s="14"/>
-      <c r="D762" s="20"/>
-      <c r="E762" s="18"/>
-      <c r="F762" s="18"/>
-      <c r="G762" s="18"/>
+      <c r="D762" s="19"/>
+      <c r="E762" s="16"/>
+      <c r="F762" s="16"/>
+      <c r="G762" s="16"/>
       <c r="H762" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I762" s="19"/>
-      <c r="J762" s="19"/>
+      <c r="I762" s="17"/>
+      <c r="J762" s="17"/>
       <c r="K762" s="10" t="s">
         <v>20</v>
       </c>
@@ -36279,17 +36246,17 @@
     </row>
     <row r="763" ht="18.0" customHeight="1">
       <c r="A763" s="6"/>
-      <c r="B763" s="16"/>
+      <c r="B763" s="15"/>
       <c r="C763" s="14"/>
-      <c r="D763" s="20"/>
-      <c r="E763" s="18"/>
-      <c r="F763" s="18"/>
-      <c r="G763" s="18"/>
+      <c r="D763" s="19"/>
+      <c r="E763" s="16"/>
+      <c r="F763" s="16"/>
+      <c r="G763" s="16"/>
       <c r="H763" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I763" s="19"/>
-      <c r="J763" s="19"/>
+      <c r="I763" s="17"/>
+      <c r="J763" s="17"/>
       <c r="K763" s="10" t="s">
         <v>20</v>
       </c>
@@ -36305,17 +36272,17 @@
     </row>
     <row r="764" ht="18.0" customHeight="1">
       <c r="A764" s="6"/>
-      <c r="B764" s="16"/>
+      <c r="B764" s="15"/>
       <c r="C764" s="14"/>
-      <c r="D764" s="20"/>
-      <c r="E764" s="18"/>
-      <c r="F764" s="18"/>
-      <c r="G764" s="18"/>
+      <c r="D764" s="19"/>
+      <c r="E764" s="16"/>
+      <c r="F764" s="16"/>
+      <c r="G764" s="16"/>
       <c r="H764" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I764" s="19"/>
-      <c r="J764" s="19"/>
+      <c r="I764" s="17"/>
+      <c r="J764" s="17"/>
       <c r="K764" s="10" t="s">
         <v>20</v>
       </c>
@@ -36331,17 +36298,17 @@
     </row>
     <row r="765" ht="18.0" customHeight="1">
       <c r="A765" s="6"/>
-      <c r="B765" s="16"/>
+      <c r="B765" s="15"/>
       <c r="C765" s="14"/>
-      <c r="D765" s="20"/>
-      <c r="E765" s="18"/>
-      <c r="F765" s="18"/>
-      <c r="G765" s="18"/>
+      <c r="D765" s="19"/>
+      <c r="E765" s="16"/>
+      <c r="F765" s="16"/>
+      <c r="G765" s="16"/>
       <c r="H765" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I765" s="19"/>
-      <c r="J765" s="19"/>
+      <c r="I765" s="17"/>
+      <c r="J765" s="17"/>
       <c r="K765" s="10" t="s">
         <v>20</v>
       </c>
@@ -36357,17 +36324,17 @@
     </row>
     <row r="766" ht="18.0" customHeight="1">
       <c r="A766" s="6"/>
-      <c r="B766" s="16"/>
+      <c r="B766" s="15"/>
       <c r="C766" s="14"/>
-      <c r="D766" s="20"/>
-      <c r="E766" s="18"/>
-      <c r="F766" s="18"/>
-      <c r="G766" s="18"/>
+      <c r="D766" s="19"/>
+      <c r="E766" s="16"/>
+      <c r="F766" s="16"/>
+      <c r="G766" s="16"/>
       <c r="H766" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I766" s="19"/>
-      <c r="J766" s="19"/>
+      <c r="I766" s="17"/>
+      <c r="J766" s="17"/>
       <c r="K766" s="10" t="s">
         <v>20</v>
       </c>
@@ -36383,17 +36350,17 @@
     </row>
     <row r="767" ht="18.0" customHeight="1">
       <c r="A767" s="6"/>
-      <c r="B767" s="16"/>
+      <c r="B767" s="15"/>
       <c r="C767" s="14"/>
-      <c r="D767" s="20"/>
-      <c r="E767" s="18"/>
-      <c r="F767" s="18"/>
-      <c r="G767" s="18"/>
+      <c r="D767" s="19"/>
+      <c r="E767" s="16"/>
+      <c r="F767" s="16"/>
+      <c r="G767" s="16"/>
       <c r="H767" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I767" s="19"/>
-      <c r="J767" s="19"/>
+      <c r="I767" s="17"/>
+      <c r="J767" s="17"/>
       <c r="K767" s="10" t="s">
         <v>20</v>
       </c>
@@ -36409,17 +36376,17 @@
     </row>
     <row r="768" ht="18.0" customHeight="1">
       <c r="A768" s="6"/>
-      <c r="B768" s="16"/>
+      <c r="B768" s="15"/>
       <c r="C768" s="14"/>
-      <c r="D768" s="20"/>
-      <c r="E768" s="18"/>
-      <c r="F768" s="18"/>
-      <c r="G768" s="18"/>
+      <c r="D768" s="19"/>
+      <c r="E768" s="16"/>
+      <c r="F768" s="16"/>
+      <c r="G768" s="16"/>
       <c r="H768" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I768" s="19"/>
-      <c r="J768" s="19"/>
+      <c r="I768" s="17"/>
+      <c r="J768" s="17"/>
       <c r="K768" s="10" t="s">
         <v>20</v>
       </c>
@@ -36435,17 +36402,17 @@
     </row>
     <row r="769" ht="18.0" customHeight="1">
       <c r="A769" s="6"/>
-      <c r="B769" s="16"/>
+      <c r="B769" s="15"/>
       <c r="C769" s="14"/>
-      <c r="D769" s="20"/>
-      <c r="E769" s="18"/>
-      <c r="F769" s="18"/>
-      <c r="G769" s="18"/>
+      <c r="D769" s="19"/>
+      <c r="E769" s="16"/>
+      <c r="F769" s="16"/>
+      <c r="G769" s="16"/>
       <c r="H769" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I769" s="19"/>
-      <c r="J769" s="19"/>
+      <c r="I769" s="17"/>
+      <c r="J769" s="17"/>
       <c r="K769" s="10" t="s">
         <v>20</v>
       </c>
@@ -36461,17 +36428,17 @@
     </row>
     <row r="770" ht="18.0" customHeight="1">
       <c r="A770" s="6"/>
-      <c r="B770" s="16"/>
+      <c r="B770" s="15"/>
       <c r="C770" s="14"/>
-      <c r="D770" s="20"/>
-      <c r="E770" s="18"/>
-      <c r="F770" s="18"/>
-      <c r="G770" s="18"/>
+      <c r="D770" s="19"/>
+      <c r="E770" s="16"/>
+      <c r="F770" s="16"/>
+      <c r="G770" s="16"/>
       <c r="H770" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I770" s="19"/>
-      <c r="J770" s="19"/>
+      <c r="I770" s="17"/>
+      <c r="J770" s="17"/>
       <c r="K770" s="10" t="s">
         <v>20</v>
       </c>
@@ -36487,17 +36454,17 @@
     </row>
     <row r="771" ht="18.0" customHeight="1">
       <c r="A771" s="6"/>
-      <c r="B771" s="16"/>
+      <c r="B771" s="15"/>
       <c r="C771" s="14"/>
-      <c r="D771" s="20"/>
-      <c r="E771" s="18"/>
-      <c r="F771" s="18"/>
-      <c r="G771" s="18"/>
+      <c r="D771" s="19"/>
+      <c r="E771" s="16"/>
+      <c r="F771" s="16"/>
+      <c r="G771" s="16"/>
       <c r="H771" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I771" s="19"/>
-      <c r="J771" s="19"/>
+      <c r="I771" s="17"/>
+      <c r="J771" s="17"/>
       <c r="K771" s="10" t="s">
         <v>20</v>
       </c>
@@ -36513,17 +36480,17 @@
     </row>
     <row r="772" ht="18.0" customHeight="1">
       <c r="A772" s="6"/>
-      <c r="B772" s="16"/>
+      <c r="B772" s="15"/>
       <c r="C772" s="14"/>
-      <c r="D772" s="20"/>
-      <c r="E772" s="18"/>
-      <c r="F772" s="18"/>
-      <c r="G772" s="18"/>
+      <c r="D772" s="19"/>
+      <c r="E772" s="16"/>
+      <c r="F772" s="16"/>
+      <c r="G772" s="16"/>
       <c r="H772" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I772" s="19"/>
-      <c r="J772" s="19"/>
+      <c r="I772" s="17"/>
+      <c r="J772" s="17"/>
       <c r="K772" s="10" t="s">
         <v>20</v>
       </c>
@@ -36539,17 +36506,17 @@
     </row>
     <row r="773" ht="18.0" customHeight="1">
       <c r="A773" s="6"/>
-      <c r="B773" s="16"/>
+      <c r="B773" s="15"/>
       <c r="C773" s="14"/>
-      <c r="D773" s="20"/>
-      <c r="E773" s="18"/>
-      <c r="F773" s="18"/>
-      <c r="G773" s="18"/>
+      <c r="D773" s="19"/>
+      <c r="E773" s="16"/>
+      <c r="F773" s="16"/>
+      <c r="G773" s="16"/>
       <c r="H773" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I773" s="19"/>
-      <c r="J773" s="19"/>
+      <c r="I773" s="17"/>
+      <c r="J773" s="17"/>
       <c r="K773" s="10" t="s">
         <v>20</v>
       </c>
@@ -36565,17 +36532,17 @@
     </row>
     <row r="774" ht="18.0" customHeight="1">
       <c r="A774" s="6"/>
-      <c r="B774" s="16"/>
+      <c r="B774" s="15"/>
       <c r="C774" s="14"/>
-      <c r="D774" s="20"/>
-      <c r="E774" s="18"/>
-      <c r="F774" s="18"/>
-      <c r="G774" s="18"/>
+      <c r="D774" s="19"/>
+      <c r="E774" s="16"/>
+      <c r="F774" s="16"/>
+      <c r="G774" s="16"/>
       <c r="H774" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I774" s="19"/>
-      <c r="J774" s="19"/>
+      <c r="I774" s="17"/>
+      <c r="J774" s="17"/>
       <c r="K774" s="10" t="s">
         <v>20</v>
       </c>
@@ -36591,17 +36558,17 @@
     </row>
     <row r="775" ht="18.0" customHeight="1">
       <c r="A775" s="6"/>
-      <c r="B775" s="16"/>
+      <c r="B775" s="15"/>
       <c r="C775" s="14"/>
-      <c r="D775" s="20"/>
-      <c r="E775" s="18"/>
-      <c r="F775" s="18"/>
-      <c r="G775" s="18"/>
+      <c r="D775" s="19"/>
+      <c r="E775" s="16"/>
+      <c r="F775" s="16"/>
+      <c r="G775" s="16"/>
       <c r="H775" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I775" s="19"/>
-      <c r="J775" s="19"/>
+      <c r="I775" s="17"/>
+      <c r="J775" s="17"/>
       <c r="K775" s="10" t="s">
         <v>20</v>
       </c>
@@ -36617,17 +36584,17 @@
     </row>
     <row r="776" ht="18.0" customHeight="1">
       <c r="A776" s="6"/>
-      <c r="B776" s="16"/>
+      <c r="B776" s="15"/>
       <c r="C776" s="14"/>
-      <c r="D776" s="20"/>
-      <c r="E776" s="18"/>
-      <c r="F776" s="18"/>
-      <c r="G776" s="18"/>
+      <c r="D776" s="19"/>
+      <c r="E776" s="16"/>
+      <c r="F776" s="16"/>
+      <c r="G776" s="16"/>
       <c r="H776" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I776" s="19"/>
-      <c r="J776" s="19"/>
+      <c r="I776" s="17"/>
+      <c r="J776" s="17"/>
       <c r="K776" s="10" t="s">
         <v>20</v>
       </c>
@@ -36643,17 +36610,17 @@
     </row>
     <row r="777" ht="18.0" customHeight="1">
       <c r="A777" s="6"/>
-      <c r="B777" s="16"/>
+      <c r="B777" s="15"/>
       <c r="C777" s="14"/>
-      <c r="D777" s="20"/>
-      <c r="E777" s="18"/>
-      <c r="F777" s="18"/>
-      <c r="G777" s="18"/>
+      <c r="D777" s="19"/>
+      <c r="E777" s="16"/>
+      <c r="F777" s="16"/>
+      <c r="G777" s="16"/>
       <c r="H777" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I777" s="19"/>
-      <c r="J777" s="19"/>
+      <c r="I777" s="17"/>
+      <c r="J777" s="17"/>
       <c r="K777" s="10" t="s">
         <v>20</v>
       </c>
@@ -36669,17 +36636,17 @@
     </row>
     <row r="778" ht="18.0" customHeight="1">
       <c r="A778" s="6"/>
-      <c r="B778" s="16"/>
+      <c r="B778" s="15"/>
       <c r="C778" s="14"/>
-      <c r="D778" s="20"/>
-      <c r="E778" s="18"/>
-      <c r="F778" s="18"/>
-      <c r="G778" s="18"/>
+      <c r="D778" s="19"/>
+      <c r="E778" s="16"/>
+      <c r="F778" s="16"/>
+      <c r="G778" s="16"/>
       <c r="H778" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I778" s="19"/>
-      <c r="J778" s="19"/>
+      <c r="I778" s="17"/>
+      <c r="J778" s="17"/>
       <c r="K778" s="10" t="s">
         <v>20</v>
       </c>
@@ -36695,17 +36662,17 @@
     </row>
     <row r="779" ht="18.0" customHeight="1">
       <c r="A779" s="6"/>
-      <c r="B779" s="16"/>
+      <c r="B779" s="15"/>
       <c r="C779" s="14"/>
-      <c r="D779" s="20"/>
-      <c r="E779" s="18"/>
-      <c r="F779" s="18"/>
-      <c r="G779" s="18"/>
+      <c r="D779" s="19"/>
+      <c r="E779" s="16"/>
+      <c r="F779" s="16"/>
+      <c r="G779" s="16"/>
       <c r="H779" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I779" s="19"/>
-      <c r="J779" s="19"/>
+      <c r="I779" s="17"/>
+      <c r="J779" s="17"/>
       <c r="K779" s="10" t="s">
         <v>20</v>
       </c>
@@ -36721,17 +36688,17 @@
     </row>
     <row r="780" ht="18.0" customHeight="1">
       <c r="A780" s="6"/>
-      <c r="B780" s="16"/>
+      <c r="B780" s="15"/>
       <c r="C780" s="14"/>
-      <c r="D780" s="20"/>
-      <c r="E780" s="18"/>
-      <c r="F780" s="18"/>
-      <c r="G780" s="18"/>
+      <c r="D780" s="19"/>
+      <c r="E780" s="16"/>
+      <c r="F780" s="16"/>
+      <c r="G780" s="16"/>
       <c r="H780" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I780" s="19"/>
-      <c r="J780" s="19"/>
+      <c r="I780" s="17"/>
+      <c r="J780" s="17"/>
       <c r="K780" s="10" t="s">
         <v>20</v>
       </c>
@@ -36747,17 +36714,17 @@
     </row>
     <row r="781" ht="18.0" customHeight="1">
       <c r="A781" s="6"/>
-      <c r="B781" s="16"/>
+      <c r="B781" s="15"/>
       <c r="C781" s="14"/>
-      <c r="D781" s="20"/>
-      <c r="E781" s="18"/>
-      <c r="F781" s="18"/>
-      <c r="G781" s="18"/>
+      <c r="D781" s="19"/>
+      <c r="E781" s="16"/>
+      <c r="F781" s="16"/>
+      <c r="G781" s="16"/>
       <c r="H781" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I781" s="19"/>
-      <c r="J781" s="19"/>
+      <c r="I781" s="17"/>
+      <c r="J781" s="17"/>
       <c r="K781" s="10" t="s">
         <v>20</v>
       </c>
@@ -36773,17 +36740,17 @@
     </row>
     <row r="782" ht="18.0" customHeight="1">
       <c r="A782" s="6"/>
-      <c r="B782" s="16"/>
+      <c r="B782" s="15"/>
       <c r="C782" s="14"/>
-      <c r="D782" s="20"/>
-      <c r="E782" s="18"/>
-      <c r="F782" s="18"/>
-      <c r="G782" s="18"/>
+      <c r="D782" s="19"/>
+      <c r="E782" s="16"/>
+      <c r="F782" s="16"/>
+      <c r="G782" s="16"/>
       <c r="H782" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I782" s="19"/>
-      <c r="J782" s="19"/>
+      <c r="I782" s="17"/>
+      <c r="J782" s="17"/>
       <c r="K782" s="10" t="s">
         <v>20</v>
       </c>
@@ -36799,17 +36766,17 @@
     </row>
     <row r="783" ht="18.0" customHeight="1">
       <c r="A783" s="6"/>
-      <c r="B783" s="16"/>
+      <c r="B783" s="15"/>
       <c r="C783" s="14"/>
-      <c r="D783" s="20"/>
-      <c r="E783" s="18"/>
-      <c r="F783" s="18"/>
-      <c r="G783" s="18"/>
+      <c r="D783" s="19"/>
+      <c r="E783" s="16"/>
+      <c r="F783" s="16"/>
+      <c r="G783" s="16"/>
       <c r="H783" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I783" s="19"/>
-      <c r="J783" s="19"/>
+      <c r="I783" s="17"/>
+      <c r="J783" s="17"/>
       <c r="K783" s="10" t="s">
         <v>20</v>
       </c>
@@ -36825,17 +36792,17 @@
     </row>
     <row r="784" ht="18.0" customHeight="1">
       <c r="A784" s="6"/>
-      <c r="B784" s="16"/>
+      <c r="B784" s="15"/>
       <c r="C784" s="14"/>
-      <c r="D784" s="20"/>
-      <c r="E784" s="18"/>
-      <c r="F784" s="18"/>
-      <c r="G784" s="18"/>
+      <c r="D784" s="19"/>
+      <c r="E784" s="16"/>
+      <c r="F784" s="16"/>
+      <c r="G784" s="16"/>
       <c r="H784" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I784" s="19"/>
-      <c r="J784" s="19"/>
+      <c r="I784" s="17"/>
+      <c r="J784" s="17"/>
       <c r="K784" s="10" t="s">
         <v>20</v>
       </c>
@@ -36851,17 +36818,17 @@
     </row>
     <row r="785" ht="18.0" customHeight="1">
       <c r="A785" s="6"/>
-      <c r="B785" s="16"/>
+      <c r="B785" s="15"/>
       <c r="C785" s="14"/>
-      <c r="D785" s="20"/>
-      <c r="E785" s="18"/>
-      <c r="F785" s="18"/>
-      <c r="G785" s="18"/>
+      <c r="D785" s="19"/>
+      <c r="E785" s="16"/>
+      <c r="F785" s="16"/>
+      <c r="G785" s="16"/>
       <c r="H785" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I785" s="19"/>
-      <c r="J785" s="19"/>
+      <c r="I785" s="17"/>
+      <c r="J785" s="17"/>
       <c r="K785" s="10" t="s">
         <v>20</v>
       </c>
@@ -36877,17 +36844,17 @@
     </row>
     <row r="786" ht="18.0" customHeight="1">
       <c r="A786" s="6"/>
-      <c r="B786" s="16"/>
+      <c r="B786" s="15"/>
       <c r="C786" s="14"/>
-      <c r="D786" s="20"/>
-      <c r="E786" s="18"/>
-      <c r="F786" s="18"/>
-      <c r="G786" s="18"/>
+      <c r="D786" s="19"/>
+      <c r="E786" s="16"/>
+      <c r="F786" s="16"/>
+      <c r="G786" s="16"/>
       <c r="H786" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I786" s="19"/>
-      <c r="J786" s="19"/>
+      <c r="I786" s="17"/>
+      <c r="J786" s="17"/>
       <c r="K786" s="10" t="s">
         <v>20</v>
       </c>
@@ -36903,17 +36870,17 @@
     </row>
     <row r="787" ht="18.0" customHeight="1">
       <c r="A787" s="6"/>
-      <c r="B787" s="16"/>
+      <c r="B787" s="15"/>
       <c r="C787" s="14"/>
-      <c r="D787" s="20"/>
-      <c r="E787" s="18"/>
-      <c r="F787" s="18"/>
-      <c r="G787" s="18"/>
+      <c r="D787" s="19"/>
+      <c r="E787" s="16"/>
+      <c r="F787" s="16"/>
+      <c r="G787" s="16"/>
       <c r="H787" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I787" s="19"/>
-      <c r="J787" s="19"/>
+      <c r="I787" s="17"/>
+      <c r="J787" s="17"/>
       <c r="K787" s="10" t="s">
         <v>20</v>
       </c>
@@ -36929,17 +36896,17 @@
     </row>
     <row r="788" ht="18.0" customHeight="1">
       <c r="A788" s="6"/>
-      <c r="B788" s="16"/>
+      <c r="B788" s="15"/>
       <c r="C788" s="14"/>
-      <c r="D788" s="20"/>
-      <c r="E788" s="18"/>
-      <c r="F788" s="18"/>
-      <c r="G788" s="18"/>
+      <c r="D788" s="19"/>
+      <c r="E788" s="16"/>
+      <c r="F788" s="16"/>
+      <c r="G788" s="16"/>
       <c r="H788" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I788" s="19"/>
-      <c r="J788" s="19"/>
+      <c r="I788" s="17"/>
+      <c r="J788" s="17"/>
       <c r="K788" s="10" t="s">
         <v>20</v>
       </c>
@@ -36955,17 +36922,17 @@
     </row>
     <row r="789" ht="18.0" customHeight="1">
       <c r="A789" s="6"/>
-      <c r="B789" s="16"/>
+      <c r="B789" s="15"/>
       <c r="C789" s="14"/>
-      <c r="D789" s="20"/>
-      <c r="E789" s="18"/>
-      <c r="F789" s="18"/>
-      <c r="G789" s="18"/>
+      <c r="D789" s="19"/>
+      <c r="E789" s="16"/>
+      <c r="F789" s="16"/>
+      <c r="G789" s="16"/>
       <c r="H789" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I789" s="19"/>
-      <c r="J789" s="19"/>
+      <c r="I789" s="17"/>
+      <c r="J789" s="17"/>
       <c r="K789" s="10" t="s">
         <v>20</v>
       </c>
@@ -36981,17 +36948,17 @@
     </row>
     <row r="790" ht="18.0" customHeight="1">
       <c r="A790" s="6"/>
-      <c r="B790" s="16"/>
+      <c r="B790" s="15"/>
       <c r="C790" s="14"/>
-      <c r="D790" s="20"/>
-      <c r="E790" s="18"/>
-      <c r="F790" s="18"/>
-      <c r="G790" s="18"/>
+      <c r="D790" s="19"/>
+      <c r="E790" s="16"/>
+      <c r="F790" s="16"/>
+      <c r="G790" s="16"/>
       <c r="H790" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I790" s="19"/>
-      <c r="J790" s="19"/>
+      <c r="I790" s="17"/>
+      <c r="J790" s="17"/>
       <c r="K790" s="10" t="s">
         <v>20</v>
       </c>
@@ -37007,17 +36974,17 @@
     </row>
     <row r="791" ht="18.0" customHeight="1">
       <c r="A791" s="6"/>
-      <c r="B791" s="16"/>
+      <c r="B791" s="15"/>
       <c r="C791" s="14"/>
-      <c r="D791" s="20"/>
-      <c r="E791" s="18"/>
-      <c r="F791" s="18"/>
-      <c r="G791" s="18"/>
+      <c r="D791" s="19"/>
+      <c r="E791" s="16"/>
+      <c r="F791" s="16"/>
+      <c r="G791" s="16"/>
       <c r="H791" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I791" s="19"/>
-      <c r="J791" s="19"/>
+      <c r="I791" s="17"/>
+      <c r="J791" s="17"/>
       <c r="K791" s="10" t="s">
         <v>20</v>
       </c>
@@ -37033,17 +37000,17 @@
     </row>
     <row r="792" ht="18.0" customHeight="1">
       <c r="A792" s="6"/>
-      <c r="B792" s="16"/>
+      <c r="B792" s="15"/>
       <c r="C792" s="14"/>
-      <c r="D792" s="20"/>
-      <c r="E792" s="18"/>
-      <c r="F792" s="18"/>
-      <c r="G792" s="18"/>
+      <c r="D792" s="19"/>
+      <c r="E792" s="16"/>
+      <c r="F792" s="16"/>
+      <c r="G792" s="16"/>
       <c r="H792" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I792" s="19"/>
-      <c r="J792" s="19"/>
+      <c r="I792" s="17"/>
+      <c r="J792" s="17"/>
       <c r="K792" s="10" t="s">
         <v>20</v>
       </c>
@@ -37059,17 +37026,17 @@
     </row>
     <row r="793" ht="18.0" customHeight="1">
       <c r="A793" s="6"/>
-      <c r="B793" s="16"/>
+      <c r="B793" s="15"/>
       <c r="C793" s="14"/>
-      <c r="D793" s="20"/>
-      <c r="E793" s="18"/>
-      <c r="F793" s="18"/>
-      <c r="G793" s="18"/>
+      <c r="D793" s="19"/>
+      <c r="E793" s="16"/>
+      <c r="F793" s="16"/>
+      <c r="G793" s="16"/>
       <c r="H793" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I793" s="19"/>
-      <c r="J793" s="19"/>
+      <c r="I793" s="17"/>
+      <c r="J793" s="17"/>
       <c r="K793" s="10" t="s">
         <v>20</v>
       </c>
@@ -37085,17 +37052,17 @@
     </row>
     <row r="794" ht="18.0" customHeight="1">
       <c r="A794" s="6"/>
-      <c r="B794" s="16"/>
+      <c r="B794" s="15"/>
       <c r="C794" s="14"/>
-      <c r="D794" s="20"/>
-      <c r="E794" s="18"/>
-      <c r="F794" s="18"/>
-      <c r="G794" s="18"/>
+      <c r="D794" s="19"/>
+      <c r="E794" s="16"/>
+      <c r="F794" s="16"/>
+      <c r="G794" s="16"/>
       <c r="H794" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I794" s="19"/>
-      <c r="J794" s="19"/>
+      <c r="I794" s="17"/>
+      <c r="J794" s="17"/>
       <c r="K794" s="10" t="s">
         <v>20</v>
       </c>
@@ -37111,17 +37078,17 @@
     </row>
     <row r="795" ht="18.0" customHeight="1">
       <c r="A795" s="6"/>
-      <c r="B795" s="16"/>
+      <c r="B795" s="15"/>
       <c r="C795" s="14"/>
-      <c r="D795" s="20"/>
-      <c r="E795" s="18"/>
-      <c r="F795" s="18"/>
-      <c r="G795" s="18"/>
+      <c r="D795" s="19"/>
+      <c r="E795" s="16"/>
+      <c r="F795" s="16"/>
+      <c r="G795" s="16"/>
       <c r="H795" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I795" s="19"/>
-      <c r="J795" s="19"/>
+      <c r="I795" s="17"/>
+      <c r="J795" s="17"/>
       <c r="K795" s="10" t="s">
         <v>20</v>
       </c>
@@ -37137,17 +37104,17 @@
     </row>
     <row r="796" ht="18.0" customHeight="1">
       <c r="A796" s="6"/>
-      <c r="B796" s="16"/>
+      <c r="B796" s="15"/>
       <c r="C796" s="14"/>
-      <c r="D796" s="20"/>
-      <c r="E796" s="18"/>
-      <c r="F796" s="18"/>
-      <c r="G796" s="18"/>
+      <c r="D796" s="19"/>
+      <c r="E796" s="16"/>
+      <c r="F796" s="16"/>
+      <c r="G796" s="16"/>
       <c r="H796" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I796" s="19"/>
-      <c r="J796" s="19"/>
+      <c r="I796" s="17"/>
+      <c r="J796" s="17"/>
       <c r="K796" s="10" t="s">
         <v>20</v>
       </c>
@@ -37163,17 +37130,17 @@
     </row>
     <row r="797" ht="18.0" customHeight="1">
       <c r="A797" s="6"/>
-      <c r="B797" s="16"/>
+      <c r="B797" s="15"/>
       <c r="C797" s="14"/>
-      <c r="D797" s="20"/>
-      <c r="E797" s="18"/>
-      <c r="F797" s="18"/>
-      <c r="G797" s="18"/>
+      <c r="D797" s="19"/>
+      <c r="E797" s="16"/>
+      <c r="F797" s="16"/>
+      <c r="G797" s="16"/>
       <c r="H797" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I797" s="19"/>
-      <c r="J797" s="19"/>
+      <c r="I797" s="17"/>
+      <c r="J797" s="17"/>
       <c r="K797" s="10" t="s">
         <v>20</v>
       </c>
@@ -37189,17 +37156,17 @@
     </row>
     <row r="798" ht="18.0" customHeight="1">
       <c r="A798" s="6"/>
-      <c r="B798" s="16"/>
+      <c r="B798" s="15"/>
       <c r="C798" s="14"/>
-      <c r="D798" s="20"/>
-      <c r="E798" s="18"/>
-      <c r="F798" s="18"/>
-      <c r="G798" s="18"/>
+      <c r="D798" s="19"/>
+      <c r="E798" s="16"/>
+      <c r="F798" s="16"/>
+      <c r="G798" s="16"/>
       <c r="H798" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I798" s="19"/>
-      <c r="J798" s="19"/>
+      <c r="I798" s="17"/>
+      <c r="J798" s="17"/>
       <c r="K798" s="10" t="s">
         <v>20</v>
       </c>
@@ -37215,17 +37182,17 @@
     </row>
     <row r="799" ht="18.0" customHeight="1">
       <c r="A799" s="6"/>
-      <c r="B799" s="16"/>
+      <c r="B799" s="15"/>
       <c r="C799" s="14"/>
-      <c r="D799" s="20"/>
-      <c r="E799" s="18"/>
-      <c r="F799" s="18"/>
-      <c r="G799" s="18"/>
+      <c r="D799" s="19"/>
+      <c r="E799" s="16"/>
+      <c r="F799" s="16"/>
+      <c r="G799" s="16"/>
       <c r="H799" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I799" s="19"/>
-      <c r="J799" s="19"/>
+      <c r="I799" s="17"/>
+      <c r="J799" s="17"/>
       <c r="K799" s="10" t="s">
         <v>20</v>
       </c>
@@ -37241,17 +37208,17 @@
     </row>
     <row r="800" ht="18.0" customHeight="1">
       <c r="A800" s="6"/>
-      <c r="B800" s="16"/>
+      <c r="B800" s="15"/>
       <c r="C800" s="14"/>
-      <c r="D800" s="20"/>
-      <c r="E800" s="18"/>
-      <c r="F800" s="18"/>
-      <c r="G800" s="18"/>
+      <c r="D800" s="19"/>
+      <c r="E800" s="16"/>
+      <c r="F800" s="16"/>
+      <c r="G800" s="16"/>
       <c r="H800" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I800" s="19"/>
-      <c r="J800" s="19"/>
+      <c r="I800" s="17"/>
+      <c r="J800" s="17"/>
       <c r="K800" s="10" t="s">
         <v>20</v>
       </c>
@@ -37267,17 +37234,17 @@
     </row>
     <row r="801" ht="18.0" customHeight="1">
       <c r="A801" s="6"/>
-      <c r="B801" s="16"/>
+      <c r="B801" s="15"/>
       <c r="C801" s="14"/>
-      <c r="D801" s="20"/>
-      <c r="E801" s="18"/>
-      <c r="F801" s="18"/>
-      <c r="G801" s="18"/>
+      <c r="D801" s="19"/>
+      <c r="E801" s="16"/>
+      <c r="F801" s="16"/>
+      <c r="G801" s="16"/>
       <c r="H801" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I801" s="19"/>
-      <c r="J801" s="19"/>
+      <c r="I801" s="17"/>
+      <c r="J801" s="17"/>
       <c r="K801" s="10" t="s">
         <v>20</v>
       </c>
@@ -37293,17 +37260,17 @@
     </row>
     <row r="802" ht="18.0" customHeight="1">
       <c r="A802" s="6"/>
-      <c r="B802" s="16"/>
+      <c r="B802" s="15"/>
       <c r="C802" s="14"/>
-      <c r="D802" s="20"/>
-      <c r="E802" s="18"/>
-      <c r="F802" s="18"/>
-      <c r="G802" s="18"/>
+      <c r="D802" s="19"/>
+      <c r="E802" s="16"/>
+      <c r="F802" s="16"/>
+      <c r="G802" s="16"/>
       <c r="H802" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I802" s="19"/>
-      <c r="J802" s="19"/>
+      <c r="I802" s="17"/>
+      <c r="J802" s="17"/>
       <c r="K802" s="10" t="s">
         <v>20</v>
       </c>
@@ -37319,17 +37286,17 @@
     </row>
     <row r="803" ht="18.0" customHeight="1">
       <c r="A803" s="6"/>
-      <c r="B803" s="16"/>
+      <c r="B803" s="15"/>
       <c r="C803" s="14"/>
-      <c r="D803" s="20"/>
-      <c r="E803" s="18"/>
-      <c r="F803" s="18"/>
-      <c r="G803" s="18"/>
+      <c r="D803" s="19"/>
+      <c r="E803" s="16"/>
+      <c r="F803" s="16"/>
+      <c r="G803" s="16"/>
       <c r="H803" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I803" s="19"/>
-      <c r="J803" s="19"/>
+      <c r="I803" s="17"/>
+      <c r="J803" s="17"/>
       <c r="K803" s="10" t="s">
         <v>20</v>
       </c>
@@ -37345,17 +37312,17 @@
     </row>
     <row r="804" ht="18.0" customHeight="1">
       <c r="A804" s="6"/>
-      <c r="B804" s="16"/>
+      <c r="B804" s="15"/>
       <c r="C804" s="14"/>
-      <c r="D804" s="20"/>
-      <c r="E804" s="18"/>
-      <c r="F804" s="18"/>
-      <c r="G804" s="18"/>
+      <c r="D804" s="19"/>
+      <c r="E804" s="16"/>
+      <c r="F804" s="16"/>
+      <c r="G804" s="16"/>
       <c r="H804" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I804" s="19"/>
-      <c r="J804" s="19"/>
+      <c r="I804" s="17"/>
+      <c r="J804" s="17"/>
       <c r="K804" s="10" t="s">
         <v>20</v>
       </c>
@@ -37371,17 +37338,17 @@
     </row>
     <row r="805" ht="18.0" customHeight="1">
       <c r="A805" s="6"/>
-      <c r="B805" s="16"/>
+      <c r="B805" s="15"/>
       <c r="C805" s="14"/>
-      <c r="D805" s="20"/>
-      <c r="E805" s="18"/>
-      <c r="F805" s="18"/>
-      <c r="G805" s="18"/>
+      <c r="D805" s="19"/>
+      <c r="E805" s="16"/>
+      <c r="F805" s="16"/>
+      <c r="G805" s="16"/>
       <c r="H805" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I805" s="19"/>
-      <c r="J805" s="19"/>
+      <c r="I805" s="17"/>
+      <c r="J805" s="17"/>
       <c r="K805" s="10" t="s">
         <v>20</v>
       </c>
@@ -37397,17 +37364,17 @@
     </row>
     <row r="806" ht="18.0" customHeight="1">
       <c r="A806" s="6"/>
-      <c r="B806" s="16"/>
+      <c r="B806" s="15"/>
       <c r="C806" s="14"/>
-      <c r="D806" s="20"/>
-      <c r="E806" s="18"/>
-      <c r="F806" s="18"/>
-      <c r="G806" s="18"/>
+      <c r="D806" s="19"/>
+      <c r="E806" s="16"/>
+      <c r="F806" s="16"/>
+      <c r="G806" s="16"/>
       <c r="H806" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I806" s="19"/>
-      <c r="J806" s="19"/>
+      <c r="I806" s="17"/>
+      <c r="J806" s="17"/>
       <c r="K806" s="10" t="s">
         <v>20</v>
       </c>
@@ -37423,17 +37390,17 @@
     </row>
     <row r="807" ht="18.0" customHeight="1">
       <c r="A807" s="6"/>
-      <c r="B807" s="16"/>
+      <c r="B807" s="15"/>
       <c r="C807" s="14"/>
-      <c r="D807" s="20"/>
-      <c r="E807" s="18"/>
-      <c r="F807" s="18"/>
-      <c r="G807" s="18"/>
+      <c r="D807" s="19"/>
+      <c r="E807" s="16"/>
+      <c r="F807" s="16"/>
+      <c r="G807" s="16"/>
       <c r="H807" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I807" s="19"/>
-      <c r="J807" s="19"/>
+      <c r="I807" s="17"/>
+      <c r="J807" s="17"/>
       <c r="K807" s="10" t="s">
         <v>20</v>
       </c>
@@ -37449,17 +37416,17 @@
     </row>
     <row r="808" ht="18.0" customHeight="1">
       <c r="A808" s="6"/>
-      <c r="B808" s="16"/>
+      <c r="B808" s="15"/>
       <c r="C808" s="14"/>
-      <c r="D808" s="20"/>
-      <c r="E808" s="18"/>
-      <c r="F808" s="18"/>
-      <c r="G808" s="18"/>
+      <c r="D808" s="19"/>
+      <c r="E808" s="16"/>
+      <c r="F808" s="16"/>
+      <c r="G808" s="16"/>
       <c r="H808" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I808" s="19"/>
-      <c r="J808" s="19"/>
+      <c r="I808" s="17"/>
+      <c r="J808" s="17"/>
       <c r="K808" s="10" t="s">
         <v>20</v>
       </c>
@@ -37475,17 +37442,17 @@
     </row>
     <row r="809" ht="18.0" customHeight="1">
       <c r="A809" s="6"/>
-      <c r="B809" s="16"/>
+      <c r="B809" s="15"/>
       <c r="C809" s="14"/>
-      <c r="D809" s="20"/>
-      <c r="E809" s="18"/>
-      <c r="F809" s="18"/>
-      <c r="G809" s="18"/>
+      <c r="D809" s="19"/>
+      <c r="E809" s="16"/>
+      <c r="F809" s="16"/>
+      <c r="G809" s="16"/>
       <c r="H809" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I809" s="19"/>
-      <c r="J809" s="19"/>
+      <c r="I809" s="17"/>
+      <c r="J809" s="17"/>
       <c r="K809" s="10" t="s">
         <v>20</v>
       </c>
@@ -37501,17 +37468,17 @@
     </row>
     <row r="810" ht="18.0" customHeight="1">
       <c r="A810" s="6"/>
-      <c r="B810" s="16"/>
+      <c r="B810" s="15"/>
       <c r="C810" s="14"/>
-      <c r="D810" s="20"/>
-      <c r="E810" s="18"/>
-      <c r="F810" s="18"/>
-      <c r="G810" s="18"/>
+      <c r="D810" s="19"/>
+      <c r="E810" s="16"/>
+      <c r="F810" s="16"/>
+      <c r="G810" s="16"/>
       <c r="H810" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I810" s="19"/>
-      <c r="J810" s="19"/>
+      <c r="I810" s="17"/>
+      <c r="J810" s="17"/>
       <c r="K810" s="10" t="s">
         <v>20</v>
       </c>
@@ -37527,17 +37494,17 @@
     </row>
     <row r="811" ht="18.0" customHeight="1">
       <c r="A811" s="6"/>
-      <c r="B811" s="16"/>
+      <c r="B811" s="15"/>
       <c r="C811" s="14"/>
-      <c r="D811" s="20"/>
-      <c r="E811" s="18"/>
-      <c r="F811" s="18"/>
-      <c r="G811" s="18"/>
+      <c r="D811" s="19"/>
+      <c r="E811" s="16"/>
+      <c r="F811" s="16"/>
+      <c r="G811" s="16"/>
       <c r="H811" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I811" s="19"/>
-      <c r="J811" s="19"/>
+      <c r="I811" s="17"/>
+      <c r="J811" s="17"/>
       <c r="K811" s="10" t="s">
         <v>20</v>
       </c>
@@ -37553,17 +37520,17 @@
     </row>
     <row r="812" ht="18.0" customHeight="1">
       <c r="A812" s="6"/>
-      <c r="B812" s="16"/>
+      <c r="B812" s="15"/>
       <c r="C812" s="14"/>
-      <c r="D812" s="20"/>
-      <c r="E812" s="18"/>
-      <c r="F812" s="18"/>
-      <c r="G812" s="18"/>
+      <c r="D812" s="19"/>
+      <c r="E812" s="16"/>
+      <c r="F812" s="16"/>
+      <c r="G812" s="16"/>
       <c r="H812" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I812" s="19"/>
-      <c r="J812" s="19"/>
+      <c r="I812" s="17"/>
+      <c r="J812" s="17"/>
       <c r="K812" s="10" t="s">
         <v>20</v>
       </c>
@@ -37579,17 +37546,17 @@
     </row>
     <row r="813" ht="18.0" customHeight="1">
       <c r="A813" s="6"/>
-      <c r="B813" s="16"/>
+      <c r="B813" s="15"/>
       <c r="C813" s="14"/>
-      <c r="D813" s="20"/>
-      <c r="E813" s="18"/>
-      <c r="F813" s="18"/>
-      <c r="G813" s="18"/>
+      <c r="D813" s="19"/>
+      <c r="E813" s="16"/>
+      <c r="F813" s="16"/>
+      <c r="G813" s="16"/>
       <c r="H813" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I813" s="19"/>
-      <c r="J813" s="19"/>
+      <c r="I813" s="17"/>
+      <c r="J813" s="17"/>
       <c r="K813" s="10" t="s">
         <v>20</v>
       </c>
@@ -37605,17 +37572,17 @@
     </row>
     <row r="814" ht="18.0" customHeight="1">
       <c r="A814" s="6"/>
-      <c r="B814" s="16"/>
+      <c r="B814" s="15"/>
       <c r="C814" s="14"/>
-      <c r="D814" s="20"/>
-      <c r="E814" s="18"/>
-      <c r="F814" s="18"/>
-      <c r="G814" s="18"/>
+      <c r="D814" s="19"/>
+      <c r="E814" s="16"/>
+      <c r="F814" s="16"/>
+      <c r="G814" s="16"/>
       <c r="H814" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I814" s="19"/>
-      <c r="J814" s="19"/>
+      <c r="I814" s="17"/>
+      <c r="J814" s="17"/>
       <c r="K814" s="10" t="s">
         <v>20</v>
       </c>
@@ -37631,17 +37598,17 @@
     </row>
     <row r="815" ht="18.0" customHeight="1">
       <c r="A815" s="6"/>
-      <c r="B815" s="16"/>
+      <c r="B815" s="15"/>
       <c r="C815" s="14"/>
-      <c r="D815" s="20"/>
-      <c r="E815" s="18"/>
-      <c r="F815" s="18"/>
-      <c r="G815" s="18"/>
+      <c r="D815" s="19"/>
+      <c r="E815" s="16"/>
+      <c r="F815" s="16"/>
+      <c r="G815" s="16"/>
       <c r="H815" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I815" s="19"/>
-      <c r="J815" s="19"/>
+      <c r="I815" s="17"/>
+      <c r="J815" s="17"/>
       <c r="K815" s="10" t="s">
         <v>20</v>
       </c>
@@ -37657,17 +37624,17 @@
     </row>
     <row r="816" ht="18.0" customHeight="1">
       <c r="A816" s="6"/>
-      <c r="B816" s="16"/>
+      <c r="B816" s="15"/>
       <c r="C816" s="14"/>
-      <c r="D816" s="20"/>
-      <c r="E816" s="18"/>
-      <c r="F816" s="18"/>
-      <c r="G816" s="18"/>
+      <c r="D816" s="19"/>
+      <c r="E816" s="16"/>
+      <c r="F816" s="16"/>
+      <c r="G816" s="16"/>
       <c r="H816" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I816" s="19"/>
-      <c r="J816" s="19"/>
+      <c r="I816" s="17"/>
+      <c r="J816" s="17"/>
       <c r="K816" s="10" t="s">
         <v>20</v>
       </c>
@@ -37683,17 +37650,17 @@
     </row>
     <row r="817" ht="18.0" customHeight="1">
       <c r="A817" s="6"/>
-      <c r="B817" s="16"/>
+      <c r="B817" s="15"/>
       <c r="C817" s="14"/>
-      <c r="D817" s="20"/>
-      <c r="E817" s="18"/>
-      <c r="F817" s="18"/>
-      <c r="G817" s="18"/>
+      <c r="D817" s="19"/>
+      <c r="E817" s="16"/>
+      <c r="F817" s="16"/>
+      <c r="G817" s="16"/>
       <c r="H817" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I817" s="19"/>
-      <c r="J817" s="19"/>
+      <c r="I817" s="17"/>
+      <c r="J817" s="17"/>
       <c r="K817" s="10" t="s">
         <v>20</v>
       </c>
@@ -37709,17 +37676,17 @@
     </row>
     <row r="818" ht="18.0" customHeight="1">
       <c r="A818" s="6"/>
-      <c r="B818" s="16"/>
+      <c r="B818" s="15"/>
       <c r="C818" s="14"/>
-      <c r="D818" s="20"/>
-      <c r="E818" s="18"/>
-      <c r="F818" s="18"/>
-      <c r="G818" s="18"/>
+      <c r="D818" s="19"/>
+      <c r="E818" s="16"/>
+      <c r="F818" s="16"/>
+      <c r="G818" s="16"/>
       <c r="H818" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I818" s="19"/>
-      <c r="J818" s="19"/>
+      <c r="I818" s="17"/>
+      <c r="J818" s="17"/>
       <c r="K818" s="10" t="s">
         <v>20</v>
       </c>
@@ -37735,17 +37702,17 @@
     </row>
     <row r="819" ht="18.0" customHeight="1">
       <c r="A819" s="6"/>
-      <c r="B819" s="16"/>
+      <c r="B819" s="15"/>
       <c r="C819" s="14"/>
-      <c r="D819" s="20"/>
-      <c r="E819" s="18"/>
-      <c r="F819" s="18"/>
-      <c r="G819" s="18"/>
+      <c r="D819" s="19"/>
+      <c r="E819" s="16"/>
+      <c r="F819" s="16"/>
+      <c r="G819" s="16"/>
       <c r="H819" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I819" s="19"/>
-      <c r="J819" s="19"/>
+      <c r="I819" s="17"/>
+      <c r="J819" s="17"/>
       <c r="K819" s="10" t="s">
         <v>20</v>
       </c>
@@ -37761,17 +37728,17 @@
     </row>
     <row r="820" ht="18.0" customHeight="1">
       <c r="A820" s="6"/>
-      <c r="B820" s="16"/>
+      <c r="B820" s="15"/>
       <c r="C820" s="14"/>
-      <c r="D820" s="20"/>
-      <c r="E820" s="18"/>
-      <c r="F820" s="18"/>
-      <c r="G820" s="18"/>
+      <c r="D820" s="19"/>
+      <c r="E820" s="16"/>
+      <c r="F820" s="16"/>
+      <c r="G820" s="16"/>
       <c r="H820" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I820" s="19"/>
-      <c r="J820" s="19"/>
+      <c r="I820" s="17"/>
+      <c r="J820" s="17"/>
       <c r="K820" s="10" t="s">
         <v>20</v>
       </c>
@@ -37787,17 +37754,17 @@
     </row>
     <row r="821" ht="18.0" customHeight="1">
       <c r="A821" s="6"/>
-      <c r="B821" s="16"/>
+      <c r="B821" s="15"/>
       <c r="C821" s="14"/>
-      <c r="D821" s="20"/>
-      <c r="E821" s="18"/>
-      <c r="F821" s="18"/>
-      <c r="G821" s="18"/>
+      <c r="D821" s="19"/>
+      <c r="E821" s="16"/>
+      <c r="F821" s="16"/>
+      <c r="G821" s="16"/>
       <c r="H821" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I821" s="19"/>
-      <c r="J821" s="19"/>
+      <c r="I821" s="17"/>
+      <c r="J821" s="17"/>
       <c r="K821" s="10" t="s">
         <v>20</v>
       </c>
@@ -37813,17 +37780,17 @@
     </row>
     <row r="822" ht="18.0" customHeight="1">
       <c r="A822" s="6"/>
-      <c r="B822" s="16"/>
+      <c r="B822" s="15"/>
       <c r="C822" s="14"/>
-      <c r="D822" s="20"/>
-      <c r="E822" s="18"/>
-      <c r="F822" s="18"/>
-      <c r="G822" s="18"/>
+      <c r="D822" s="19"/>
+      <c r="E822" s="16"/>
+      <c r="F822" s="16"/>
+      <c r="G822" s="16"/>
       <c r="H822" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I822" s="19"/>
-      <c r="J822" s="19"/>
+      <c r="I822" s="17"/>
+      <c r="J822" s="17"/>
       <c r="K822" s="10" t="s">
         <v>20</v>
       </c>
@@ -37839,17 +37806,17 @@
     </row>
     <row r="823" ht="18.0" customHeight="1">
       <c r="A823" s="6"/>
-      <c r="B823" s="16"/>
+      <c r="B823" s="15"/>
       <c r="C823" s="14"/>
-      <c r="D823" s="20"/>
-      <c r="E823" s="18"/>
-      <c r="F823" s="18"/>
-      <c r="G823" s="18"/>
+      <c r="D823" s="19"/>
+      <c r="E823" s="16"/>
+      <c r="F823" s="16"/>
+      <c r="G823" s="16"/>
       <c r="H823" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I823" s="19"/>
-      <c r="J823" s="19"/>
+      <c r="I823" s="17"/>
+      <c r="J823" s="17"/>
       <c r="K823" s="10" t="s">
         <v>20</v>
       </c>
@@ -37865,17 +37832,17 @@
     </row>
     <row r="824" ht="18.0" customHeight="1">
       <c r="A824" s="6"/>
-      <c r="B824" s="16"/>
+      <c r="B824" s="15"/>
       <c r="C824" s="14"/>
-      <c r="D824" s="20"/>
-      <c r="E824" s="18"/>
-      <c r="F824" s="18"/>
-      <c r="G824" s="18"/>
+      <c r="D824" s="19"/>
+      <c r="E824" s="16"/>
+      <c r="F824" s="16"/>
+      <c r="G824" s="16"/>
       <c r="H824" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I824" s="19"/>
-      <c r="J824" s="19"/>
+      <c r="I824" s="17"/>
+      <c r="J824" s="17"/>
       <c r="K824" s="10" t="s">
         <v>20</v>
       </c>
@@ -37891,17 +37858,17 @@
     </row>
     <row r="825" ht="18.0" customHeight="1">
       <c r="A825" s="6"/>
-      <c r="B825" s="16"/>
+      <c r="B825" s="15"/>
       <c r="C825" s="14"/>
-      <c r="D825" s="20"/>
-      <c r="E825" s="18"/>
-      <c r="F825" s="18"/>
-      <c r="G825" s="18"/>
+      <c r="D825" s="19"/>
+      <c r="E825" s="16"/>
+      <c r="F825" s="16"/>
+      <c r="G825" s="16"/>
       <c r="H825" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I825" s="19"/>
-      <c r="J825" s="19"/>
+      <c r="I825" s="17"/>
+      <c r="J825" s="17"/>
       <c r="K825" s="10" t="s">
         <v>20</v>
       </c>
@@ -37917,17 +37884,17 @@
     </row>
     <row r="826" ht="18.0" customHeight="1">
       <c r="A826" s="6"/>
-      <c r="B826" s="16"/>
+      <c r="B826" s="15"/>
       <c r="C826" s="14"/>
-      <c r="D826" s="20"/>
-      <c r="E826" s="18"/>
-      <c r="F826" s="18"/>
-      <c r="G826" s="18"/>
+      <c r="D826" s="19"/>
+      <c r="E826" s="16"/>
+      <c r="F826" s="16"/>
+      <c r="G826" s="16"/>
       <c r="H826" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I826" s="19"/>
-      <c r="J826" s="19"/>
+      <c r="I826" s="17"/>
+      <c r="J826" s="17"/>
       <c r="K826" s="10" t="s">
         <v>20</v>
       </c>
@@ -37943,17 +37910,17 @@
     </row>
     <row r="827" ht="18.0" customHeight="1">
       <c r="A827" s="6"/>
-      <c r="B827" s="16"/>
+      <c r="B827" s="15"/>
       <c r="C827" s="14"/>
-      <c r="D827" s="20"/>
-      <c r="E827" s="18"/>
-      <c r="F827" s="18"/>
-      <c r="G827" s="18"/>
+      <c r="D827" s="19"/>
+      <c r="E827" s="16"/>
+      <c r="F827" s="16"/>
+      <c r="G827" s="16"/>
       <c r="H827" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I827" s="19"/>
-      <c r="J827" s="19"/>
+      <c r="I827" s="17"/>
+      <c r="J827" s="17"/>
       <c r="K827" s="10" t="s">
         <v>20</v>
       </c>
@@ -37969,17 +37936,17 @@
     </row>
     <row r="828" ht="18.0" customHeight="1">
       <c r="A828" s="6"/>
-      <c r="B828" s="16"/>
+      <c r="B828" s="15"/>
       <c r="C828" s="14"/>
-      <c r="D828" s="20"/>
-      <c r="E828" s="18"/>
-      <c r="F828" s="18"/>
-      <c r="G828" s="18"/>
+      <c r="D828" s="19"/>
+      <c r="E828" s="16"/>
+      <c r="F828" s="16"/>
+      <c r="G828" s="16"/>
       <c r="H828" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I828" s="19"/>
-      <c r="J828" s="19"/>
+      <c r="I828" s="17"/>
+      <c r="J828" s="17"/>
       <c r="K828" s="10" t="s">
         <v>20</v>
       </c>
@@ -37995,17 +37962,17 @@
     </row>
     <row r="829" ht="18.0" customHeight="1">
       <c r="A829" s="6"/>
-      <c r="B829" s="16"/>
+      <c r="B829" s="15"/>
       <c r="C829" s="14"/>
-      <c r="D829" s="20"/>
-      <c r="E829" s="18"/>
-      <c r="F829" s="18"/>
-      <c r="G829" s="18"/>
+      <c r="D829" s="19"/>
+      <c r="E829" s="16"/>
+      <c r="F829" s="16"/>
+      <c r="G829" s="16"/>
       <c r="H829" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I829" s="19"/>
-      <c r="J829" s="19"/>
+      <c r="I829" s="17"/>
+      <c r="J829" s="17"/>
       <c r="K829" s="10" t="s">
         <v>20</v>
       </c>
@@ -38021,17 +37988,17 @@
     </row>
     <row r="830" ht="18.0" customHeight="1">
       <c r="A830" s="6"/>
-      <c r="B830" s="16"/>
+      <c r="B830" s="15"/>
       <c r="C830" s="14"/>
-      <c r="D830" s="20"/>
-      <c r="E830" s="18"/>
-      <c r="F830" s="18"/>
-      <c r="G830" s="18"/>
+      <c r="D830" s="19"/>
+      <c r="E830" s="16"/>
+      <c r="F830" s="16"/>
+      <c r="G830" s="16"/>
       <c r="H830" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I830" s="19"/>
-      <c r="J830" s="19"/>
+      <c r="I830" s="17"/>
+      <c r="J830" s="17"/>
       <c r="K830" s="10" t="s">
         <v>20</v>
       </c>
@@ -38047,17 +38014,17 @@
     </row>
     <row r="831" ht="18.0" customHeight="1">
       <c r="A831" s="6"/>
-      <c r="B831" s="16"/>
+      <c r="B831" s="15"/>
       <c r="C831" s="14"/>
-      <c r="D831" s="20"/>
-      <c r="E831" s="18"/>
-      <c r="F831" s="18"/>
-      <c r="G831" s="18"/>
+      <c r="D831" s="19"/>
+      <c r="E831" s="16"/>
+      <c r="F831" s="16"/>
+      <c r="G831" s="16"/>
       <c r="H831" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I831" s="19"/>
-      <c r="J831" s="19"/>
+      <c r="I831" s="17"/>
+      <c r="J831" s="17"/>
       <c r="K831" s="10" t="s">
         <v>20</v>
       </c>
@@ -38073,17 +38040,17 @@
     </row>
     <row r="832" ht="18.0" customHeight="1">
       <c r="A832" s="6"/>
-      <c r="B832" s="16"/>
+      <c r="B832" s="15"/>
       <c r="C832" s="14"/>
-      <c r="D832" s="20"/>
-      <c r="E832" s="18"/>
-      <c r="F832" s="18"/>
-      <c r="G832" s="18"/>
+      <c r="D832" s="19"/>
+      <c r="E832" s="16"/>
+      <c r="F832" s="16"/>
+      <c r="G832" s="16"/>
       <c r="H832" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I832" s="19"/>
-      <c r="J832" s="19"/>
+      <c r="I832" s="17"/>
+      <c r="J832" s="17"/>
       <c r="K832" s="10" t="s">
         <v>20</v>
       </c>
@@ -38099,17 +38066,17 @@
     </row>
     <row r="833" ht="18.0" customHeight="1">
       <c r="A833" s="6"/>
-      <c r="B833" s="16"/>
+      <c r="B833" s="15"/>
       <c r="C833" s="14"/>
-      <c r="D833" s="20"/>
-      <c r="E833" s="18"/>
-      <c r="F833" s="18"/>
-      <c r="G833" s="18"/>
+      <c r="D833" s="19"/>
+      <c r="E833" s="16"/>
+      <c r="F833" s="16"/>
+      <c r="G833" s="16"/>
       <c r="H833" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I833" s="19"/>
-      <c r="J833" s="19"/>
+      <c r="I833" s="17"/>
+      <c r="J833" s="17"/>
       <c r="K833" s="10" t="s">
         <v>20</v>
       </c>
@@ -38125,17 +38092,17 @@
     </row>
     <row r="834" ht="18.0" customHeight="1">
       <c r="A834" s="6"/>
-      <c r="B834" s="16"/>
+      <c r="B834" s="15"/>
       <c r="C834" s="14"/>
-      <c r="D834" s="20"/>
-      <c r="E834" s="18"/>
-      <c r="F834" s="18"/>
-      <c r="G834" s="18"/>
+      <c r="D834" s="19"/>
+      <c r="E834" s="16"/>
+      <c r="F834" s="16"/>
+      <c r="G834" s="16"/>
       <c r="H834" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I834" s="19"/>
-      <c r="J834" s="19"/>
+      <c r="I834" s="17"/>
+      <c r="J834" s="17"/>
       <c r="K834" s="10" t="s">
         <v>20</v>
       </c>
@@ -38151,17 +38118,17 @@
     </row>
     <row r="835" ht="18.0" customHeight="1">
       <c r="A835" s="6"/>
-      <c r="B835" s="16"/>
+      <c r="B835" s="15"/>
       <c r="C835" s="14"/>
-      <c r="D835" s="20"/>
-      <c r="E835" s="18"/>
-      <c r="F835" s="18"/>
-      <c r="G835" s="18"/>
+      <c r="D835" s="19"/>
+      <c r="E835" s="16"/>
+      <c r="F835" s="16"/>
+      <c r="G835" s="16"/>
       <c r="H835" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I835" s="19"/>
-      <c r="J835" s="19"/>
+      <c r="I835" s="17"/>
+      <c r="J835" s="17"/>
       <c r="K835" s="10" t="s">
         <v>20</v>
       </c>
@@ -38177,17 +38144,17 @@
     </row>
     <row r="836" ht="18.0" customHeight="1">
       <c r="A836" s="6"/>
-      <c r="B836" s="16"/>
+      <c r="B836" s="15"/>
       <c r="C836" s="14"/>
-      <c r="D836" s="20"/>
-      <c r="E836" s="18"/>
-      <c r="F836" s="18"/>
-      <c r="G836" s="18"/>
+      <c r="D836" s="19"/>
+      <c r="E836" s="16"/>
+      <c r="F836" s="16"/>
+      <c r="G836" s="16"/>
       <c r="H836" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I836" s="19"/>
-      <c r="J836" s="19"/>
+      <c r="I836" s="17"/>
+      <c r="J836" s="17"/>
       <c r="K836" s="10" t="s">
         <v>20</v>
       </c>
@@ -38203,17 +38170,17 @@
     </row>
     <row r="837" ht="18.0" customHeight="1">
       <c r="A837" s="6"/>
-      <c r="B837" s="16"/>
+      <c r="B837" s="15"/>
       <c r="C837" s="14"/>
-      <c r="D837" s="20"/>
-      <c r="E837" s="18"/>
-      <c r="F837" s="18"/>
-      <c r="G837" s="18"/>
+      <c r="D837" s="19"/>
+      <c r="E837" s="16"/>
+      <c r="F837" s="16"/>
+      <c r="G837" s="16"/>
       <c r="H837" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I837" s="19"/>
-      <c r="J837" s="19"/>
+      <c r="I837" s="17"/>
+      <c r="J837" s="17"/>
       <c r="K837" s="10" t="s">
         <v>20</v>
       </c>
@@ -38229,17 +38196,17 @@
     </row>
     <row r="838" ht="18.0" customHeight="1">
       <c r="A838" s="6"/>
-      <c r="B838" s="16"/>
+      <c r="B838" s="15"/>
       <c r="C838" s="14"/>
-      <c r="D838" s="20"/>
-      <c r="E838" s="18"/>
-      <c r="F838" s="18"/>
-      <c r="G838" s="18"/>
+      <c r="D838" s="19"/>
+      <c r="E838" s="16"/>
+      <c r="F838" s="16"/>
+      <c r="G838" s="16"/>
       <c r="H838" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I838" s="19"/>
-      <c r="J838" s="19"/>
+      <c r="I838" s="17"/>
+      <c r="J838" s="17"/>
       <c r="K838" s="10" t="s">
         <v>20</v>
       </c>
@@ -38255,17 +38222,17 @@
     </row>
     <row r="839" ht="18.0" customHeight="1">
       <c r="A839" s="6"/>
-      <c r="B839" s="16"/>
+      <c r="B839" s="15"/>
       <c r="C839" s="14"/>
-      <c r="D839" s="20"/>
-      <c r="E839" s="18"/>
-      <c r="F839" s="18"/>
-      <c r="G839" s="18"/>
+      <c r="D839" s="19"/>
+      <c r="E839" s="16"/>
+      <c r="F839" s="16"/>
+      <c r="G839" s="16"/>
       <c r="H839" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I839" s="19"/>
-      <c r="J839" s="19"/>
+      <c r="I839" s="17"/>
+      <c r="J839" s="17"/>
       <c r="K839" s="10" t="s">
         <v>20</v>
       </c>
@@ -38281,17 +38248,17 @@
     </row>
     <row r="840" ht="18.0" customHeight="1">
       <c r="A840" s="6"/>
-      <c r="B840" s="16"/>
+      <c r="B840" s="15"/>
       <c r="C840" s="14"/>
-      <c r="D840" s="20"/>
-      <c r="E840" s="18"/>
-      <c r="F840" s="18"/>
-      <c r="G840" s="18"/>
+      <c r="D840" s="19"/>
+      <c r="E840" s="16"/>
+      <c r="F840" s="16"/>
+      <c r="G840" s="16"/>
       <c r="H840" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I840" s="19"/>
-      <c r="J840" s="19"/>
+      <c r="I840" s="17"/>
+      <c r="J840" s="17"/>
       <c r="K840" s="10" t="s">
         <v>20</v>
       </c>
@@ -38307,17 +38274,17 @@
     </row>
     <row r="841" ht="18.0" customHeight="1">
       <c r="A841" s="6"/>
-      <c r="B841" s="16"/>
+      <c r="B841" s="15"/>
       <c r="C841" s="14"/>
-      <c r="D841" s="20"/>
-      <c r="E841" s="18"/>
-      <c r="F841" s="18"/>
-      <c r="G841" s="18"/>
+      <c r="D841" s="19"/>
+      <c r="E841" s="16"/>
+      <c r="F841" s="16"/>
+      <c r="G841" s="16"/>
       <c r="H841" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I841" s="19"/>
-      <c r="J841" s="19"/>
+      <c r="I841" s="17"/>
+      <c r="J841" s="17"/>
       <c r="K841" s="10" t="s">
         <v>20</v>
       </c>
@@ -38333,17 +38300,17 @@
     </row>
     <row r="842" ht="18.0" customHeight="1">
       <c r="A842" s="6"/>
-      <c r="B842" s="16"/>
+      <c r="B842" s="15"/>
       <c r="C842" s="14"/>
-      <c r="D842" s="20"/>
-      <c r="E842" s="18"/>
-      <c r="F842" s="18"/>
-      <c r="G842" s="18"/>
+      <c r="D842" s="19"/>
+      <c r="E842" s="16"/>
+      <c r="F842" s="16"/>
+      <c r="G842" s="16"/>
       <c r="H842" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I842" s="19"/>
-      <c r="J842" s="19"/>
+      <c r="I842" s="17"/>
+      <c r="J842" s="17"/>
       <c r="K842" s="10" t="s">
         <v>20</v>
       </c>
@@ -38359,17 +38326,17 @@
     </row>
     <row r="843" ht="18.0" customHeight="1">
       <c r="A843" s="6"/>
-      <c r="B843" s="16"/>
+      <c r="B843" s="15"/>
       <c r="C843" s="14"/>
-      <c r="D843" s="20"/>
-      <c r="E843" s="18"/>
-      <c r="F843" s="18"/>
-      <c r="G843" s="18"/>
+      <c r="D843" s="19"/>
+      <c r="E843" s="16"/>
+      <c r="F843" s="16"/>
+      <c r="G843" s="16"/>
       <c r="H843" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I843" s="19"/>
-      <c r="J843" s="19"/>
+      <c r="I843" s="17"/>
+      <c r="J843" s="17"/>
       <c r="K843" s="10" t="s">
         <v>20</v>
       </c>
@@ -38385,17 +38352,17 @@
     </row>
     <row r="844" ht="18.0" customHeight="1">
       <c r="A844" s="6"/>
-      <c r="B844" s="16"/>
+      <c r="B844" s="15"/>
       <c r="C844" s="14"/>
-      <c r="D844" s="20"/>
-      <c r="E844" s="18"/>
-      <c r="F844" s="18"/>
-      <c r="G844" s="18"/>
+      <c r="D844" s="19"/>
+      <c r="E844" s="16"/>
+      <c r="F844" s="16"/>
+      <c r="G844" s="16"/>
       <c r="H844" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I844" s="19"/>
-      <c r="J844" s="19"/>
+      <c r="I844" s="17"/>
+      <c r="J844" s="17"/>
       <c r="K844" s="10" t="s">
         <v>20</v>
       </c>
@@ -38411,17 +38378,17 @@
     </row>
     <row r="845" ht="18.0" customHeight="1">
       <c r="A845" s="6"/>
-      <c r="B845" s="16"/>
+      <c r="B845" s="15"/>
       <c r="C845" s="14"/>
-      <c r="D845" s="20"/>
-      <c r="E845" s="18"/>
-      <c r="F845" s="18"/>
-      <c r="G845" s="18"/>
+      <c r="D845" s="19"/>
+      <c r="E845" s="16"/>
+      <c r="F845" s="16"/>
+      <c r="G845" s="16"/>
       <c r="H845" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I845" s="19"/>
-      <c r="J845" s="19"/>
+      <c r="I845" s="17"/>
+      <c r="J845" s="17"/>
       <c r="K845" s="10" t="s">
         <v>20</v>
       </c>
@@ -38437,17 +38404,17 @@
     </row>
     <row r="846" ht="18.0" customHeight="1">
       <c r="A846" s="6"/>
-      <c r="B846" s="16"/>
+      <c r="B846" s="15"/>
       <c r="C846" s="14"/>
-      <c r="D846" s="20"/>
-      <c r="E846" s="18"/>
-      <c r="F846" s="18"/>
-      <c r="G846" s="18"/>
+      <c r="D846" s="19"/>
+      <c r="E846" s="16"/>
+      <c r="F846" s="16"/>
+      <c r="G846" s="16"/>
       <c r="H846" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I846" s="19"/>
-      <c r="J846" s="19"/>
+      <c r="I846" s="17"/>
+      <c r="J846" s="17"/>
       <c r="K846" s="10" t="s">
         <v>20</v>
       </c>
@@ -38463,17 +38430,17 @@
     </row>
     <row r="847" ht="18.0" customHeight="1">
       <c r="A847" s="6"/>
-      <c r="B847" s="16"/>
+      <c r="B847" s="15"/>
       <c r="C847" s="14"/>
-      <c r="D847" s="20"/>
-      <c r="E847" s="18"/>
-      <c r="F847" s="18"/>
-      <c r="G847" s="18"/>
+      <c r="D847" s="19"/>
+      <c r="E847" s="16"/>
+      <c r="F847" s="16"/>
+      <c r="G847" s="16"/>
       <c r="H847" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I847" s="19"/>
-      <c r="J847" s="19"/>
+      <c r="I847" s="17"/>
+      <c r="J847" s="17"/>
       <c r="K847" s="10" t="s">
         <v>20</v>
       </c>
@@ -38489,17 +38456,17 @@
     </row>
     <row r="848" ht="18.0" customHeight="1">
       <c r="A848" s="6"/>
-      <c r="B848" s="16"/>
+      <c r="B848" s="15"/>
       <c r="C848" s="14"/>
-      <c r="D848" s="20"/>
-      <c r="E848" s="18"/>
-      <c r="F848" s="18"/>
-      <c r="G848" s="18"/>
+      <c r="D848" s="19"/>
+      <c r="E848" s="16"/>
+      <c r="F848" s="16"/>
+      <c r="G848" s="16"/>
       <c r="H848" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I848" s="19"/>
-      <c r="J848" s="19"/>
+      <c r="I848" s="17"/>
+      <c r="J848" s="17"/>
       <c r="K848" s="10" t="s">
         <v>20</v>
       </c>
@@ -38515,17 +38482,17 @@
     </row>
     <row r="849" ht="18.0" customHeight="1">
       <c r="A849" s="6"/>
-      <c r="B849" s="16"/>
+      <c r="B849" s="15"/>
       <c r="C849" s="14"/>
-      <c r="D849" s="20"/>
-      <c r="E849" s="18"/>
-      <c r="F849" s="18"/>
-      <c r="G849" s="18"/>
+      <c r="D849" s="19"/>
+      <c r="E849" s="16"/>
+      <c r="F849" s="16"/>
+      <c r="G849" s="16"/>
       <c r="H849" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I849" s="19"/>
-      <c r="J849" s="19"/>
+      <c r="I849" s="17"/>
+      <c r="J849" s="17"/>
       <c r="K849" s="10" t="s">
         <v>20</v>
       </c>
@@ -38541,17 +38508,17 @@
     </row>
     <row r="850" ht="18.0" customHeight="1">
       <c r="A850" s="6"/>
-      <c r="B850" s="16"/>
+      <c r="B850" s="15"/>
       <c r="C850" s="14"/>
-      <c r="D850" s="20"/>
-      <c r="E850" s="18"/>
-      <c r="F850" s="18"/>
-      <c r="G850" s="18"/>
+      <c r="D850" s="19"/>
+      <c r="E850" s="16"/>
+      <c r="F850" s="16"/>
+      <c r="G850" s="16"/>
       <c r="H850" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I850" s="19"/>
-      <c r="J850" s="19"/>
+      <c r="I850" s="17"/>
+      <c r="J850" s="17"/>
       <c r="K850" s="10" t="s">
         <v>20</v>
       </c>
@@ -38567,17 +38534,17 @@
     </row>
     <row r="851" ht="18.0" customHeight="1">
       <c r="A851" s="6"/>
-      <c r="B851" s="16"/>
+      <c r="B851" s="15"/>
       <c r="C851" s="14"/>
-      <c r="D851" s="20"/>
-      <c r="E851" s="18"/>
-      <c r="F851" s="18"/>
-      <c r="G851" s="18"/>
+      <c r="D851" s="19"/>
+      <c r="E851" s="16"/>
+      <c r="F851" s="16"/>
+      <c r="G851" s="16"/>
       <c r="H851" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I851" s="19"/>
-      <c r="J851" s="19"/>
+      <c r="I851" s="17"/>
+      <c r="J851" s="17"/>
       <c r="K851" s="10" t="s">
         <v>20</v>
       </c>
@@ -38593,17 +38560,17 @@
     </row>
     <row r="852" ht="18.0" customHeight="1">
       <c r="A852" s="6"/>
-      <c r="B852" s="16"/>
+      <c r="B852" s="15"/>
       <c r="C852" s="14"/>
-      <c r="D852" s="20"/>
-      <c r="E852" s="18"/>
-      <c r="F852" s="18"/>
-      <c r="G852" s="18"/>
+      <c r="D852" s="19"/>
+      <c r="E852" s="16"/>
+      <c r="F852" s="16"/>
+      <c r="G852" s="16"/>
       <c r="H852" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I852" s="19"/>
-      <c r="J852" s="19"/>
+      <c r="I852" s="17"/>
+      <c r="J852" s="17"/>
       <c r="K852" s="10" t="s">
         <v>20</v>
       </c>
@@ -38619,17 +38586,17 @@
     </row>
     <row r="853" ht="18.0" customHeight="1">
       <c r="A853" s="6"/>
-      <c r="B853" s="16"/>
+      <c r="B853" s="15"/>
       <c r="C853" s="14"/>
-      <c r="D853" s="20"/>
-      <c r="E853" s="18"/>
-      <c r="F853" s="18"/>
-      <c r="G853" s="18"/>
+      <c r="D853" s="19"/>
+      <c r="E853" s="16"/>
+      <c r="F853" s="16"/>
+      <c r="G853" s="16"/>
       <c r="H853" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I853" s="19"/>
-      <c r="J853" s="19"/>
+      <c r="I853" s="17"/>
+      <c r="J853" s="17"/>
       <c r="K853" s="10" t="s">
         <v>20</v>
       </c>
@@ -38645,17 +38612,17 @@
     </row>
     <row r="854" ht="18.0" customHeight="1">
       <c r="A854" s="6"/>
-      <c r="B854" s="16"/>
+      <c r="B854" s="15"/>
       <c r="C854" s="14"/>
-      <c r="D854" s="20"/>
-      <c r="E854" s="18"/>
-      <c r="F854" s="18"/>
-      <c r="G854" s="18"/>
+      <c r="D854" s="19"/>
+      <c r="E854" s="16"/>
+      <c r="F854" s="16"/>
+      <c r="G854" s="16"/>
       <c r="H854" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I854" s="19"/>
-      <c r="J854" s="19"/>
+      <c r="I854" s="17"/>
+      <c r="J854" s="17"/>
       <c r="K854" s="10" t="s">
         <v>20</v>
       </c>
@@ -38671,17 +38638,17 @@
     </row>
     <row r="855" ht="18.0" customHeight="1">
       <c r="A855" s="6"/>
-      <c r="B855" s="16"/>
+      <c r="B855" s="15"/>
       <c r="C855" s="14"/>
-      <c r="D855" s="20"/>
-      <c r="E855" s="18"/>
-      <c r="F855" s="18"/>
-      <c r="G855" s="18"/>
+      <c r="D855" s="19"/>
+      <c r="E855" s="16"/>
+      <c r="F855" s="16"/>
+      <c r="G855" s="16"/>
       <c r="H855" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I855" s="19"/>
-      <c r="J855" s="19"/>
+      <c r="I855" s="17"/>
+      <c r="J855" s="17"/>
       <c r="K855" s="10" t="s">
         <v>20</v>
       </c>
@@ -38697,17 +38664,17 @@
     </row>
     <row r="856" ht="18.0" customHeight="1">
       <c r="A856" s="6"/>
-      <c r="B856" s="16"/>
+      <c r="B856" s="15"/>
       <c r="C856" s="14"/>
-      <c r="D856" s="20"/>
-      <c r="E856" s="18"/>
-      <c r="F856" s="18"/>
-      <c r="G856" s="18"/>
+      <c r="D856" s="19"/>
+      <c r="E856" s="16"/>
+      <c r="F856" s="16"/>
+      <c r="G856" s="16"/>
       <c r="H856" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I856" s="19"/>
-      <c r="J856" s="19"/>
+      <c r="I856" s="17"/>
+      <c r="J856" s="17"/>
       <c r="K856" s="10" t="s">
         <v>20</v>
       </c>
@@ -38723,17 +38690,17 @@
     </row>
     <row r="857" ht="18.0" customHeight="1">
       <c r="A857" s="6"/>
-      <c r="B857" s="16"/>
+      <c r="B857" s="15"/>
       <c r="C857" s="14"/>
-      <c r="D857" s="20"/>
-      <c r="E857" s="18"/>
-      <c r="F857" s="18"/>
-      <c r="G857" s="18"/>
+      <c r="D857" s="19"/>
+      <c r="E857" s="16"/>
+      <c r="F857" s="16"/>
+      <c r="G857" s="16"/>
       <c r="H857" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I857" s="19"/>
-      <c r="J857" s="19"/>
+      <c r="I857" s="17"/>
+      <c r="J857" s="17"/>
       <c r="K857" s="10" t="s">
         <v>20</v>
       </c>
@@ -38749,17 +38716,17 @@
     </row>
     <row r="858" ht="18.0" customHeight="1">
       <c r="A858" s="6"/>
-      <c r="B858" s="16"/>
+      <c r="B858" s="15"/>
       <c r="C858" s="14"/>
-      <c r="D858" s="20"/>
-      <c r="E858" s="18"/>
-      <c r="F858" s="18"/>
-      <c r="G858" s="18"/>
+      <c r="D858" s="19"/>
+      <c r="E858" s="16"/>
+      <c r="F858" s="16"/>
+      <c r="G858" s="16"/>
       <c r="H858" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I858" s="19"/>
-      <c r="J858" s="19"/>
+      <c r="I858" s="17"/>
+      <c r="J858" s="17"/>
       <c r="K858" s="10" t="s">
         <v>20</v>
       </c>
@@ -38775,17 +38742,17 @@
     </row>
     <row r="859" ht="18.0" customHeight="1">
       <c r="A859" s="6"/>
-      <c r="B859" s="16"/>
+      <c r="B859" s="15"/>
       <c r="C859" s="14"/>
-      <c r="D859" s="20"/>
-      <c r="E859" s="18"/>
-      <c r="F859" s="18"/>
-      <c r="G859" s="18"/>
+      <c r="D859" s="19"/>
+      <c r="E859" s="16"/>
+      <c r="F859" s="16"/>
+      <c r="G859" s="16"/>
       <c r="H859" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I859" s="19"/>
-      <c r="J859" s="19"/>
+      <c r="I859" s="17"/>
+      <c r="J859" s="17"/>
       <c r="K859" s="10" t="s">
         <v>20</v>
       </c>
@@ -38801,17 +38768,17 @@
     </row>
     <row r="860" ht="18.0" customHeight="1">
       <c r="A860" s="6"/>
-      <c r="B860" s="16"/>
+      <c r="B860" s="15"/>
       <c r="C860" s="14"/>
-      <c r="D860" s="20"/>
-      <c r="E860" s="18"/>
-      <c r="F860" s="18"/>
-      <c r="G860" s="18"/>
+      <c r="D860" s="19"/>
+      <c r="E860" s="16"/>
+      <c r="F860" s="16"/>
+      <c r="G860" s="16"/>
       <c r="H860" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I860" s="19"/>
-      <c r="J860" s="19"/>
+      <c r="I860" s="17"/>
+      <c r="J860" s="17"/>
       <c r="K860" s="10" t="s">
         <v>20</v>
       </c>
@@ -38827,17 +38794,17 @@
     </row>
     <row r="861" ht="18.0" customHeight="1">
       <c r="A861" s="6"/>
-      <c r="B861" s="16"/>
+      <c r="B861" s="15"/>
       <c r="C861" s="14"/>
-      <c r="D861" s="20"/>
-      <c r="E861" s="18"/>
-      <c r="F861" s="18"/>
-      <c r="G861" s="18"/>
+      <c r="D861" s="19"/>
+      <c r="E861" s="16"/>
+      <c r="F861" s="16"/>
+      <c r="G861" s="16"/>
       <c r="H861" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I861" s="19"/>
-      <c r="J861" s="19"/>
+      <c r="I861" s="17"/>
+      <c r="J861" s="17"/>
       <c r="K861" s="10" t="s">
         <v>20</v>
       </c>
@@ -38853,17 +38820,17 @@
     </row>
     <row r="862" ht="18.0" customHeight="1">
       <c r="A862" s="6"/>
-      <c r="B862" s="16"/>
+      <c r="B862" s="15"/>
       <c r="C862" s="14"/>
-      <c r="D862" s="20"/>
-      <c r="E862" s="18"/>
-      <c r="F862" s="18"/>
-      <c r="G862" s="18"/>
+      <c r="D862" s="19"/>
+      <c r="E862" s="16"/>
+      <c r="F862" s="16"/>
+      <c r="G862" s="16"/>
       <c r="H862" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I862" s="19"/>
-      <c r="J862" s="19"/>
+      <c r="I862" s="17"/>
+      <c r="J862" s="17"/>
       <c r="K862" s="10" t="s">
         <v>20</v>
       </c>
@@ -38879,17 +38846,17 @@
     </row>
     <row r="863" ht="18.0" customHeight="1">
       <c r="A863" s="6"/>
-      <c r="B863" s="16"/>
+      <c r="B863" s="15"/>
       <c r="C863" s="14"/>
-      <c r="D863" s="20"/>
-      <c r="E863" s="18"/>
-      <c r="F863" s="18"/>
-      <c r="G863" s="18"/>
+      <c r="D863" s="19"/>
+      <c r="E863" s="16"/>
+      <c r="F863" s="16"/>
+      <c r="G863" s="16"/>
       <c r="H863" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I863" s="19"/>
-      <c r="J863" s="19"/>
+      <c r="I863" s="17"/>
+      <c r="J863" s="17"/>
       <c r="K863" s="10" t="s">
         <v>20</v>
       </c>
@@ -38905,17 +38872,17 @@
     </row>
     <row r="864" ht="18.0" customHeight="1">
       <c r="A864" s="6"/>
-      <c r="B864" s="16"/>
+      <c r="B864" s="15"/>
       <c r="C864" s="14"/>
-      <c r="D864" s="20"/>
-      <c r="E864" s="18"/>
-      <c r="F864" s="18"/>
-      <c r="G864" s="18"/>
+      <c r="D864" s="19"/>
+      <c r="E864" s="16"/>
+      <c r="F864" s="16"/>
+      <c r="G864" s="16"/>
       <c r="H864" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I864" s="19"/>
-      <c r="J864" s="19"/>
+      <c r="I864" s="17"/>
+      <c r="J864" s="17"/>
       <c r="K864" s="10" t="s">
         <v>20</v>
       </c>
@@ -38931,17 +38898,17 @@
     </row>
     <row r="865" ht="18.0" customHeight="1">
       <c r="A865" s="6"/>
-      <c r="B865" s="16"/>
+      <c r="B865" s="15"/>
       <c r="C865" s="14"/>
-      <c r="D865" s="20"/>
-      <c r="E865" s="18"/>
-      <c r="F865" s="18"/>
-      <c r="G865" s="18"/>
+      <c r="D865" s="19"/>
+      <c r="E865" s="16"/>
+      <c r="F865" s="16"/>
+      <c r="G865" s="16"/>
       <c r="H865" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I865" s="19"/>
-      <c r="J865" s="19"/>
+      <c r="I865" s="17"/>
+      <c r="J865" s="17"/>
       <c r="K865" s="10" t="s">
         <v>20</v>
       </c>
@@ -38957,17 +38924,17 @@
     </row>
     <row r="866" ht="18.0" customHeight="1">
       <c r="A866" s="6"/>
-      <c r="B866" s="16"/>
+      <c r="B866" s="15"/>
       <c r="C866" s="14"/>
-      <c r="D866" s="20"/>
-      <c r="E866" s="18"/>
-      <c r="F866" s="18"/>
-      <c r="G866" s="18"/>
+      <c r="D866" s="19"/>
+      <c r="E866" s="16"/>
+      <c r="F866" s="16"/>
+      <c r="G866" s="16"/>
       <c r="H866" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I866" s="19"/>
-      <c r="J866" s="19"/>
+      <c r="I866" s="17"/>
+      <c r="J866" s="17"/>
       <c r="K866" s="10" t="s">
         <v>20</v>
       </c>
@@ -38983,17 +38950,17 @@
     </row>
     <row r="867" ht="18.0" customHeight="1">
       <c r="A867" s="6"/>
-      <c r="B867" s="16"/>
+      <c r="B867" s="15"/>
       <c r="C867" s="14"/>
-      <c r="D867" s="20"/>
-      <c r="E867" s="18"/>
-      <c r="F867" s="18"/>
-      <c r="G867" s="18"/>
+      <c r="D867" s="19"/>
+      <c r="E867" s="16"/>
+      <c r="F867" s="16"/>
+      <c r="G867" s="16"/>
       <c r="H867" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I867" s="19"/>
-      <c r="J867" s="19"/>
+      <c r="I867" s="17"/>
+      <c r="J867" s="17"/>
       <c r="K867" s="10" t="s">
         <v>20</v>
       </c>
@@ -39009,17 +38976,17 @@
     </row>
     <row r="868" ht="18.0" customHeight="1">
       <c r="A868" s="6"/>
-      <c r="B868" s="16"/>
+      <c r="B868" s="15"/>
       <c r="C868" s="14"/>
-      <c r="D868" s="20"/>
-      <c r="E868" s="18"/>
-      <c r="F868" s="18"/>
-      <c r="G868" s="18"/>
+      <c r="D868" s="19"/>
+      <c r="E868" s="16"/>
+      <c r="F868" s="16"/>
+      <c r="G868" s="16"/>
       <c r="H868" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I868" s="19"/>
-      <c r="J868" s="19"/>
+      <c r="I868" s="17"/>
+      <c r="J868" s="17"/>
       <c r="K868" s="10" t="s">
         <v>20</v>
       </c>
@@ -39035,17 +39002,17 @@
     </row>
     <row r="869" ht="18.0" customHeight="1">
       <c r="A869" s="6"/>
-      <c r="B869" s="16"/>
+      <c r="B869" s="15"/>
       <c r="C869" s="14"/>
-      <c r="D869" s="20"/>
-      <c r="E869" s="18"/>
-      <c r="F869" s="18"/>
-      <c r="G869" s="18"/>
+      <c r="D869" s="19"/>
+      <c r="E869" s="16"/>
+      <c r="F869" s="16"/>
+      <c r="G869" s="16"/>
       <c r="H869" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I869" s="19"/>
-      <c r="J869" s="19"/>
+      <c r="I869" s="17"/>
+      <c r="J869" s="17"/>
       <c r="K869" s="10" t="s">
         <v>20</v>
       </c>
@@ -39061,17 +39028,17 @@
     </row>
     <row r="870" ht="18.0" customHeight="1">
       <c r="A870" s="6"/>
-      <c r="B870" s="16"/>
+      <c r="B870" s="15"/>
       <c r="C870" s="14"/>
-      <c r="D870" s="20"/>
-      <c r="E870" s="18"/>
-      <c r="F870" s="18"/>
-      <c r="G870" s="18"/>
+      <c r="D870" s="19"/>
+      <c r="E870" s="16"/>
+      <c r="F870" s="16"/>
+      <c r="G870" s="16"/>
       <c r="H870" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I870" s="19"/>
-      <c r="J870" s="19"/>
+      <c r="I870" s="17"/>
+      <c r="J870" s="17"/>
       <c r="K870" s="10" t="s">
         <v>20</v>
       </c>
@@ -39087,17 +39054,17 @@
     </row>
     <row r="871" ht="18.0" customHeight="1">
       <c r="A871" s="6"/>
-      <c r="B871" s="16"/>
+      <c r="B871" s="15"/>
       <c r="C871" s="14"/>
-      <c r="D871" s="20"/>
-      <c r="E871" s="18"/>
-      <c r="F871" s="18"/>
-      <c r="G871" s="18"/>
+      <c r="D871" s="19"/>
+      <c r="E871" s="16"/>
+      <c r="F871" s="16"/>
+      <c r="G871" s="16"/>
       <c r="H871" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I871" s="19"/>
-      <c r="J871" s="19"/>
+      <c r="I871" s="17"/>
+      <c r="J871" s="17"/>
       <c r="K871" s="10" t="s">
         <v>20</v>
       </c>
@@ -39113,17 +39080,17 @@
     </row>
     <row r="872" ht="18.0" customHeight="1">
       <c r="A872" s="6"/>
-      <c r="B872" s="16"/>
+      <c r="B872" s="15"/>
       <c r="C872" s="14"/>
-      <c r="D872" s="20"/>
-      <c r="E872" s="18"/>
-      <c r="F872" s="18"/>
-      <c r="G872" s="18"/>
+      <c r="D872" s="19"/>
+      <c r="E872" s="16"/>
+      <c r="F872" s="16"/>
+      <c r="G872" s="16"/>
       <c r="H872" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I872" s="19"/>
-      <c r="J872" s="19"/>
+      <c r="I872" s="17"/>
+      <c r="J872" s="17"/>
       <c r="K872" s="10" t="s">
         <v>20</v>
       </c>
@@ -39139,17 +39106,17 @@
     </row>
     <row r="873" ht="18.0" customHeight="1">
       <c r="A873" s="6"/>
-      <c r="B873" s="16"/>
+      <c r="B873" s="15"/>
       <c r="C873" s="14"/>
-      <c r="D873" s="20"/>
-      <c r="E873" s="18"/>
-      <c r="F873" s="18"/>
-      <c r="G873" s="18"/>
+      <c r="D873" s="19"/>
+      <c r="E873" s="16"/>
+      <c r="F873" s="16"/>
+      <c r="G873" s="16"/>
       <c r="H873" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I873" s="19"/>
-      <c r="J873" s="19"/>
+      <c r="I873" s="17"/>
+      <c r="J873" s="17"/>
       <c r="K873" s="10" t="s">
         <v>20</v>
       </c>
@@ -39165,17 +39132,17 @@
     </row>
     <row r="874" ht="18.0" customHeight="1">
       <c r="A874" s="6"/>
-      <c r="B874" s="16"/>
+      <c r="B874" s="15"/>
       <c r="C874" s="14"/>
-      <c r="D874" s="20"/>
-      <c r="E874" s="18"/>
-      <c r="F874" s="18"/>
-      <c r="G874" s="18"/>
+      <c r="D874" s="19"/>
+      <c r="E874" s="16"/>
+      <c r="F874" s="16"/>
+      <c r="G874" s="16"/>
       <c r="H874" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I874" s="19"/>
-      <c r="J874" s="19"/>
+      <c r="I874" s="17"/>
+      <c r="J874" s="17"/>
       <c r="K874" s="10" t="s">
         <v>20</v>
       </c>
@@ -39191,17 +39158,17 @@
     </row>
     <row r="875" ht="18.0" customHeight="1">
       <c r="A875" s="6"/>
-      <c r="B875" s="16"/>
+      <c r="B875" s="15"/>
       <c r="C875" s="14"/>
-      <c r="D875" s="20"/>
-      <c r="E875" s="18"/>
-      <c r="F875" s="18"/>
-      <c r="G875" s="18"/>
+      <c r="D875" s="19"/>
+      <c r="E875" s="16"/>
+      <c r="F875" s="16"/>
+      <c r="G875" s="16"/>
       <c r="H875" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I875" s="19"/>
-      <c r="J875" s="19"/>
+      <c r="I875" s="17"/>
+      <c r="J875" s="17"/>
       <c r="K875" s="10" t="s">
         <v>20</v>
       </c>
@@ -39217,17 +39184,17 @@
     </row>
     <row r="876" ht="18.0" customHeight="1">
       <c r="A876" s="6"/>
-      <c r="B876" s="16"/>
+      <c r="B876" s="15"/>
       <c r="C876" s="14"/>
-      <c r="D876" s="20"/>
-      <c r="E876" s="18"/>
-      <c r="F876" s="18"/>
-      <c r="G876" s="18"/>
+      <c r="D876" s="19"/>
+      <c r="E876" s="16"/>
+      <c r="F876" s="16"/>
+      <c r="G876" s="16"/>
       <c r="H876" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I876" s="19"/>
-      <c r="J876" s="19"/>
+      <c r="I876" s="17"/>
+      <c r="J876" s="17"/>
       <c r="K876" s="10" t="s">
         <v>20</v>
       </c>
@@ -39243,17 +39210,17 @@
     </row>
     <row r="877" ht="18.0" customHeight="1">
       <c r="A877" s="6"/>
-      <c r="B877" s="16"/>
+      <c r="B877" s="15"/>
       <c r="C877" s="14"/>
-      <c r="D877" s="20"/>
-      <c r="E877" s="18"/>
-      <c r="F877" s="18"/>
-      <c r="G877" s="18"/>
+      <c r="D877" s="19"/>
+      <c r="E877" s="16"/>
+      <c r="F877" s="16"/>
+      <c r="G877" s="16"/>
       <c r="H877" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I877" s="19"/>
-      <c r="J877" s="19"/>
+      <c r="I877" s="17"/>
+      <c r="J877" s="17"/>
       <c r="K877" s="10" t="s">
         <v>20</v>
       </c>
@@ -39269,17 +39236,17 @@
     </row>
     <row r="878" ht="18.0" customHeight="1">
       <c r="A878" s="6"/>
-      <c r="B878" s="16"/>
+      <c r="B878" s="15"/>
       <c r="C878" s="14"/>
-      <c r="D878" s="20"/>
-      <c r="E878" s="18"/>
-      <c r="F878" s="18"/>
-      <c r="G878" s="18"/>
+      <c r="D878" s="19"/>
+      <c r="E878" s="16"/>
+      <c r="F878" s="16"/>
+      <c r="G878" s="16"/>
       <c r="H878" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I878" s="19"/>
-      <c r="J878" s="19"/>
+      <c r="I878" s="17"/>
+      <c r="J878" s="17"/>
       <c r="K878" s="10" t="s">
         <v>20</v>
       </c>
@@ -39295,17 +39262,17 @@
     </row>
     <row r="879" ht="18.0" customHeight="1">
       <c r="A879" s="6"/>
-      <c r="B879" s="16"/>
+      <c r="B879" s="15"/>
       <c r="C879" s="14"/>
-      <c r="D879" s="20"/>
-      <c r="E879" s="18"/>
-      <c r="F879" s="18"/>
-      <c r="G879" s="18"/>
+      <c r="D879" s="19"/>
+      <c r="E879" s="16"/>
+      <c r="F879" s="16"/>
+      <c r="G879" s="16"/>
       <c r="H879" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I879" s="19"/>
-      <c r="J879" s="19"/>
+      <c r="I879" s="17"/>
+      <c r="J879" s="17"/>
       <c r="K879" s="10" t="s">
         <v>20</v>
       </c>
@@ -39321,17 +39288,17 @@
     </row>
     <row r="880" ht="18.0" customHeight="1">
       <c r="A880" s="6"/>
-      <c r="B880" s="16"/>
+      <c r="B880" s="15"/>
       <c r="C880" s="14"/>
-      <c r="D880" s="20"/>
-      <c r="E880" s="18"/>
-      <c r="F880" s="18"/>
-      <c r="G880" s="18"/>
+      <c r="D880" s="19"/>
+      <c r="E880" s="16"/>
+      <c r="F880" s="16"/>
+      <c r="G880" s="16"/>
       <c r="H880" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I880" s="19"/>
-      <c r="J880" s="19"/>
+      <c r="I880" s="17"/>
+      <c r="J880" s="17"/>
       <c r="K880" s="10" t="s">
         <v>20</v>
       </c>
@@ -39347,17 +39314,17 @@
     </row>
     <row r="881" ht="18.0" customHeight="1">
       <c r="A881" s="6"/>
-      <c r="B881" s="16"/>
+      <c r="B881" s="15"/>
       <c r="C881" s="14"/>
-      <c r="D881" s="20"/>
-      <c r="E881" s="18"/>
-      <c r="F881" s="18"/>
-      <c r="G881" s="18"/>
+      <c r="D881" s="19"/>
+      <c r="E881" s="16"/>
+      <c r="F881" s="16"/>
+      <c r="G881" s="16"/>
       <c r="H881" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I881" s="19"/>
-      <c r="J881" s="19"/>
+      <c r="I881" s="17"/>
+      <c r="J881" s="17"/>
       <c r="K881" s="10" t="s">
         <v>20</v>
       </c>
@@ -39373,17 +39340,17 @@
     </row>
     <row r="882" ht="18.0" customHeight="1">
       <c r="A882" s="6"/>
-      <c r="B882" s="16"/>
+      <c r="B882" s="15"/>
       <c r="C882" s="14"/>
-      <c r="D882" s="20"/>
-      <c r="E882" s="18"/>
-      <c r="F882" s="18"/>
-      <c r="G882" s="18"/>
+      <c r="D882" s="19"/>
+      <c r="E882" s="16"/>
+      <c r="F882" s="16"/>
+      <c r="G882" s="16"/>
       <c r="H882" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I882" s="19"/>
-      <c r="J882" s="19"/>
+      <c r="I882" s="17"/>
+      <c r="J882" s="17"/>
       <c r="K882" s="10" t="s">
         <v>20</v>
       </c>
@@ -39399,17 +39366,17 @@
     </row>
     <row r="883" ht="18.0" customHeight="1">
       <c r="A883" s="6"/>
-      <c r="B883" s="16"/>
+      <c r="B883" s="15"/>
       <c r="C883" s="14"/>
-      <c r="D883" s="20"/>
-      <c r="E883" s="18"/>
-      <c r="F883" s="18"/>
-      <c r="G883" s="18"/>
+      <c r="D883" s="19"/>
+      <c r="E883" s="16"/>
+      <c r="F883" s="16"/>
+      <c r="G883" s="16"/>
       <c r="H883" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I883" s="19"/>
-      <c r="J883" s="19"/>
+      <c r="I883" s="17"/>
+      <c r="J883" s="17"/>
       <c r="K883" s="10" t="s">
         <v>20</v>
       </c>
@@ -39425,17 +39392,17 @@
     </row>
     <row r="884" ht="18.0" customHeight="1">
       <c r="A884" s="6"/>
-      <c r="B884" s="16"/>
+      <c r="B884" s="15"/>
       <c r="C884" s="14"/>
-      <c r="D884" s="20"/>
-      <c r="E884" s="18"/>
-      <c r="F884" s="18"/>
-      <c r="G884" s="18"/>
+      <c r="D884" s="19"/>
+      <c r="E884" s="16"/>
+      <c r="F884" s="16"/>
+      <c r="G884" s="16"/>
       <c r="H884" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I884" s="19"/>
-      <c r="J884" s="19"/>
+      <c r="I884" s="17"/>
+      <c r="J884" s="17"/>
       <c r="K884" s="10" t="s">
         <v>20</v>
       </c>
@@ -39451,17 +39418,17 @@
     </row>
     <row r="885" ht="18.0" customHeight="1">
       <c r="A885" s="6"/>
-      <c r="B885" s="16"/>
+      <c r="B885" s="15"/>
       <c r="C885" s="14"/>
-      <c r="D885" s="20"/>
-      <c r="E885" s="18"/>
-      <c r="F885" s="18"/>
-      <c r="G885" s="18"/>
+      <c r="D885" s="19"/>
+      <c r="E885" s="16"/>
+      <c r="F885" s="16"/>
+      <c r="G885" s="16"/>
       <c r="H885" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I885" s="19"/>
-      <c r="J885" s="19"/>
+      <c r="I885" s="17"/>
+      <c r="J885" s="17"/>
       <c r="K885" s="10" t="s">
         <v>20</v>
       </c>
@@ -39477,17 +39444,17 @@
     </row>
     <row r="886" ht="18.0" customHeight="1">
       <c r="A886" s="6"/>
-      <c r="B886" s="16"/>
+      <c r="B886" s="15"/>
       <c r="C886" s="14"/>
-      <c r="D886" s="20"/>
-      <c r="E886" s="18"/>
-      <c r="F886" s="18"/>
-      <c r="G886" s="18"/>
+      <c r="D886" s="19"/>
+      <c r="E886" s="16"/>
+      <c r="F886" s="16"/>
+      <c r="G886" s="16"/>
       <c r="H886" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I886" s="19"/>
-      <c r="J886" s="19"/>
+      <c r="I886" s="17"/>
+      <c r="J886" s="17"/>
       <c r="K886" s="10" t="s">
         <v>20</v>
       </c>
@@ -39503,17 +39470,17 @@
     </row>
     <row r="887" ht="18.0" customHeight="1">
       <c r="A887" s="6"/>
-      <c r="B887" s="16"/>
+      <c r="B887" s="15"/>
       <c r="C887" s="14"/>
-      <c r="D887" s="20"/>
-      <c r="E887" s="18"/>
-      <c r="F887" s="18"/>
-      <c r="G887" s="18"/>
+      <c r="D887" s="19"/>
+      <c r="E887" s="16"/>
+      <c r="F887" s="16"/>
+      <c r="G887" s="16"/>
       <c r="H887" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I887" s="19"/>
-      <c r="J887" s="19"/>
+      <c r="I887" s="17"/>
+      <c r="J887" s="17"/>
       <c r="K887" s="10" t="s">
         <v>20</v>
       </c>
@@ -39529,17 +39496,17 @@
     </row>
     <row r="888" ht="18.0" customHeight="1">
       <c r="A888" s="6"/>
-      <c r="B888" s="16"/>
+      <c r="B888" s="15"/>
       <c r="C888" s="14"/>
-      <c r="D888" s="20"/>
-      <c r="E888" s="18"/>
-      <c r="F888" s="18"/>
-      <c r="G888" s="18"/>
+      <c r="D888" s="19"/>
+      <c r="E888" s="16"/>
+      <c r="F888" s="16"/>
+      <c r="G888" s="16"/>
       <c r="H888" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I888" s="19"/>
-      <c r="J888" s="19"/>
+      <c r="I888" s="17"/>
+      <c r="J888" s="17"/>
       <c r="K888" s="10" t="s">
         <v>20</v>
       </c>
@@ -39555,17 +39522,17 @@
     </row>
     <row r="889" ht="18.0" customHeight="1">
       <c r="A889" s="6"/>
-      <c r="B889" s="16"/>
+      <c r="B889" s="15"/>
       <c r="C889" s="14"/>
-      <c r="D889" s="20"/>
-      <c r="E889" s="18"/>
-      <c r="F889" s="18"/>
-      <c r="G889" s="18"/>
+      <c r="D889" s="19"/>
+      <c r="E889" s="16"/>
+      <c r="F889" s="16"/>
+      <c r="G889" s="16"/>
       <c r="H889" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I889" s="19"/>
-      <c r="J889" s="19"/>
+      <c r="I889" s="17"/>
+      <c r="J889" s="17"/>
       <c r="K889" s="10" t="s">
         <v>20</v>
       </c>
@@ -39581,17 +39548,17 @@
     </row>
     <row r="890" ht="18.0" customHeight="1">
       <c r="A890" s="6"/>
-      <c r="B890" s="16"/>
+      <c r="B890" s="15"/>
       <c r="C890" s="14"/>
-      <c r="D890" s="20"/>
-      <c r="E890" s="18"/>
-      <c r="F890" s="18"/>
-      <c r="G890" s="18"/>
+      <c r="D890" s="19"/>
+      <c r="E890" s="16"/>
+      <c r="F890" s="16"/>
+      <c r="G890" s="16"/>
       <c r="H890" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I890" s="19"/>
-      <c r="J890" s="19"/>
+      <c r="I890" s="17"/>
+      <c r="J890" s="17"/>
       <c r="K890" s="10" t="s">
         <v>20</v>
       </c>
@@ -39607,17 +39574,17 @@
     </row>
     <row r="891" ht="18.0" customHeight="1">
       <c r="A891" s="6"/>
-      <c r="B891" s="16"/>
+      <c r="B891" s="15"/>
       <c r="C891" s="14"/>
-      <c r="D891" s="20"/>
-      <c r="E891" s="18"/>
-      <c r="F891" s="18"/>
-      <c r="G891" s="18"/>
+      <c r="D891" s="19"/>
+      <c r="E891" s="16"/>
+      <c r="F891" s="16"/>
+      <c r="G891" s="16"/>
       <c r="H891" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I891" s="19"/>
-      <c r="J891" s="19"/>
+      <c r="I891" s="17"/>
+      <c r="J891" s="17"/>
       <c r="K891" s="10" t="s">
         <v>20</v>
       </c>
@@ -39633,17 +39600,17 @@
     </row>
     <row r="892" ht="18.0" customHeight="1">
       <c r="A892" s="6"/>
-      <c r="B892" s="16"/>
+      <c r="B892" s="15"/>
       <c r="C892" s="14"/>
-      <c r="D892" s="20"/>
-      <c r="E892" s="18"/>
-      <c r="F892" s="18"/>
-      <c r="G892" s="18"/>
+      <c r="D892" s="19"/>
+      <c r="E892" s="16"/>
+      <c r="F892" s="16"/>
+      <c r="G892" s="16"/>
       <c r="H892" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I892" s="19"/>
-      <c r="J892" s="19"/>
+      <c r="I892" s="17"/>
+      <c r="J892" s="17"/>
       <c r="K892" s="10" t="s">
         <v>20</v>
       </c>
@@ -39659,17 +39626,17 @@
     </row>
     <row r="893" ht="18.0" customHeight="1">
       <c r="A893" s="6"/>
-      <c r="B893" s="16"/>
+      <c r="B893" s="15"/>
       <c r="C893" s="14"/>
-      <c r="D893" s="20"/>
-      <c r="E893" s="18"/>
-      <c r="F893" s="18"/>
-      <c r="G893" s="18"/>
+      <c r="D893" s="19"/>
+      <c r="E893" s="16"/>
+      <c r="F893" s="16"/>
+      <c r="G893" s="16"/>
       <c r="H893" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I893" s="19"/>
-      <c r="J893" s="19"/>
+      <c r="I893" s="17"/>
+      <c r="J893" s="17"/>
       <c r="K893" s="10" t="s">
         <v>20</v>
       </c>
@@ -39685,17 +39652,17 @@
     </row>
     <row r="894" ht="18.0" customHeight="1">
       <c r="A894" s="6"/>
-      <c r="B894" s="16"/>
+      <c r="B894" s="15"/>
       <c r="C894" s="14"/>
-      <c r="D894" s="20"/>
-      <c r="E894" s="18"/>
-      <c r="F894" s="18"/>
-      <c r="G894" s="18"/>
+      <c r="D894" s="19"/>
+      <c r="E894" s="16"/>
+      <c r="F894" s="16"/>
+      <c r="G894" s="16"/>
       <c r="H894" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I894" s="19"/>
-      <c r="J894" s="19"/>
+      <c r="I894" s="17"/>
+      <c r="J894" s="17"/>
       <c r="K894" s="10" t="s">
         <v>20</v>
       </c>
@@ -39711,17 +39678,17 @@
     </row>
     <row r="895" ht="18.0" customHeight="1">
       <c r="A895" s="6"/>
-      <c r="B895" s="16"/>
+      <c r="B895" s="15"/>
       <c r="C895" s="14"/>
-      <c r="D895" s="20"/>
-      <c r="E895" s="18"/>
-      <c r="F895" s="18"/>
-      <c r="G895" s="18"/>
+      <c r="D895" s="19"/>
+      <c r="E895" s="16"/>
+      <c r="F895" s="16"/>
+      <c r="G895" s="16"/>
       <c r="H895" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I895" s="19"/>
-      <c r="J895" s="19"/>
+      <c r="I895" s="17"/>
+      <c r="J895" s="17"/>
       <c r="K895" s="10" t="s">
         <v>20</v>
       </c>
@@ -39737,17 +39704,17 @@
     </row>
     <row r="896" ht="18.0" customHeight="1">
       <c r="A896" s="6"/>
-      <c r="B896" s="16"/>
+      <c r="B896" s="15"/>
       <c r="C896" s="14"/>
-      <c r="D896" s="20"/>
-      <c r="E896" s="18"/>
-      <c r="F896" s="18"/>
-      <c r="G896" s="18"/>
+      <c r="D896" s="19"/>
+      <c r="E896" s="16"/>
+      <c r="F896" s="16"/>
+      <c r="G896" s="16"/>
       <c r="H896" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I896" s="19"/>
-      <c r="J896" s="19"/>
+      <c r="I896" s="17"/>
+      <c r="J896" s="17"/>
       <c r="K896" s="10" t="s">
         <v>20</v>
       </c>
@@ -39763,17 +39730,17 @@
     </row>
     <row r="897" ht="18.0" customHeight="1">
       <c r="A897" s="6"/>
-      <c r="B897" s="16"/>
+      <c r="B897" s="15"/>
       <c r="C897" s="14"/>
-      <c r="D897" s="20"/>
-      <c r="E897" s="18"/>
-      <c r="F897" s="18"/>
-      <c r="G897" s="18"/>
+      <c r="D897" s="19"/>
+      <c r="E897" s="16"/>
+      <c r="F897" s="16"/>
+      <c r="G897" s="16"/>
       <c r="H897" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I897" s="19"/>
-      <c r="J897" s="19"/>
+      <c r="I897" s="17"/>
+      <c r="J897" s="17"/>
       <c r="K897" s="10" t="s">
         <v>20</v>
       </c>
@@ -39789,17 +39756,17 @@
     </row>
     <row r="898" ht="18.0" customHeight="1">
       <c r="A898" s="6"/>
-      <c r="B898" s="16"/>
+      <c r="B898" s="15"/>
       <c r="C898" s="14"/>
-      <c r="D898" s="20"/>
-      <c r="E898" s="18"/>
-      <c r="F898" s="18"/>
-      <c r="G898" s="18"/>
+      <c r="D898" s="19"/>
+      <c r="E898" s="16"/>
+      <c r="F898" s="16"/>
+      <c r="G898" s="16"/>
       <c r="H898" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I898" s="19"/>
-      <c r="J898" s="19"/>
+      <c r="I898" s="17"/>
+      <c r="J898" s="17"/>
       <c r="K898" s="10" t="s">
         <v>20</v>
       </c>
@@ -39815,17 +39782,17 @@
     </row>
     <row r="899" ht="18.0" customHeight="1">
       <c r="A899" s="6"/>
-      <c r="B899" s="16"/>
+      <c r="B899" s="15"/>
       <c r="C899" s="14"/>
-      <c r="D899" s="20"/>
-      <c r="E899" s="18"/>
-      <c r="F899" s="18"/>
-      <c r="G899" s="18"/>
+      <c r="D899" s="19"/>
+      <c r="E899" s="16"/>
+      <c r="F899" s="16"/>
+      <c r="G899" s="16"/>
       <c r="H899" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I899" s="19"/>
-      <c r="J899" s="19"/>
+      <c r="I899" s="17"/>
+      <c r="J899" s="17"/>
       <c r="K899" s="10" t="s">
         <v>20</v>
       </c>
@@ -39841,17 +39808,17 @@
     </row>
     <row r="900" ht="18.0" customHeight="1">
       <c r="A900" s="6"/>
-      <c r="B900" s="16"/>
+      <c r="B900" s="15"/>
       <c r="C900" s="14"/>
-      <c r="D900" s="20"/>
-      <c r="E900" s="18"/>
-      <c r="F900" s="18"/>
-      <c r="G900" s="18"/>
+      <c r="D900" s="19"/>
+      <c r="E900" s="16"/>
+      <c r="F900" s="16"/>
+      <c r="G900" s="16"/>
       <c r="H900" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I900" s="19"/>
-      <c r="J900" s="19"/>
+      <c r="I900" s="17"/>
+      <c r="J900" s="17"/>
       <c r="K900" s="10" t="s">
         <v>20</v>
       </c>
@@ -39867,17 +39834,17 @@
     </row>
     <row r="901" ht="18.0" customHeight="1">
       <c r="A901" s="6"/>
-      <c r="B901" s="16"/>
+      <c r="B901" s="15"/>
       <c r="C901" s="14"/>
-      <c r="D901" s="20"/>
-      <c r="E901" s="18"/>
-      <c r="F901" s="18"/>
-      <c r="G901" s="18"/>
+      <c r="D901" s="19"/>
+      <c r="E901" s="16"/>
+      <c r="F901" s="16"/>
+      <c r="G901" s="16"/>
       <c r="H901" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I901" s="19"/>
-      <c r="J901" s="19"/>
+      <c r="I901" s="17"/>
+      <c r="J901" s="17"/>
       <c r="K901" s="10" t="s">
         <v>20</v>
       </c>
@@ -39893,17 +39860,17 @@
     </row>
     <row r="902" ht="18.0" customHeight="1">
       <c r="A902" s="6"/>
-      <c r="B902" s="16"/>
+      <c r="B902" s="15"/>
       <c r="C902" s="14"/>
-      <c r="D902" s="20"/>
-      <c r="E902" s="18"/>
-      <c r="F902" s="18"/>
-      <c r="G902" s="18"/>
+      <c r="D902" s="19"/>
+      <c r="E902" s="16"/>
+      <c r="F902" s="16"/>
+      <c r="G902" s="16"/>
       <c r="H902" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I902" s="19"/>
-      <c r="J902" s="19"/>
+      <c r="I902" s="17"/>
+      <c r="J902" s="17"/>
       <c r="K902" s="10" t="s">
         <v>20</v>
       </c>
@@ -39919,17 +39886,17 @@
     </row>
     <row r="903" ht="18.0" customHeight="1">
       <c r="A903" s="6"/>
-      <c r="B903" s="16"/>
+      <c r="B903" s="15"/>
       <c r="C903" s="14"/>
-      <c r="D903" s="20"/>
-      <c r="E903" s="18"/>
-      <c r="F903" s="18"/>
-      <c r="G903" s="18"/>
+      <c r="D903" s="19"/>
+      <c r="E903" s="16"/>
+      <c r="F903" s="16"/>
+      <c r="G903" s="16"/>
       <c r="H903" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I903" s="19"/>
-      <c r="J903" s="19"/>
+      <c r="I903" s="17"/>
+      <c r="J903" s="17"/>
       <c r="K903" s="10" t="s">
         <v>20</v>
       </c>
@@ -39945,17 +39912,17 @@
     </row>
     <row r="904" ht="18.0" customHeight="1">
       <c r="A904" s="6"/>
-      <c r="B904" s="16"/>
+      <c r="B904" s="15"/>
       <c r="C904" s="14"/>
-      <c r="D904" s="20"/>
-      <c r="E904" s="18"/>
-      <c r="F904" s="18"/>
-      <c r="G904" s="18"/>
+      <c r="D904" s="19"/>
+      <c r="E904" s="16"/>
+      <c r="F904" s="16"/>
+      <c r="G904" s="16"/>
       <c r="H904" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I904" s="19"/>
-      <c r="J904" s="19"/>
+      <c r="I904" s="17"/>
+      <c r="J904" s="17"/>
       <c r="K904" s="10" t="s">
         <v>20</v>
       </c>
@@ -39971,17 +39938,17 @@
     </row>
     <row r="905" ht="18.0" customHeight="1">
       <c r="A905" s="6"/>
-      <c r="B905" s="16"/>
+      <c r="B905" s="15"/>
       <c r="C905" s="14"/>
-      <c r="D905" s="20"/>
-      <c r="E905" s="18"/>
-      <c r="F905" s="18"/>
-      <c r="G905" s="18"/>
+      <c r="D905" s="19"/>
+      <c r="E905" s="16"/>
+      <c r="F905" s="16"/>
+      <c r="G905" s="16"/>
       <c r="H905" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I905" s="19"/>
-      <c r="J905" s="19"/>
+      <c r="I905" s="17"/>
+      <c r="J905" s="17"/>
       <c r="K905" s="10" t="s">
         <v>20</v>
       </c>
@@ -39997,17 +39964,17 @@
     </row>
     <row r="906" ht="18.0" customHeight="1">
       <c r="A906" s="6"/>
-      <c r="B906" s="16"/>
+      <c r="B906" s="15"/>
       <c r="C906" s="14"/>
-      <c r="D906" s="20"/>
-      <c r="E906" s="18"/>
-      <c r="F906" s="18"/>
-      <c r="G906" s="18"/>
+      <c r="D906" s="19"/>
+      <c r="E906" s="16"/>
+      <c r="F906" s="16"/>
+      <c r="G906" s="16"/>
       <c r="H906" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I906" s="19"/>
-      <c r="J906" s="19"/>
+      <c r="I906" s="17"/>
+      <c r="J906" s="17"/>
       <c r="K906" s="10" t="s">
         <v>20</v>
       </c>
@@ -40023,17 +39990,17 @@
     </row>
     <row r="907" ht="18.0" customHeight="1">
       <c r="A907" s="6"/>
-      <c r="B907" s="16"/>
+      <c r="B907" s="15"/>
       <c r="C907" s="14"/>
-      <c r="D907" s="20"/>
-      <c r="E907" s="18"/>
-      <c r="F907" s="18"/>
-      <c r="G907" s="18"/>
+      <c r="D907" s="19"/>
+      <c r="E907" s="16"/>
+      <c r="F907" s="16"/>
+      <c r="G907" s="16"/>
       <c r="H907" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I907" s="19"/>
-      <c r="J907" s="19"/>
+      <c r="I907" s="17"/>
+      <c r="J907" s="17"/>
       <c r="K907" s="10" t="s">
         <v>20</v>
       </c>
@@ -40049,17 +40016,17 @@
     </row>
     <row r="908" ht="18.0" customHeight="1">
       <c r="A908" s="6"/>
-      <c r="B908" s="16"/>
+      <c r="B908" s="15"/>
       <c r="C908" s="14"/>
-      <c r="D908" s="20"/>
-      <c r="E908" s="18"/>
-      <c r="F908" s="18"/>
-      <c r="G908" s="18"/>
+      <c r="D908" s="19"/>
+      <c r="E908" s="16"/>
+      <c r="F908" s="16"/>
+      <c r="G908" s="16"/>
       <c r="H908" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I908" s="19"/>
-      <c r="J908" s="19"/>
+      <c r="I908" s="17"/>
+      <c r="J908" s="17"/>
       <c r="K908" s="10" t="s">
         <v>20</v>
       </c>
@@ -40075,17 +40042,17 @@
     </row>
     <row r="909" ht="18.0" customHeight="1">
       <c r="A909" s="6"/>
-      <c r="B909" s="16"/>
+      <c r="B909" s="15"/>
       <c r="C909" s="14"/>
-      <c r="D909" s="20"/>
-      <c r="E909" s="18"/>
-      <c r="F909" s="18"/>
-      <c r="G909" s="18"/>
+      <c r="D909" s="19"/>
+      <c r="E909" s="16"/>
+      <c r="F909" s="16"/>
+      <c r="G909" s="16"/>
       <c r="H909" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I909" s="19"/>
-      <c r="J909" s="19"/>
+      <c r="I909" s="17"/>
+      <c r="J909" s="17"/>
       <c r="K909" s="10" t="s">
         <v>20</v>
       </c>
@@ -40101,17 +40068,17 @@
     </row>
     <row r="910" ht="18.0" customHeight="1">
       <c r="A910" s="6"/>
-      <c r="B910" s="16"/>
+      <c r="B910" s="15"/>
       <c r="C910" s="14"/>
-      <c r="D910" s="20"/>
-      <c r="E910" s="18"/>
-      <c r="F910" s="18"/>
-      <c r="G910" s="18"/>
+      <c r="D910" s="19"/>
+      <c r="E910" s="16"/>
+      <c r="F910" s="16"/>
+      <c r="G910" s="16"/>
       <c r="H910" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I910" s="19"/>
-      <c r="J910" s="19"/>
+      <c r="I910" s="17"/>
+      <c r="J910" s="17"/>
       <c r="K910" s="10" t="s">
         <v>20</v>
       </c>
@@ -40127,17 +40094,17 @@
     </row>
     <row r="911" ht="18.0" customHeight="1">
       <c r="A911" s="6"/>
-      <c r="B911" s="16"/>
+      <c r="B911" s="15"/>
       <c r="C911" s="14"/>
-      <c r="D911" s="20"/>
-      <c r="E911" s="18"/>
-      <c r="F911" s="18"/>
-      <c r="G911" s="18"/>
+      <c r="D911" s="19"/>
+      <c r="E911" s="16"/>
+      <c r="F911" s="16"/>
+      <c r="G911" s="16"/>
       <c r="H911" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I911" s="19"/>
-      <c r="J911" s="19"/>
+      <c r="I911" s="17"/>
+      <c r="J911" s="17"/>
       <c r="K911" s="10" t="s">
         <v>20</v>
       </c>
@@ -40153,17 +40120,17 @@
     </row>
     <row r="912" ht="18.0" customHeight="1">
       <c r="A912" s="6"/>
-      <c r="B912" s="16"/>
+      <c r="B912" s="15"/>
       <c r="C912" s="14"/>
-      <c r="D912" s="20"/>
-      <c r="E912" s="18"/>
-      <c r="F912" s="18"/>
-      <c r="G912" s="18"/>
+      <c r="D912" s="19"/>
+      <c r="E912" s="16"/>
+      <c r="F912" s="16"/>
+      <c r="G912" s="16"/>
       <c r="H912" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I912" s="19"/>
-      <c r="J912" s="19"/>
+      <c r="I912" s="17"/>
+      <c r="J912" s="17"/>
       <c r="K912" s="10" t="s">
         <v>20</v>
       </c>
@@ -40179,17 +40146,17 @@
     </row>
     <row r="913" ht="18.0" customHeight="1">
       <c r="A913" s="6"/>
-      <c r="B913" s="16"/>
+      <c r="B913" s="15"/>
       <c r="C913" s="14"/>
-      <c r="D913" s="20"/>
-      <c r="E913" s="18"/>
-      <c r="F913" s="18"/>
-      <c r="G913" s="18"/>
+      <c r="D913" s="19"/>
+      <c r="E913" s="16"/>
+      <c r="F913" s="16"/>
+      <c r="G913" s="16"/>
       <c r="H913" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I913" s="19"/>
-      <c r="J913" s="19"/>
+      <c r="I913" s="17"/>
+      <c r="J913" s="17"/>
       <c r="K913" s="10" t="s">
         <v>20</v>
       </c>
@@ -40205,17 +40172,17 @@
     </row>
     <row r="914" ht="18.0" customHeight="1">
       <c r="A914" s="6"/>
-      <c r="B914" s="16"/>
+      <c r="B914" s="15"/>
       <c r="C914" s="14"/>
-      <c r="D914" s="20"/>
-      <c r="E914" s="18"/>
-      <c r="F914" s="18"/>
-      <c r="G914" s="18"/>
+      <c r="D914" s="19"/>
+      <c r="E914" s="16"/>
+      <c r="F914" s="16"/>
+      <c r="G914" s="16"/>
       <c r="H914" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I914" s="19"/>
-      <c r="J914" s="19"/>
+      <c r="I914" s="17"/>
+      <c r="J914" s="17"/>
       <c r="K914" s="10" t="s">
         <v>20</v>
       </c>
@@ -40231,17 +40198,17 @@
     </row>
     <row r="915" ht="18.0" customHeight="1">
       <c r="A915" s="6"/>
-      <c r="B915" s="16"/>
+      <c r="B915" s="15"/>
       <c r="C915" s="14"/>
-      <c r="D915" s="20"/>
-      <c r="E915" s="18"/>
-      <c r="F915" s="18"/>
-      <c r="G915" s="18"/>
+      <c r="D915" s="19"/>
+      <c r="E915" s="16"/>
+      <c r="F915" s="16"/>
+      <c r="G915" s="16"/>
       <c r="H915" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I915" s="19"/>
-      <c r="J915" s="19"/>
+      <c r="I915" s="17"/>
+      <c r="J915" s="17"/>
       <c r="K915" s="10" t="s">
         <v>20</v>
       </c>
@@ -40257,17 +40224,17 @@
     </row>
     <row r="916" ht="18.0" customHeight="1">
       <c r="A916" s="6"/>
-      <c r="B916" s="16"/>
+      <c r="B916" s="15"/>
       <c r="C916" s="14"/>
-      <c r="D916" s="20"/>
-      <c r="E916" s="18"/>
-      <c r="F916" s="18"/>
-      <c r="G916" s="18"/>
+      <c r="D916" s="19"/>
+      <c r="E916" s="16"/>
+      <c r="F916" s="16"/>
+      <c r="G916" s="16"/>
       <c r="H916" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I916" s="19"/>
-      <c r="J916" s="19"/>
+      <c r="I916" s="17"/>
+      <c r="J916" s="17"/>
       <c r="K916" s="10" t="s">
         <v>20</v>
       </c>
@@ -40283,17 +40250,17 @@
     </row>
     <row r="917" ht="18.0" customHeight="1">
       <c r="A917" s="6"/>
-      <c r="B917" s="16"/>
+      <c r="B917" s="15"/>
       <c r="C917" s="14"/>
-      <c r="D917" s="20"/>
-      <c r="E917" s="18"/>
-      <c r="F917" s="18"/>
-      <c r="G917" s="18"/>
+      <c r="D917" s="19"/>
+      <c r="E917" s="16"/>
+      <c r="F917" s="16"/>
+      <c r="G917" s="16"/>
       <c r="H917" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I917" s="19"/>
-      <c r="J917" s="19"/>
+      <c r="I917" s="17"/>
+      <c r="J917" s="17"/>
       <c r="K917" s="10" t="s">
         <v>20</v>
       </c>
@@ -40309,17 +40276,17 @@
     </row>
     <row r="918" ht="18.0" customHeight="1">
       <c r="A918" s="6"/>
-      <c r="B918" s="16"/>
+      <c r="B918" s="15"/>
       <c r="C918" s="14"/>
-      <c r="D918" s="20"/>
-      <c r="E918" s="18"/>
-      <c r="F918" s="18"/>
-      <c r="G918" s="18"/>
+      <c r="D918" s="19"/>
+      <c r="E918" s="16"/>
+      <c r="F918" s="16"/>
+      <c r="G918" s="16"/>
       <c r="H918" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I918" s="19"/>
-      <c r="J918" s="19"/>
+      <c r="I918" s="17"/>
+      <c r="J918" s="17"/>
       <c r="K918" s="10" t="s">
         <v>20</v>
       </c>
@@ -40335,17 +40302,17 @@
     </row>
     <row r="919" ht="18.0" customHeight="1">
       <c r="A919" s="6"/>
-      <c r="B919" s="16"/>
+      <c r="B919" s="15"/>
       <c r="C919" s="14"/>
-      <c r="D919" s="20"/>
-      <c r="E919" s="18"/>
-      <c r="F919" s="18"/>
-      <c r="G919" s="18"/>
+      <c r="D919" s="19"/>
+      <c r="E919" s="16"/>
+      <c r="F919" s="16"/>
+      <c r="G919" s="16"/>
       <c r="H919" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I919" s="19"/>
-      <c r="J919" s="19"/>
+      <c r="I919" s="17"/>
+      <c r="J919" s="17"/>
       <c r="K919" s="10" t="s">
         <v>20</v>
       </c>
@@ -40361,17 +40328,17 @@
     </row>
     <row r="920" ht="18.0" customHeight="1">
       <c r="A920" s="6"/>
-      <c r="B920" s="16"/>
+      <c r="B920" s="15"/>
       <c r="C920" s="14"/>
-      <c r="D920" s="20"/>
-      <c r="E920" s="18"/>
-      <c r="F920" s="18"/>
-      <c r="G920" s="18"/>
+      <c r="D920" s="19"/>
+      <c r="E920" s="16"/>
+      <c r="F920" s="16"/>
+      <c r="G920" s="16"/>
       <c r="H920" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I920" s="19"/>
-      <c r="J920" s="19"/>
+      <c r="I920" s="17"/>
+      <c r="J920" s="17"/>
       <c r="K920" s="10" t="s">
         <v>20</v>
       </c>
@@ -40387,17 +40354,17 @@
     </row>
     <row r="921" ht="18.0" customHeight="1">
       <c r="A921" s="6"/>
-      <c r="B921" s="16"/>
+      <c r="B921" s="15"/>
       <c r="C921" s="14"/>
-      <c r="D921" s="20"/>
-      <c r="E921" s="18"/>
-      <c r="F921" s="18"/>
-      <c r="G921" s="18"/>
+      <c r="D921" s="19"/>
+      <c r="E921" s="16"/>
+      <c r="F921" s="16"/>
+      <c r="G921" s="16"/>
       <c r="H921" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I921" s="19"/>
-      <c r="J921" s="19"/>
+      <c r="I921" s="17"/>
+      <c r="J921" s="17"/>
       <c r="K921" s="10" t="s">
         <v>20</v>
       </c>
@@ -40413,17 +40380,17 @@
     </row>
     <row r="922" ht="18.0" customHeight="1">
       <c r="A922" s="6"/>
-      <c r="B922" s="16"/>
+      <c r="B922" s="15"/>
       <c r="C922" s="14"/>
-      <c r="D922" s="20"/>
-      <c r="E922" s="18"/>
-      <c r="F922" s="18"/>
-      <c r="G922" s="18"/>
+      <c r="D922" s="19"/>
+      <c r="E922" s="16"/>
+      <c r="F922" s="16"/>
+      <c r="G922" s="16"/>
       <c r="H922" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I922" s="19"/>
-      <c r="J922" s="19"/>
+      <c r="I922" s="17"/>
+      <c r="J922" s="17"/>
       <c r="K922" s="10" t="s">
         <v>20</v>
       </c>
@@ -40439,17 +40406,17 @@
     </row>
     <row r="923" ht="18.0" customHeight="1">
       <c r="A923" s="6"/>
-      <c r="B923" s="16"/>
+      <c r="B923" s="15"/>
       <c r="C923" s="14"/>
-      <c r="D923" s="20"/>
-      <c r="E923" s="18"/>
-      <c r="F923" s="18"/>
-      <c r="G923" s="18"/>
+      <c r="D923" s="19"/>
+      <c r="E923" s="16"/>
+      <c r="F923" s="16"/>
+      <c r="G923" s="16"/>
       <c r="H923" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I923" s="19"/>
-      <c r="J923" s="19"/>
+      <c r="I923" s="17"/>
+      <c r="J923" s="17"/>
       <c r="K923" s="10" t="s">
         <v>20</v>
       </c>
@@ -40465,17 +40432,17 @@
     </row>
     <row r="924" ht="18.0" customHeight="1">
       <c r="A924" s="6"/>
-      <c r="B924" s="16"/>
+      <c r="B924" s="15"/>
       <c r="C924" s="14"/>
-      <c r="D924" s="20"/>
-      <c r="E924" s="18"/>
-      <c r="F924" s="18"/>
-      <c r="G924" s="18"/>
+      <c r="D924" s="19"/>
+      <c r="E924" s="16"/>
+      <c r="F924" s="16"/>
+      <c r="G924" s="16"/>
       <c r="H924" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I924" s="19"/>
-      <c r="J924" s="19"/>
+      <c r="I924" s="17"/>
+      <c r="J924" s="17"/>
       <c r="K924" s="10" t="s">
         <v>20</v>
       </c>
@@ -40491,17 +40458,17 @@
     </row>
     <row r="925" ht="18.0" customHeight="1">
       <c r="A925" s="6"/>
-      <c r="B925" s="16"/>
+      <c r="B925" s="15"/>
       <c r="C925" s="14"/>
-      <c r="D925" s="20"/>
-      <c r="E925" s="18"/>
-      <c r="F925" s="18"/>
-      <c r="G925" s="18"/>
+      <c r="D925" s="19"/>
+      <c r="E925" s="16"/>
+      <c r="F925" s="16"/>
+      <c r="G925" s="16"/>
       <c r="H925" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I925" s="19"/>
-      <c r="J925" s="19"/>
+      <c r="I925" s="17"/>
+      <c r="J925" s="17"/>
       <c r="K925" s="10" t="s">
         <v>20</v>
       </c>
@@ -40517,17 +40484,17 @@
     </row>
     <row r="926" ht="18.0" customHeight="1">
       <c r="A926" s="6"/>
-      <c r="B926" s="16"/>
+      <c r="B926" s="15"/>
       <c r="C926" s="14"/>
-      <c r="D926" s="20"/>
-      <c r="E926" s="18"/>
-      <c r="F926" s="18"/>
-      <c r="G926" s="18"/>
+      <c r="D926" s="19"/>
+      <c r="E926" s="16"/>
+      <c r="F926" s="16"/>
+      <c r="G926" s="16"/>
       <c r="H926" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I926" s="19"/>
-      <c r="J926" s="19"/>
+      <c r="I926" s="17"/>
+      <c r="J926" s="17"/>
       <c r="K926" s="10" t="s">
         <v>20</v>
       </c>
@@ -40543,17 +40510,17 @@
     </row>
     <row r="927" ht="18.0" customHeight="1">
       <c r="A927" s="6"/>
-      <c r="B927" s="16"/>
+      <c r="B927" s="15"/>
       <c r="C927" s="14"/>
-      <c r="D927" s="20"/>
-      <c r="E927" s="18"/>
-      <c r="F927" s="18"/>
-      <c r="G927" s="18"/>
+      <c r="D927" s="19"/>
+      <c r="E927" s="16"/>
+      <c r="F927" s="16"/>
+      <c r="G927" s="16"/>
       <c r="H927" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I927" s="19"/>
-      <c r="J927" s="19"/>
+      <c r="I927" s="17"/>
+      <c r="J927" s="17"/>
       <c r="K927" s="10" t="s">
         <v>20</v>
       </c>
@@ -40569,17 +40536,17 @@
     </row>
     <row r="928" ht="18.0" customHeight="1">
       <c r="A928" s="6"/>
-      <c r="B928" s="16"/>
+      <c r="B928" s="15"/>
       <c r="C928" s="14"/>
-      <c r="D928" s="20"/>
-      <c r="E928" s="18"/>
-      <c r="F928" s="18"/>
-      <c r="G928" s="18"/>
+      <c r="D928" s="19"/>
+      <c r="E928" s="16"/>
+      <c r="F928" s="16"/>
+      <c r="G928" s="16"/>
       <c r="H928" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I928" s="19"/>
-      <c r="J928" s="19"/>
+      <c r="I928" s="17"/>
+      <c r="J928" s="17"/>
       <c r="K928" s="10" t="s">
         <v>20</v>
       </c>
@@ -40595,17 +40562,17 @@
     </row>
     <row r="929" ht="18.0" customHeight="1">
       <c r="A929" s="6"/>
-      <c r="B929" s="16"/>
+      <c r="B929" s="15"/>
       <c r="C929" s="14"/>
-      <c r="D929" s="20"/>
-      <c r="E929" s="18"/>
-      <c r="F929" s="18"/>
-      <c r="G929" s="18"/>
+      <c r="D929" s="19"/>
+      <c r="E929" s="16"/>
+      <c r="F929" s="16"/>
+      <c r="G929" s="16"/>
       <c r="H929" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I929" s="19"/>
-      <c r="J929" s="19"/>
+      <c r="I929" s="17"/>
+      <c r="J929" s="17"/>
       <c r="K929" s="10" t="s">
         <v>20</v>
       </c>
@@ -40621,17 +40588,17 @@
     </row>
     <row r="930" ht="18.0" customHeight="1">
       <c r="A930" s="6"/>
-      <c r="B930" s="16"/>
+      <c r="B930" s="15"/>
       <c r="C930" s="14"/>
-      <c r="D930" s="20"/>
-      <c r="E930" s="18"/>
-      <c r="F930" s="18"/>
-      <c r="G930" s="18"/>
+      <c r="D930" s="19"/>
+      <c r="E930" s="16"/>
+      <c r="F930" s="16"/>
+      <c r="G930" s="16"/>
       <c r="H930" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I930" s="19"/>
-      <c r="J930" s="19"/>
+      <c r="I930" s="17"/>
+      <c r="J930" s="17"/>
       <c r="K930" s="10" t="s">
         <v>20</v>
       </c>
@@ -40647,17 +40614,17 @@
     </row>
     <row r="931" ht="18.0" customHeight="1">
       <c r="A931" s="6"/>
-      <c r="B931" s="16"/>
+      <c r="B931" s="15"/>
       <c r="C931" s="14"/>
-      <c r="D931" s="20"/>
-      <c r="E931" s="18"/>
-      <c r="F931" s="18"/>
-      <c r="G931" s="18"/>
+      <c r="D931" s="19"/>
+      <c r="E931" s="16"/>
+      <c r="F931" s="16"/>
+      <c r="G931" s="16"/>
       <c r="H931" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I931" s="19"/>
-      <c r="J931" s="19"/>
+      <c r="I931" s="17"/>
+      <c r="J931" s="17"/>
       <c r="K931" s="10" t="s">
         <v>20</v>
       </c>
@@ -40673,17 +40640,17 @@
     </row>
     <row r="932" ht="18.0" customHeight="1">
       <c r="A932" s="6"/>
-      <c r="B932" s="16"/>
+      <c r="B932" s="15"/>
       <c r="C932" s="14"/>
-      <c r="D932" s="20"/>
-      <c r="E932" s="18"/>
-      <c r="F932" s="18"/>
-      <c r="G932" s="18"/>
+      <c r="D932" s="19"/>
+      <c r="E932" s="16"/>
+      <c r="F932" s="16"/>
+      <c r="G932" s="16"/>
       <c r="H932" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I932" s="19"/>
-      <c r="J932" s="19"/>
+      <c r="I932" s="17"/>
+      <c r="J932" s="17"/>
       <c r="K932" s="10" t="s">
         <v>20</v>
       </c>
@@ -40699,17 +40666,17 @@
     </row>
     <row r="933" ht="18.0" customHeight="1">
       <c r="A933" s="6"/>
-      <c r="B933" s="16"/>
+      <c r="B933" s="15"/>
       <c r="C933" s="14"/>
-      <c r="D933" s="20"/>
-      <c r="E933" s="18"/>
-      <c r="F933" s="18"/>
-      <c r="G933" s="18"/>
+      <c r="D933" s="19"/>
+      <c r="E933" s="16"/>
+      <c r="F933" s="16"/>
+      <c r="G933" s="16"/>
       <c r="H933" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I933" s="19"/>
-      <c r="J933" s="19"/>
+      <c r="I933" s="17"/>
+      <c r="J933" s="17"/>
       <c r="K933" s="10" t="s">
         <v>20</v>
       </c>
@@ -40725,17 +40692,17 @@
     </row>
     <row r="934" ht="18.0" customHeight="1">
       <c r="A934" s="6"/>
-      <c r="B934" s="16"/>
+      <c r="B934" s="15"/>
       <c r="C934" s="14"/>
-      <c r="D934" s="20"/>
-      <c r="E934" s="18"/>
-      <c r="F934" s="18"/>
-      <c r="G934" s="18"/>
+      <c r="D934" s="19"/>
+      <c r="E934" s="16"/>
+      <c r="F934" s="16"/>
+      <c r="G934" s="16"/>
       <c r="H934" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I934" s="19"/>
-      <c r="J934" s="19"/>
+      <c r="I934" s="17"/>
+      <c r="J934" s="17"/>
       <c r="K934" s="10" t="s">
         <v>20</v>
       </c>
@@ -40751,17 +40718,17 @@
     </row>
     <row r="935" ht="18.0" customHeight="1">
       <c r="A935" s="6"/>
-      <c r="B935" s="16"/>
+      <c r="B935" s="15"/>
       <c r="C935" s="14"/>
-      <c r="D935" s="20"/>
-      <c r="E935" s="18"/>
-      <c r="F935" s="18"/>
-      <c r="G935" s="18"/>
+      <c r="D935" s="19"/>
+      <c r="E935" s="16"/>
+      <c r="F935" s="16"/>
+      <c r="G935" s="16"/>
       <c r="H935" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I935" s="19"/>
-      <c r="J935" s="19"/>
+      <c r="I935" s="17"/>
+      <c r="J935" s="17"/>
       <c r="K935" s="10" t="s">
         <v>20</v>
       </c>
@@ -40777,17 +40744,17 @@
     </row>
     <row r="936" ht="18.0" customHeight="1">
       <c r="A936" s="6"/>
-      <c r="B936" s="16"/>
+      <c r="B936" s="15"/>
       <c r="C936" s="14"/>
-      <c r="D936" s="20"/>
-      <c r="E936" s="18"/>
-      <c r="F936" s="18"/>
-      <c r="G936" s="18"/>
+      <c r="D936" s="19"/>
+      <c r="E936" s="16"/>
+      <c r="F936" s="16"/>
+      <c r="G936" s="16"/>
       <c r="H936" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I936" s="19"/>
-      <c r="J936" s="19"/>
+      <c r="I936" s="17"/>
+      <c r="J936" s="17"/>
       <c r="K936" s="10" t="s">
         <v>20</v>
       </c>
@@ -40803,17 +40770,17 @@
     </row>
     <row r="937" ht="18.0" customHeight="1">
       <c r="A937" s="6"/>
-      <c r="B937" s="16"/>
+      <c r="B937" s="15"/>
       <c r="C937" s="14"/>
-      <c r="D937" s="20"/>
-      <c r="E937" s="18"/>
-      <c r="F937" s="18"/>
-      <c r="G937" s="18"/>
+      <c r="D937" s="19"/>
+      <c r="E937" s="16"/>
+      <c r="F937" s="16"/>
+      <c r="G937" s="16"/>
       <c r="H937" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I937" s="19"/>
-      <c r="J937" s="19"/>
+      <c r="I937" s="17"/>
+      <c r="J937" s="17"/>
       <c r="K937" s="10" t="s">
         <v>20</v>
       </c>
@@ -40829,17 +40796,17 @@
     </row>
     <row r="938" ht="18.0" customHeight="1">
       <c r="A938" s="6"/>
-      <c r="B938" s="16"/>
+      <c r="B938" s="15"/>
       <c r="C938" s="14"/>
-      <c r="D938" s="20"/>
-      <c r="E938" s="18"/>
-      <c r="F938" s="18"/>
-      <c r="G938" s="18"/>
+      <c r="D938" s="19"/>
+      <c r="E938" s="16"/>
+      <c r="F938" s="16"/>
+      <c r="G938" s="16"/>
       <c r="H938" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I938" s="19"/>
-      <c r="J938" s="19"/>
+      <c r="I938" s="17"/>
+      <c r="J938" s="17"/>
       <c r="K938" s="10" t="s">
         <v>20</v>
       </c>
@@ -40855,17 +40822,17 @@
     </row>
     <row r="939" ht="18.0" customHeight="1">
       <c r="A939" s="6"/>
-      <c r="B939" s="16"/>
+      <c r="B939" s="15"/>
       <c r="C939" s="14"/>
-      <c r="D939" s="20"/>
-      <c r="E939" s="18"/>
-      <c r="F939" s="18"/>
-      <c r="G939" s="18"/>
+      <c r="D939" s="19"/>
+      <c r="E939" s="16"/>
+      <c r="F939" s="16"/>
+      <c r="G939" s="16"/>
       <c r="H939" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I939" s="19"/>
-      <c r="J939" s="19"/>
+      <c r="I939" s="17"/>
+      <c r="J939" s="17"/>
       <c r="K939" s="10" t="s">
         <v>20</v>
       </c>
@@ -40881,17 +40848,17 @@
     </row>
     <row r="940" ht="18.0" customHeight="1">
       <c r="A940" s="6"/>
-      <c r="B940" s="16"/>
+      <c r="B940" s="15"/>
       <c r="C940" s="14"/>
-      <c r="D940" s="20"/>
-      <c r="E940" s="18"/>
-      <c r="F940" s="18"/>
-      <c r="G940" s="18"/>
+      <c r="D940" s="19"/>
+      <c r="E940" s="16"/>
+      <c r="F940" s="16"/>
+      <c r="G940" s="16"/>
       <c r="H940" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I940" s="19"/>
-      <c r="J940" s="19"/>
+      <c r="I940" s="17"/>
+      <c r="J940" s="17"/>
       <c r="K940" s="10" t="s">
         <v>20</v>
       </c>
@@ -40907,17 +40874,17 @@
     </row>
     <row r="941" ht="18.0" customHeight="1">
       <c r="A941" s="6"/>
-      <c r="B941" s="16"/>
+      <c r="B941" s="15"/>
       <c r="C941" s="14"/>
-      <c r="D941" s="20"/>
-      <c r="E941" s="18"/>
-      <c r="F941" s="18"/>
-      <c r="G941" s="18"/>
+      <c r="D941" s="19"/>
+      <c r="E941" s="16"/>
+      <c r="F941" s="16"/>
+      <c r="G941" s="16"/>
       <c r="H941" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I941" s="19"/>
-      <c r="J941" s="19"/>
+      <c r="I941" s="17"/>
+      <c r="J941" s="17"/>
       <c r="K941" s="10" t="s">
         <v>20</v>
       </c>
@@ -40933,17 +40900,17 @@
     </row>
     <row r="942" ht="18.0" customHeight="1">
       <c r="A942" s="6"/>
-      <c r="B942" s="16"/>
+      <c r="B942" s="15"/>
       <c r="C942" s="14"/>
-      <c r="D942" s="20"/>
-      <c r="E942" s="18"/>
-      <c r="F942" s="18"/>
-      <c r="G942" s="18"/>
+      <c r="D942" s="19"/>
+      <c r="E942" s="16"/>
+      <c r="F942" s="16"/>
+      <c r="G942" s="16"/>
       <c r="H942" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I942" s="19"/>
-      <c r="J942" s="19"/>
+      <c r="I942" s="17"/>
+      <c r="J942" s="17"/>
       <c r="K942" s="10" t="s">
         <v>20</v>
       </c>
@@ -40959,17 +40926,17 @@
     </row>
     <row r="943" ht="18.0" customHeight="1">
       <c r="A943" s="6"/>
-      <c r="B943" s="16"/>
+      <c r="B943" s="15"/>
       <c r="C943" s="14"/>
-      <c r="D943" s="20"/>
-      <c r="E943" s="18"/>
-      <c r="F943" s="18"/>
-      <c r="G943" s="18"/>
+      <c r="D943" s="19"/>
+      <c r="E943" s="16"/>
+      <c r="F943" s="16"/>
+      <c r="G943" s="16"/>
       <c r="H943" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I943" s="19"/>
-      <c r="J943" s="19"/>
+      <c r="I943" s="17"/>
+      <c r="J943" s="17"/>
       <c r="K943" s="10" t="s">
         <v>20</v>
       </c>
@@ -40985,17 +40952,17 @@
     </row>
     <row r="944" ht="18.0" customHeight="1">
       <c r="A944" s="6"/>
-      <c r="B944" s="16"/>
+      <c r="B944" s="15"/>
       <c r="C944" s="14"/>
-      <c r="D944" s="20"/>
-      <c r="E944" s="18"/>
-      <c r="F944" s="18"/>
-      <c r="G944" s="18"/>
+      <c r="D944" s="19"/>
+      <c r="E944" s="16"/>
+      <c r="F944" s="16"/>
+      <c r="G944" s="16"/>
       <c r="H944" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I944" s="19"/>
-      <c r="J944" s="19"/>
+      <c r="I944" s="17"/>
+      <c r="J944" s="17"/>
       <c r="K944" s="10" t="s">
         <v>20</v>
       </c>
@@ -41011,17 +40978,17 @@
     </row>
     <row r="945" ht="18.0" customHeight="1">
       <c r="A945" s="6"/>
-      <c r="B945" s="16"/>
+      <c r="B945" s="15"/>
       <c r="C945" s="14"/>
-      <c r="D945" s="20"/>
-      <c r="E945" s="18"/>
-      <c r="F945" s="18"/>
-      <c r="G945" s="18"/>
+      <c r="D945" s="19"/>
+      <c r="E945" s="16"/>
+      <c r="F945" s="16"/>
+      <c r="G945" s="16"/>
       <c r="H945" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I945" s="19"/>
-      <c r="J945" s="19"/>
+      <c r="I945" s="17"/>
+      <c r="J945" s="17"/>
       <c r="K945" s="10" t="s">
         <v>20</v>
       </c>
@@ -41037,17 +41004,17 @@
     </row>
     <row r="946" ht="18.0" customHeight="1">
       <c r="A946" s="6"/>
-      <c r="B946" s="16"/>
+      <c r="B946" s="15"/>
       <c r="C946" s="14"/>
-      <c r="D946" s="20"/>
-      <c r="E946" s="18"/>
-      <c r="F946" s="18"/>
-      <c r="G946" s="18"/>
+      <c r="D946" s="19"/>
+      <c r="E946" s="16"/>
+      <c r="F946" s="16"/>
+      <c r="G946" s="16"/>
       <c r="H946" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I946" s="19"/>
-      <c r="J946" s="19"/>
+      <c r="I946" s="17"/>
+      <c r="J946" s="17"/>
       <c r="K946" s="10" t="s">
         <v>20</v>
       </c>
@@ -41063,17 +41030,17 @@
     </row>
     <row r="947" ht="18.0" customHeight="1">
       <c r="A947" s="6"/>
-      <c r="B947" s="16"/>
+      <c r="B947" s="15"/>
       <c r="C947" s="14"/>
-      <c r="D947" s="20"/>
-      <c r="E947" s="18"/>
-      <c r="F947" s="18"/>
-      <c r="G947" s="18"/>
+      <c r="D947" s="19"/>
+      <c r="E947" s="16"/>
+      <c r="F947" s="16"/>
+      <c r="G947" s="16"/>
       <c r="H947" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I947" s="19"/>
-      <c r="J947" s="19"/>
+      <c r="I947" s="17"/>
+      <c r="J947" s="17"/>
       <c r="K947" s="10" t="s">
         <v>20</v>
       </c>
@@ -41089,17 +41056,17 @@
     </row>
     <row r="948" ht="18.0" customHeight="1">
       <c r="A948" s="6"/>
-      <c r="B948" s="16"/>
+      <c r="B948" s="15"/>
       <c r="C948" s="14"/>
-      <c r="D948" s="20"/>
-      <c r="E948" s="18"/>
-      <c r="F948" s="18"/>
-      <c r="G948" s="18"/>
+      <c r="D948" s="19"/>
+      <c r="E948" s="16"/>
+      <c r="F948" s="16"/>
+      <c r="G948" s="16"/>
       <c r="H948" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I948" s="19"/>
-      <c r="J948" s="19"/>
+      <c r="I948" s="17"/>
+      <c r="J948" s="17"/>
       <c r="K948" s="10" t="s">
         <v>20</v>
       </c>
@@ -41115,17 +41082,17 @@
     </row>
     <row r="949" ht="18.0" customHeight="1">
       <c r="A949" s="6"/>
-      <c r="B949" s="16"/>
+      <c r="B949" s="15"/>
       <c r="C949" s="14"/>
-      <c r="D949" s="20"/>
-      <c r="E949" s="18"/>
-      <c r="F949" s="18"/>
-      <c r="G949" s="18"/>
+      <c r="D949" s="19"/>
+      <c r="E949" s="16"/>
+      <c r="F949" s="16"/>
+      <c r="G949" s="16"/>
       <c r="H949" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I949" s="19"/>
-      <c r="J949" s="19"/>
+      <c r="I949" s="17"/>
+      <c r="J949" s="17"/>
       <c r="K949" s="10" t="s">
         <v>20</v>
       </c>
@@ -41141,17 +41108,17 @@
     </row>
     <row r="950" ht="18.0" customHeight="1">
       <c r="A950" s="6"/>
-      <c r="B950" s="16"/>
+      <c r="B950" s="15"/>
       <c r="C950" s="14"/>
-      <c r="D950" s="20"/>
-      <c r="E950" s="18"/>
-      <c r="F950" s="18"/>
-      <c r="G950" s="18"/>
+      <c r="D950" s="19"/>
+      <c r="E950" s="16"/>
+      <c r="F950" s="16"/>
+      <c r="G950" s="16"/>
       <c r="H950" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I950" s="19"/>
-      <c r="J950" s="19"/>
+      <c r="I950" s="17"/>
+      <c r="J950" s="17"/>
       <c r="K950" s="10" t="s">
         <v>20</v>
       </c>
@@ -41167,17 +41134,17 @@
     </row>
     <row r="951" ht="18.0" customHeight="1">
       <c r="A951" s="6"/>
-      <c r="B951" s="16"/>
+      <c r="B951" s="15"/>
       <c r="C951" s="14"/>
-      <c r="D951" s="20"/>
-      <c r="E951" s="18"/>
-      <c r="F951" s="18"/>
-      <c r="G951" s="18"/>
+      <c r="D951" s="19"/>
+      <c r="E951" s="16"/>
+      <c r="F951" s="16"/>
+      <c r="G951" s="16"/>
       <c r="H951" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I951" s="19"/>
-      <c r="J951" s="19"/>
+      <c r="I951" s="17"/>
+      <c r="J951" s="17"/>
       <c r="K951" s="10" t="s">
         <v>20</v>
       </c>
@@ -41193,17 +41160,17 @@
     </row>
     <row r="952" ht="18.0" customHeight="1">
       <c r="A952" s="6"/>
-      <c r="B952" s="16"/>
+      <c r="B952" s="15"/>
       <c r="C952" s="14"/>
-      <c r="D952" s="20"/>
-      <c r="E952" s="18"/>
-      <c r="F952" s="18"/>
-      <c r="G952" s="18"/>
+      <c r="D952" s="19"/>
+      <c r="E952" s="16"/>
+      <c r="F952" s="16"/>
+      <c r="G952" s="16"/>
       <c r="H952" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I952" s="19"/>
-      <c r="J952" s="19"/>
+      <c r="I952" s="17"/>
+      <c r="J952" s="17"/>
       <c r="K952" s="10" t="s">
         <v>20</v>
       </c>
@@ -41219,17 +41186,17 @@
     </row>
     <row r="953" ht="18.0" customHeight="1">
       <c r="A953" s="6"/>
-      <c r="B953" s="16"/>
+      <c r="B953" s="15"/>
       <c r="C953" s="14"/>
-      <c r="D953" s="20"/>
-      <c r="E953" s="18"/>
-      <c r="F953" s="18"/>
-      <c r="G953" s="18"/>
+      <c r="D953" s="19"/>
+      <c r="E953" s="16"/>
+      <c r="F953" s="16"/>
+      <c r="G953" s="16"/>
       <c r="H953" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I953" s="19"/>
-      <c r="J953" s="19"/>
+      <c r="I953" s="17"/>
+      <c r="J953" s="17"/>
       <c r="K953" s="10" t="s">
         <v>20</v>
       </c>
@@ -41245,17 +41212,17 @@
     </row>
     <row r="954" ht="18.0" customHeight="1">
       <c r="A954" s="6"/>
-      <c r="B954" s="16"/>
+      <c r="B954" s="15"/>
       <c r="C954" s="14"/>
-      <c r="D954" s="20"/>
-      <c r="E954" s="18"/>
-      <c r="F954" s="18"/>
-      <c r="G954" s="18"/>
+      <c r="D954" s="19"/>
+      <c r="E954" s="16"/>
+      <c r="F954" s="16"/>
+      <c r="G954" s="16"/>
       <c r="H954" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I954" s="19"/>
-      <c r="J954" s="19"/>
+      <c r="I954" s="17"/>
+      <c r="J954" s="17"/>
       <c r="K954" s="10" t="s">
         <v>20</v>
       </c>
@@ -41271,17 +41238,17 @@
     </row>
     <row r="955" ht="18.0" customHeight="1">
       <c r="A955" s="6"/>
-      <c r="B955" s="16"/>
+      <c r="B955" s="15"/>
       <c r="C955" s="14"/>
-      <c r="D955" s="20"/>
-      <c r="E955" s="18"/>
-      <c r="F955" s="18"/>
-      <c r="G955" s="18"/>
+      <c r="D955" s="19"/>
+      <c r="E955" s="16"/>
+      <c r="F955" s="16"/>
+      <c r="G955" s="16"/>
       <c r="H955" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I955" s="19"/>
-      <c r="J955" s="19"/>
+      <c r="I955" s="17"/>
+      <c r="J955" s="17"/>
       <c r="K955" s="10" t="s">
         <v>20</v>
       </c>
@@ -41297,17 +41264,17 @@
     </row>
     <row r="956" ht="18.0" customHeight="1">
       <c r="A956" s="6"/>
-      <c r="B956" s="16"/>
+      <c r="B956" s="15"/>
       <c r="C956" s="14"/>
-      <c r="D956" s="20"/>
-      <c r="E956" s="18"/>
-      <c r="F956" s="18"/>
-      <c r="G956" s="18"/>
+      <c r="D956" s="19"/>
+      <c r="E956" s="16"/>
+      <c r="F956" s="16"/>
+      <c r="G956" s="16"/>
       <c r="H956" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I956" s="19"/>
-      <c r="J956" s="19"/>
+      <c r="I956" s="17"/>
+      <c r="J956" s="17"/>
       <c r="K956" s="10" t="s">
         <v>20</v>
       </c>
@@ -41323,17 +41290,17 @@
     </row>
     <row r="957" ht="18.0" customHeight="1">
       <c r="A957" s="6"/>
-      <c r="B957" s="16"/>
+      <c r="B957" s="15"/>
       <c r="C957" s="14"/>
-      <c r="D957" s="20"/>
-      <c r="E957" s="18"/>
-      <c r="F957" s="18"/>
-      <c r="G957" s="18"/>
+      <c r="D957" s="19"/>
+      <c r="E957" s="16"/>
+      <c r="F957" s="16"/>
+      <c r="G957" s="16"/>
       <c r="H957" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I957" s="19"/>
-      <c r="J957" s="19"/>
+      <c r="I957" s="17"/>
+      <c r="J957" s="17"/>
       <c r="K957" s="10" t="s">
         <v>20</v>
       </c>
@@ -41349,17 +41316,17 @@
     </row>
     <row r="958" ht="18.0" customHeight="1">
       <c r="A958" s="6"/>
-      <c r="B958" s="16"/>
+      <c r="B958" s="15"/>
       <c r="C958" s="14"/>
-      <c r="D958" s="20"/>
-      <c r="E958" s="18"/>
-      <c r="F958" s="18"/>
-      <c r="G958" s="18"/>
+      <c r="D958" s="19"/>
+      <c r="E958" s="16"/>
+      <c r="F958" s="16"/>
+      <c r="G958" s="16"/>
       <c r="H958" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I958" s="19"/>
-      <c r="J958" s="19"/>
+      <c r="I958" s="17"/>
+      <c r="J958" s="17"/>
       <c r="K958" s="10" t="s">
         <v>20</v>
       </c>
@@ -41375,17 +41342,17 @@
     </row>
     <row r="959" ht="18.0" customHeight="1">
       <c r="A959" s="6"/>
-      <c r="B959" s="16"/>
+      <c r="B959" s="15"/>
       <c r="C959" s="14"/>
-      <c r="D959" s="20"/>
-      <c r="E959" s="18"/>
-      <c r="F959" s="18"/>
-      <c r="G959" s="18"/>
+      <c r="D959" s="19"/>
+      <c r="E959" s="16"/>
+      <c r="F959" s="16"/>
+      <c r="G959" s="16"/>
       <c r="H959" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I959" s="19"/>
-      <c r="J959" s="19"/>
+      <c r="I959" s="17"/>
+      <c r="J959" s="17"/>
       <c r="K959" s="10" t="s">
         <v>20</v>
       </c>
@@ -41401,17 +41368,17 @@
     </row>
     <row r="960" ht="18.0" customHeight="1">
       <c r="A960" s="6"/>
-      <c r="B960" s="16"/>
+      <c r="B960" s="15"/>
       <c r="C960" s="14"/>
-      <c r="D960" s="20"/>
-      <c r="E960" s="18"/>
-      <c r="F960" s="18"/>
-      <c r="G960" s="18"/>
+      <c r="D960" s="19"/>
+      <c r="E960" s="16"/>
+      <c r="F960" s="16"/>
+      <c r="G960" s="16"/>
       <c r="H960" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I960" s="19"/>
-      <c r="J960" s="19"/>
+      <c r="I960" s="17"/>
+      <c r="J960" s="17"/>
       <c r="K960" s="10" t="s">
         <v>20</v>
       </c>
@@ -41427,17 +41394,17 @@
     </row>
     <row r="961" ht="18.0" customHeight="1">
       <c r="A961" s="6"/>
-      <c r="B961" s="16"/>
+      <c r="B961" s="15"/>
       <c r="C961" s="14"/>
-      <c r="D961" s="20"/>
-      <c r="E961" s="18"/>
-      <c r="F961" s="18"/>
-      <c r="G961" s="18"/>
+      <c r="D961" s="19"/>
+      <c r="E961" s="16"/>
+      <c r="F961" s="16"/>
+      <c r="G961" s="16"/>
       <c r="H961" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I961" s="19"/>
-      <c r="J961" s="19"/>
+      <c r="I961" s="17"/>
+      <c r="J961" s="17"/>
       <c r="K961" s="10" t="s">
         <v>20</v>
       </c>
@@ -41453,17 +41420,17 @@
     </row>
     <row r="962" ht="18.0" customHeight="1">
       <c r="A962" s="6"/>
-      <c r="B962" s="16"/>
+      <c r="B962" s="15"/>
       <c r="C962" s="14"/>
-      <c r="D962" s="20"/>
-      <c r="E962" s="18"/>
-      <c r="F962" s="18"/>
-      <c r="G962" s="18"/>
+      <c r="D962" s="19"/>
+      <c r="E962" s="16"/>
+      <c r="F962" s="16"/>
+      <c r="G962" s="16"/>
       <c r="H962" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I962" s="19"/>
-      <c r="J962" s="19"/>
+      <c r="I962" s="17"/>
+      <c r="J962" s="17"/>
       <c r="K962" s="10" t="s">
         <v>20</v>
       </c>
@@ -41479,17 +41446,17 @@
     </row>
     <row r="963" ht="18.0" customHeight="1">
       <c r="A963" s="6"/>
-      <c r="B963" s="16"/>
+      <c r="B963" s="15"/>
       <c r="C963" s="14"/>
-      <c r="D963" s="20"/>
-      <c r="E963" s="18"/>
-      <c r="F963" s="18"/>
-      <c r="G963" s="18"/>
+      <c r="D963" s="19"/>
+      <c r="E963" s="16"/>
+      <c r="F963" s="16"/>
+      <c r="G963" s="16"/>
       <c r="H963" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I963" s="19"/>
-      <c r="J963" s="19"/>
+      <c r="I963" s="17"/>
+      <c r="J963" s="17"/>
       <c r="K963" s="10" t="s">
         <v>20</v>
       </c>
@@ -41505,17 +41472,17 @@
     </row>
     <row r="964" ht="18.0" customHeight="1">
       <c r="A964" s="6"/>
-      <c r="B964" s="16"/>
+      <c r="B964" s="15"/>
       <c r="C964" s="14"/>
-      <c r="D964" s="20"/>
-      <c r="E964" s="18"/>
-      <c r="F964" s="18"/>
-      <c r="G964" s="18"/>
+      <c r="D964" s="19"/>
+      <c r="E964" s="16"/>
+      <c r="F964" s="16"/>
+      <c r="G964" s="16"/>
       <c r="H964" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I964" s="19"/>
-      <c r="J964" s="19"/>
+      <c r="I964" s="17"/>
+      <c r="J964" s="17"/>
       <c r="K964" s="10" t="s">
         <v>20</v>
       </c>
@@ -41531,17 +41498,17 @@
     </row>
     <row r="965" ht="18.0" customHeight="1">
       <c r="A965" s="6"/>
-      <c r="B965" s="16"/>
+      <c r="B965" s="15"/>
       <c r="C965" s="14"/>
-      <c r="D965" s="20"/>
-      <c r="E965" s="18"/>
-      <c r="F965" s="18"/>
-      <c r="G965" s="18"/>
+      <c r="D965" s="19"/>
+      <c r="E965" s="16"/>
+      <c r="F965" s="16"/>
+      <c r="G965" s="16"/>
       <c r="H965" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I965" s="19"/>
-      <c r="J965" s="19"/>
+      <c r="I965" s="17"/>
+      <c r="J965" s="17"/>
       <c r="K965" s="10" t="s">
         <v>20</v>
       </c>
@@ -41557,17 +41524,17 @@
     </row>
     <row r="966" ht="18.0" customHeight="1">
       <c r="A966" s="6"/>
-      <c r="B966" s="16"/>
+      <c r="B966" s="15"/>
       <c r="C966" s="14"/>
-      <c r="D966" s="20"/>
-      <c r="E966" s="18"/>
-      <c r="F966" s="18"/>
-      <c r="G966" s="18"/>
+      <c r="D966" s="19"/>
+      <c r="E966" s="16"/>
+      <c r="F966" s="16"/>
+      <c r="G966" s="16"/>
       <c r="H966" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I966" s="19"/>
-      <c r="J966" s="19"/>
+      <c r="I966" s="17"/>
+      <c r="J966" s="17"/>
       <c r="K966" s="10" t="s">
         <v>20</v>
       </c>
@@ -41583,17 +41550,17 @@
     </row>
     <row r="967" ht="18.0" customHeight="1">
       <c r="A967" s="6"/>
-      <c r="B967" s="16"/>
+      <c r="B967" s="15"/>
       <c r="C967" s="14"/>
-      <c r="D967" s="20"/>
-      <c r="E967" s="18"/>
-      <c r="F967" s="18"/>
-      <c r="G967" s="18"/>
+      <c r="D967" s="19"/>
+      <c r="E967" s="16"/>
+      <c r="F967" s="16"/>
+      <c r="G967" s="16"/>
       <c r="H967" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I967" s="19"/>
-      <c r="J967" s="19"/>
+      <c r="I967" s="17"/>
+      <c r="J967" s="17"/>
       <c r="K967" s="10" t="s">
         <v>20</v>
       </c>
@@ -41609,17 +41576,17 @@
     </row>
     <row r="968" ht="18.0" customHeight="1">
       <c r="A968" s="6"/>
-      <c r="B968" s="16"/>
+      <c r="B968" s="15"/>
       <c r="C968" s="14"/>
-      <c r="D968" s="20"/>
-      <c r="E968" s="18"/>
-      <c r="F968" s="18"/>
-      <c r="G968" s="18"/>
+      <c r="D968" s="19"/>
+      <c r="E968" s="16"/>
+      <c r="F968" s="16"/>
+      <c r="G968" s="16"/>
       <c r="H968" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I968" s="19"/>
-      <c r="J968" s="19"/>
+      <c r="I968" s="17"/>
+      <c r="J968" s="17"/>
       <c r="K968" s="10" t="s">
         <v>20</v>
       </c>
@@ -41635,17 +41602,17 @@
     </row>
     <row r="969" ht="18.0" customHeight="1">
       <c r="A969" s="6"/>
-      <c r="B969" s="16"/>
+      <c r="B969" s="15"/>
       <c r="C969" s="14"/>
-      <c r="D969" s="20"/>
-      <c r="E969" s="18"/>
-      <c r="F969" s="18"/>
-      <c r="G969" s="18"/>
+      <c r="D969" s="19"/>
+      <c r="E969" s="16"/>
+      <c r="F969" s="16"/>
+      <c r="G969" s="16"/>
       <c r="H969" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I969" s="19"/>
-      <c r="J969" s="19"/>
+      <c r="I969" s="17"/>
+      <c r="J969" s="17"/>
       <c r="K969" s="10" t="s">
         <v>20</v>
       </c>
@@ -41661,17 +41628,17 @@
     </row>
     <row r="970" ht="18.0" customHeight="1">
       <c r="A970" s="6"/>
-      <c r="B970" s="16"/>
+      <c r="B970" s="15"/>
       <c r="C970" s="14"/>
-      <c r="D970" s="20"/>
-      <c r="E970" s="18"/>
-      <c r="F970" s="18"/>
-      <c r="G970" s="18"/>
+      <c r="D970" s="19"/>
+      <c r="E970" s="16"/>
+      <c r="F970" s="16"/>
+      <c r="G970" s="16"/>
       <c r="H970" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I970" s="19"/>
-      <c r="J970" s="19"/>
+      <c r="I970" s="17"/>
+      <c r="J970" s="17"/>
       <c r="K970" s="10" t="s">
         <v>20</v>
       </c>
@@ -41687,17 +41654,17 @@
     </row>
     <row r="971" ht="18.0" customHeight="1">
       <c r="A971" s="6"/>
-      <c r="B971" s="16"/>
+      <c r="B971" s="15"/>
       <c r="C971" s="14"/>
-      <c r="D971" s="20"/>
-      <c r="E971" s="18"/>
-      <c r="F971" s="18"/>
-      <c r="G971" s="18"/>
+      <c r="D971" s="19"/>
+      <c r="E971" s="16"/>
+      <c r="F971" s="16"/>
+      <c r="G971" s="16"/>
       <c r="H971" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I971" s="19"/>
-      <c r="J971" s="19"/>
+      <c r="I971" s="17"/>
+      <c r="J971" s="17"/>
       <c r="K971" s="10" t="s">
         <v>20</v>
       </c>
@@ -41713,17 +41680,17 @@
     </row>
     <row r="972" ht="18.0" customHeight="1">
       <c r="A972" s="6"/>
-      <c r="B972" s="16"/>
+      <c r="B972" s="15"/>
       <c r="C972" s="14"/>
-      <c r="D972" s="20"/>
-      <c r="E972" s="18"/>
-      <c r="F972" s="18"/>
-      <c r="G972" s="18"/>
+      <c r="D972" s="19"/>
+      <c r="E972" s="16"/>
+      <c r="F972" s="16"/>
+      <c r="G972" s="16"/>
       <c r="H972" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I972" s="19"/>
-      <c r="J972" s="19"/>
+      <c r="I972" s="17"/>
+      <c r="J972" s="17"/>
       <c r="K972" s="10" t="s">
         <v>20</v>
       </c>
@@ -41739,17 +41706,17 @@
     </row>
     <row r="973" ht="18.0" customHeight="1">
       <c r="A973" s="6"/>
-      <c r="B973" s="16"/>
+      <c r="B973" s="15"/>
       <c r="C973" s="14"/>
-      <c r="D973" s="20"/>
-      <c r="E973" s="18"/>
-      <c r="F973" s="18"/>
-      <c r="G973" s="18"/>
+      <c r="D973" s="19"/>
+      <c r="E973" s="16"/>
+      <c r="F973" s="16"/>
+      <c r="G973" s="16"/>
       <c r="H973" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I973" s="19"/>
-      <c r="J973" s="19"/>
+      <c r="I973" s="17"/>
+      <c r="J973" s="17"/>
       <c r="K973" s="10" t="s">
         <v>20</v>
       </c>
@@ -41765,17 +41732,17 @@
     </row>
     <row r="974" ht="18.0" customHeight="1">
       <c r="A974" s="6"/>
-      <c r="B974" s="16"/>
+      <c r="B974" s="15"/>
       <c r="C974" s="14"/>
-      <c r="D974" s="20"/>
-      <c r="E974" s="18"/>
-      <c r="F974" s="18"/>
-      <c r="G974" s="18"/>
+      <c r="D974" s="19"/>
+      <c r="E974" s="16"/>
+      <c r="F974" s="16"/>
+      <c r="G974" s="16"/>
       <c r="H974" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I974" s="19"/>
-      <c r="J974" s="19"/>
+      <c r="I974" s="17"/>
+      <c r="J974" s="17"/>
       <c r="K974" s="10" t="s">
         <v>20</v>
       </c>
@@ -41791,17 +41758,17 @@
     </row>
     <row r="975" ht="18.0" customHeight="1">
       <c r="A975" s="6"/>
-      <c r="B975" s="16"/>
+      <c r="B975" s="15"/>
       <c r="C975" s="14"/>
-      <c r="D975" s="20"/>
-      <c r="E975" s="18"/>
-      <c r="F975" s="18"/>
-      <c r="G975" s="18"/>
+      <c r="D975" s="19"/>
+      <c r="E975" s="16"/>
+      <c r="F975" s="16"/>
+      <c r="G975" s="16"/>
       <c r="H975" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I975" s="19"/>
-      <c r="J975" s="19"/>
+      <c r="I975" s="17"/>
+      <c r="J975" s="17"/>
       <c r="K975" s="10" t="s">
         <v>20</v>
       </c>
@@ -41817,17 +41784,17 @@
     </row>
     <row r="976" ht="18.0" customHeight="1">
       <c r="A976" s="6"/>
-      <c r="B976" s="16"/>
+      <c r="B976" s="15"/>
       <c r="C976" s="14"/>
-      <c r="D976" s="20"/>
-      <c r="E976" s="18"/>
-      <c r="F976" s="18"/>
-      <c r="G976" s="18"/>
+      <c r="D976" s="19"/>
+      <c r="E976" s="16"/>
+      <c r="F976" s="16"/>
+      <c r="G976" s="16"/>
       <c r="H976" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I976" s="19"/>
-      <c r="J976" s="19"/>
+      <c r="I976" s="17"/>
+      <c r="J976" s="17"/>
       <c r="K976" s="10" t="s">
         <v>20</v>
       </c>
@@ -41843,17 +41810,17 @@
     </row>
     <row r="977" ht="18.0" customHeight="1">
       <c r="A977" s="6"/>
-      <c r="B977" s="16"/>
+      <c r="B977" s="15"/>
       <c r="C977" s="14"/>
-      <c r="D977" s="20"/>
-      <c r="E977" s="18"/>
-      <c r="F977" s="18"/>
-      <c r="G977" s="18"/>
+      <c r="D977" s="19"/>
+      <c r="E977" s="16"/>
+      <c r="F977" s="16"/>
+      <c r="G977" s="16"/>
       <c r="H977" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I977" s="19"/>
-      <c r="J977" s="19"/>
+      <c r="I977" s="17"/>
+      <c r="J977" s="17"/>
       <c r="K977" s="10" t="s">
         <v>20</v>
       </c>
@@ -41869,17 +41836,17 @@
     </row>
     <row r="978" ht="18.0" customHeight="1">
       <c r="A978" s="6"/>
-      <c r="B978" s="16"/>
+      <c r="B978" s="15"/>
       <c r="C978" s="14"/>
-      <c r="D978" s="20"/>
-      <c r="E978" s="18"/>
-      <c r="F978" s="18"/>
-      <c r="G978" s="18"/>
+      <c r="D978" s="19"/>
+      <c r="E978" s="16"/>
+      <c r="F978" s="16"/>
+      <c r="G978" s="16"/>
       <c r="H978" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I978" s="19"/>
-      <c r="J978" s="19"/>
+      <c r="I978" s="17"/>
+      <c r="J978" s="17"/>
       <c r="K978" s="10" t="s">
         <v>20</v>
       </c>
@@ -41895,17 +41862,17 @@
     </row>
     <row r="979" ht="18.0" customHeight="1">
       <c r="A979" s="6"/>
-      <c r="B979" s="16"/>
+      <c r="B979" s="15"/>
       <c r="C979" s="14"/>
-      <c r="D979" s="20"/>
-      <c r="E979" s="18"/>
-      <c r="F979" s="18"/>
-      <c r="G979" s="18"/>
+      <c r="D979" s="19"/>
+      <c r="E979" s="16"/>
+      <c r="F979" s="16"/>
+      <c r="G979" s="16"/>
       <c r="H979" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I979" s="19"/>
-      <c r="J979" s="19"/>
+      <c r="I979" s="17"/>
+      <c r="J979" s="17"/>
       <c r="K979" s="10" t="s">
         <v>20</v>
       </c>
@@ -41921,17 +41888,17 @@
     </row>
     <row r="980" ht="18.0" customHeight="1">
       <c r="A980" s="6"/>
-      <c r="B980" s="16"/>
+      <c r="B980" s="15"/>
       <c r="C980" s="14"/>
-      <c r="D980" s="20"/>
-      <c r="E980" s="18"/>
-      <c r="F980" s="18"/>
-      <c r="G980" s="18"/>
+      <c r="D980" s="19"/>
+      <c r="E980" s="16"/>
+      <c r="F980" s="16"/>
+      <c r="G980" s="16"/>
       <c r="H980" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I980" s="19"/>
-      <c r="J980" s="19"/>
+      <c r="I980" s="17"/>
+      <c r="J980" s="17"/>
       <c r="K980" s="10" t="s">
         <v>20</v>
       </c>
@@ -41947,17 +41914,17 @@
     </row>
     <row r="981" ht="18.0" customHeight="1">
       <c r="A981" s="6"/>
-      <c r="B981" s="16"/>
+      <c r="B981" s="15"/>
       <c r="C981" s="14"/>
-      <c r="D981" s="20"/>
-      <c r="E981" s="18"/>
-      <c r="F981" s="18"/>
-      <c r="G981" s="18"/>
+      <c r="D981" s="19"/>
+      <c r="E981" s="16"/>
+      <c r="F981" s="16"/>
+      <c r="G981" s="16"/>
       <c r="H981" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I981" s="19"/>
-      <c r="J981" s="19"/>
+      <c r="I981" s="17"/>
+      <c r="J981" s="17"/>
       <c r="K981" s="10" t="s">
         <v>20</v>
       </c>
@@ -41973,17 +41940,17 @@
     </row>
     <row r="982" ht="18.0" customHeight="1">
       <c r="A982" s="6"/>
-      <c r="B982" s="16"/>
+      <c r="B982" s="15"/>
       <c r="C982" s="14"/>
-      <c r="D982" s="20"/>
-      <c r="E982" s="18"/>
-      <c r="F982" s="18"/>
-      <c r="G982" s="18"/>
+      <c r="D982" s="19"/>
+      <c r="E982" s="16"/>
+      <c r="F982" s="16"/>
+      <c r="G982" s="16"/>
       <c r="H982" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I982" s="19"/>
-      <c r="J982" s="19"/>
+      <c r="I982" s="17"/>
+      <c r="J982" s="17"/>
       <c r="K982" s="10" t="s">
         <v>20</v>
       </c>
@@ -41999,17 +41966,17 @@
     </row>
     <row r="983" ht="18.0" customHeight="1">
       <c r="A983" s="6"/>
-      <c r="B983" s="16"/>
+      <c r="B983" s="15"/>
       <c r="C983" s="14"/>
-      <c r="D983" s="20"/>
-      <c r="E983" s="18"/>
-      <c r="F983" s="18"/>
-      <c r="G983" s="18"/>
+      <c r="D983" s="19"/>
+      <c r="E983" s="16"/>
+      <c r="F983" s="16"/>
+      <c r="G983" s="16"/>
       <c r="H983" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I983" s="19"/>
-      <c r="J983" s="19"/>
+      <c r="I983" s="17"/>
+      <c r="J983" s="17"/>
       <c r="K983" s="10" t="s">
         <v>20</v>
       </c>
@@ -42025,17 +41992,17 @@
     </row>
     <row r="984" ht="18.0" customHeight="1">
       <c r="A984" s="6"/>
-      <c r="B984" s="16"/>
+      <c r="B984" s="15"/>
       <c r="C984" s="14"/>
-      <c r="D984" s="20"/>
-      <c r="E984" s="18"/>
-      <c r="F984" s="18"/>
-      <c r="G984" s="18"/>
+      <c r="D984" s="19"/>
+      <c r="E984" s="16"/>
+      <c r="F984" s="16"/>
+      <c r="G984" s="16"/>
       <c r="H984" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I984" s="19"/>
-      <c r="J984" s="19"/>
+      <c r="I984" s="17"/>
+      <c r="J984" s="17"/>
       <c r="K984" s="10" t="s">
         <v>20</v>
       </c>
@@ -42051,17 +42018,17 @@
     </row>
     <row r="985" ht="18.0" customHeight="1">
       <c r="A985" s="6"/>
-      <c r="B985" s="16"/>
+      <c r="B985" s="15"/>
       <c r="C985" s="14"/>
-      <c r="D985" s="20"/>
-      <c r="E985" s="18"/>
-      <c r="F985" s="18"/>
-      <c r="G985" s="18"/>
+      <c r="D985" s="19"/>
+      <c r="E985" s="16"/>
+      <c r="F985" s="16"/>
+      <c r="G985" s="16"/>
       <c r="H985" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I985" s="19"/>
-      <c r="J985" s="19"/>
+      <c r="I985" s="17"/>
+      <c r="J985" s="17"/>
       <c r="K985" s="10" t="s">
         <v>20</v>
       </c>
@@ -42077,17 +42044,17 @@
     </row>
     <row r="986" ht="18.0" customHeight="1">
       <c r="A986" s="6"/>
-      <c r="B986" s="16"/>
+      <c r="B986" s="15"/>
       <c r="C986" s="14"/>
-      <c r="D986" s="20"/>
-      <c r="E986" s="18"/>
-      <c r="F986" s="18"/>
-      <c r="G986" s="18"/>
+      <c r="D986" s="19"/>
+      <c r="E986" s="16"/>
+      <c r="F986" s="16"/>
+      <c r="G986" s="16"/>
       <c r="H986" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I986" s="19"/>
-      <c r="J986" s="19"/>
+      <c r="I986" s="17"/>
+      <c r="J986" s="17"/>
       <c r="K986" s="10" t="s">
         <v>20</v>
       </c>
@@ -42103,17 +42070,17 @@
     </row>
     <row r="987" ht="18.0" customHeight="1">
       <c r="A987" s="6"/>
-      <c r="B987" s="16"/>
+      <c r="B987" s="15"/>
       <c r="C987" s="14"/>
-      <c r="D987" s="20"/>
-      <c r="E987" s="18"/>
-      <c r="F987" s="18"/>
-      <c r="G987" s="18"/>
+      <c r="D987" s="19"/>
+      <c r="E987" s="16"/>
+      <c r="F987" s="16"/>
+      <c r="G987" s="16"/>
       <c r="H987" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I987" s="19"/>
-      <c r="J987" s="19"/>
+      <c r="I987" s="17"/>
+      <c r="J987" s="17"/>
       <c r="K987" s="10" t="s">
         <v>20</v>
       </c>
@@ -42129,17 +42096,17 @@
     </row>
     <row r="988" ht="18.0" customHeight="1">
       <c r="A988" s="6"/>
-      <c r="B988" s="16"/>
+      <c r="B988" s="15"/>
       <c r="C988" s="14"/>
-      <c r="D988" s="20"/>
-      <c r="E988" s="18"/>
-      <c r="F988" s="18"/>
-      <c r="G988" s="18"/>
+      <c r="D988" s="19"/>
+      <c r="E988" s="16"/>
+      <c r="F988" s="16"/>
+      <c r="G988" s="16"/>
       <c r="H988" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I988" s="19"/>
-      <c r="J988" s="19"/>
+      <c r="I988" s="17"/>
+      <c r="J988" s="17"/>
       <c r="K988" s="10" t="s">
         <v>20</v>
       </c>
@@ -42155,17 +42122,17 @@
     </row>
     <row r="989" ht="18.0" customHeight="1">
       <c r="A989" s="6"/>
-      <c r="B989" s="16"/>
+      <c r="B989" s="15"/>
       <c r="C989" s="14"/>
-      <c r="D989" s="20"/>
-      <c r="E989" s="18"/>
-      <c r="F989" s="18"/>
-      <c r="G989" s="18"/>
+      <c r="D989" s="19"/>
+      <c r="E989" s="16"/>
+      <c r="F989" s="16"/>
+      <c r="G989" s="16"/>
       <c r="H989" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I989" s="19"/>
-      <c r="J989" s="19"/>
+      <c r="I989" s="17"/>
+      <c r="J989" s="17"/>
       <c r="K989" s="10" t="s">
         <v>20</v>
       </c>
@@ -42181,17 +42148,17 @@
     </row>
     <row r="990" ht="18.0" customHeight="1">
       <c r="A990" s="6"/>
-      <c r="B990" s="16"/>
+      <c r="B990" s="15"/>
       <c r="C990" s="14"/>
-      <c r="D990" s="20"/>
-      <c r="E990" s="18"/>
-      <c r="F990" s="18"/>
-      <c r="G990" s="18"/>
+      <c r="D990" s="19"/>
+      <c r="E990" s="16"/>
+      <c r="F990" s="16"/>
+      <c r="G990" s="16"/>
       <c r="H990" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I990" s="19"/>
-      <c r="J990" s="19"/>
+      <c r="I990" s="17"/>
+      <c r="J990" s="17"/>
       <c r="K990" s="10" t="s">
         <v>20</v>
       </c>
@@ -42207,17 +42174,17 @@
     </row>
     <row r="991" ht="18.0" customHeight="1">
       <c r="A991" s="6"/>
-      <c r="B991" s="16"/>
+      <c r="B991" s="15"/>
       <c r="C991" s="14"/>
-      <c r="D991" s="20"/>
-      <c r="E991" s="18"/>
-      <c r="F991" s="18"/>
-      <c r="G991" s="18"/>
+      <c r="D991" s="19"/>
+      <c r="E991" s="16"/>
+      <c r="F991" s="16"/>
+      <c r="G991" s="16"/>
       <c r="H991" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I991" s="19"/>
-      <c r="J991" s="19"/>
+      <c r="I991" s="17"/>
+      <c r="J991" s="17"/>
       <c r="K991" s="10" t="s">
         <v>20</v>
       </c>
@@ -42233,17 +42200,17 @@
     </row>
     <row r="992" ht="18.0" customHeight="1">
       <c r="A992" s="6"/>
-      <c r="B992" s="16"/>
+      <c r="B992" s="15"/>
       <c r="C992" s="14"/>
-      <c r="D992" s="20"/>
-      <c r="E992" s="18"/>
-      <c r="F992" s="18"/>
-      <c r="G992" s="18"/>
+      <c r="D992" s="19"/>
+      <c r="E992" s="16"/>
+      <c r="F992" s="16"/>
+      <c r="G992" s="16"/>
       <c r="H992" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I992" s="19"/>
-      <c r="J992" s="19"/>
+      <c r="I992" s="17"/>
+      <c r="J992" s="17"/>
       <c r="K992" s="10" t="s">
         <v>20</v>
       </c>
@@ -42259,17 +42226,17 @@
     </row>
     <row r="993" ht="18.0" customHeight="1">
       <c r="A993" s="6"/>
-      <c r="B993" s="16"/>
+      <c r="B993" s="15"/>
       <c r="C993" s="14"/>
-      <c r="D993" s="20"/>
-      <c r="E993" s="18"/>
-      <c r="F993" s="18"/>
-      <c r="G993" s="18"/>
+      <c r="D993" s="19"/>
+      <c r="E993" s="16"/>
+      <c r="F993" s="16"/>
+      <c r="G993" s="16"/>
       <c r="H993" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I993" s="19"/>
-      <c r="J993" s="19"/>
+      <c r="I993" s="17"/>
+      <c r="J993" s="17"/>
       <c r="K993" s="10" t="s">
         <v>20</v>
       </c>
@@ -42285,17 +42252,17 @@
     </row>
     <row r="994" ht="18.0" customHeight="1">
       <c r="A994" s="6"/>
-      <c r="B994" s="16"/>
+      <c r="B994" s="15"/>
       <c r="C994" s="14"/>
-      <c r="D994" s="20"/>
-      <c r="E994" s="18"/>
-      <c r="F994" s="18"/>
-      <c r="G994" s="18"/>
+      <c r="D994" s="19"/>
+      <c r="E994" s="16"/>
+      <c r="F994" s="16"/>
+      <c r="G994" s="16"/>
       <c r="H994" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I994" s="19"/>
-      <c r="J994" s="19"/>
+      <c r="I994" s="17"/>
+      <c r="J994" s="17"/>
       <c r="K994" s="10" t="s">
         <v>20</v>
       </c>
@@ -42311,17 +42278,17 @@
     </row>
     <row r="995" ht="18.0" customHeight="1">
       <c r="A995" s="6"/>
-      <c r="B995" s="16"/>
+      <c r="B995" s="15"/>
       <c r="C995" s="14"/>
-      <c r="D995" s="20"/>
-      <c r="E995" s="18"/>
-      <c r="F995" s="18"/>
-      <c r="G995" s="18"/>
+      <c r="D995" s="19"/>
+      <c r="E995" s="16"/>
+      <c r="F995" s="16"/>
+      <c r="G995" s="16"/>
       <c r="H995" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I995" s="19"/>
-      <c r="J995" s="19"/>
+      <c r="I995" s="17"/>
+      <c r="J995" s="17"/>
       <c r="K995" s="10" t="s">
         <v>20</v>
       </c>
@@ -42337,17 +42304,17 @@
     </row>
     <row r="996" ht="18.0" customHeight="1">
       <c r="A996" s="6"/>
-      <c r="B996" s="16"/>
+      <c r="B996" s="15"/>
       <c r="C996" s="14"/>
-      <c r="D996" s="20"/>
-      <c r="E996" s="18"/>
-      <c r="F996" s="18"/>
-      <c r="G996" s="18"/>
+      <c r="D996" s="19"/>
+      <c r="E996" s="16"/>
+      <c r="F996" s="16"/>
+      <c r="G996" s="16"/>
       <c r="H996" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I996" s="19"/>
-      <c r="J996" s="19"/>
+      <c r="I996" s="17"/>
+      <c r="J996" s="17"/>
       <c r="K996" s="10" t="s">
         <v>20</v>
       </c>
@@ -42363,17 +42330,17 @@
     </row>
     <row r="997" ht="18.0" customHeight="1">
       <c r="A997" s="6"/>
-      <c r="B997" s="16"/>
+      <c r="B997" s="15"/>
       <c r="C997" s="14"/>
-      <c r="D997" s="20"/>
-      <c r="E997" s="18"/>
-      <c r="F997" s="18"/>
-      <c r="G997" s="18"/>
+      <c r="D997" s="19"/>
+      <c r="E997" s="16"/>
+      <c r="F997" s="16"/>
+      <c r="G997" s="16"/>
       <c r="H997" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I997" s="19"/>
-      <c r="J997" s="19"/>
+      <c r="I997" s="17"/>
+      <c r="J997" s="17"/>
       <c r="K997" s="10" t="s">
         <v>20</v>
       </c>
@@ -42389,17 +42356,17 @@
     </row>
     <row r="998" ht="18.0" customHeight="1">
       <c r="A998" s="6"/>
-      <c r="B998" s="16"/>
+      <c r="B998" s="15"/>
       <c r="C998" s="14"/>
-      <c r="D998" s="20"/>
-      <c r="E998" s="18"/>
-      <c r="F998" s="18"/>
-      <c r="G998" s="18"/>
+      <c r="D998" s="19"/>
+      <c r="E998" s="16"/>
+      <c r="F998" s="16"/>
+      <c r="G998" s="16"/>
       <c r="H998" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I998" s="19"/>
-      <c r="J998" s="19"/>
+      <c r="I998" s="17"/>
+      <c r="J998" s="17"/>
       <c r="K998" s="10" t="s">
         <v>20</v>
       </c>
@@ -42415,17 +42382,17 @@
     </row>
     <row r="999" ht="18.0" customHeight="1">
       <c r="A999" s="6"/>
-      <c r="B999" s="16"/>
+      <c r="B999" s="15"/>
       <c r="C999" s="14"/>
-      <c r="D999" s="20"/>
-      <c r="E999" s="18"/>
-      <c r="F999" s="18"/>
-      <c r="G999" s="18"/>
+      <c r="D999" s="19"/>
+      <c r="E999" s="16"/>
+      <c r="F999" s="16"/>
+      <c r="G999" s="16"/>
       <c r="H999" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I999" s="19"/>
-      <c r="J999" s="19"/>
+      <c r="I999" s="17"/>
+      <c r="J999" s="17"/>
       <c r="K999" s="10" t="s">
         <v>20</v>
       </c>
@@ -42441,17 +42408,17 @@
     </row>
     <row r="1000" ht="18.0" customHeight="1">
       <c r="A1000" s="6"/>
-      <c r="B1000" s="16"/>
+      <c r="B1000" s="15"/>
       <c r="C1000" s="14"/>
-      <c r="D1000" s="20"/>
-      <c r="E1000" s="18"/>
-      <c r="F1000" s="18"/>
-      <c r="G1000" s="18"/>
+      <c r="D1000" s="19"/>
+      <c r="E1000" s="16"/>
+      <c r="F1000" s="16"/>
+      <c r="G1000" s="16"/>
       <c r="H1000" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I1000" s="19"/>
-      <c r="J1000" s="19"/>
+      <c r="I1000" s="17"/>
+      <c r="J1000" s="17"/>
       <c r="K1000" s="10" t="s">
         <v>20</v>
       </c>

--- a/data/leaves.xlsx
+++ b/data/leaves.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7299" uniqueCount="1207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7304" uniqueCount="1211">
   <si>
     <t>leave_id</t>
   </si>
@@ -3632,6 +3632,18 @@
   </si>
   <si>
     <t>LV-685</t>
+  </si>
+  <si>
+    <t>LV-686</t>
+  </si>
+  <si>
+    <t>محمد صبحي أحمد</t>
+  </si>
+  <si>
+    <t>MOHAMMED SUBHY AHMED</t>
+  </si>
+  <si>
+    <t>-</t>
   </si>
 </sst>
 </file>
@@ -3708,7 +3720,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -3754,7 +3766,13 @@
     <xf borderId="0" fillId="0" fontId="4" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -3762,9 +3780,6 @@
     </xf>
     <xf borderId="0" fillId="3" fontId="4" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" readingOrder="1" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
@@ -34139,18 +34154,36 @@
       <c r="R681" s="7"/>
     </row>
     <row r="682" ht="18.0" customHeight="1">
-      <c r="A682" s="6"/>
-      <c r="B682" s="15"/>
-      <c r="C682" s="14"/>
-      <c r="D682" s="9"/>
-      <c r="E682" s="16"/>
-      <c r="F682" s="16"/>
-      <c r="G682" s="16"/>
+      <c r="A682" s="6" t="s">
+        <v>1207</v>
+      </c>
+      <c r="B682" s="8">
+        <v>28798.0</v>
+      </c>
+      <c r="C682" s="14">
+        <v>28798.0</v>
+      </c>
+      <c r="D682" s="9" t="s">
+        <v>1208</v>
+      </c>
+      <c r="E682" s="15" t="s">
+        <v>1209</v>
+      </c>
+      <c r="F682" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="G682" s="15" t="s">
+        <v>1210</v>
+      </c>
       <c r="H682" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I682" s="17"/>
-      <c r="J682" s="17"/>
+      <c r="I682" s="11">
+        <v>46235.0</v>
+      </c>
+      <c r="J682" s="11">
+        <v>46265.0</v>
+      </c>
       <c r="K682" s="10" t="s">
         <v>20</v>
       </c>
@@ -34166,17 +34199,17 @@
     </row>
     <row r="683" ht="18.0" customHeight="1">
       <c r="A683" s="6"/>
-      <c r="B683" s="15"/>
+      <c r="B683" s="16"/>
       <c r="C683" s="14"/>
-      <c r="D683" s="18"/>
-      <c r="E683" s="16"/>
-      <c r="F683" s="16"/>
-      <c r="G683" s="16"/>
+      <c r="D683" s="17"/>
+      <c r="E683" s="18"/>
+      <c r="F683" s="18"/>
+      <c r="G683" s="18"/>
       <c r="H683" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I683" s="17"/>
-      <c r="J683" s="17"/>
+      <c r="I683" s="19"/>
+      <c r="J683" s="19"/>
       <c r="K683" s="10" t="s">
         <v>20</v>
       </c>
@@ -34192,17 +34225,17 @@
     </row>
     <row r="684" ht="18.0" customHeight="1">
       <c r="A684" s="6"/>
-      <c r="B684" s="15"/>
+      <c r="B684" s="16"/>
       <c r="C684" s="14"/>
-      <c r="D684" s="18"/>
-      <c r="E684" s="16"/>
-      <c r="F684" s="16"/>
-      <c r="G684" s="16"/>
+      <c r="D684" s="17"/>
+      <c r="E684" s="18"/>
+      <c r="F684" s="18"/>
+      <c r="G684" s="18"/>
       <c r="H684" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I684" s="17"/>
-      <c r="J684" s="17"/>
+      <c r="I684" s="19"/>
+      <c r="J684" s="19"/>
       <c r="K684" s="10" t="s">
         <v>20</v>
       </c>
@@ -34218,17 +34251,17 @@
     </row>
     <row r="685" ht="18.0" customHeight="1">
       <c r="A685" s="6"/>
-      <c r="B685" s="15"/>
+      <c r="B685" s="16"/>
       <c r="C685" s="14"/>
-      <c r="D685" s="18"/>
-      <c r="E685" s="16"/>
-      <c r="F685" s="16"/>
-      <c r="G685" s="16"/>
+      <c r="D685" s="17"/>
+      <c r="E685" s="18"/>
+      <c r="F685" s="18"/>
+      <c r="G685" s="18"/>
       <c r="H685" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I685" s="17"/>
-      <c r="J685" s="17"/>
+      <c r="I685" s="19"/>
+      <c r="J685" s="19"/>
       <c r="K685" s="10" t="s">
         <v>20</v>
       </c>
@@ -34244,17 +34277,17 @@
     </row>
     <row r="686" ht="18.0" customHeight="1">
       <c r="A686" s="6"/>
-      <c r="B686" s="15"/>
+      <c r="B686" s="16"/>
       <c r="C686" s="14"/>
-      <c r="D686" s="18"/>
-      <c r="E686" s="16"/>
-      <c r="F686" s="16"/>
-      <c r="G686" s="16"/>
+      <c r="D686" s="17"/>
+      <c r="E686" s="18"/>
+      <c r="F686" s="18"/>
+      <c r="G686" s="18"/>
       <c r="H686" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I686" s="17"/>
-      <c r="J686" s="17"/>
+      <c r="I686" s="19"/>
+      <c r="J686" s="19"/>
       <c r="K686" s="10" t="s">
         <v>20</v>
       </c>
@@ -34270,17 +34303,17 @@
     </row>
     <row r="687" ht="18.0" customHeight="1">
       <c r="A687" s="6"/>
-      <c r="B687" s="15"/>
+      <c r="B687" s="16"/>
       <c r="C687" s="14"/>
-      <c r="D687" s="18"/>
-      <c r="E687" s="16"/>
-      <c r="F687" s="16"/>
-      <c r="G687" s="16"/>
+      <c r="D687" s="17"/>
+      <c r="E687" s="18"/>
+      <c r="F687" s="18"/>
+      <c r="G687" s="18"/>
       <c r="H687" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I687" s="17"/>
-      <c r="J687" s="17"/>
+      <c r="I687" s="19"/>
+      <c r="J687" s="19"/>
       <c r="K687" s="10" t="s">
         <v>20</v>
       </c>
@@ -34296,17 +34329,17 @@
     </row>
     <row r="688" ht="18.0" customHeight="1">
       <c r="A688" s="6"/>
-      <c r="B688" s="15"/>
+      <c r="B688" s="16"/>
       <c r="C688" s="14"/>
-      <c r="D688" s="18"/>
-      <c r="E688" s="16"/>
-      <c r="F688" s="16"/>
-      <c r="G688" s="16"/>
+      <c r="D688" s="17"/>
+      <c r="E688" s="18"/>
+      <c r="F688" s="18"/>
+      <c r="G688" s="18"/>
       <c r="H688" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I688" s="17"/>
-      <c r="J688" s="17"/>
+      <c r="I688" s="19"/>
+      <c r="J688" s="19"/>
       <c r="K688" s="10" t="s">
         <v>20</v>
       </c>
@@ -34322,17 +34355,17 @@
     </row>
     <row r="689" ht="18.0" customHeight="1">
       <c r="A689" s="6"/>
-      <c r="B689" s="15"/>
+      <c r="B689" s="16"/>
       <c r="C689" s="14"/>
-      <c r="D689" s="18"/>
-      <c r="E689" s="16"/>
-      <c r="F689" s="16"/>
-      <c r="G689" s="16"/>
+      <c r="D689" s="17"/>
+      <c r="E689" s="18"/>
+      <c r="F689" s="18"/>
+      <c r="G689" s="18"/>
       <c r="H689" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I689" s="17"/>
-      <c r="J689" s="17"/>
+      <c r="I689" s="19"/>
+      <c r="J689" s="19"/>
       <c r="K689" s="10" t="s">
         <v>20</v>
       </c>
@@ -34348,17 +34381,17 @@
     </row>
     <row r="690" ht="18.0" customHeight="1">
       <c r="A690" s="6"/>
-      <c r="B690" s="15"/>
+      <c r="B690" s="16"/>
       <c r="C690" s="14"/>
-      <c r="D690" s="18"/>
-      <c r="E690" s="16"/>
-      <c r="F690" s="16"/>
-      <c r="G690" s="16"/>
+      <c r="D690" s="17"/>
+      <c r="E690" s="18"/>
+      <c r="F690" s="18"/>
+      <c r="G690" s="18"/>
       <c r="H690" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I690" s="17"/>
-      <c r="J690" s="17"/>
+      <c r="I690" s="19"/>
+      <c r="J690" s="19"/>
       <c r="K690" s="10" t="s">
         <v>20</v>
       </c>
@@ -34374,17 +34407,17 @@
     </row>
     <row r="691" ht="18.0" customHeight="1">
       <c r="A691" s="6"/>
-      <c r="B691" s="15"/>
+      <c r="B691" s="16"/>
       <c r="C691" s="14"/>
-      <c r="D691" s="18"/>
-      <c r="E691" s="16"/>
-      <c r="F691" s="16"/>
-      <c r="G691" s="16"/>
+      <c r="D691" s="17"/>
+      <c r="E691" s="18"/>
+      <c r="F691" s="18"/>
+      <c r="G691" s="18"/>
       <c r="H691" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I691" s="17"/>
-      <c r="J691" s="17"/>
+      <c r="I691" s="19"/>
+      <c r="J691" s="19"/>
       <c r="K691" s="10" t="s">
         <v>20</v>
       </c>
@@ -34400,17 +34433,17 @@
     </row>
     <row r="692" ht="18.0" customHeight="1">
       <c r="A692" s="6"/>
-      <c r="B692" s="15"/>
+      <c r="B692" s="16"/>
       <c r="C692" s="14"/>
-      <c r="D692" s="18"/>
-      <c r="E692" s="16"/>
-      <c r="F692" s="16"/>
-      <c r="G692" s="16"/>
+      <c r="D692" s="17"/>
+      <c r="E692" s="18"/>
+      <c r="F692" s="18"/>
+      <c r="G692" s="18"/>
       <c r="H692" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I692" s="17"/>
-      <c r="J692" s="17"/>
+      <c r="I692" s="19"/>
+      <c r="J692" s="19"/>
       <c r="K692" s="10" t="s">
         <v>20</v>
       </c>
@@ -34426,17 +34459,17 @@
     </row>
     <row r="693" ht="18.0" customHeight="1">
       <c r="A693" s="6"/>
-      <c r="B693" s="15"/>
+      <c r="B693" s="16"/>
       <c r="C693" s="14"/>
-      <c r="D693" s="18"/>
-      <c r="E693" s="16"/>
-      <c r="F693" s="16"/>
-      <c r="G693" s="16"/>
+      <c r="D693" s="17"/>
+      <c r="E693" s="18"/>
+      <c r="F693" s="18"/>
+      <c r="G693" s="18"/>
       <c r="H693" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I693" s="17"/>
-      <c r="J693" s="17"/>
+      <c r="I693" s="19"/>
+      <c r="J693" s="19"/>
       <c r="K693" s="10" t="s">
         <v>20</v>
       </c>
@@ -34452,17 +34485,17 @@
     </row>
     <row r="694" ht="18.0" customHeight="1">
       <c r="A694" s="6"/>
-      <c r="B694" s="15"/>
+      <c r="B694" s="16"/>
       <c r="C694" s="14"/>
-      <c r="D694" s="19"/>
-      <c r="E694" s="16"/>
-      <c r="F694" s="16"/>
-      <c r="G694" s="16"/>
+      <c r="D694" s="20"/>
+      <c r="E694" s="18"/>
+      <c r="F694" s="18"/>
+      <c r="G694" s="18"/>
       <c r="H694" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I694" s="17"/>
-      <c r="J694" s="17"/>
+      <c r="I694" s="19"/>
+      <c r="J694" s="19"/>
       <c r="K694" s="10" t="s">
         <v>20</v>
       </c>
@@ -34478,17 +34511,17 @@
     </row>
     <row r="695" ht="18.0" customHeight="1">
       <c r="A695" s="6"/>
-      <c r="B695" s="15"/>
+      <c r="B695" s="16"/>
       <c r="C695" s="14"/>
-      <c r="D695" s="19"/>
-      <c r="E695" s="16"/>
-      <c r="F695" s="16"/>
-      <c r="G695" s="16"/>
+      <c r="D695" s="20"/>
+      <c r="E695" s="18"/>
+      <c r="F695" s="18"/>
+      <c r="G695" s="18"/>
       <c r="H695" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I695" s="17"/>
-      <c r="J695" s="17"/>
+      <c r="I695" s="19"/>
+      <c r="J695" s="19"/>
       <c r="K695" s="10" t="s">
         <v>20</v>
       </c>
@@ -34504,17 +34537,17 @@
     </row>
     <row r="696" ht="18.0" customHeight="1">
       <c r="A696" s="6"/>
-      <c r="B696" s="15"/>
+      <c r="B696" s="16"/>
       <c r="C696" s="14"/>
-      <c r="D696" s="19"/>
-      <c r="E696" s="16"/>
-      <c r="F696" s="16"/>
-      <c r="G696" s="16"/>
+      <c r="D696" s="20"/>
+      <c r="E696" s="18"/>
+      <c r="F696" s="18"/>
+      <c r="G696" s="18"/>
       <c r="H696" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I696" s="17"/>
-      <c r="J696" s="17"/>
+      <c r="I696" s="19"/>
+      <c r="J696" s="19"/>
       <c r="K696" s="10" t="s">
         <v>20</v>
       </c>
@@ -34530,17 +34563,17 @@
     </row>
     <row r="697" ht="18.0" customHeight="1">
       <c r="A697" s="6"/>
-      <c r="B697" s="15"/>
+      <c r="B697" s="16"/>
       <c r="C697" s="14"/>
-      <c r="D697" s="19"/>
-      <c r="E697" s="16"/>
-      <c r="F697" s="16"/>
-      <c r="G697" s="16"/>
+      <c r="D697" s="20"/>
+      <c r="E697" s="18"/>
+      <c r="F697" s="18"/>
+      <c r="G697" s="18"/>
       <c r="H697" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I697" s="17"/>
-      <c r="J697" s="17"/>
+      <c r="I697" s="19"/>
+      <c r="J697" s="19"/>
       <c r="K697" s="10" t="s">
         <v>20</v>
       </c>
@@ -34556,17 +34589,17 @@
     </row>
     <row r="698" ht="18.0" customHeight="1">
       <c r="A698" s="6"/>
-      <c r="B698" s="15"/>
+      <c r="B698" s="16"/>
       <c r="C698" s="14"/>
-      <c r="D698" s="19"/>
-      <c r="E698" s="16"/>
-      <c r="F698" s="16"/>
-      <c r="G698" s="16"/>
+      <c r="D698" s="20"/>
+      <c r="E698" s="18"/>
+      <c r="F698" s="18"/>
+      <c r="G698" s="18"/>
       <c r="H698" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I698" s="17"/>
-      <c r="J698" s="17"/>
+      <c r="I698" s="19"/>
+      <c r="J698" s="19"/>
       <c r="K698" s="10" t="s">
         <v>20</v>
       </c>
@@ -34582,17 +34615,17 @@
     </row>
     <row r="699" ht="18.0" customHeight="1">
       <c r="A699" s="6"/>
-      <c r="B699" s="15"/>
+      <c r="B699" s="16"/>
       <c r="C699" s="14"/>
-      <c r="D699" s="19"/>
-      <c r="E699" s="16"/>
-      <c r="F699" s="16"/>
-      <c r="G699" s="16"/>
+      <c r="D699" s="20"/>
+      <c r="E699" s="18"/>
+      <c r="F699" s="18"/>
+      <c r="G699" s="18"/>
       <c r="H699" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I699" s="17"/>
-      <c r="J699" s="17"/>
+      <c r="I699" s="19"/>
+      <c r="J699" s="19"/>
       <c r="K699" s="10" t="s">
         <v>20</v>
       </c>
@@ -34608,17 +34641,17 @@
     </row>
     <row r="700" ht="18.0" customHeight="1">
       <c r="A700" s="6"/>
-      <c r="B700" s="15"/>
+      <c r="B700" s="16"/>
       <c r="C700" s="14"/>
-      <c r="D700" s="19"/>
-      <c r="E700" s="16"/>
-      <c r="F700" s="16"/>
-      <c r="G700" s="16"/>
+      <c r="D700" s="20"/>
+      <c r="E700" s="18"/>
+      <c r="F700" s="18"/>
+      <c r="G700" s="18"/>
       <c r="H700" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I700" s="17"/>
-      <c r="J700" s="17"/>
+      <c r="I700" s="19"/>
+      <c r="J700" s="19"/>
       <c r="K700" s="10" t="s">
         <v>20</v>
       </c>
@@ -34634,17 +34667,17 @@
     </row>
     <row r="701" ht="18.0" customHeight="1">
       <c r="A701" s="6"/>
-      <c r="B701" s="15"/>
+      <c r="B701" s="16"/>
       <c r="C701" s="14"/>
-      <c r="D701" s="19"/>
-      <c r="E701" s="16"/>
-      <c r="F701" s="16"/>
-      <c r="G701" s="16"/>
+      <c r="D701" s="20"/>
+      <c r="E701" s="18"/>
+      <c r="F701" s="18"/>
+      <c r="G701" s="18"/>
       <c r="H701" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I701" s="17"/>
-      <c r="J701" s="17"/>
+      <c r="I701" s="19"/>
+      <c r="J701" s="19"/>
       <c r="K701" s="10" t="s">
         <v>20</v>
       </c>
@@ -34660,17 +34693,17 @@
     </row>
     <row r="702" ht="18.0" customHeight="1">
       <c r="A702" s="6"/>
-      <c r="B702" s="15"/>
+      <c r="B702" s="16"/>
       <c r="C702" s="14"/>
-      <c r="D702" s="19"/>
-      <c r="E702" s="16"/>
-      <c r="F702" s="16"/>
-      <c r="G702" s="16"/>
+      <c r="D702" s="20"/>
+      <c r="E702" s="18"/>
+      <c r="F702" s="18"/>
+      <c r="G702" s="18"/>
       <c r="H702" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I702" s="17"/>
-      <c r="J702" s="17"/>
+      <c r="I702" s="19"/>
+      <c r="J702" s="19"/>
       <c r="K702" s="10" t="s">
         <v>20</v>
       </c>
@@ -34686,17 +34719,17 @@
     </row>
     <row r="703" ht="18.0" customHeight="1">
       <c r="A703" s="6"/>
-      <c r="B703" s="15"/>
+      <c r="B703" s="16"/>
       <c r="C703" s="14"/>
-      <c r="D703" s="19"/>
-      <c r="E703" s="16"/>
-      <c r="F703" s="16"/>
-      <c r="G703" s="16"/>
+      <c r="D703" s="20"/>
+      <c r="E703" s="18"/>
+      <c r="F703" s="18"/>
+      <c r="G703" s="18"/>
       <c r="H703" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I703" s="17"/>
-      <c r="J703" s="17"/>
+      <c r="I703" s="19"/>
+      <c r="J703" s="19"/>
       <c r="K703" s="10" t="s">
         <v>20</v>
       </c>
@@ -34712,17 +34745,17 @@
     </row>
     <row r="704" ht="18.0" customHeight="1">
       <c r="A704" s="6"/>
-      <c r="B704" s="15"/>
+      <c r="B704" s="16"/>
       <c r="C704" s="14"/>
-      <c r="D704" s="19"/>
-      <c r="E704" s="16"/>
-      <c r="F704" s="16"/>
-      <c r="G704" s="16"/>
+      <c r="D704" s="20"/>
+      <c r="E704" s="18"/>
+      <c r="F704" s="18"/>
+      <c r="G704" s="18"/>
       <c r="H704" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I704" s="17"/>
-      <c r="J704" s="17"/>
+      <c r="I704" s="19"/>
+      <c r="J704" s="19"/>
       <c r="K704" s="10" t="s">
         <v>20</v>
       </c>
@@ -34738,17 +34771,17 @@
     </row>
     <row r="705" ht="18.0" customHeight="1">
       <c r="A705" s="6"/>
-      <c r="B705" s="15"/>
+      <c r="B705" s="16"/>
       <c r="C705" s="14"/>
-      <c r="D705" s="19"/>
-      <c r="E705" s="16"/>
-      <c r="F705" s="16"/>
-      <c r="G705" s="16"/>
+      <c r="D705" s="20"/>
+      <c r="E705" s="18"/>
+      <c r="F705" s="18"/>
+      <c r="G705" s="18"/>
       <c r="H705" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I705" s="17"/>
-      <c r="J705" s="17"/>
+      <c r="I705" s="19"/>
+      <c r="J705" s="19"/>
       <c r="K705" s="10" t="s">
         <v>20</v>
       </c>
@@ -34764,17 +34797,17 @@
     </row>
     <row r="706" ht="18.0" customHeight="1">
       <c r="A706" s="6"/>
-      <c r="B706" s="15"/>
+      <c r="B706" s="16"/>
       <c r="C706" s="14"/>
-      <c r="D706" s="19"/>
-      <c r="E706" s="16"/>
-      <c r="F706" s="16"/>
-      <c r="G706" s="16"/>
+      <c r="D706" s="20"/>
+      <c r="E706" s="18"/>
+      <c r="F706" s="18"/>
+      <c r="G706" s="18"/>
       <c r="H706" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I706" s="17"/>
-      <c r="J706" s="17"/>
+      <c r="I706" s="19"/>
+      <c r="J706" s="19"/>
       <c r="K706" s="10" t="s">
         <v>20</v>
       </c>
@@ -34790,17 +34823,17 @@
     </row>
     <row r="707" ht="18.0" customHeight="1">
       <c r="A707" s="6"/>
-      <c r="B707" s="15"/>
+      <c r="B707" s="16"/>
       <c r="C707" s="14"/>
-      <c r="D707" s="19"/>
-      <c r="E707" s="16"/>
-      <c r="F707" s="16"/>
-      <c r="G707" s="16"/>
+      <c r="D707" s="20"/>
+      <c r="E707" s="18"/>
+      <c r="F707" s="18"/>
+      <c r="G707" s="18"/>
       <c r="H707" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I707" s="17"/>
-      <c r="J707" s="17"/>
+      <c r="I707" s="19"/>
+      <c r="J707" s="19"/>
       <c r="K707" s="10" t="s">
         <v>20</v>
       </c>
@@ -34816,17 +34849,17 @@
     </row>
     <row r="708" ht="18.0" customHeight="1">
       <c r="A708" s="6"/>
-      <c r="B708" s="15"/>
+      <c r="B708" s="16"/>
       <c r="C708" s="14"/>
-      <c r="D708" s="19"/>
-      <c r="E708" s="16"/>
-      <c r="F708" s="16"/>
-      <c r="G708" s="16"/>
+      <c r="D708" s="20"/>
+      <c r="E708" s="18"/>
+      <c r="F708" s="18"/>
+      <c r="G708" s="18"/>
       <c r="H708" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I708" s="17"/>
-      <c r="J708" s="17"/>
+      <c r="I708" s="19"/>
+      <c r="J708" s="19"/>
       <c r="K708" s="10" t="s">
         <v>20</v>
       </c>
@@ -34842,17 +34875,17 @@
     </row>
     <row r="709" ht="18.0" customHeight="1">
       <c r="A709" s="6"/>
-      <c r="B709" s="15"/>
+      <c r="B709" s="16"/>
       <c r="C709" s="14"/>
-      <c r="D709" s="19"/>
-      <c r="E709" s="16"/>
-      <c r="F709" s="16"/>
-      <c r="G709" s="16"/>
+      <c r="D709" s="20"/>
+      <c r="E709" s="18"/>
+      <c r="F709" s="18"/>
+      <c r="G709" s="18"/>
       <c r="H709" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I709" s="17"/>
-      <c r="J709" s="17"/>
+      <c r="I709" s="19"/>
+      <c r="J709" s="19"/>
       <c r="K709" s="10" t="s">
         <v>20</v>
       </c>
@@ -34868,17 +34901,17 @@
     </row>
     <row r="710" ht="18.0" customHeight="1">
       <c r="A710" s="6"/>
-      <c r="B710" s="15"/>
+      <c r="B710" s="16"/>
       <c r="C710" s="14"/>
-      <c r="D710" s="19"/>
-      <c r="E710" s="16"/>
-      <c r="F710" s="16"/>
-      <c r="G710" s="16"/>
+      <c r="D710" s="20"/>
+      <c r="E710" s="18"/>
+      <c r="F710" s="18"/>
+      <c r="G710" s="18"/>
       <c r="H710" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I710" s="17"/>
-      <c r="J710" s="17"/>
+      <c r="I710" s="19"/>
+      <c r="J710" s="19"/>
       <c r="K710" s="10" t="s">
         <v>20</v>
       </c>
@@ -34894,17 +34927,17 @@
     </row>
     <row r="711" ht="18.0" customHeight="1">
       <c r="A711" s="6"/>
-      <c r="B711" s="15"/>
+      <c r="B711" s="16"/>
       <c r="C711" s="14"/>
-      <c r="D711" s="19"/>
-      <c r="E711" s="16"/>
-      <c r="F711" s="16"/>
-      <c r="G711" s="16"/>
+      <c r="D711" s="20"/>
+      <c r="E711" s="18"/>
+      <c r="F711" s="18"/>
+      <c r="G711" s="18"/>
       <c r="H711" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I711" s="17"/>
-      <c r="J711" s="17"/>
+      <c r="I711" s="19"/>
+      <c r="J711" s="19"/>
       <c r="K711" s="10" t="s">
         <v>20</v>
       </c>
@@ -34920,17 +34953,17 @@
     </row>
     <row r="712" ht="18.0" customHeight="1">
       <c r="A712" s="6"/>
-      <c r="B712" s="15"/>
+      <c r="B712" s="16"/>
       <c r="C712" s="14"/>
-      <c r="D712" s="19"/>
-      <c r="E712" s="16"/>
-      <c r="F712" s="16"/>
-      <c r="G712" s="16"/>
+      <c r="D712" s="20"/>
+      <c r="E712" s="18"/>
+      <c r="F712" s="18"/>
+      <c r="G712" s="18"/>
       <c r="H712" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I712" s="17"/>
-      <c r="J712" s="17"/>
+      <c r="I712" s="19"/>
+      <c r="J712" s="19"/>
       <c r="K712" s="10" t="s">
         <v>20</v>
       </c>
@@ -34946,17 +34979,17 @@
     </row>
     <row r="713" ht="18.0" customHeight="1">
       <c r="A713" s="6"/>
-      <c r="B713" s="15"/>
+      <c r="B713" s="16"/>
       <c r="C713" s="14"/>
-      <c r="D713" s="19"/>
-      <c r="E713" s="16"/>
-      <c r="F713" s="16"/>
-      <c r="G713" s="16"/>
+      <c r="D713" s="20"/>
+      <c r="E713" s="18"/>
+      <c r="F713" s="18"/>
+      <c r="G713" s="18"/>
       <c r="H713" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I713" s="17"/>
-      <c r="J713" s="17"/>
+      <c r="I713" s="19"/>
+      <c r="J713" s="19"/>
       <c r="K713" s="10" t="s">
         <v>20</v>
       </c>
@@ -34972,17 +35005,17 @@
     </row>
     <row r="714" ht="18.0" customHeight="1">
       <c r="A714" s="6"/>
-      <c r="B714" s="15"/>
+      <c r="B714" s="16"/>
       <c r="C714" s="14"/>
-      <c r="D714" s="19"/>
-      <c r="E714" s="16"/>
-      <c r="F714" s="16"/>
-      <c r="G714" s="16"/>
+      <c r="D714" s="20"/>
+      <c r="E714" s="18"/>
+      <c r="F714" s="18"/>
+      <c r="G714" s="18"/>
       <c r="H714" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I714" s="17"/>
-      <c r="J714" s="17"/>
+      <c r="I714" s="19"/>
+      <c r="J714" s="19"/>
       <c r="K714" s="10" t="s">
         <v>20</v>
       </c>
@@ -34998,17 +35031,17 @@
     </row>
     <row r="715" ht="18.0" customHeight="1">
       <c r="A715" s="6"/>
-      <c r="B715" s="15"/>
+      <c r="B715" s="16"/>
       <c r="C715" s="14"/>
-      <c r="D715" s="19"/>
-      <c r="E715" s="16"/>
-      <c r="F715" s="16"/>
-      <c r="G715" s="16"/>
+      <c r="D715" s="20"/>
+      <c r="E715" s="18"/>
+      <c r="F715" s="18"/>
+      <c r="G715" s="18"/>
       <c r="H715" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I715" s="17"/>
-      <c r="J715" s="17"/>
+      <c r="I715" s="19"/>
+      <c r="J715" s="19"/>
       <c r="K715" s="10" t="s">
         <v>20</v>
       </c>
@@ -35024,17 +35057,17 @@
     </row>
     <row r="716" ht="18.0" customHeight="1">
       <c r="A716" s="6"/>
-      <c r="B716" s="15"/>
+      <c r="B716" s="16"/>
       <c r="C716" s="14"/>
-      <c r="D716" s="19"/>
-      <c r="E716" s="16"/>
-      <c r="F716" s="16"/>
-      <c r="G716" s="16"/>
+      <c r="D716" s="20"/>
+      <c r="E716" s="18"/>
+      <c r="F716" s="18"/>
+      <c r="G716" s="18"/>
       <c r="H716" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I716" s="17"/>
-      <c r="J716" s="17"/>
+      <c r="I716" s="19"/>
+      <c r="J716" s="19"/>
       <c r="K716" s="10" t="s">
         <v>20</v>
       </c>
@@ -35050,17 +35083,17 @@
     </row>
     <row r="717" ht="18.0" customHeight="1">
       <c r="A717" s="6"/>
-      <c r="B717" s="15"/>
+      <c r="B717" s="16"/>
       <c r="C717" s="14"/>
-      <c r="D717" s="19"/>
-      <c r="E717" s="16"/>
-      <c r="F717" s="16"/>
-      <c r="G717" s="16"/>
+      <c r="D717" s="20"/>
+      <c r="E717" s="18"/>
+      <c r="F717" s="18"/>
+      <c r="G717" s="18"/>
       <c r="H717" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I717" s="17"/>
-      <c r="J717" s="17"/>
+      <c r="I717" s="19"/>
+      <c r="J717" s="19"/>
       <c r="K717" s="10" t="s">
         <v>20</v>
       </c>
@@ -35076,17 +35109,17 @@
     </row>
     <row r="718" ht="18.0" customHeight="1">
       <c r="A718" s="6"/>
-      <c r="B718" s="15"/>
+      <c r="B718" s="16"/>
       <c r="C718" s="14"/>
-      <c r="D718" s="19"/>
-      <c r="E718" s="16"/>
-      <c r="F718" s="16"/>
-      <c r="G718" s="16"/>
+      <c r="D718" s="20"/>
+      <c r="E718" s="18"/>
+      <c r="F718" s="18"/>
+      <c r="G718" s="18"/>
       <c r="H718" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I718" s="17"/>
-      <c r="J718" s="17"/>
+      <c r="I718" s="19"/>
+      <c r="J718" s="19"/>
       <c r="K718" s="10" t="s">
         <v>20</v>
       </c>
@@ -35102,17 +35135,17 @@
     </row>
     <row r="719" ht="18.0" customHeight="1">
       <c r="A719" s="6"/>
-      <c r="B719" s="15"/>
+      <c r="B719" s="16"/>
       <c r="C719" s="14"/>
-      <c r="D719" s="19"/>
-      <c r="E719" s="16"/>
-      <c r="F719" s="16"/>
-      <c r="G719" s="16"/>
+      <c r="D719" s="20"/>
+      <c r="E719" s="18"/>
+      <c r="F719" s="18"/>
+      <c r="G719" s="18"/>
       <c r="H719" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I719" s="17"/>
-      <c r="J719" s="17"/>
+      <c r="I719" s="19"/>
+      <c r="J719" s="19"/>
       <c r="K719" s="10" t="s">
         <v>20</v>
       </c>
@@ -35128,17 +35161,17 @@
     </row>
     <row r="720" ht="18.0" customHeight="1">
       <c r="A720" s="6"/>
-      <c r="B720" s="15"/>
+      <c r="B720" s="16"/>
       <c r="C720" s="14"/>
-      <c r="D720" s="19"/>
-      <c r="E720" s="16"/>
-      <c r="F720" s="16"/>
-      <c r="G720" s="16"/>
+      <c r="D720" s="20"/>
+      <c r="E720" s="18"/>
+      <c r="F720" s="18"/>
+      <c r="G720" s="18"/>
       <c r="H720" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I720" s="17"/>
-      <c r="J720" s="17"/>
+      <c r="I720" s="19"/>
+      <c r="J720" s="19"/>
       <c r="K720" s="10" t="s">
         <v>20</v>
       </c>
@@ -35154,17 +35187,17 @@
     </row>
     <row r="721" ht="18.0" customHeight="1">
       <c r="A721" s="6"/>
-      <c r="B721" s="15"/>
+      <c r="B721" s="16"/>
       <c r="C721" s="14"/>
-      <c r="D721" s="19"/>
-      <c r="E721" s="16"/>
-      <c r="F721" s="16"/>
-      <c r="G721" s="16"/>
+      <c r="D721" s="20"/>
+      <c r="E721" s="18"/>
+      <c r="F721" s="18"/>
+      <c r="G721" s="18"/>
       <c r="H721" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I721" s="17"/>
-      <c r="J721" s="17"/>
+      <c r="I721" s="19"/>
+      <c r="J721" s="19"/>
       <c r="K721" s="10" t="s">
         <v>20</v>
       </c>
@@ -35180,17 +35213,17 @@
     </row>
     <row r="722" ht="18.0" customHeight="1">
       <c r="A722" s="6"/>
-      <c r="B722" s="15"/>
+      <c r="B722" s="16"/>
       <c r="C722" s="14"/>
-      <c r="D722" s="19"/>
-      <c r="E722" s="16"/>
-      <c r="F722" s="16"/>
-      <c r="G722" s="16"/>
+      <c r="D722" s="20"/>
+      <c r="E722" s="18"/>
+      <c r="F722" s="18"/>
+      <c r="G722" s="18"/>
       <c r="H722" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I722" s="17"/>
-      <c r="J722" s="17"/>
+      <c r="I722" s="19"/>
+      <c r="J722" s="19"/>
       <c r="K722" s="10" t="s">
         <v>20</v>
       </c>
@@ -35206,17 +35239,17 @@
     </row>
     <row r="723" ht="18.0" customHeight="1">
       <c r="A723" s="6"/>
-      <c r="B723" s="15"/>
+      <c r="B723" s="16"/>
       <c r="C723" s="14"/>
-      <c r="D723" s="19"/>
-      <c r="E723" s="16"/>
-      <c r="F723" s="16"/>
-      <c r="G723" s="16"/>
+      <c r="D723" s="20"/>
+      <c r="E723" s="18"/>
+      <c r="F723" s="18"/>
+      <c r="G723" s="18"/>
       <c r="H723" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I723" s="17"/>
-      <c r="J723" s="17"/>
+      <c r="I723" s="19"/>
+      <c r="J723" s="19"/>
       <c r="K723" s="10" t="s">
         <v>20</v>
       </c>
@@ -35232,17 +35265,17 @@
     </row>
     <row r="724" ht="18.0" customHeight="1">
       <c r="A724" s="6"/>
-      <c r="B724" s="15"/>
+      <c r="B724" s="16"/>
       <c r="C724" s="14"/>
-      <c r="D724" s="19"/>
-      <c r="E724" s="16"/>
-      <c r="F724" s="16"/>
-      <c r="G724" s="16"/>
+      <c r="D724" s="20"/>
+      <c r="E724" s="18"/>
+      <c r="F724" s="18"/>
+      <c r="G724" s="18"/>
       <c r="H724" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I724" s="17"/>
-      <c r="J724" s="17"/>
+      <c r="I724" s="19"/>
+      <c r="J724" s="19"/>
       <c r="K724" s="10" t="s">
         <v>20</v>
       </c>
@@ -35258,17 +35291,17 @@
     </row>
     <row r="725" ht="18.0" customHeight="1">
       <c r="A725" s="6"/>
-      <c r="B725" s="15"/>
+      <c r="B725" s="16"/>
       <c r="C725" s="14"/>
-      <c r="D725" s="19"/>
-      <c r="E725" s="16"/>
-      <c r="F725" s="16"/>
-      <c r="G725" s="16"/>
+      <c r="D725" s="20"/>
+      <c r="E725" s="18"/>
+      <c r="F725" s="18"/>
+      <c r="G725" s="18"/>
       <c r="H725" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I725" s="17"/>
-      <c r="J725" s="17"/>
+      <c r="I725" s="19"/>
+      <c r="J725" s="19"/>
       <c r="K725" s="10" t="s">
         <v>20</v>
       </c>
@@ -35284,17 +35317,17 @@
     </row>
     <row r="726" ht="18.0" customHeight="1">
       <c r="A726" s="6"/>
-      <c r="B726" s="15"/>
+      <c r="B726" s="16"/>
       <c r="C726" s="14"/>
-      <c r="D726" s="19"/>
-      <c r="E726" s="16"/>
-      <c r="F726" s="16"/>
-      <c r="G726" s="16"/>
+      <c r="D726" s="20"/>
+      <c r="E726" s="18"/>
+      <c r="F726" s="18"/>
+      <c r="G726" s="18"/>
       <c r="H726" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I726" s="17"/>
-      <c r="J726" s="17"/>
+      <c r="I726" s="19"/>
+      <c r="J726" s="19"/>
       <c r="K726" s="10" t="s">
         <v>20</v>
       </c>
@@ -35310,17 +35343,17 @@
     </row>
     <row r="727" ht="18.0" customHeight="1">
       <c r="A727" s="6"/>
-      <c r="B727" s="15"/>
+      <c r="B727" s="16"/>
       <c r="C727" s="14"/>
-      <c r="D727" s="19"/>
-      <c r="E727" s="16"/>
-      <c r="F727" s="16"/>
-      <c r="G727" s="16"/>
+      <c r="D727" s="20"/>
+      <c r="E727" s="18"/>
+      <c r="F727" s="18"/>
+      <c r="G727" s="18"/>
       <c r="H727" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I727" s="17"/>
-      <c r="J727" s="17"/>
+      <c r="I727" s="19"/>
+      <c r="J727" s="19"/>
       <c r="K727" s="10" t="s">
         <v>20</v>
       </c>
@@ -35336,17 +35369,17 @@
     </row>
     <row r="728" ht="18.0" customHeight="1">
       <c r="A728" s="6"/>
-      <c r="B728" s="15"/>
+      <c r="B728" s="16"/>
       <c r="C728" s="14"/>
-      <c r="D728" s="19"/>
-      <c r="E728" s="16"/>
-      <c r="F728" s="16"/>
-      <c r="G728" s="16"/>
+      <c r="D728" s="20"/>
+      <c r="E728" s="18"/>
+      <c r="F728" s="18"/>
+      <c r="G728" s="18"/>
       <c r="H728" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I728" s="17"/>
-      <c r="J728" s="17"/>
+      <c r="I728" s="19"/>
+      <c r="J728" s="19"/>
       <c r="K728" s="10" t="s">
         <v>20</v>
       </c>
@@ -35362,17 +35395,17 @@
     </row>
     <row r="729" ht="18.0" customHeight="1">
       <c r="A729" s="6"/>
-      <c r="B729" s="15"/>
+      <c r="B729" s="16"/>
       <c r="C729" s="14"/>
-      <c r="D729" s="19"/>
-      <c r="E729" s="16"/>
-      <c r="F729" s="16"/>
-      <c r="G729" s="16"/>
+      <c r="D729" s="20"/>
+      <c r="E729" s="18"/>
+      <c r="F729" s="18"/>
+      <c r="G729" s="18"/>
       <c r="H729" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I729" s="17"/>
-      <c r="J729" s="17"/>
+      <c r="I729" s="19"/>
+      <c r="J729" s="19"/>
       <c r="K729" s="10" t="s">
         <v>20</v>
       </c>
@@ -35388,17 +35421,17 @@
     </row>
     <row r="730" ht="18.0" customHeight="1">
       <c r="A730" s="6"/>
-      <c r="B730" s="15"/>
+      <c r="B730" s="16"/>
       <c r="C730" s="14"/>
-      <c r="D730" s="19"/>
-      <c r="E730" s="16"/>
-      <c r="F730" s="16"/>
-      <c r="G730" s="16"/>
+      <c r="D730" s="20"/>
+      <c r="E730" s="18"/>
+      <c r="F730" s="18"/>
+      <c r="G730" s="18"/>
       <c r="H730" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I730" s="17"/>
-      <c r="J730" s="17"/>
+      <c r="I730" s="19"/>
+      <c r="J730" s="19"/>
       <c r="K730" s="10" t="s">
         <v>20</v>
       </c>
@@ -35414,17 +35447,17 @@
     </row>
     <row r="731" ht="18.0" customHeight="1">
       <c r="A731" s="6"/>
-      <c r="B731" s="15"/>
+      <c r="B731" s="16"/>
       <c r="C731" s="14"/>
-      <c r="D731" s="19"/>
-      <c r="E731" s="16"/>
-      <c r="F731" s="16"/>
-      <c r="G731" s="16"/>
+      <c r="D731" s="20"/>
+      <c r="E731" s="18"/>
+      <c r="F731" s="18"/>
+      <c r="G731" s="18"/>
       <c r="H731" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I731" s="17"/>
-      <c r="J731" s="17"/>
+      <c r="I731" s="19"/>
+      <c r="J731" s="19"/>
       <c r="K731" s="10" t="s">
         <v>20</v>
       </c>
@@ -35440,17 +35473,17 @@
     </row>
     <row r="732" ht="18.0" customHeight="1">
       <c r="A732" s="6"/>
-      <c r="B732" s="15"/>
+      <c r="B732" s="16"/>
       <c r="C732" s="14"/>
-      <c r="D732" s="19"/>
-      <c r="E732" s="16"/>
-      <c r="F732" s="16"/>
-      <c r="G732" s="16"/>
+      <c r="D732" s="20"/>
+      <c r="E732" s="18"/>
+      <c r="F732" s="18"/>
+      <c r="G732" s="18"/>
       <c r="H732" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I732" s="17"/>
-      <c r="J732" s="17"/>
+      <c r="I732" s="19"/>
+      <c r="J732" s="19"/>
       <c r="K732" s="10" t="s">
         <v>20</v>
       </c>
@@ -35466,17 +35499,17 @@
     </row>
     <row r="733" ht="18.0" customHeight="1">
       <c r="A733" s="6"/>
-      <c r="B733" s="15"/>
+      <c r="B733" s="16"/>
       <c r="C733" s="14"/>
-      <c r="D733" s="19"/>
-      <c r="E733" s="16"/>
-      <c r="F733" s="16"/>
-      <c r="G733" s="16"/>
+      <c r="D733" s="20"/>
+      <c r="E733" s="18"/>
+      <c r="F733" s="18"/>
+      <c r="G733" s="18"/>
       <c r="H733" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I733" s="17"/>
-      <c r="J733" s="17"/>
+      <c r="I733" s="19"/>
+      <c r="J733" s="19"/>
       <c r="K733" s="10" t="s">
         <v>20</v>
       </c>
@@ -35492,17 +35525,17 @@
     </row>
     <row r="734" ht="18.0" customHeight="1">
       <c r="A734" s="6"/>
-      <c r="B734" s="15"/>
+      <c r="B734" s="16"/>
       <c r="C734" s="14"/>
-      <c r="D734" s="19"/>
-      <c r="E734" s="16"/>
-      <c r="F734" s="16"/>
-      <c r="G734" s="16"/>
+      <c r="D734" s="20"/>
+      <c r="E734" s="18"/>
+      <c r="F734" s="18"/>
+      <c r="G734" s="18"/>
       <c r="H734" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I734" s="17"/>
-      <c r="J734" s="17"/>
+      <c r="I734" s="19"/>
+      <c r="J734" s="19"/>
       <c r="K734" s="10" t="s">
         <v>20</v>
       </c>
@@ -35518,17 +35551,17 @@
     </row>
     <row r="735" ht="18.0" customHeight="1">
       <c r="A735" s="6"/>
-      <c r="B735" s="15"/>
+      <c r="B735" s="16"/>
       <c r="C735" s="14"/>
-      <c r="D735" s="19"/>
-      <c r="E735" s="16"/>
-      <c r="F735" s="16"/>
-      <c r="G735" s="16"/>
+      <c r="D735" s="20"/>
+      <c r="E735" s="18"/>
+      <c r="F735" s="18"/>
+      <c r="G735" s="18"/>
       <c r="H735" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I735" s="17"/>
-      <c r="J735" s="17"/>
+      <c r="I735" s="19"/>
+      <c r="J735" s="19"/>
       <c r="K735" s="10" t="s">
         <v>20</v>
       </c>
@@ -35544,17 +35577,17 @@
     </row>
     <row r="736" ht="18.0" customHeight="1">
       <c r="A736" s="6"/>
-      <c r="B736" s="15"/>
+      <c r="B736" s="16"/>
       <c r="C736" s="14"/>
-      <c r="D736" s="19"/>
-      <c r="E736" s="16"/>
-      <c r="F736" s="16"/>
-      <c r="G736" s="16"/>
+      <c r="D736" s="20"/>
+      <c r="E736" s="18"/>
+      <c r="F736" s="18"/>
+      <c r="G736" s="18"/>
       <c r="H736" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I736" s="17"/>
-      <c r="J736" s="17"/>
+      <c r="I736" s="19"/>
+      <c r="J736" s="19"/>
       <c r="K736" s="10" t="s">
         <v>20</v>
       </c>
@@ -35570,17 +35603,17 @@
     </row>
     <row r="737" ht="18.0" customHeight="1">
       <c r="A737" s="6"/>
-      <c r="B737" s="15"/>
+      <c r="B737" s="16"/>
       <c r="C737" s="14"/>
-      <c r="D737" s="19"/>
-      <c r="E737" s="16"/>
-      <c r="F737" s="16"/>
-      <c r="G737" s="16"/>
+      <c r="D737" s="20"/>
+      <c r="E737" s="18"/>
+      <c r="F737" s="18"/>
+      <c r="G737" s="18"/>
       <c r="H737" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I737" s="17"/>
-      <c r="J737" s="17"/>
+      <c r="I737" s="19"/>
+      <c r="J737" s="19"/>
       <c r="K737" s="10" t="s">
         <v>20</v>
       </c>
@@ -35596,17 +35629,17 @@
     </row>
     <row r="738" ht="18.0" customHeight="1">
       <c r="A738" s="6"/>
-      <c r="B738" s="15"/>
+      <c r="B738" s="16"/>
       <c r="C738" s="14"/>
-      <c r="D738" s="19"/>
-      <c r="E738" s="16"/>
-      <c r="F738" s="16"/>
-      <c r="G738" s="16"/>
+      <c r="D738" s="20"/>
+      <c r="E738" s="18"/>
+      <c r="F738" s="18"/>
+      <c r="G738" s="18"/>
       <c r="H738" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I738" s="17"/>
-      <c r="J738" s="17"/>
+      <c r="I738" s="19"/>
+      <c r="J738" s="19"/>
       <c r="K738" s="10" t="s">
         <v>20</v>
       </c>
@@ -35622,17 +35655,17 @@
     </row>
     <row r="739" ht="18.0" customHeight="1">
       <c r="A739" s="6"/>
-      <c r="B739" s="15"/>
+      <c r="B739" s="16"/>
       <c r="C739" s="14"/>
-      <c r="D739" s="19"/>
-      <c r="E739" s="16"/>
-      <c r="F739" s="16"/>
-      <c r="G739" s="16"/>
+      <c r="D739" s="20"/>
+      <c r="E739" s="18"/>
+      <c r="F739" s="18"/>
+      <c r="G739" s="18"/>
       <c r="H739" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I739" s="17"/>
-      <c r="J739" s="17"/>
+      <c r="I739" s="19"/>
+      <c r="J739" s="19"/>
       <c r="K739" s="10" t="s">
         <v>20</v>
       </c>
@@ -35648,17 +35681,17 @@
     </row>
     <row r="740" ht="18.0" customHeight="1">
       <c r="A740" s="6"/>
-      <c r="B740" s="15"/>
+      <c r="B740" s="16"/>
       <c r="C740" s="14"/>
-      <c r="D740" s="19"/>
-      <c r="E740" s="16"/>
-      <c r="F740" s="16"/>
-      <c r="G740" s="16"/>
+      <c r="D740" s="20"/>
+      <c r="E740" s="18"/>
+      <c r="F740" s="18"/>
+      <c r="G740" s="18"/>
       <c r="H740" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I740" s="17"/>
-      <c r="J740" s="17"/>
+      <c r="I740" s="19"/>
+      <c r="J740" s="19"/>
       <c r="K740" s="10" t="s">
         <v>20</v>
       </c>
@@ -35674,17 +35707,17 @@
     </row>
     <row r="741" ht="18.0" customHeight="1">
       <c r="A741" s="6"/>
-      <c r="B741" s="15"/>
+      <c r="B741" s="16"/>
       <c r="C741" s="14"/>
-      <c r="D741" s="19"/>
-      <c r="E741" s="16"/>
-      <c r="F741" s="16"/>
-      <c r="G741" s="16"/>
+      <c r="D741" s="20"/>
+      <c r="E741" s="18"/>
+      <c r="F741" s="18"/>
+      <c r="G741" s="18"/>
       <c r="H741" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I741" s="17"/>
-      <c r="J741" s="17"/>
+      <c r="I741" s="19"/>
+      <c r="J741" s="19"/>
       <c r="K741" s="10" t="s">
         <v>20</v>
       </c>
@@ -35700,17 +35733,17 @@
     </row>
     <row r="742" ht="18.0" customHeight="1">
       <c r="A742" s="6"/>
-      <c r="B742" s="15"/>
+      <c r="B742" s="16"/>
       <c r="C742" s="14"/>
-      <c r="D742" s="19"/>
-      <c r="E742" s="16"/>
-      <c r="F742" s="16"/>
-      <c r="G742" s="16"/>
+      <c r="D742" s="20"/>
+      <c r="E742" s="18"/>
+      <c r="F742" s="18"/>
+      <c r="G742" s="18"/>
       <c r="H742" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I742" s="17"/>
-      <c r="J742" s="17"/>
+      <c r="I742" s="19"/>
+      <c r="J742" s="19"/>
       <c r="K742" s="10" t="s">
         <v>20</v>
       </c>
@@ -35726,17 +35759,17 @@
     </row>
     <row r="743" ht="18.0" customHeight="1">
       <c r="A743" s="6"/>
-      <c r="B743" s="15"/>
+      <c r="B743" s="16"/>
       <c r="C743" s="14"/>
-      <c r="D743" s="19"/>
-      <c r="E743" s="16"/>
-      <c r="F743" s="16"/>
-      <c r="G743" s="16"/>
+      <c r="D743" s="20"/>
+      <c r="E743" s="18"/>
+      <c r="F743" s="18"/>
+      <c r="G743" s="18"/>
       <c r="H743" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I743" s="17"/>
-      <c r="J743" s="17"/>
+      <c r="I743" s="19"/>
+      <c r="J743" s="19"/>
       <c r="K743" s="10" t="s">
         <v>20</v>
       </c>
@@ -35752,17 +35785,17 @@
     </row>
     <row r="744" ht="18.0" customHeight="1">
       <c r="A744" s="6"/>
-      <c r="B744" s="15"/>
+      <c r="B744" s="16"/>
       <c r="C744" s="14"/>
-      <c r="D744" s="19"/>
-      <c r="E744" s="16"/>
-      <c r="F744" s="16"/>
-      <c r="G744" s="16"/>
+      <c r="D744" s="20"/>
+      <c r="E744" s="18"/>
+      <c r="F744" s="18"/>
+      <c r="G744" s="18"/>
       <c r="H744" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I744" s="17"/>
-      <c r="J744" s="17"/>
+      <c r="I744" s="19"/>
+      <c r="J744" s="19"/>
       <c r="K744" s="10" t="s">
         <v>20</v>
       </c>
@@ -35778,17 +35811,17 @@
     </row>
     <row r="745" ht="18.0" customHeight="1">
       <c r="A745" s="6"/>
-      <c r="B745" s="15"/>
+      <c r="B745" s="16"/>
       <c r="C745" s="14"/>
-      <c r="D745" s="19"/>
-      <c r="E745" s="16"/>
-      <c r="F745" s="16"/>
-      <c r="G745" s="16"/>
+      <c r="D745" s="20"/>
+      <c r="E745" s="18"/>
+      <c r="F745" s="18"/>
+      <c r="G745" s="18"/>
       <c r="H745" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I745" s="17"/>
-      <c r="J745" s="17"/>
+      <c r="I745" s="19"/>
+      <c r="J745" s="19"/>
       <c r="K745" s="10" t="s">
         <v>20</v>
       </c>
@@ -35804,17 +35837,17 @@
     </row>
     <row r="746" ht="18.0" customHeight="1">
       <c r="A746" s="6"/>
-      <c r="B746" s="15"/>
+      <c r="B746" s="16"/>
       <c r="C746" s="14"/>
-      <c r="D746" s="19"/>
-      <c r="E746" s="16"/>
-      <c r="F746" s="16"/>
-      <c r="G746" s="16"/>
+      <c r="D746" s="20"/>
+      <c r="E746" s="18"/>
+      <c r="F746" s="18"/>
+      <c r="G746" s="18"/>
       <c r="H746" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I746" s="17"/>
-      <c r="J746" s="17"/>
+      <c r="I746" s="19"/>
+      <c r="J746" s="19"/>
       <c r="K746" s="10" t="s">
         <v>20</v>
       </c>
@@ -35830,17 +35863,17 @@
     </row>
     <row r="747" ht="18.0" customHeight="1">
       <c r="A747" s="6"/>
-      <c r="B747" s="15"/>
+      <c r="B747" s="16"/>
       <c r="C747" s="14"/>
-      <c r="D747" s="19"/>
-      <c r="E747" s="16"/>
-      <c r="F747" s="16"/>
-      <c r="G747" s="16"/>
+      <c r="D747" s="20"/>
+      <c r="E747" s="18"/>
+      <c r="F747" s="18"/>
+      <c r="G747" s="18"/>
       <c r="H747" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I747" s="17"/>
-      <c r="J747" s="17"/>
+      <c r="I747" s="19"/>
+      <c r="J747" s="19"/>
       <c r="K747" s="10" t="s">
         <v>20</v>
       </c>
@@ -35856,17 +35889,17 @@
     </row>
     <row r="748" ht="18.0" customHeight="1">
       <c r="A748" s="6"/>
-      <c r="B748" s="15"/>
+      <c r="B748" s="16"/>
       <c r="C748" s="14"/>
-      <c r="D748" s="19"/>
-      <c r="E748" s="16"/>
-      <c r="F748" s="16"/>
-      <c r="G748" s="16"/>
+      <c r="D748" s="20"/>
+      <c r="E748" s="18"/>
+      <c r="F748" s="18"/>
+      <c r="G748" s="18"/>
       <c r="H748" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I748" s="17"/>
-      <c r="J748" s="17"/>
+      <c r="I748" s="19"/>
+      <c r="J748" s="19"/>
       <c r="K748" s="10" t="s">
         <v>20</v>
       </c>
@@ -35882,17 +35915,17 @@
     </row>
     <row r="749" ht="18.0" customHeight="1">
       <c r="A749" s="6"/>
-      <c r="B749" s="15"/>
+      <c r="B749" s="16"/>
       <c r="C749" s="14"/>
-      <c r="D749" s="19"/>
-      <c r="E749" s="16"/>
-      <c r="F749" s="16"/>
-      <c r="G749" s="16"/>
+      <c r="D749" s="20"/>
+      <c r="E749" s="18"/>
+      <c r="F749" s="18"/>
+      <c r="G749" s="18"/>
       <c r="H749" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I749" s="17"/>
-      <c r="J749" s="17"/>
+      <c r="I749" s="19"/>
+      <c r="J749" s="19"/>
       <c r="K749" s="10" t="s">
         <v>20</v>
       </c>
@@ -35908,17 +35941,17 @@
     </row>
     <row r="750" ht="18.0" customHeight="1">
       <c r="A750" s="6"/>
-      <c r="B750" s="15"/>
+      <c r="B750" s="16"/>
       <c r="C750" s="14"/>
-      <c r="D750" s="19"/>
-      <c r="E750" s="16"/>
-      <c r="F750" s="16"/>
-      <c r="G750" s="16"/>
+      <c r="D750" s="20"/>
+      <c r="E750" s="18"/>
+      <c r="F750" s="18"/>
+      <c r="G750" s="18"/>
       <c r="H750" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I750" s="17"/>
-      <c r="J750" s="17"/>
+      <c r="I750" s="19"/>
+      <c r="J750" s="19"/>
       <c r="K750" s="10" t="s">
         <v>20</v>
       </c>
@@ -35934,17 +35967,17 @@
     </row>
     <row r="751" ht="18.0" customHeight="1">
       <c r="A751" s="6"/>
-      <c r="B751" s="15"/>
+      <c r="B751" s="16"/>
       <c r="C751" s="14"/>
-      <c r="D751" s="19"/>
-      <c r="E751" s="16"/>
-      <c r="F751" s="16"/>
-      <c r="G751" s="16"/>
+      <c r="D751" s="20"/>
+      <c r="E751" s="18"/>
+      <c r="F751" s="18"/>
+      <c r="G751" s="18"/>
       <c r="H751" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I751" s="17"/>
-      <c r="J751" s="17"/>
+      <c r="I751" s="19"/>
+      <c r="J751" s="19"/>
       <c r="K751" s="10" t="s">
         <v>20</v>
       </c>
@@ -35960,17 +35993,17 @@
     </row>
     <row r="752" ht="18.0" customHeight="1">
       <c r="A752" s="6"/>
-      <c r="B752" s="15"/>
+      <c r="B752" s="16"/>
       <c r="C752" s="14"/>
-      <c r="D752" s="19"/>
-      <c r="E752" s="16"/>
-      <c r="F752" s="16"/>
-      <c r="G752" s="16"/>
+      <c r="D752" s="20"/>
+      <c r="E752" s="18"/>
+      <c r="F752" s="18"/>
+      <c r="G752" s="18"/>
       <c r="H752" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I752" s="17"/>
-      <c r="J752" s="17"/>
+      <c r="I752" s="19"/>
+      <c r="J752" s="19"/>
       <c r="K752" s="10" t="s">
         <v>20</v>
       </c>
@@ -35986,17 +36019,17 @@
     </row>
     <row r="753" ht="18.0" customHeight="1">
       <c r="A753" s="6"/>
-      <c r="B753" s="15"/>
+      <c r="B753" s="16"/>
       <c r="C753" s="14"/>
-      <c r="D753" s="19"/>
-      <c r="E753" s="16"/>
-      <c r="F753" s="16"/>
-      <c r="G753" s="16"/>
+      <c r="D753" s="20"/>
+      <c r="E753" s="18"/>
+      <c r="F753" s="18"/>
+      <c r="G753" s="18"/>
       <c r="H753" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I753" s="17"/>
-      <c r="J753" s="17"/>
+      <c r="I753" s="19"/>
+      <c r="J753" s="19"/>
       <c r="K753" s="10" t="s">
         <v>20</v>
       </c>
@@ -36012,17 +36045,17 @@
     </row>
     <row r="754" ht="18.0" customHeight="1">
       <c r="A754" s="6"/>
-      <c r="B754" s="15"/>
+      <c r="B754" s="16"/>
       <c r="C754" s="14"/>
-      <c r="D754" s="19"/>
-      <c r="E754" s="16"/>
-      <c r="F754" s="16"/>
-      <c r="G754" s="16"/>
+      <c r="D754" s="20"/>
+      <c r="E754" s="18"/>
+      <c r="F754" s="18"/>
+      <c r="G754" s="18"/>
       <c r="H754" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I754" s="17"/>
-      <c r="J754" s="17"/>
+      <c r="I754" s="19"/>
+      <c r="J754" s="19"/>
       <c r="K754" s="10" t="s">
         <v>20</v>
       </c>
@@ -36038,17 +36071,17 @@
     </row>
     <row r="755" ht="18.0" customHeight="1">
       <c r="A755" s="6"/>
-      <c r="B755" s="15"/>
+      <c r="B755" s="16"/>
       <c r="C755" s="14"/>
-      <c r="D755" s="19"/>
-      <c r="E755" s="16"/>
-      <c r="F755" s="16"/>
-      <c r="G755" s="16"/>
+      <c r="D755" s="20"/>
+      <c r="E755" s="18"/>
+      <c r="F755" s="18"/>
+      <c r="G755" s="18"/>
       <c r="H755" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I755" s="17"/>
-      <c r="J755" s="17"/>
+      <c r="I755" s="19"/>
+      <c r="J755" s="19"/>
       <c r="K755" s="10" t="s">
         <v>20</v>
       </c>
@@ -36064,17 +36097,17 @@
     </row>
     <row r="756" ht="18.0" customHeight="1">
       <c r="A756" s="6"/>
-      <c r="B756" s="15"/>
+      <c r="B756" s="16"/>
       <c r="C756" s="14"/>
-      <c r="D756" s="19"/>
-      <c r="E756" s="16"/>
-      <c r="F756" s="16"/>
-      <c r="G756" s="16"/>
+      <c r="D756" s="20"/>
+      <c r="E756" s="18"/>
+      <c r="F756" s="18"/>
+      <c r="G756" s="18"/>
       <c r="H756" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I756" s="17"/>
-      <c r="J756" s="17"/>
+      <c r="I756" s="19"/>
+      <c r="J756" s="19"/>
       <c r="K756" s="10" t="s">
         <v>20</v>
       </c>
@@ -36090,17 +36123,17 @@
     </row>
     <row r="757" ht="18.0" customHeight="1">
       <c r="A757" s="6"/>
-      <c r="B757" s="15"/>
+      <c r="B757" s="16"/>
       <c r="C757" s="14"/>
-      <c r="D757" s="19"/>
-      <c r="E757" s="16"/>
-      <c r="F757" s="16"/>
-      <c r="G757" s="16"/>
+      <c r="D757" s="20"/>
+      <c r="E757" s="18"/>
+      <c r="F757" s="18"/>
+      <c r="G757" s="18"/>
       <c r="H757" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I757" s="17"/>
-      <c r="J757" s="17"/>
+      <c r="I757" s="19"/>
+      <c r="J757" s="19"/>
       <c r="K757" s="10" t="s">
         <v>20</v>
       </c>
@@ -36116,17 +36149,17 @@
     </row>
     <row r="758" ht="18.0" customHeight="1">
       <c r="A758" s="6"/>
-      <c r="B758" s="15"/>
+      <c r="B758" s="16"/>
       <c r="C758" s="14"/>
-      <c r="D758" s="19"/>
-      <c r="E758" s="16"/>
-      <c r="F758" s="16"/>
-      <c r="G758" s="16"/>
+      <c r="D758" s="20"/>
+      <c r="E758" s="18"/>
+      <c r="F758" s="18"/>
+      <c r="G758" s="18"/>
       <c r="H758" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I758" s="17"/>
-      <c r="J758" s="17"/>
+      <c r="I758" s="19"/>
+      <c r="J758" s="19"/>
       <c r="K758" s="10" t="s">
         <v>20</v>
       </c>
@@ -36142,17 +36175,17 @@
     </row>
     <row r="759" ht="18.0" customHeight="1">
       <c r="A759" s="6"/>
-      <c r="B759" s="15"/>
+      <c r="B759" s="16"/>
       <c r="C759" s="14"/>
-      <c r="D759" s="19"/>
-      <c r="E759" s="16"/>
-      <c r="F759" s="16"/>
-      <c r="G759" s="16"/>
+      <c r="D759" s="20"/>
+      <c r="E759" s="18"/>
+      <c r="F759" s="18"/>
+      <c r="G759" s="18"/>
       <c r="H759" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I759" s="17"/>
-      <c r="J759" s="17"/>
+      <c r="I759" s="19"/>
+      <c r="J759" s="19"/>
       <c r="K759" s="10" t="s">
         <v>20</v>
       </c>
@@ -36168,17 +36201,17 @@
     </row>
     <row r="760" ht="18.0" customHeight="1">
       <c r="A760" s="6"/>
-      <c r="B760" s="15"/>
+      <c r="B760" s="16"/>
       <c r="C760" s="14"/>
-      <c r="D760" s="19"/>
-      <c r="E760" s="16"/>
-      <c r="F760" s="16"/>
-      <c r="G760" s="16"/>
+      <c r="D760" s="20"/>
+      <c r="E760" s="18"/>
+      <c r="F760" s="18"/>
+      <c r="G760" s="18"/>
       <c r="H760" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I760" s="17"/>
-      <c r="J760" s="17"/>
+      <c r="I760" s="19"/>
+      <c r="J760" s="19"/>
       <c r="K760" s="10" t="s">
         <v>20</v>
       </c>
@@ -36194,17 +36227,17 @@
     </row>
     <row r="761" ht="18.0" customHeight="1">
       <c r="A761" s="6"/>
-      <c r="B761" s="15"/>
+      <c r="B761" s="16"/>
       <c r="C761" s="14"/>
-      <c r="D761" s="19"/>
-      <c r="E761" s="16"/>
-      <c r="F761" s="16"/>
-      <c r="G761" s="16"/>
+      <c r="D761" s="20"/>
+      <c r="E761" s="18"/>
+      <c r="F761" s="18"/>
+      <c r="G761" s="18"/>
       <c r="H761" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I761" s="17"/>
-      <c r="J761" s="17"/>
+      <c r="I761" s="19"/>
+      <c r="J761" s="19"/>
       <c r="K761" s="10" t="s">
         <v>20</v>
       </c>
@@ -36220,17 +36253,17 @@
     </row>
     <row r="762" ht="18.0" customHeight="1">
       <c r="A762" s="6"/>
-      <c r="B762" s="15"/>
+      <c r="B762" s="16"/>
       <c r="C762" s="14"/>
-      <c r="D762" s="19"/>
-      <c r="E762" s="16"/>
-      <c r="F762" s="16"/>
-      <c r="G762" s="16"/>
+      <c r="D762" s="20"/>
+      <c r="E762" s="18"/>
+      <c r="F762" s="18"/>
+      <c r="G762" s="18"/>
       <c r="H762" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I762" s="17"/>
-      <c r="J762" s="17"/>
+      <c r="I762" s="19"/>
+      <c r="J762" s="19"/>
       <c r="K762" s="10" t="s">
         <v>20</v>
       </c>
@@ -36246,17 +36279,17 @@
     </row>
     <row r="763" ht="18.0" customHeight="1">
       <c r="A763" s="6"/>
-      <c r="B763" s="15"/>
+      <c r="B763" s="16"/>
       <c r="C763" s="14"/>
-      <c r="D763" s="19"/>
-      <c r="E763" s="16"/>
-      <c r="F763" s="16"/>
-      <c r="G763" s="16"/>
+      <c r="D763" s="20"/>
+      <c r="E763" s="18"/>
+      <c r="F763" s="18"/>
+      <c r="G763" s="18"/>
       <c r="H763" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I763" s="17"/>
-      <c r="J763" s="17"/>
+      <c r="I763" s="19"/>
+      <c r="J763" s="19"/>
       <c r="K763" s="10" t="s">
         <v>20</v>
       </c>
@@ -36272,17 +36305,17 @@
     </row>
     <row r="764" ht="18.0" customHeight="1">
       <c r="A764" s="6"/>
-      <c r="B764" s="15"/>
+      <c r="B764" s="16"/>
       <c r="C764" s="14"/>
-      <c r="D764" s="19"/>
-      <c r="E764" s="16"/>
-      <c r="F764" s="16"/>
-      <c r="G764" s="16"/>
+      <c r="D764" s="20"/>
+      <c r="E764" s="18"/>
+      <c r="F764" s="18"/>
+      <c r="G764" s="18"/>
       <c r="H764" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I764" s="17"/>
-      <c r="J764" s="17"/>
+      <c r="I764" s="19"/>
+      <c r="J764" s="19"/>
       <c r="K764" s="10" t="s">
         <v>20</v>
       </c>
@@ -36298,17 +36331,17 @@
     </row>
     <row r="765" ht="18.0" customHeight="1">
       <c r="A765" s="6"/>
-      <c r="B765" s="15"/>
+      <c r="B765" s="16"/>
       <c r="C765" s="14"/>
-      <c r="D765" s="19"/>
-      <c r="E765" s="16"/>
-      <c r="F765" s="16"/>
-      <c r="G765" s="16"/>
+      <c r="D765" s="20"/>
+      <c r="E765" s="18"/>
+      <c r="F765" s="18"/>
+      <c r="G765" s="18"/>
       <c r="H765" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I765" s="17"/>
-      <c r="J765" s="17"/>
+      <c r="I765" s="19"/>
+      <c r="J765" s="19"/>
       <c r="K765" s="10" t="s">
         <v>20</v>
       </c>
@@ -36324,17 +36357,17 @@
     </row>
     <row r="766" ht="18.0" customHeight="1">
       <c r="A766" s="6"/>
-      <c r="B766" s="15"/>
+      <c r="B766" s="16"/>
       <c r="C766" s="14"/>
-      <c r="D766" s="19"/>
-      <c r="E766" s="16"/>
-      <c r="F766" s="16"/>
-      <c r="G766" s="16"/>
+      <c r="D766" s="20"/>
+      <c r="E766" s="18"/>
+      <c r="F766" s="18"/>
+      <c r="G766" s="18"/>
       <c r="H766" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I766" s="17"/>
-      <c r="J766" s="17"/>
+      <c r="I766" s="19"/>
+      <c r="J766" s="19"/>
       <c r="K766" s="10" t="s">
         <v>20</v>
       </c>
@@ -36350,17 +36383,17 @@
     </row>
     <row r="767" ht="18.0" customHeight="1">
       <c r="A767" s="6"/>
-      <c r="B767" s="15"/>
+      <c r="B767" s="16"/>
       <c r="C767" s="14"/>
-      <c r="D767" s="19"/>
-      <c r="E767" s="16"/>
-      <c r="F767" s="16"/>
-      <c r="G767" s="16"/>
+      <c r="D767" s="20"/>
+      <c r="E767" s="18"/>
+      <c r="F767" s="18"/>
+      <c r="G767" s="18"/>
       <c r="H767" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I767" s="17"/>
-      <c r="J767" s="17"/>
+      <c r="I767" s="19"/>
+      <c r="J767" s="19"/>
       <c r="K767" s="10" t="s">
         <v>20</v>
       </c>
@@ -36376,17 +36409,17 @@
     </row>
     <row r="768" ht="18.0" customHeight="1">
       <c r="A768" s="6"/>
-      <c r="B768" s="15"/>
+      <c r="B768" s="16"/>
       <c r="C768" s="14"/>
-      <c r="D768" s="19"/>
-      <c r="E768" s="16"/>
-      <c r="F768" s="16"/>
-      <c r="G768" s="16"/>
+      <c r="D768" s="20"/>
+      <c r="E768" s="18"/>
+      <c r="F768" s="18"/>
+      <c r="G768" s="18"/>
       <c r="H768" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I768" s="17"/>
-      <c r="J768" s="17"/>
+      <c r="I768" s="19"/>
+      <c r="J768" s="19"/>
       <c r="K768" s="10" t="s">
         <v>20</v>
       </c>
@@ -36402,17 +36435,17 @@
     </row>
     <row r="769" ht="18.0" customHeight="1">
       <c r="A769" s="6"/>
-      <c r="B769" s="15"/>
+      <c r="B769" s="16"/>
       <c r="C769" s="14"/>
-      <c r="D769" s="19"/>
-      <c r="E769" s="16"/>
-      <c r="F769" s="16"/>
-      <c r="G769" s="16"/>
+      <c r="D769" s="20"/>
+      <c r="E769" s="18"/>
+      <c r="F769" s="18"/>
+      <c r="G769" s="18"/>
       <c r="H769" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I769" s="17"/>
-      <c r="J769" s="17"/>
+      <c r="I769" s="19"/>
+      <c r="J769" s="19"/>
       <c r="K769" s="10" t="s">
         <v>20</v>
       </c>
@@ -36428,17 +36461,17 @@
     </row>
     <row r="770" ht="18.0" customHeight="1">
       <c r="A770" s="6"/>
-      <c r="B770" s="15"/>
+      <c r="B770" s="16"/>
       <c r="C770" s="14"/>
-      <c r="D770" s="19"/>
-      <c r="E770" s="16"/>
-      <c r="F770" s="16"/>
-      <c r="G770" s="16"/>
+      <c r="D770" s="20"/>
+      <c r="E770" s="18"/>
+      <c r="F770" s="18"/>
+      <c r="G770" s="18"/>
       <c r="H770" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I770" s="17"/>
-      <c r="J770" s="17"/>
+      <c r="I770" s="19"/>
+      <c r="J770" s="19"/>
       <c r="K770" s="10" t="s">
         <v>20</v>
       </c>
@@ -36454,17 +36487,17 @@
     </row>
     <row r="771" ht="18.0" customHeight="1">
       <c r="A771" s="6"/>
-      <c r="B771" s="15"/>
+      <c r="B771" s="16"/>
       <c r="C771" s="14"/>
-      <c r="D771" s="19"/>
-      <c r="E771" s="16"/>
-      <c r="F771" s="16"/>
-      <c r="G771" s="16"/>
+      <c r="D771" s="20"/>
+      <c r="E771" s="18"/>
+      <c r="F771" s="18"/>
+      <c r="G771" s="18"/>
       <c r="H771" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I771" s="17"/>
-      <c r="J771" s="17"/>
+      <c r="I771" s="19"/>
+      <c r="J771" s="19"/>
       <c r="K771" s="10" t="s">
         <v>20</v>
       </c>
@@ -36480,17 +36513,17 @@
     </row>
     <row r="772" ht="18.0" customHeight="1">
       <c r="A772" s="6"/>
-      <c r="B772" s="15"/>
+      <c r="B772" s="16"/>
       <c r="C772" s="14"/>
-      <c r="D772" s="19"/>
-      <c r="E772" s="16"/>
-      <c r="F772" s="16"/>
-      <c r="G772" s="16"/>
+      <c r="D772" s="20"/>
+      <c r="E772" s="18"/>
+      <c r="F772" s="18"/>
+      <c r="G772" s="18"/>
       <c r="H772" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I772" s="17"/>
-      <c r="J772" s="17"/>
+      <c r="I772" s="19"/>
+      <c r="J772" s="19"/>
       <c r="K772" s="10" t="s">
         <v>20</v>
       </c>
@@ -36506,17 +36539,17 @@
     </row>
     <row r="773" ht="18.0" customHeight="1">
       <c r="A773" s="6"/>
-      <c r="B773" s="15"/>
+      <c r="B773" s="16"/>
       <c r="C773" s="14"/>
-      <c r="D773" s="19"/>
-      <c r="E773" s="16"/>
-      <c r="F773" s="16"/>
-      <c r="G773" s="16"/>
+      <c r="D773" s="20"/>
+      <c r="E773" s="18"/>
+      <c r="F773" s="18"/>
+      <c r="G773" s="18"/>
       <c r="H773" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I773" s="17"/>
-      <c r="J773" s="17"/>
+      <c r="I773" s="19"/>
+      <c r="J773" s="19"/>
       <c r="K773" s="10" t="s">
         <v>20</v>
       </c>
@@ -36532,17 +36565,17 @@
     </row>
     <row r="774" ht="18.0" customHeight="1">
       <c r="A774" s="6"/>
-      <c r="B774" s="15"/>
+      <c r="B774" s="16"/>
       <c r="C774" s="14"/>
-      <c r="D774" s="19"/>
-      <c r="E774" s="16"/>
-      <c r="F774" s="16"/>
-      <c r="G774" s="16"/>
+      <c r="D774" s="20"/>
+      <c r="E774" s="18"/>
+      <c r="F774" s="18"/>
+      <c r="G774" s="18"/>
       <c r="H774" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I774" s="17"/>
-      <c r="J774" s="17"/>
+      <c r="I774" s="19"/>
+      <c r="J774" s="19"/>
       <c r="K774" s="10" t="s">
         <v>20</v>
       </c>
@@ -36558,17 +36591,17 @@
     </row>
     <row r="775" ht="18.0" customHeight="1">
       <c r="A775" s="6"/>
-      <c r="B775" s="15"/>
+      <c r="B775" s="16"/>
       <c r="C775" s="14"/>
-      <c r="D775" s="19"/>
-      <c r="E775" s="16"/>
-      <c r="F775" s="16"/>
-      <c r="G775" s="16"/>
+      <c r="D775" s="20"/>
+      <c r="E775" s="18"/>
+      <c r="F775" s="18"/>
+      <c r="G775" s="18"/>
       <c r="H775" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I775" s="17"/>
-      <c r="J775" s="17"/>
+      <c r="I775" s="19"/>
+      <c r="J775" s="19"/>
       <c r="K775" s="10" t="s">
         <v>20</v>
       </c>
@@ -36584,17 +36617,17 @@
     </row>
     <row r="776" ht="18.0" customHeight="1">
       <c r="A776" s="6"/>
-      <c r="B776" s="15"/>
+      <c r="B776" s="16"/>
       <c r="C776" s="14"/>
-      <c r="D776" s="19"/>
-      <c r="E776" s="16"/>
-      <c r="F776" s="16"/>
-      <c r="G776" s="16"/>
+      <c r="D776" s="20"/>
+      <c r="E776" s="18"/>
+      <c r="F776" s="18"/>
+      <c r="G776" s="18"/>
       <c r="H776" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I776" s="17"/>
-      <c r="J776" s="17"/>
+      <c r="I776" s="19"/>
+      <c r="J776" s="19"/>
       <c r="K776" s="10" t="s">
         <v>20</v>
       </c>
@@ -36610,17 +36643,17 @@
     </row>
     <row r="777" ht="18.0" customHeight="1">
       <c r="A777" s="6"/>
-      <c r="B777" s="15"/>
+      <c r="B777" s="16"/>
       <c r="C777" s="14"/>
-      <c r="D777" s="19"/>
-      <c r="E777" s="16"/>
-      <c r="F777" s="16"/>
-      <c r="G777" s="16"/>
+      <c r="D777" s="20"/>
+      <c r="E777" s="18"/>
+      <c r="F777" s="18"/>
+      <c r="G777" s="18"/>
       <c r="H777" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I777" s="17"/>
-      <c r="J777" s="17"/>
+      <c r="I777" s="19"/>
+      <c r="J777" s="19"/>
       <c r="K777" s="10" t="s">
         <v>20</v>
       </c>
@@ -36636,17 +36669,17 @@
     </row>
     <row r="778" ht="18.0" customHeight="1">
       <c r="A778" s="6"/>
-      <c r="B778" s="15"/>
+      <c r="B778" s="16"/>
       <c r="C778" s="14"/>
-      <c r="D778" s="19"/>
-      <c r="E778" s="16"/>
-      <c r="F778" s="16"/>
-      <c r="G778" s="16"/>
+      <c r="D778" s="20"/>
+      <c r="E778" s="18"/>
+      <c r="F778" s="18"/>
+      <c r="G778" s="18"/>
       <c r="H778" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I778" s="17"/>
-      <c r="J778" s="17"/>
+      <c r="I778" s="19"/>
+      <c r="J778" s="19"/>
       <c r="K778" s="10" t="s">
         <v>20</v>
       </c>
@@ -36662,17 +36695,17 @@
     </row>
     <row r="779" ht="18.0" customHeight="1">
       <c r="A779" s="6"/>
-      <c r="B779" s="15"/>
+      <c r="B779" s="16"/>
       <c r="C779" s="14"/>
-      <c r="D779" s="19"/>
-      <c r="E779" s="16"/>
-      <c r="F779" s="16"/>
-      <c r="G779" s="16"/>
+      <c r="D779" s="20"/>
+      <c r="E779" s="18"/>
+      <c r="F779" s="18"/>
+      <c r="G779" s="18"/>
       <c r="H779" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I779" s="17"/>
-      <c r="J779" s="17"/>
+      <c r="I779" s="19"/>
+      <c r="J779" s="19"/>
       <c r="K779" s="10" t="s">
         <v>20</v>
       </c>
@@ -36688,17 +36721,17 @@
     </row>
     <row r="780" ht="18.0" customHeight="1">
       <c r="A780" s="6"/>
-      <c r="B780" s="15"/>
+      <c r="B780" s="16"/>
       <c r="C780" s="14"/>
-      <c r="D780" s="19"/>
-      <c r="E780" s="16"/>
-      <c r="F780" s="16"/>
-      <c r="G780" s="16"/>
+      <c r="D780" s="20"/>
+      <c r="E780" s="18"/>
+      <c r="F780" s="18"/>
+      <c r="G780" s="18"/>
       <c r="H780" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I780" s="17"/>
-      <c r="J780" s="17"/>
+      <c r="I780" s="19"/>
+      <c r="J780" s="19"/>
       <c r="K780" s="10" t="s">
         <v>20</v>
       </c>
@@ -36714,17 +36747,17 @@
     </row>
     <row r="781" ht="18.0" customHeight="1">
       <c r="A781" s="6"/>
-      <c r="B781" s="15"/>
+      <c r="B781" s="16"/>
       <c r="C781" s="14"/>
-      <c r="D781" s="19"/>
-      <c r="E781" s="16"/>
-      <c r="F781" s="16"/>
-      <c r="G781" s="16"/>
+      <c r="D781" s="20"/>
+      <c r="E781" s="18"/>
+      <c r="F781" s="18"/>
+      <c r="G781" s="18"/>
       <c r="H781" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I781" s="17"/>
-      <c r="J781" s="17"/>
+      <c r="I781" s="19"/>
+      <c r="J781" s="19"/>
       <c r="K781" s="10" t="s">
         <v>20</v>
       </c>
@@ -36740,17 +36773,17 @@
     </row>
     <row r="782" ht="18.0" customHeight="1">
       <c r="A782" s="6"/>
-      <c r="B782" s="15"/>
+      <c r="B782" s="16"/>
       <c r="C782" s="14"/>
-      <c r="D782" s="19"/>
-      <c r="E782" s="16"/>
-      <c r="F782" s="16"/>
-      <c r="G782" s="16"/>
+      <c r="D782" s="20"/>
+      <c r="E782" s="18"/>
+      <c r="F782" s="18"/>
+      <c r="G782" s="18"/>
       <c r="H782" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I782" s="17"/>
-      <c r="J782" s="17"/>
+      <c r="I782" s="19"/>
+      <c r="J782" s="19"/>
       <c r="K782" s="10" t="s">
         <v>20</v>
       </c>
@@ -36766,17 +36799,17 @@
     </row>
     <row r="783" ht="18.0" customHeight="1">
       <c r="A783" s="6"/>
-      <c r="B783" s="15"/>
+      <c r="B783" s="16"/>
       <c r="C783" s="14"/>
-      <c r="D783" s="19"/>
-      <c r="E783" s="16"/>
-      <c r="F783" s="16"/>
-      <c r="G783" s="16"/>
+      <c r="D783" s="20"/>
+      <c r="E783" s="18"/>
+      <c r="F783" s="18"/>
+      <c r="G783" s="18"/>
       <c r="H783" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I783" s="17"/>
-      <c r="J783" s="17"/>
+      <c r="I783" s="19"/>
+      <c r="J783" s="19"/>
       <c r="K783" s="10" t="s">
         <v>20</v>
       </c>
@@ -36792,17 +36825,17 @@
     </row>
     <row r="784" ht="18.0" customHeight="1">
       <c r="A784" s="6"/>
-      <c r="B784" s="15"/>
+      <c r="B784" s="16"/>
       <c r="C784" s="14"/>
-      <c r="D784" s="19"/>
-      <c r="E784" s="16"/>
-      <c r="F784" s="16"/>
-      <c r="G784" s="16"/>
+      <c r="D784" s="20"/>
+      <c r="E784" s="18"/>
+      <c r="F784" s="18"/>
+      <c r="G784" s="18"/>
       <c r="H784" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I784" s="17"/>
-      <c r="J784" s="17"/>
+      <c r="I784" s="19"/>
+      <c r="J784" s="19"/>
       <c r="K784" s="10" t="s">
         <v>20</v>
       </c>
@@ -36818,17 +36851,17 @@
     </row>
     <row r="785" ht="18.0" customHeight="1">
       <c r="A785" s="6"/>
-      <c r="B785" s="15"/>
+      <c r="B785" s="16"/>
       <c r="C785" s="14"/>
-      <c r="D785" s="19"/>
-      <c r="E785" s="16"/>
-      <c r="F785" s="16"/>
-      <c r="G785" s="16"/>
+      <c r="D785" s="20"/>
+      <c r="E785" s="18"/>
+      <c r="F785" s="18"/>
+      <c r="G785" s="18"/>
       <c r="H785" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I785" s="17"/>
-      <c r="J785" s="17"/>
+      <c r="I785" s="19"/>
+      <c r="J785" s="19"/>
       <c r="K785" s="10" t="s">
         <v>20</v>
       </c>
@@ -36844,17 +36877,17 @@
     </row>
     <row r="786" ht="18.0" customHeight="1">
       <c r="A786" s="6"/>
-      <c r="B786" s="15"/>
+      <c r="B786" s="16"/>
       <c r="C786" s="14"/>
-      <c r="D786" s="19"/>
-      <c r="E786" s="16"/>
-      <c r="F786" s="16"/>
-      <c r="G786" s="16"/>
+      <c r="D786" s="20"/>
+      <c r="E786" s="18"/>
+      <c r="F786" s="18"/>
+      <c r="G786" s="18"/>
       <c r="H786" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I786" s="17"/>
-      <c r="J786" s="17"/>
+      <c r="I786" s="19"/>
+      <c r="J786" s="19"/>
       <c r="K786" s="10" t="s">
         <v>20</v>
       </c>
@@ -36870,17 +36903,17 @@
     </row>
     <row r="787" ht="18.0" customHeight="1">
       <c r="A787" s="6"/>
-      <c r="B787" s="15"/>
+      <c r="B787" s="16"/>
       <c r="C787" s="14"/>
-      <c r="D787" s="19"/>
-      <c r="E787" s="16"/>
-      <c r="F787" s="16"/>
-      <c r="G787" s="16"/>
+      <c r="D787" s="20"/>
+      <c r="E787" s="18"/>
+      <c r="F787" s="18"/>
+      <c r="G787" s="18"/>
       <c r="H787" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I787" s="17"/>
-      <c r="J787" s="17"/>
+      <c r="I787" s="19"/>
+      <c r="J787" s="19"/>
       <c r="K787" s="10" t="s">
         <v>20</v>
       </c>
@@ -36896,17 +36929,17 @@
     </row>
     <row r="788" ht="18.0" customHeight="1">
       <c r="A788" s="6"/>
-      <c r="B788" s="15"/>
+      <c r="B788" s="16"/>
       <c r="C788" s="14"/>
-      <c r="D788" s="19"/>
-      <c r="E788" s="16"/>
-      <c r="F788" s="16"/>
-      <c r="G788" s="16"/>
+      <c r="D788" s="20"/>
+      <c r="E788" s="18"/>
+      <c r="F788" s="18"/>
+      <c r="G788" s="18"/>
       <c r="H788" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I788" s="17"/>
-      <c r="J788" s="17"/>
+      <c r="I788" s="19"/>
+      <c r="J788" s="19"/>
       <c r="K788" s="10" t="s">
         <v>20</v>
       </c>
@@ -36922,17 +36955,17 @@
     </row>
     <row r="789" ht="18.0" customHeight="1">
       <c r="A789" s="6"/>
-      <c r="B789" s="15"/>
+      <c r="B789" s="16"/>
       <c r="C789" s="14"/>
-      <c r="D789" s="19"/>
-      <c r="E789" s="16"/>
-      <c r="F789" s="16"/>
-      <c r="G789" s="16"/>
+      <c r="D789" s="20"/>
+      <c r="E789" s="18"/>
+      <c r="F789" s="18"/>
+      <c r="G789" s="18"/>
       <c r="H789" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I789" s="17"/>
-      <c r="J789" s="17"/>
+      <c r="I789" s="19"/>
+      <c r="J789" s="19"/>
       <c r="K789" s="10" t="s">
         <v>20</v>
       </c>
@@ -36948,17 +36981,17 @@
     </row>
     <row r="790" ht="18.0" customHeight="1">
       <c r="A790" s="6"/>
-      <c r="B790" s="15"/>
+      <c r="B790" s="16"/>
       <c r="C790" s="14"/>
-      <c r="D790" s="19"/>
-      <c r="E790" s="16"/>
-      <c r="F790" s="16"/>
-      <c r="G790" s="16"/>
+      <c r="D790" s="20"/>
+      <c r="E790" s="18"/>
+      <c r="F790" s="18"/>
+      <c r="G790" s="18"/>
       <c r="H790" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I790" s="17"/>
-      <c r="J790" s="17"/>
+      <c r="I790" s="19"/>
+      <c r="J790" s="19"/>
       <c r="K790" s="10" t="s">
         <v>20</v>
       </c>
@@ -36974,17 +37007,17 @@
     </row>
     <row r="791" ht="18.0" customHeight="1">
       <c r="A791" s="6"/>
-      <c r="B791" s="15"/>
+      <c r="B791" s="16"/>
       <c r="C791" s="14"/>
-      <c r="D791" s="19"/>
-      <c r="E791" s="16"/>
-      <c r="F791" s="16"/>
-      <c r="G791" s="16"/>
+      <c r="D791" s="20"/>
+      <c r="E791" s="18"/>
+      <c r="F791" s="18"/>
+      <c r="G791" s="18"/>
       <c r="H791" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I791" s="17"/>
-      <c r="J791" s="17"/>
+      <c r="I791" s="19"/>
+      <c r="J791" s="19"/>
       <c r="K791" s="10" t="s">
         <v>20</v>
       </c>
@@ -37000,17 +37033,17 @@
     </row>
     <row r="792" ht="18.0" customHeight="1">
       <c r="A792" s="6"/>
-      <c r="B792" s="15"/>
+      <c r="B792" s="16"/>
       <c r="C792" s="14"/>
-      <c r="D792" s="19"/>
-      <c r="E792" s="16"/>
-      <c r="F792" s="16"/>
-      <c r="G792" s="16"/>
+      <c r="D792" s="20"/>
+      <c r="E792" s="18"/>
+      <c r="F792" s="18"/>
+      <c r="G792" s="18"/>
       <c r="H792" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I792" s="17"/>
-      <c r="J792" s="17"/>
+      <c r="I792" s="19"/>
+      <c r="J792" s="19"/>
       <c r="K792" s="10" t="s">
         <v>20</v>
       </c>
@@ -37026,17 +37059,17 @@
     </row>
     <row r="793" ht="18.0" customHeight="1">
       <c r="A793" s="6"/>
-      <c r="B793" s="15"/>
+      <c r="B793" s="16"/>
       <c r="C793" s="14"/>
-      <c r="D793" s="19"/>
-      <c r="E793" s="16"/>
-      <c r="F793" s="16"/>
-      <c r="G793" s="16"/>
+      <c r="D793" s="20"/>
+      <c r="E793" s="18"/>
+      <c r="F793" s="18"/>
+      <c r="G793" s="18"/>
       <c r="H793" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I793" s="17"/>
-      <c r="J793" s="17"/>
+      <c r="I793" s="19"/>
+      <c r="J793" s="19"/>
       <c r="K793" s="10" t="s">
         <v>20</v>
       </c>
@@ -37052,17 +37085,17 @@
     </row>
     <row r="794" ht="18.0" customHeight="1">
       <c r="A794" s="6"/>
-      <c r="B794" s="15"/>
+      <c r="B794" s="16"/>
       <c r="C794" s="14"/>
-      <c r="D794" s="19"/>
-      <c r="E794" s="16"/>
-      <c r="F794" s="16"/>
-      <c r="G794" s="16"/>
+      <c r="D794" s="20"/>
+      <c r="E794" s="18"/>
+      <c r="F794" s="18"/>
+      <c r="G794" s="18"/>
       <c r="H794" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I794" s="17"/>
-      <c r="J794" s="17"/>
+      <c r="I794" s="19"/>
+      <c r="J794" s="19"/>
       <c r="K794" s="10" t="s">
         <v>20</v>
       </c>
@@ -37078,17 +37111,17 @@
     </row>
     <row r="795" ht="18.0" customHeight="1">
       <c r="A795" s="6"/>
-      <c r="B795" s="15"/>
+      <c r="B795" s="16"/>
       <c r="C795" s="14"/>
-      <c r="D795" s="19"/>
-      <c r="E795" s="16"/>
-      <c r="F795" s="16"/>
-      <c r="G795" s="16"/>
+      <c r="D795" s="20"/>
+      <c r="E795" s="18"/>
+      <c r="F795" s="18"/>
+      <c r="G795" s="18"/>
       <c r="H795" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I795" s="17"/>
-      <c r="J795" s="17"/>
+      <c r="I795" s="19"/>
+      <c r="J795" s="19"/>
       <c r="K795" s="10" t="s">
         <v>20</v>
       </c>
@@ -37104,17 +37137,17 @@
     </row>
     <row r="796" ht="18.0" customHeight="1">
       <c r="A796" s="6"/>
-      <c r="B796" s="15"/>
+      <c r="B796" s="16"/>
       <c r="C796" s="14"/>
-      <c r="D796" s="19"/>
-      <c r="E796" s="16"/>
-      <c r="F796" s="16"/>
-      <c r="G796" s="16"/>
+      <c r="D796" s="20"/>
+      <c r="E796" s="18"/>
+      <c r="F796" s="18"/>
+      <c r="G796" s="18"/>
       <c r="H796" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I796" s="17"/>
-      <c r="J796" s="17"/>
+      <c r="I796" s="19"/>
+      <c r="J796" s="19"/>
       <c r="K796" s="10" t="s">
         <v>20</v>
       </c>
@@ -37130,17 +37163,17 @@
     </row>
     <row r="797" ht="18.0" customHeight="1">
       <c r="A797" s="6"/>
-      <c r="B797" s="15"/>
+      <c r="B797" s="16"/>
       <c r="C797" s="14"/>
-      <c r="D797" s="19"/>
-      <c r="E797" s="16"/>
-      <c r="F797" s="16"/>
-      <c r="G797" s="16"/>
+      <c r="D797" s="20"/>
+      <c r="E797" s="18"/>
+      <c r="F797" s="18"/>
+      <c r="G797" s="18"/>
       <c r="H797" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I797" s="17"/>
-      <c r="J797" s="17"/>
+      <c r="I797" s="19"/>
+      <c r="J797" s="19"/>
       <c r="K797" s="10" t="s">
         <v>20</v>
       </c>
@@ -37156,17 +37189,17 @@
     </row>
     <row r="798" ht="18.0" customHeight="1">
       <c r="A798" s="6"/>
-      <c r="B798" s="15"/>
+      <c r="B798" s="16"/>
       <c r="C798" s="14"/>
-      <c r="D798" s="19"/>
-      <c r="E798" s="16"/>
-      <c r="F798" s="16"/>
-      <c r="G798" s="16"/>
+      <c r="D798" s="20"/>
+      <c r="E798" s="18"/>
+      <c r="F798" s="18"/>
+      <c r="G798" s="18"/>
       <c r="H798" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I798" s="17"/>
-      <c r="J798" s="17"/>
+      <c r="I798" s="19"/>
+      <c r="J798" s="19"/>
       <c r="K798" s="10" t="s">
         <v>20</v>
       </c>
@@ -37182,17 +37215,17 @@
     </row>
     <row r="799" ht="18.0" customHeight="1">
       <c r="A799" s="6"/>
-      <c r="B799" s="15"/>
+      <c r="B799" s="16"/>
       <c r="C799" s="14"/>
-      <c r="D799" s="19"/>
-      <c r="E799" s="16"/>
-      <c r="F799" s="16"/>
-      <c r="G799" s="16"/>
+      <c r="D799" s="20"/>
+      <c r="E799" s="18"/>
+      <c r="F799" s="18"/>
+      <c r="G799" s="18"/>
       <c r="H799" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I799" s="17"/>
-      <c r="J799" s="17"/>
+      <c r="I799" s="19"/>
+      <c r="J799" s="19"/>
       <c r="K799" s="10" t="s">
         <v>20</v>
       </c>
@@ -37208,17 +37241,17 @@
     </row>
     <row r="800" ht="18.0" customHeight="1">
       <c r="A800" s="6"/>
-      <c r="B800" s="15"/>
+      <c r="B800" s="16"/>
       <c r="C800" s="14"/>
-      <c r="D800" s="19"/>
-      <c r="E800" s="16"/>
-      <c r="F800" s="16"/>
-      <c r="G800" s="16"/>
+      <c r="D800" s="20"/>
+      <c r="E800" s="18"/>
+      <c r="F800" s="18"/>
+      <c r="G800" s="18"/>
       <c r="H800" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I800" s="17"/>
-      <c r="J800" s="17"/>
+      <c r="I800" s="19"/>
+      <c r="J800" s="19"/>
       <c r="K800" s="10" t="s">
         <v>20</v>
       </c>
@@ -37234,17 +37267,17 @@
     </row>
     <row r="801" ht="18.0" customHeight="1">
       <c r="A801" s="6"/>
-      <c r="B801" s="15"/>
+      <c r="B801" s="16"/>
       <c r="C801" s="14"/>
-      <c r="D801" s="19"/>
-      <c r="E801" s="16"/>
-      <c r="F801" s="16"/>
-      <c r="G801" s="16"/>
+      <c r="D801" s="20"/>
+      <c r="E801" s="18"/>
+      <c r="F801" s="18"/>
+      <c r="G801" s="18"/>
       <c r="H801" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I801" s="17"/>
-      <c r="J801" s="17"/>
+      <c r="I801" s="19"/>
+      <c r="J801" s="19"/>
       <c r="K801" s="10" t="s">
         <v>20</v>
       </c>
@@ -37260,17 +37293,17 @@
     </row>
     <row r="802" ht="18.0" customHeight="1">
       <c r="A802" s="6"/>
-      <c r="B802" s="15"/>
+      <c r="B802" s="16"/>
       <c r="C802" s="14"/>
-      <c r="D802" s="19"/>
-      <c r="E802" s="16"/>
-      <c r="F802" s="16"/>
-      <c r="G802" s="16"/>
+      <c r="D802" s="20"/>
+      <c r="E802" s="18"/>
+      <c r="F802" s="18"/>
+      <c r="G802" s="18"/>
       <c r="H802" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I802" s="17"/>
-      <c r="J802" s="17"/>
+      <c r="I802" s="19"/>
+      <c r="J802" s="19"/>
       <c r="K802" s="10" t="s">
         <v>20</v>
       </c>
@@ -37286,17 +37319,17 @@
     </row>
     <row r="803" ht="18.0" customHeight="1">
       <c r="A803" s="6"/>
-      <c r="B803" s="15"/>
+      <c r="B803" s="16"/>
       <c r="C803" s="14"/>
-      <c r="D803" s="19"/>
-      <c r="E803" s="16"/>
-      <c r="F803" s="16"/>
-      <c r="G803" s="16"/>
+      <c r="D803" s="20"/>
+      <c r="E803" s="18"/>
+      <c r="F803" s="18"/>
+      <c r="G803" s="18"/>
       <c r="H803" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I803" s="17"/>
-      <c r="J803" s="17"/>
+      <c r="I803" s="19"/>
+      <c r="J803" s="19"/>
       <c r="K803" s="10" t="s">
         <v>20</v>
       </c>
@@ -37312,17 +37345,17 @@
     </row>
     <row r="804" ht="18.0" customHeight="1">
       <c r="A804" s="6"/>
-      <c r="B804" s="15"/>
+      <c r="B804" s="16"/>
       <c r="C804" s="14"/>
-      <c r="D804" s="19"/>
-      <c r="E804" s="16"/>
-      <c r="F804" s="16"/>
-      <c r="G804" s="16"/>
+      <c r="D804" s="20"/>
+      <c r="E804" s="18"/>
+      <c r="F804" s="18"/>
+      <c r="G804" s="18"/>
       <c r="H804" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I804" s="17"/>
-      <c r="J804" s="17"/>
+      <c r="I804" s="19"/>
+      <c r="J804" s="19"/>
       <c r="K804" s="10" t="s">
         <v>20</v>
       </c>
@@ -37338,17 +37371,17 @@
     </row>
     <row r="805" ht="18.0" customHeight="1">
       <c r="A805" s="6"/>
-      <c r="B805" s="15"/>
+      <c r="B805" s="16"/>
       <c r="C805" s="14"/>
-      <c r="D805" s="19"/>
-      <c r="E805" s="16"/>
-      <c r="F805" s="16"/>
-      <c r="G805" s="16"/>
+      <c r="D805" s="20"/>
+      <c r="E805" s="18"/>
+      <c r="F805" s="18"/>
+      <c r="G805" s="18"/>
       <c r="H805" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I805" s="17"/>
-      <c r="J805" s="17"/>
+      <c r="I805" s="19"/>
+      <c r="J805" s="19"/>
       <c r="K805" s="10" t="s">
         <v>20</v>
       </c>
@@ -37364,17 +37397,17 @@
     </row>
     <row r="806" ht="18.0" customHeight="1">
       <c r="A806" s="6"/>
-      <c r="B806" s="15"/>
+      <c r="B806" s="16"/>
       <c r="C806" s="14"/>
-      <c r="D806" s="19"/>
-      <c r="E806" s="16"/>
-      <c r="F806" s="16"/>
-      <c r="G806" s="16"/>
+      <c r="D806" s="20"/>
+      <c r="E806" s="18"/>
+      <c r="F806" s="18"/>
+      <c r="G806" s="18"/>
       <c r="H806" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I806" s="17"/>
-      <c r="J806" s="17"/>
+      <c r="I806" s="19"/>
+      <c r="J806" s="19"/>
       <c r="K806" s="10" t="s">
         <v>20</v>
       </c>
@@ -37390,17 +37423,17 @@
     </row>
     <row r="807" ht="18.0" customHeight="1">
       <c r="A807" s="6"/>
-      <c r="B807" s="15"/>
+      <c r="B807" s="16"/>
       <c r="C807" s="14"/>
-      <c r="D807" s="19"/>
-      <c r="E807" s="16"/>
-      <c r="F807" s="16"/>
-      <c r="G807" s="16"/>
+      <c r="D807" s="20"/>
+      <c r="E807" s="18"/>
+      <c r="F807" s="18"/>
+      <c r="G807" s="18"/>
       <c r="H807" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I807" s="17"/>
-      <c r="J807" s="17"/>
+      <c r="I807" s="19"/>
+      <c r="J807" s="19"/>
       <c r="K807" s="10" t="s">
         <v>20</v>
       </c>
@@ -37416,17 +37449,17 @@
     </row>
     <row r="808" ht="18.0" customHeight="1">
       <c r="A808" s="6"/>
-      <c r="B808" s="15"/>
+      <c r="B808" s="16"/>
       <c r="C808" s="14"/>
-      <c r="D808" s="19"/>
-      <c r="E808" s="16"/>
-      <c r="F808" s="16"/>
-      <c r="G808" s="16"/>
+      <c r="D808" s="20"/>
+      <c r="E808" s="18"/>
+      <c r="F808" s="18"/>
+      <c r="G808" s="18"/>
       <c r="H808" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I808" s="17"/>
-      <c r="J808" s="17"/>
+      <c r="I808" s="19"/>
+      <c r="J808" s="19"/>
       <c r="K808" s="10" t="s">
         <v>20</v>
       </c>
@@ -37442,17 +37475,17 @@
     </row>
     <row r="809" ht="18.0" customHeight="1">
       <c r="A809" s="6"/>
-      <c r="B809" s="15"/>
+      <c r="B809" s="16"/>
       <c r="C809" s="14"/>
-      <c r="D809" s="19"/>
-      <c r="E809" s="16"/>
-      <c r="F809" s="16"/>
-      <c r="G809" s="16"/>
+      <c r="D809" s="20"/>
+      <c r="E809" s="18"/>
+      <c r="F809" s="18"/>
+      <c r="G809" s="18"/>
       <c r="H809" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I809" s="17"/>
-      <c r="J809" s="17"/>
+      <c r="I809" s="19"/>
+      <c r="J809" s="19"/>
       <c r="K809" s="10" t="s">
         <v>20</v>
       </c>
@@ -37468,17 +37501,17 @@
     </row>
     <row r="810" ht="18.0" customHeight="1">
       <c r="A810" s="6"/>
-      <c r="B810" s="15"/>
+      <c r="B810" s="16"/>
       <c r="C810" s="14"/>
-      <c r="D810" s="19"/>
-      <c r="E810" s="16"/>
-      <c r="F810" s="16"/>
-      <c r="G810" s="16"/>
+      <c r="D810" s="20"/>
+      <c r="E810" s="18"/>
+      <c r="F810" s="18"/>
+      <c r="G810" s="18"/>
       <c r="H810" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I810" s="17"/>
-      <c r="J810" s="17"/>
+      <c r="I810" s="19"/>
+      <c r="J810" s="19"/>
       <c r="K810" s="10" t="s">
         <v>20</v>
       </c>
@@ -37494,17 +37527,17 @@
     </row>
     <row r="811" ht="18.0" customHeight="1">
       <c r="A811" s="6"/>
-      <c r="B811" s="15"/>
+      <c r="B811" s="16"/>
       <c r="C811" s="14"/>
-      <c r="D811" s="19"/>
-      <c r="E811" s="16"/>
-      <c r="F811" s="16"/>
-      <c r="G811" s="16"/>
+      <c r="D811" s="20"/>
+      <c r="E811" s="18"/>
+      <c r="F811" s="18"/>
+      <c r="G811" s="18"/>
       <c r="H811" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I811" s="17"/>
-      <c r="J811" s="17"/>
+      <c r="I811" s="19"/>
+      <c r="J811" s="19"/>
       <c r="K811" s="10" t="s">
         <v>20</v>
       </c>
@@ -37520,17 +37553,17 @@
     </row>
     <row r="812" ht="18.0" customHeight="1">
       <c r="A812" s="6"/>
-      <c r="B812" s="15"/>
+      <c r="B812" s="16"/>
       <c r="C812" s="14"/>
-      <c r="D812" s="19"/>
-      <c r="E812" s="16"/>
-      <c r="F812" s="16"/>
-      <c r="G812" s="16"/>
+      <c r="D812" s="20"/>
+      <c r="E812" s="18"/>
+      <c r="F812" s="18"/>
+      <c r="G812" s="18"/>
       <c r="H812" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I812" s="17"/>
-      <c r="J812" s="17"/>
+      <c r="I812" s="19"/>
+      <c r="J812" s="19"/>
       <c r="K812" s="10" t="s">
         <v>20</v>
       </c>
@@ -37546,17 +37579,17 @@
     </row>
     <row r="813" ht="18.0" customHeight="1">
       <c r="A813" s="6"/>
-      <c r="B813" s="15"/>
+      <c r="B813" s="16"/>
       <c r="C813" s="14"/>
-      <c r="D813" s="19"/>
-      <c r="E813" s="16"/>
-      <c r="F813" s="16"/>
-      <c r="G813" s="16"/>
+      <c r="D813" s="20"/>
+      <c r="E813" s="18"/>
+      <c r="F813" s="18"/>
+      <c r="G813" s="18"/>
       <c r="H813" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I813" s="17"/>
-      <c r="J813" s="17"/>
+      <c r="I813" s="19"/>
+      <c r="J813" s="19"/>
       <c r="K813" s="10" t="s">
         <v>20</v>
       </c>
@@ -37572,17 +37605,17 @@
     </row>
     <row r="814" ht="18.0" customHeight="1">
       <c r="A814" s="6"/>
-      <c r="B814" s="15"/>
+      <c r="B814" s="16"/>
       <c r="C814" s="14"/>
-      <c r="D814" s="19"/>
-      <c r="E814" s="16"/>
-      <c r="F814" s="16"/>
-      <c r="G814" s="16"/>
+      <c r="D814" s="20"/>
+      <c r="E814" s="18"/>
+      <c r="F814" s="18"/>
+      <c r="G814" s="18"/>
       <c r="H814" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I814" s="17"/>
-      <c r="J814" s="17"/>
+      <c r="I814" s="19"/>
+      <c r="J814" s="19"/>
       <c r="K814" s="10" t="s">
         <v>20</v>
       </c>
@@ -37598,17 +37631,17 @@
     </row>
     <row r="815" ht="18.0" customHeight="1">
       <c r="A815" s="6"/>
-      <c r="B815" s="15"/>
+      <c r="B815" s="16"/>
       <c r="C815" s="14"/>
-      <c r="D815" s="19"/>
-      <c r="E815" s="16"/>
-      <c r="F815" s="16"/>
-      <c r="G815" s="16"/>
+      <c r="D815" s="20"/>
+      <c r="E815" s="18"/>
+      <c r="F815" s="18"/>
+      <c r="G815" s="18"/>
       <c r="H815" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I815" s="17"/>
-      <c r="J815" s="17"/>
+      <c r="I815" s="19"/>
+      <c r="J815" s="19"/>
       <c r="K815" s="10" t="s">
         <v>20</v>
       </c>
@@ -37624,17 +37657,17 @@
     </row>
     <row r="816" ht="18.0" customHeight="1">
       <c r="A816" s="6"/>
-      <c r="B816" s="15"/>
+      <c r="B816" s="16"/>
       <c r="C816" s="14"/>
-      <c r="D816" s="19"/>
-      <c r="E816" s="16"/>
-      <c r="F816" s="16"/>
-      <c r="G816" s="16"/>
+      <c r="D816" s="20"/>
+      <c r="E816" s="18"/>
+      <c r="F816" s="18"/>
+      <c r="G816" s="18"/>
       <c r="H816" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I816" s="17"/>
-      <c r="J816" s="17"/>
+      <c r="I816" s="19"/>
+      <c r="J816" s="19"/>
       <c r="K816" s="10" t="s">
         <v>20</v>
       </c>
@@ -37650,17 +37683,17 @@
     </row>
     <row r="817" ht="18.0" customHeight="1">
       <c r="A817" s="6"/>
-      <c r="B817" s="15"/>
+      <c r="B817" s="16"/>
       <c r="C817" s="14"/>
-      <c r="D817" s="19"/>
-      <c r="E817" s="16"/>
-      <c r="F817" s="16"/>
-      <c r="G817" s="16"/>
+      <c r="D817" s="20"/>
+      <c r="E817" s="18"/>
+      <c r="F817" s="18"/>
+      <c r="G817" s="18"/>
       <c r="H817" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I817" s="17"/>
-      <c r="J817" s="17"/>
+      <c r="I817" s="19"/>
+      <c r="J817" s="19"/>
       <c r="K817" s="10" t="s">
         <v>20</v>
       </c>
@@ -37676,17 +37709,17 @@
     </row>
     <row r="818" ht="18.0" customHeight="1">
       <c r="A818" s="6"/>
-      <c r="B818" s="15"/>
+      <c r="B818" s="16"/>
       <c r="C818" s="14"/>
-      <c r="D818" s="19"/>
-      <c r="E818" s="16"/>
-      <c r="F818" s="16"/>
-      <c r="G818" s="16"/>
+      <c r="D818" s="20"/>
+      <c r="E818" s="18"/>
+      <c r="F818" s="18"/>
+      <c r="G818" s="18"/>
       <c r="H818" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I818" s="17"/>
-      <c r="J818" s="17"/>
+      <c r="I818" s="19"/>
+      <c r="J818" s="19"/>
       <c r="K818" s="10" t="s">
         <v>20</v>
       </c>
@@ -37702,17 +37735,17 @@
     </row>
     <row r="819" ht="18.0" customHeight="1">
       <c r="A819" s="6"/>
-      <c r="B819" s="15"/>
+      <c r="B819" s="16"/>
       <c r="C819" s="14"/>
-      <c r="D819" s="19"/>
-      <c r="E819" s="16"/>
-      <c r="F819" s="16"/>
-      <c r="G819" s="16"/>
+      <c r="D819" s="20"/>
+      <c r="E819" s="18"/>
+      <c r="F819" s="18"/>
+      <c r="G819" s="18"/>
       <c r="H819" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I819" s="17"/>
-      <c r="J819" s="17"/>
+      <c r="I819" s="19"/>
+      <c r="J819" s="19"/>
       <c r="K819" s="10" t="s">
         <v>20</v>
       </c>
@@ -37728,17 +37761,17 @@
     </row>
     <row r="820" ht="18.0" customHeight="1">
       <c r="A820" s="6"/>
-      <c r="B820" s="15"/>
+      <c r="B820" s="16"/>
       <c r="C820" s="14"/>
-      <c r="D820" s="19"/>
-      <c r="E820" s="16"/>
-      <c r="F820" s="16"/>
-      <c r="G820" s="16"/>
+      <c r="D820" s="20"/>
+      <c r="E820" s="18"/>
+      <c r="F820" s="18"/>
+      <c r="G820" s="18"/>
       <c r="H820" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I820" s="17"/>
-      <c r="J820" s="17"/>
+      <c r="I820" s="19"/>
+      <c r="J820" s="19"/>
       <c r="K820" s="10" t="s">
         <v>20</v>
       </c>
@@ -37754,17 +37787,17 @@
     </row>
     <row r="821" ht="18.0" customHeight="1">
       <c r="A821" s="6"/>
-      <c r="B821" s="15"/>
+      <c r="B821" s="16"/>
       <c r="C821" s="14"/>
-      <c r="D821" s="19"/>
-      <c r="E821" s="16"/>
-      <c r="F821" s="16"/>
-      <c r="G821" s="16"/>
+      <c r="D821" s="20"/>
+      <c r="E821" s="18"/>
+      <c r="F821" s="18"/>
+      <c r="G821" s="18"/>
       <c r="H821" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I821" s="17"/>
-      <c r="J821" s="17"/>
+      <c r="I821" s="19"/>
+      <c r="J821" s="19"/>
       <c r="K821" s="10" t="s">
         <v>20</v>
       </c>
@@ -37780,17 +37813,17 @@
     </row>
     <row r="822" ht="18.0" customHeight="1">
       <c r="A822" s="6"/>
-      <c r="B822" s="15"/>
+      <c r="B822" s="16"/>
       <c r="C822" s="14"/>
-      <c r="D822" s="19"/>
-      <c r="E822" s="16"/>
-      <c r="F822" s="16"/>
-      <c r="G822" s="16"/>
+      <c r="D822" s="20"/>
+      <c r="E822" s="18"/>
+      <c r="F822" s="18"/>
+      <c r="G822" s="18"/>
       <c r="H822" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I822" s="17"/>
-      <c r="J822" s="17"/>
+      <c r="I822" s="19"/>
+      <c r="J822" s="19"/>
       <c r="K822" s="10" t="s">
         <v>20</v>
       </c>
@@ -37806,17 +37839,17 @@
     </row>
     <row r="823" ht="18.0" customHeight="1">
       <c r="A823" s="6"/>
-      <c r="B823" s="15"/>
+      <c r="B823" s="16"/>
       <c r="C823" s="14"/>
-      <c r="D823" s="19"/>
-      <c r="E823" s="16"/>
-      <c r="F823" s="16"/>
-      <c r="G823" s="16"/>
+      <c r="D823" s="20"/>
+      <c r="E823" s="18"/>
+      <c r="F823" s="18"/>
+      <c r="G823" s="18"/>
       <c r="H823" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I823" s="17"/>
-      <c r="J823" s="17"/>
+      <c r="I823" s="19"/>
+      <c r="J823" s="19"/>
       <c r="K823" s="10" t="s">
         <v>20</v>
       </c>
@@ -37832,17 +37865,17 @@
     </row>
     <row r="824" ht="18.0" customHeight="1">
       <c r="A824" s="6"/>
-      <c r="B824" s="15"/>
+      <c r="B824" s="16"/>
       <c r="C824" s="14"/>
-      <c r="D824" s="19"/>
-      <c r="E824" s="16"/>
-      <c r="F824" s="16"/>
-      <c r="G824" s="16"/>
+      <c r="D824" s="20"/>
+      <c r="E824" s="18"/>
+      <c r="F824" s="18"/>
+      <c r="G824" s="18"/>
       <c r="H824" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I824" s="17"/>
-      <c r="J824" s="17"/>
+      <c r="I824" s="19"/>
+      <c r="J824" s="19"/>
       <c r="K824" s="10" t="s">
         <v>20</v>
       </c>
@@ -37858,17 +37891,17 @@
     </row>
     <row r="825" ht="18.0" customHeight="1">
       <c r="A825" s="6"/>
-      <c r="B825" s="15"/>
+      <c r="B825" s="16"/>
       <c r="C825" s="14"/>
-      <c r="D825" s="19"/>
-      <c r="E825" s="16"/>
-      <c r="F825" s="16"/>
-      <c r="G825" s="16"/>
+      <c r="D825" s="20"/>
+      <c r="E825" s="18"/>
+      <c r="F825" s="18"/>
+      <c r="G825" s="18"/>
       <c r="H825" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I825" s="17"/>
-      <c r="J825" s="17"/>
+      <c r="I825" s="19"/>
+      <c r="J825" s="19"/>
       <c r="K825" s="10" t="s">
         <v>20</v>
       </c>
@@ -37884,17 +37917,17 @@
     </row>
     <row r="826" ht="18.0" customHeight="1">
       <c r="A826" s="6"/>
-      <c r="B826" s="15"/>
+      <c r="B826" s="16"/>
       <c r="C826" s="14"/>
-      <c r="D826" s="19"/>
-      <c r="E826" s="16"/>
-      <c r="F826" s="16"/>
-      <c r="G826" s="16"/>
+      <c r="D826" s="20"/>
+      <c r="E826" s="18"/>
+      <c r="F826" s="18"/>
+      <c r="G826" s="18"/>
       <c r="H826" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I826" s="17"/>
-      <c r="J826" s="17"/>
+      <c r="I826" s="19"/>
+      <c r="J826" s="19"/>
       <c r="K826" s="10" t="s">
         <v>20</v>
       </c>
@@ -37910,17 +37943,17 @@
     </row>
     <row r="827" ht="18.0" customHeight="1">
       <c r="A827" s="6"/>
-      <c r="B827" s="15"/>
+      <c r="B827" s="16"/>
       <c r="C827" s="14"/>
-      <c r="D827" s="19"/>
-      <c r="E827" s="16"/>
-      <c r="F827" s="16"/>
-      <c r="G827" s="16"/>
+      <c r="D827" s="20"/>
+      <c r="E827" s="18"/>
+      <c r="F827" s="18"/>
+      <c r="G827" s="18"/>
       <c r="H827" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I827" s="17"/>
-      <c r="J827" s="17"/>
+      <c r="I827" s="19"/>
+      <c r="J827" s="19"/>
       <c r="K827" s="10" t="s">
         <v>20</v>
       </c>
@@ -37936,17 +37969,17 @@
     </row>
     <row r="828" ht="18.0" customHeight="1">
       <c r="A828" s="6"/>
-      <c r="B828" s="15"/>
+      <c r="B828" s="16"/>
       <c r="C828" s="14"/>
-      <c r="D828" s="19"/>
-      <c r="E828" s="16"/>
-      <c r="F828" s="16"/>
-      <c r="G828" s="16"/>
+      <c r="D828" s="20"/>
+      <c r="E828" s="18"/>
+      <c r="F828" s="18"/>
+      <c r="G828" s="18"/>
       <c r="H828" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I828" s="17"/>
-      <c r="J828" s="17"/>
+      <c r="I828" s="19"/>
+      <c r="J828" s="19"/>
       <c r="K828" s="10" t="s">
         <v>20</v>
       </c>
@@ -37962,17 +37995,17 @@
     </row>
     <row r="829" ht="18.0" customHeight="1">
       <c r="A829" s="6"/>
-      <c r="B829" s="15"/>
+      <c r="B829" s="16"/>
       <c r="C829" s="14"/>
-      <c r="D829" s="19"/>
-      <c r="E829" s="16"/>
-      <c r="F829" s="16"/>
-      <c r="G829" s="16"/>
+      <c r="D829" s="20"/>
+      <c r="E829" s="18"/>
+      <c r="F829" s="18"/>
+      <c r="G829" s="18"/>
       <c r="H829" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I829" s="17"/>
-      <c r="J829" s="17"/>
+      <c r="I829" s="19"/>
+      <c r="J829" s="19"/>
       <c r="K829" s="10" t="s">
         <v>20</v>
       </c>
@@ -37988,17 +38021,17 @@
     </row>
     <row r="830" ht="18.0" customHeight="1">
       <c r="A830" s="6"/>
-      <c r="B830" s="15"/>
+      <c r="B830" s="16"/>
       <c r="C830" s="14"/>
-      <c r="D830" s="19"/>
-      <c r="E830" s="16"/>
-      <c r="F830" s="16"/>
-      <c r="G830" s="16"/>
+      <c r="D830" s="20"/>
+      <c r="E830" s="18"/>
+      <c r="F830" s="18"/>
+      <c r="G830" s="18"/>
       <c r="H830" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I830" s="17"/>
-      <c r="J830" s="17"/>
+      <c r="I830" s="19"/>
+      <c r="J830" s="19"/>
       <c r="K830" s="10" t="s">
         <v>20</v>
       </c>
@@ -38014,17 +38047,17 @@
     </row>
     <row r="831" ht="18.0" customHeight="1">
       <c r="A831" s="6"/>
-      <c r="B831" s="15"/>
+      <c r="B831" s="16"/>
       <c r="C831" s="14"/>
-      <c r="D831" s="19"/>
-      <c r="E831" s="16"/>
-      <c r="F831" s="16"/>
-      <c r="G831" s="16"/>
+      <c r="D831" s="20"/>
+      <c r="E831" s="18"/>
+      <c r="F831" s="18"/>
+      <c r="G831" s="18"/>
       <c r="H831" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I831" s="17"/>
-      <c r="J831" s="17"/>
+      <c r="I831" s="19"/>
+      <c r="J831" s="19"/>
       <c r="K831" s="10" t="s">
         <v>20</v>
       </c>
@@ -38040,17 +38073,17 @@
     </row>
     <row r="832" ht="18.0" customHeight="1">
       <c r="A832" s="6"/>
-      <c r="B832" s="15"/>
+      <c r="B832" s="16"/>
       <c r="C832" s="14"/>
-      <c r="D832" s="19"/>
-      <c r="E832" s="16"/>
-      <c r="F832" s="16"/>
-      <c r="G832" s="16"/>
+      <c r="D832" s="20"/>
+      <c r="E832" s="18"/>
+      <c r="F832" s="18"/>
+      <c r="G832" s="18"/>
       <c r="H832" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I832" s="17"/>
-      <c r="J832" s="17"/>
+      <c r="I832" s="19"/>
+      <c r="J832" s="19"/>
       <c r="K832" s="10" t="s">
         <v>20</v>
       </c>
@@ -38066,17 +38099,17 @@
     </row>
     <row r="833" ht="18.0" customHeight="1">
       <c r="A833" s="6"/>
-      <c r="B833" s="15"/>
+      <c r="B833" s="16"/>
       <c r="C833" s="14"/>
-      <c r="D833" s="19"/>
-      <c r="E833" s="16"/>
-      <c r="F833" s="16"/>
-      <c r="G833" s="16"/>
+      <c r="D833" s="20"/>
+      <c r="E833" s="18"/>
+      <c r="F833" s="18"/>
+      <c r="G833" s="18"/>
       <c r="H833" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I833" s="17"/>
-      <c r="J833" s="17"/>
+      <c r="I833" s="19"/>
+      <c r="J833" s="19"/>
       <c r="K833" s="10" t="s">
         <v>20</v>
       </c>
@@ -38092,17 +38125,17 @@
     </row>
     <row r="834" ht="18.0" customHeight="1">
       <c r="A834" s="6"/>
-      <c r="B834" s="15"/>
+      <c r="B834" s="16"/>
       <c r="C834" s="14"/>
-      <c r="D834" s="19"/>
-      <c r="E834" s="16"/>
-      <c r="F834" s="16"/>
-      <c r="G834" s="16"/>
+      <c r="D834" s="20"/>
+      <c r="E834" s="18"/>
+      <c r="F834" s="18"/>
+      <c r="G834" s="18"/>
       <c r="H834" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I834" s="17"/>
-      <c r="J834" s="17"/>
+      <c r="I834" s="19"/>
+      <c r="J834" s="19"/>
       <c r="K834" s="10" t="s">
         <v>20</v>
       </c>
@@ -38118,17 +38151,17 @@
     </row>
     <row r="835" ht="18.0" customHeight="1">
       <c r="A835" s="6"/>
-      <c r="B835" s="15"/>
+      <c r="B835" s="16"/>
       <c r="C835" s="14"/>
-      <c r="D835" s="19"/>
-      <c r="E835" s="16"/>
-      <c r="F835" s="16"/>
-      <c r="G835" s="16"/>
+      <c r="D835" s="20"/>
+      <c r="E835" s="18"/>
+      <c r="F835" s="18"/>
+      <c r="G835" s="18"/>
       <c r="H835" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I835" s="17"/>
-      <c r="J835" s="17"/>
+      <c r="I835" s="19"/>
+      <c r="J835" s="19"/>
       <c r="K835" s="10" t="s">
         <v>20</v>
       </c>
@@ -38144,17 +38177,17 @@
     </row>
     <row r="836" ht="18.0" customHeight="1">
       <c r="A836" s="6"/>
-      <c r="B836" s="15"/>
+      <c r="B836" s="16"/>
       <c r="C836" s="14"/>
-      <c r="D836" s="19"/>
-      <c r="E836" s="16"/>
-      <c r="F836" s="16"/>
-      <c r="G836" s="16"/>
+      <c r="D836" s="20"/>
+      <c r="E836" s="18"/>
+      <c r="F836" s="18"/>
+      <c r="G836" s="18"/>
       <c r="H836" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I836" s="17"/>
-      <c r="J836" s="17"/>
+      <c r="I836" s="19"/>
+      <c r="J836" s="19"/>
       <c r="K836" s="10" t="s">
         <v>20</v>
       </c>
@@ -38170,17 +38203,17 @@
     </row>
     <row r="837" ht="18.0" customHeight="1">
       <c r="A837" s="6"/>
-      <c r="B837" s="15"/>
+      <c r="B837" s="16"/>
       <c r="C837" s="14"/>
-      <c r="D837" s="19"/>
-      <c r="E837" s="16"/>
-      <c r="F837" s="16"/>
-      <c r="G837" s="16"/>
+      <c r="D837" s="20"/>
+      <c r="E837" s="18"/>
+      <c r="F837" s="18"/>
+      <c r="G837" s="18"/>
       <c r="H837" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I837" s="17"/>
-      <c r="J837" s="17"/>
+      <c r="I837" s="19"/>
+      <c r="J837" s="19"/>
       <c r="K837" s="10" t="s">
         <v>20</v>
       </c>
@@ -38196,17 +38229,17 @@
     </row>
     <row r="838" ht="18.0" customHeight="1">
       <c r="A838" s="6"/>
-      <c r="B838" s="15"/>
+      <c r="B838" s="16"/>
       <c r="C838" s="14"/>
-      <c r="D838" s="19"/>
-      <c r="E838" s="16"/>
-      <c r="F838" s="16"/>
-      <c r="G838" s="16"/>
+      <c r="D838" s="20"/>
+      <c r="E838" s="18"/>
+      <c r="F838" s="18"/>
+      <c r="G838" s="18"/>
       <c r="H838" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I838" s="17"/>
-      <c r="J838" s="17"/>
+      <c r="I838" s="19"/>
+      <c r="J838" s="19"/>
       <c r="K838" s="10" t="s">
         <v>20</v>
       </c>
@@ -38222,17 +38255,17 @@
     </row>
     <row r="839" ht="18.0" customHeight="1">
       <c r="A839" s="6"/>
-      <c r="B839" s="15"/>
+      <c r="B839" s="16"/>
       <c r="C839" s="14"/>
-      <c r="D839" s="19"/>
-      <c r="E839" s="16"/>
-      <c r="F839" s="16"/>
-      <c r="G839" s="16"/>
+      <c r="D839" s="20"/>
+      <c r="E839" s="18"/>
+      <c r="F839" s="18"/>
+      <c r="G839" s="18"/>
       <c r="H839" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I839" s="17"/>
-      <c r="J839" s="17"/>
+      <c r="I839" s="19"/>
+      <c r="J839" s="19"/>
       <c r="K839" s="10" t="s">
         <v>20</v>
       </c>
@@ -38248,17 +38281,17 @@
     </row>
     <row r="840" ht="18.0" customHeight="1">
       <c r="A840" s="6"/>
-      <c r="B840" s="15"/>
+      <c r="B840" s="16"/>
       <c r="C840" s="14"/>
-      <c r="D840" s="19"/>
-      <c r="E840" s="16"/>
-      <c r="F840" s="16"/>
-      <c r="G840" s="16"/>
+      <c r="D840" s="20"/>
+      <c r="E840" s="18"/>
+      <c r="F840" s="18"/>
+      <c r="G840" s="18"/>
       <c r="H840" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I840" s="17"/>
-      <c r="J840" s="17"/>
+      <c r="I840" s="19"/>
+      <c r="J840" s="19"/>
       <c r="K840" s="10" t="s">
         <v>20</v>
       </c>
@@ -38274,17 +38307,17 @@
     </row>
     <row r="841" ht="18.0" customHeight="1">
       <c r="A841" s="6"/>
-      <c r="B841" s="15"/>
+      <c r="B841" s="16"/>
       <c r="C841" s="14"/>
-      <c r="D841" s="19"/>
-      <c r="E841" s="16"/>
-      <c r="F841" s="16"/>
-      <c r="G841" s="16"/>
+      <c r="D841" s="20"/>
+      <c r="E841" s="18"/>
+      <c r="F841" s="18"/>
+      <c r="G841" s="18"/>
       <c r="H841" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I841" s="17"/>
-      <c r="J841" s="17"/>
+      <c r="I841" s="19"/>
+      <c r="J841" s="19"/>
       <c r="K841" s="10" t="s">
         <v>20</v>
       </c>
@@ -38300,17 +38333,17 @@
     </row>
     <row r="842" ht="18.0" customHeight="1">
       <c r="A842" s="6"/>
-      <c r="B842" s="15"/>
+      <c r="B842" s="16"/>
       <c r="C842" s="14"/>
-      <c r="D842" s="19"/>
-      <c r="E842" s="16"/>
-      <c r="F842" s="16"/>
-      <c r="G842" s="16"/>
+      <c r="D842" s="20"/>
+      <c r="E842" s="18"/>
+      <c r="F842" s="18"/>
+      <c r="G842" s="18"/>
       <c r="H842" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I842" s="17"/>
-      <c r="J842" s="17"/>
+      <c r="I842" s="19"/>
+      <c r="J842" s="19"/>
       <c r="K842" s="10" t="s">
         <v>20</v>
       </c>
@@ -38326,17 +38359,17 @@
     </row>
     <row r="843" ht="18.0" customHeight="1">
       <c r="A843" s="6"/>
-      <c r="B843" s="15"/>
+      <c r="B843" s="16"/>
       <c r="C843" s="14"/>
-      <c r="D843" s="19"/>
-      <c r="E843" s="16"/>
-      <c r="F843" s="16"/>
-      <c r="G843" s="16"/>
+      <c r="D843" s="20"/>
+      <c r="E843" s="18"/>
+      <c r="F843" s="18"/>
+      <c r="G843" s="18"/>
       <c r="H843" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I843" s="17"/>
-      <c r="J843" s="17"/>
+      <c r="I843" s="19"/>
+      <c r="J843" s="19"/>
       <c r="K843" s="10" t="s">
         <v>20</v>
       </c>
@@ -38352,17 +38385,17 @@
     </row>
     <row r="844" ht="18.0" customHeight="1">
       <c r="A844" s="6"/>
-      <c r="B844" s="15"/>
+      <c r="B844" s="16"/>
       <c r="C844" s="14"/>
-      <c r="D844" s="19"/>
-      <c r="E844" s="16"/>
-      <c r="F844" s="16"/>
-      <c r="G844" s="16"/>
+      <c r="D844" s="20"/>
+      <c r="E844" s="18"/>
+      <c r="F844" s="18"/>
+      <c r="G844" s="18"/>
       <c r="H844" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I844" s="17"/>
-      <c r="J844" s="17"/>
+      <c r="I844" s="19"/>
+      <c r="J844" s="19"/>
       <c r="K844" s="10" t="s">
         <v>20</v>
       </c>
@@ -38378,17 +38411,17 @@
     </row>
     <row r="845" ht="18.0" customHeight="1">
       <c r="A845" s="6"/>
-      <c r="B845" s="15"/>
+      <c r="B845" s="16"/>
       <c r="C845" s="14"/>
-      <c r="D845" s="19"/>
-      <c r="E845" s="16"/>
-      <c r="F845" s="16"/>
-      <c r="G845" s="16"/>
+      <c r="D845" s="20"/>
+      <c r="E845" s="18"/>
+      <c r="F845" s="18"/>
+      <c r="G845" s="18"/>
       <c r="H845" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I845" s="17"/>
-      <c r="J845" s="17"/>
+      <c r="I845" s="19"/>
+      <c r="J845" s="19"/>
       <c r="K845" s="10" t="s">
         <v>20</v>
       </c>
@@ -38404,17 +38437,17 @@
     </row>
     <row r="846" ht="18.0" customHeight="1">
       <c r="A846" s="6"/>
-      <c r="B846" s="15"/>
+      <c r="B846" s="16"/>
       <c r="C846" s="14"/>
-      <c r="D846" s="19"/>
-      <c r="E846" s="16"/>
-      <c r="F846" s="16"/>
-      <c r="G846" s="16"/>
+      <c r="D846" s="20"/>
+      <c r="E846" s="18"/>
+      <c r="F846" s="18"/>
+      <c r="G846" s="18"/>
       <c r="H846" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I846" s="17"/>
-      <c r="J846" s="17"/>
+      <c r="I846" s="19"/>
+      <c r="J846" s="19"/>
       <c r="K846" s="10" t="s">
         <v>20</v>
       </c>
@@ -38430,17 +38463,17 @@
     </row>
     <row r="847" ht="18.0" customHeight="1">
       <c r="A847" s="6"/>
-      <c r="B847" s="15"/>
+      <c r="B847" s="16"/>
       <c r="C847" s="14"/>
-      <c r="D847" s="19"/>
-      <c r="E847" s="16"/>
-      <c r="F847" s="16"/>
-      <c r="G847" s="16"/>
+      <c r="D847" s="20"/>
+      <c r="E847" s="18"/>
+      <c r="F847" s="18"/>
+      <c r="G847" s="18"/>
       <c r="H847" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I847" s="17"/>
-      <c r="J847" s="17"/>
+      <c r="I847" s="19"/>
+      <c r="J847" s="19"/>
       <c r="K847" s="10" t="s">
         <v>20</v>
       </c>
@@ -38456,17 +38489,17 @@
     </row>
     <row r="848" ht="18.0" customHeight="1">
       <c r="A848" s="6"/>
-      <c r="B848" s="15"/>
+      <c r="B848" s="16"/>
       <c r="C848" s="14"/>
-      <c r="D848" s="19"/>
-      <c r="E848" s="16"/>
-      <c r="F848" s="16"/>
-      <c r="G848" s="16"/>
+      <c r="D848" s="20"/>
+      <c r="E848" s="18"/>
+      <c r="F848" s="18"/>
+      <c r="G848" s="18"/>
       <c r="H848" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I848" s="17"/>
-      <c r="J848" s="17"/>
+      <c r="I848" s="19"/>
+      <c r="J848" s="19"/>
       <c r="K848" s="10" t="s">
         <v>20</v>
       </c>
@@ -38482,17 +38515,17 @@
     </row>
     <row r="849" ht="18.0" customHeight="1">
       <c r="A849" s="6"/>
-      <c r="B849" s="15"/>
+      <c r="B849" s="16"/>
       <c r="C849" s="14"/>
-      <c r="D849" s="19"/>
-      <c r="E849" s="16"/>
-      <c r="F849" s="16"/>
-      <c r="G849" s="16"/>
+      <c r="D849" s="20"/>
+      <c r="E849" s="18"/>
+      <c r="F849" s="18"/>
+      <c r="G849" s="18"/>
       <c r="H849" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I849" s="17"/>
-      <c r="J849" s="17"/>
+      <c r="I849" s="19"/>
+      <c r="J849" s="19"/>
       <c r="K849" s="10" t="s">
         <v>20</v>
       </c>
@@ -38508,17 +38541,17 @@
     </row>
     <row r="850" ht="18.0" customHeight="1">
       <c r="A850" s="6"/>
-      <c r="B850" s="15"/>
+      <c r="B850" s="16"/>
       <c r="C850" s="14"/>
-      <c r="D850" s="19"/>
-      <c r="E850" s="16"/>
-      <c r="F850" s="16"/>
-      <c r="G850" s="16"/>
+      <c r="D850" s="20"/>
+      <c r="E850" s="18"/>
+      <c r="F850" s="18"/>
+      <c r="G850" s="18"/>
       <c r="H850" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I850" s="17"/>
-      <c r="J850" s="17"/>
+      <c r="I850" s="19"/>
+      <c r="J850" s="19"/>
       <c r="K850" s="10" t="s">
         <v>20</v>
       </c>
@@ -38534,17 +38567,17 @@
     </row>
     <row r="851" ht="18.0" customHeight="1">
       <c r="A851" s="6"/>
-      <c r="B851" s="15"/>
+      <c r="B851" s="16"/>
       <c r="C851" s="14"/>
-      <c r="D851" s="19"/>
-      <c r="E851" s="16"/>
-      <c r="F851" s="16"/>
-      <c r="G851" s="16"/>
+      <c r="D851" s="20"/>
+      <c r="E851" s="18"/>
+      <c r="F851" s="18"/>
+      <c r="G851" s="18"/>
       <c r="H851" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I851" s="17"/>
-      <c r="J851" s="17"/>
+      <c r="I851" s="19"/>
+      <c r="J851" s="19"/>
       <c r="K851" s="10" t="s">
         <v>20</v>
       </c>
@@ -38560,17 +38593,17 @@
     </row>
     <row r="852" ht="18.0" customHeight="1">
       <c r="A852" s="6"/>
-      <c r="B852" s="15"/>
+      <c r="B852" s="16"/>
       <c r="C852" s="14"/>
-      <c r="D852" s="19"/>
-      <c r="E852" s="16"/>
-      <c r="F852" s="16"/>
-      <c r="G852" s="16"/>
+      <c r="D852" s="20"/>
+      <c r="E852" s="18"/>
+      <c r="F852" s="18"/>
+      <c r="G852" s="18"/>
       <c r="H852" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I852" s="17"/>
-      <c r="J852" s="17"/>
+      <c r="I852" s="19"/>
+      <c r="J852" s="19"/>
       <c r="K852" s="10" t="s">
         <v>20</v>
       </c>
@@ -38586,17 +38619,17 @@
     </row>
     <row r="853" ht="18.0" customHeight="1">
       <c r="A853" s="6"/>
-      <c r="B853" s="15"/>
+      <c r="B853" s="16"/>
       <c r="C853" s="14"/>
-      <c r="D853" s="19"/>
-      <c r="E853" s="16"/>
-      <c r="F853" s="16"/>
-      <c r="G853" s="16"/>
+      <c r="D853" s="20"/>
+      <c r="E853" s="18"/>
+      <c r="F853" s="18"/>
+      <c r="G853" s="18"/>
       <c r="H853" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I853" s="17"/>
-      <c r="J853" s="17"/>
+      <c r="I853" s="19"/>
+      <c r="J853" s="19"/>
       <c r="K853" s="10" t="s">
         <v>20</v>
       </c>
@@ -38612,17 +38645,17 @@
     </row>
     <row r="854" ht="18.0" customHeight="1">
       <c r="A854" s="6"/>
-      <c r="B854" s="15"/>
+      <c r="B854" s="16"/>
       <c r="C854" s="14"/>
-      <c r="D854" s="19"/>
-      <c r="E854" s="16"/>
-      <c r="F854" s="16"/>
-      <c r="G854" s="16"/>
+      <c r="D854" s="20"/>
+      <c r="E854" s="18"/>
+      <c r="F854" s="18"/>
+      <c r="G854" s="18"/>
       <c r="H854" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I854" s="17"/>
-      <c r="J854" s="17"/>
+      <c r="I854" s="19"/>
+      <c r="J854" s="19"/>
       <c r="K854" s="10" t="s">
         <v>20</v>
       </c>
@@ -38638,17 +38671,17 @@
     </row>
     <row r="855" ht="18.0" customHeight="1">
       <c r="A855" s="6"/>
-      <c r="B855" s="15"/>
+      <c r="B855" s="16"/>
       <c r="C855" s="14"/>
-      <c r="D855" s="19"/>
-      <c r="E855" s="16"/>
-      <c r="F855" s="16"/>
-      <c r="G855" s="16"/>
+      <c r="D855" s="20"/>
+      <c r="E855" s="18"/>
+      <c r="F855" s="18"/>
+      <c r="G855" s="18"/>
       <c r="H855" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I855" s="17"/>
-      <c r="J855" s="17"/>
+      <c r="I855" s="19"/>
+      <c r="J855" s="19"/>
       <c r="K855" s="10" t="s">
         <v>20</v>
       </c>
@@ -38664,17 +38697,17 @@
     </row>
     <row r="856" ht="18.0" customHeight="1">
       <c r="A856" s="6"/>
-      <c r="B856" s="15"/>
+      <c r="B856" s="16"/>
       <c r="C856" s="14"/>
-      <c r="D856" s="19"/>
-      <c r="E856" s="16"/>
-      <c r="F856" s="16"/>
-      <c r="G856" s="16"/>
+      <c r="D856" s="20"/>
+      <c r="E856" s="18"/>
+      <c r="F856" s="18"/>
+      <c r="G856" s="18"/>
       <c r="H856" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I856" s="17"/>
-      <c r="J856" s="17"/>
+      <c r="I856" s="19"/>
+      <c r="J856" s="19"/>
       <c r="K856" s="10" t="s">
         <v>20</v>
       </c>
@@ -38690,17 +38723,17 @@
     </row>
     <row r="857" ht="18.0" customHeight="1">
       <c r="A857" s="6"/>
-      <c r="B857" s="15"/>
+      <c r="B857" s="16"/>
       <c r="C857" s="14"/>
-      <c r="D857" s="19"/>
-      <c r="E857" s="16"/>
-      <c r="F857" s="16"/>
-      <c r="G857" s="16"/>
+      <c r="D857" s="20"/>
+      <c r="E857" s="18"/>
+      <c r="F857" s="18"/>
+      <c r="G857" s="18"/>
       <c r="H857" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I857" s="17"/>
-      <c r="J857" s="17"/>
+      <c r="I857" s="19"/>
+      <c r="J857" s="19"/>
       <c r="K857" s="10" t="s">
         <v>20</v>
       </c>
@@ -38716,17 +38749,17 @@
     </row>
     <row r="858" ht="18.0" customHeight="1">
       <c r="A858" s="6"/>
-      <c r="B858" s="15"/>
+      <c r="B858" s="16"/>
       <c r="C858" s="14"/>
-      <c r="D858" s="19"/>
-      <c r="E858" s="16"/>
-      <c r="F858" s="16"/>
-      <c r="G858" s="16"/>
+      <c r="D858" s="20"/>
+      <c r="E858" s="18"/>
+      <c r="F858" s="18"/>
+      <c r="G858" s="18"/>
       <c r="H858" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I858" s="17"/>
-      <c r="J858" s="17"/>
+      <c r="I858" s="19"/>
+      <c r="J858" s="19"/>
       <c r="K858" s="10" t="s">
         <v>20</v>
       </c>
@@ -38742,17 +38775,17 @@
     </row>
     <row r="859" ht="18.0" customHeight="1">
       <c r="A859" s="6"/>
-      <c r="B859" s="15"/>
+      <c r="B859" s="16"/>
       <c r="C859" s="14"/>
-      <c r="D859" s="19"/>
-      <c r="E859" s="16"/>
-      <c r="F859" s="16"/>
-      <c r="G859" s="16"/>
+      <c r="D859" s="20"/>
+      <c r="E859" s="18"/>
+      <c r="F859" s="18"/>
+      <c r="G859" s="18"/>
       <c r="H859" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I859" s="17"/>
-      <c r="J859" s="17"/>
+      <c r="I859" s="19"/>
+      <c r="J859" s="19"/>
       <c r="K859" s="10" t="s">
         <v>20</v>
       </c>
@@ -38768,17 +38801,17 @@
     </row>
     <row r="860" ht="18.0" customHeight="1">
       <c r="A860" s="6"/>
-      <c r="B860" s="15"/>
+      <c r="B860" s="16"/>
       <c r="C860" s="14"/>
-      <c r="D860" s="19"/>
-      <c r="E860" s="16"/>
-      <c r="F860" s="16"/>
-      <c r="G860" s="16"/>
+      <c r="D860" s="20"/>
+      <c r="E860" s="18"/>
+      <c r="F860" s="18"/>
+      <c r="G860" s="18"/>
       <c r="H860" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I860" s="17"/>
-      <c r="J860" s="17"/>
+      <c r="I860" s="19"/>
+      <c r="J860" s="19"/>
       <c r="K860" s="10" t="s">
         <v>20</v>
       </c>
@@ -38794,17 +38827,17 @@
     </row>
     <row r="861" ht="18.0" customHeight="1">
       <c r="A861" s="6"/>
-      <c r="B861" s="15"/>
+      <c r="B861" s="16"/>
       <c r="C861" s="14"/>
-      <c r="D861" s="19"/>
-      <c r="E861" s="16"/>
-      <c r="F861" s="16"/>
-      <c r="G861" s="16"/>
+      <c r="D861" s="20"/>
+      <c r="E861" s="18"/>
+      <c r="F861" s="18"/>
+      <c r="G861" s="18"/>
       <c r="H861" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I861" s="17"/>
-      <c r="J861" s="17"/>
+      <c r="I861" s="19"/>
+      <c r="J861" s="19"/>
       <c r="K861" s="10" t="s">
         <v>20</v>
       </c>
@@ -38820,17 +38853,17 @@
     </row>
     <row r="862" ht="18.0" customHeight="1">
       <c r="A862" s="6"/>
-      <c r="B862" s="15"/>
+      <c r="B862" s="16"/>
       <c r="C862" s="14"/>
-      <c r="D862" s="19"/>
-      <c r="E862" s="16"/>
-      <c r="F862" s="16"/>
-      <c r="G862" s="16"/>
+      <c r="D862" s="20"/>
+      <c r="E862" s="18"/>
+      <c r="F862" s="18"/>
+      <c r="G862" s="18"/>
       <c r="H862" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I862" s="17"/>
-      <c r="J862" s="17"/>
+      <c r="I862" s="19"/>
+      <c r="J862" s="19"/>
       <c r="K862" s="10" t="s">
         <v>20</v>
       </c>
@@ -38846,17 +38879,17 @@
     </row>
     <row r="863" ht="18.0" customHeight="1">
       <c r="A863" s="6"/>
-      <c r="B863" s="15"/>
+      <c r="B863" s="16"/>
       <c r="C863" s="14"/>
-      <c r="D863" s="19"/>
-      <c r="E863" s="16"/>
-      <c r="F863" s="16"/>
-      <c r="G863" s="16"/>
+      <c r="D863" s="20"/>
+      <c r="E863" s="18"/>
+      <c r="F863" s="18"/>
+      <c r="G863" s="18"/>
       <c r="H863" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I863" s="17"/>
-      <c r="J863" s="17"/>
+      <c r="I863" s="19"/>
+      <c r="J863" s="19"/>
       <c r="K863" s="10" t="s">
         <v>20</v>
       </c>
@@ -38872,17 +38905,17 @@
     </row>
     <row r="864" ht="18.0" customHeight="1">
       <c r="A864" s="6"/>
-      <c r="B864" s="15"/>
+      <c r="B864" s="16"/>
       <c r="C864" s="14"/>
-      <c r="D864" s="19"/>
-      <c r="E864" s="16"/>
-      <c r="F864" s="16"/>
-      <c r="G864" s="16"/>
+      <c r="D864" s="20"/>
+      <c r="E864" s="18"/>
+      <c r="F864" s="18"/>
+      <c r="G864" s="18"/>
       <c r="H864" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I864" s="17"/>
-      <c r="J864" s="17"/>
+      <c r="I864" s="19"/>
+      <c r="J864" s="19"/>
       <c r="K864" s="10" t="s">
         <v>20</v>
       </c>
@@ -38898,17 +38931,17 @@
     </row>
     <row r="865" ht="18.0" customHeight="1">
       <c r="A865" s="6"/>
-      <c r="B865" s="15"/>
+      <c r="B865" s="16"/>
       <c r="C865" s="14"/>
-      <c r="D865" s="19"/>
-      <c r="E865" s="16"/>
-      <c r="F865" s="16"/>
-      <c r="G865" s="16"/>
+      <c r="D865" s="20"/>
+      <c r="E865" s="18"/>
+      <c r="F865" s="18"/>
+      <c r="G865" s="18"/>
       <c r="H865" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I865" s="17"/>
-      <c r="J865" s="17"/>
+      <c r="I865" s="19"/>
+      <c r="J865" s="19"/>
       <c r="K865" s="10" t="s">
         <v>20</v>
       </c>
@@ -38924,17 +38957,17 @@
     </row>
     <row r="866" ht="18.0" customHeight="1">
       <c r="A866" s="6"/>
-      <c r="B866" s="15"/>
+      <c r="B866" s="16"/>
       <c r="C866" s="14"/>
-      <c r="D866" s="19"/>
-      <c r="E866" s="16"/>
-      <c r="F866" s="16"/>
-      <c r="G866" s="16"/>
+      <c r="D866" s="20"/>
+      <c r="E866" s="18"/>
+      <c r="F866" s="18"/>
+      <c r="G866" s="18"/>
       <c r="H866" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I866" s="17"/>
-      <c r="J866" s="17"/>
+      <c r="I866" s="19"/>
+      <c r="J866" s="19"/>
       <c r="K866" s="10" t="s">
         <v>20</v>
       </c>
@@ -38950,17 +38983,17 @@
     </row>
     <row r="867" ht="18.0" customHeight="1">
       <c r="A867" s="6"/>
-      <c r="B867" s="15"/>
+      <c r="B867" s="16"/>
       <c r="C867" s="14"/>
-      <c r="D867" s="19"/>
-      <c r="E867" s="16"/>
-      <c r="F867" s="16"/>
-      <c r="G867" s="16"/>
+      <c r="D867" s="20"/>
+      <c r="E867" s="18"/>
+      <c r="F867" s="18"/>
+      <c r="G867" s="18"/>
       <c r="H867" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I867" s="17"/>
-      <c r="J867" s="17"/>
+      <c r="I867" s="19"/>
+      <c r="J867" s="19"/>
       <c r="K867" s="10" t="s">
         <v>20</v>
       </c>
@@ -38976,17 +39009,17 @@
     </row>
     <row r="868" ht="18.0" customHeight="1">
       <c r="A868" s="6"/>
-      <c r="B868" s="15"/>
+      <c r="B868" s="16"/>
       <c r="C868" s="14"/>
-      <c r="D868" s="19"/>
-      <c r="E868" s="16"/>
-      <c r="F868" s="16"/>
-      <c r="G868" s="16"/>
+      <c r="D868" s="20"/>
+      <c r="E868" s="18"/>
+      <c r="F868" s="18"/>
+      <c r="G868" s="18"/>
       <c r="H868" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I868" s="17"/>
-      <c r="J868" s="17"/>
+      <c r="I868" s="19"/>
+      <c r="J868" s="19"/>
       <c r="K868" s="10" t="s">
         <v>20</v>
       </c>
@@ -39002,17 +39035,17 @@
     </row>
     <row r="869" ht="18.0" customHeight="1">
       <c r="A869" s="6"/>
-      <c r="B869" s="15"/>
+      <c r="B869" s="16"/>
       <c r="C869" s="14"/>
-      <c r="D869" s="19"/>
-      <c r="E869" s="16"/>
-      <c r="F869" s="16"/>
-      <c r="G869" s="16"/>
+      <c r="D869" s="20"/>
+      <c r="E869" s="18"/>
+      <c r="F869" s="18"/>
+      <c r="G869" s="18"/>
       <c r="H869" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I869" s="17"/>
-      <c r="J869" s="17"/>
+      <c r="I869" s="19"/>
+      <c r="J869" s="19"/>
       <c r="K869" s="10" t="s">
         <v>20</v>
       </c>
@@ -39028,17 +39061,17 @@
     </row>
     <row r="870" ht="18.0" customHeight="1">
       <c r="A870" s="6"/>
-      <c r="B870" s="15"/>
+      <c r="B870" s="16"/>
       <c r="C870" s="14"/>
-      <c r="D870" s="19"/>
-      <c r="E870" s="16"/>
-      <c r="F870" s="16"/>
-      <c r="G870" s="16"/>
+      <c r="D870" s="20"/>
+      <c r="E870" s="18"/>
+      <c r="F870" s="18"/>
+      <c r="G870" s="18"/>
       <c r="H870" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I870" s="17"/>
-      <c r="J870" s="17"/>
+      <c r="I870" s="19"/>
+      <c r="J870" s="19"/>
       <c r="K870" s="10" t="s">
         <v>20</v>
       </c>
@@ -39054,17 +39087,17 @@
     </row>
     <row r="871" ht="18.0" customHeight="1">
       <c r="A871" s="6"/>
-      <c r="B871" s="15"/>
+      <c r="B871" s="16"/>
       <c r="C871" s="14"/>
-      <c r="D871" s="19"/>
-      <c r="E871" s="16"/>
-      <c r="F871" s="16"/>
-      <c r="G871" s="16"/>
+      <c r="D871" s="20"/>
+      <c r="E871" s="18"/>
+      <c r="F871" s="18"/>
+      <c r="G871" s="18"/>
       <c r="H871" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I871" s="17"/>
-      <c r="J871" s="17"/>
+      <c r="I871" s="19"/>
+      <c r="J871" s="19"/>
       <c r="K871" s="10" t="s">
         <v>20</v>
       </c>
@@ -39080,17 +39113,17 @@
     </row>
     <row r="872" ht="18.0" customHeight="1">
       <c r="A872" s="6"/>
-      <c r="B872" s="15"/>
+      <c r="B872" s="16"/>
       <c r="C872" s="14"/>
-      <c r="D872" s="19"/>
-      <c r="E872" s="16"/>
-      <c r="F872" s="16"/>
-      <c r="G872" s="16"/>
+      <c r="D872" s="20"/>
+      <c r="E872" s="18"/>
+      <c r="F872" s="18"/>
+      <c r="G872" s="18"/>
       <c r="H872" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I872" s="17"/>
-      <c r="J872" s="17"/>
+      <c r="I872" s="19"/>
+      <c r="J872" s="19"/>
       <c r="K872" s="10" t="s">
         <v>20</v>
       </c>
@@ -39106,17 +39139,17 @@
     </row>
     <row r="873" ht="18.0" customHeight="1">
       <c r="A873" s="6"/>
-      <c r="B873" s="15"/>
+      <c r="B873" s="16"/>
       <c r="C873" s="14"/>
-      <c r="D873" s="19"/>
-      <c r="E873" s="16"/>
-      <c r="F873" s="16"/>
-      <c r="G873" s="16"/>
+      <c r="D873" s="20"/>
+      <c r="E873" s="18"/>
+      <c r="F873" s="18"/>
+      <c r="G873" s="18"/>
       <c r="H873" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I873" s="17"/>
-      <c r="J873" s="17"/>
+      <c r="I873" s="19"/>
+      <c r="J873" s="19"/>
       <c r="K873" s="10" t="s">
         <v>20</v>
       </c>
@@ -39132,17 +39165,17 @@
     </row>
     <row r="874" ht="18.0" customHeight="1">
       <c r="A874" s="6"/>
-      <c r="B874" s="15"/>
+      <c r="B874" s="16"/>
       <c r="C874" s="14"/>
-      <c r="D874" s="19"/>
-      <c r="E874" s="16"/>
-      <c r="F874" s="16"/>
-      <c r="G874" s="16"/>
+      <c r="D874" s="20"/>
+      <c r="E874" s="18"/>
+      <c r="F874" s="18"/>
+      <c r="G874" s="18"/>
       <c r="H874" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I874" s="17"/>
-      <c r="J874" s="17"/>
+      <c r="I874" s="19"/>
+      <c r="J874" s="19"/>
       <c r="K874" s="10" t="s">
         <v>20</v>
       </c>
@@ -39158,17 +39191,17 @@
     </row>
     <row r="875" ht="18.0" customHeight="1">
       <c r="A875" s="6"/>
-      <c r="B875" s="15"/>
+      <c r="B875" s="16"/>
       <c r="C875" s="14"/>
-      <c r="D875" s="19"/>
-      <c r="E875" s="16"/>
-      <c r="F875" s="16"/>
-      <c r="G875" s="16"/>
+      <c r="D875" s="20"/>
+      <c r="E875" s="18"/>
+      <c r="F875" s="18"/>
+      <c r="G875" s="18"/>
       <c r="H875" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I875" s="17"/>
-      <c r="J875" s="17"/>
+      <c r="I875" s="19"/>
+      <c r="J875" s="19"/>
       <c r="K875" s="10" t="s">
         <v>20</v>
       </c>
@@ -39184,17 +39217,17 @@
     </row>
     <row r="876" ht="18.0" customHeight="1">
       <c r="A876" s="6"/>
-      <c r="B876" s="15"/>
+      <c r="B876" s="16"/>
       <c r="C876" s="14"/>
-      <c r="D876" s="19"/>
-      <c r="E876" s="16"/>
-      <c r="F876" s="16"/>
-      <c r="G876" s="16"/>
+      <c r="D876" s="20"/>
+      <c r="E876" s="18"/>
+      <c r="F876" s="18"/>
+      <c r="G876" s="18"/>
       <c r="H876" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I876" s="17"/>
-      <c r="J876" s="17"/>
+      <c r="I876" s="19"/>
+      <c r="J876" s="19"/>
       <c r="K876" s="10" t="s">
         <v>20</v>
       </c>
@@ -39210,17 +39243,17 @@
     </row>
     <row r="877" ht="18.0" customHeight="1">
       <c r="A877" s="6"/>
-      <c r="B877" s="15"/>
+      <c r="B877" s="16"/>
       <c r="C877" s="14"/>
-      <c r="D877" s="19"/>
-      <c r="E877" s="16"/>
-      <c r="F877" s="16"/>
-      <c r="G877" s="16"/>
+      <c r="D877" s="20"/>
+      <c r="E877" s="18"/>
+      <c r="F877" s="18"/>
+      <c r="G877" s="18"/>
       <c r="H877" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I877" s="17"/>
-      <c r="J877" s="17"/>
+      <c r="I877" s="19"/>
+      <c r="J877" s="19"/>
       <c r="K877" s="10" t="s">
         <v>20</v>
       </c>
@@ -39236,17 +39269,17 @@
     </row>
     <row r="878" ht="18.0" customHeight="1">
       <c r="A878" s="6"/>
-      <c r="B878" s="15"/>
+      <c r="B878" s="16"/>
       <c r="C878" s="14"/>
-      <c r="D878" s="19"/>
-      <c r="E878" s="16"/>
-      <c r="F878" s="16"/>
-      <c r="G878" s="16"/>
+      <c r="D878" s="20"/>
+      <c r="E878" s="18"/>
+      <c r="F878" s="18"/>
+      <c r="G878" s="18"/>
       <c r="H878" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I878" s="17"/>
-      <c r="J878" s="17"/>
+      <c r="I878" s="19"/>
+      <c r="J878" s="19"/>
       <c r="K878" s="10" t="s">
         <v>20</v>
       </c>
@@ -39262,17 +39295,17 @@
     </row>
     <row r="879" ht="18.0" customHeight="1">
       <c r="A879" s="6"/>
-      <c r="B879" s="15"/>
+      <c r="B879" s="16"/>
       <c r="C879" s="14"/>
-      <c r="D879" s="19"/>
-      <c r="E879" s="16"/>
-      <c r="F879" s="16"/>
-      <c r="G879" s="16"/>
+      <c r="D879" s="20"/>
+      <c r="E879" s="18"/>
+      <c r="F879" s="18"/>
+      <c r="G879" s="18"/>
       <c r="H879" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I879" s="17"/>
-      <c r="J879" s="17"/>
+      <c r="I879" s="19"/>
+      <c r="J879" s="19"/>
       <c r="K879" s="10" t="s">
         <v>20</v>
       </c>
@@ -39288,17 +39321,17 @@
     </row>
     <row r="880" ht="18.0" customHeight="1">
       <c r="A880" s="6"/>
-      <c r="B880" s="15"/>
+      <c r="B880" s="16"/>
       <c r="C880" s="14"/>
-      <c r="D880" s="19"/>
-      <c r="E880" s="16"/>
-      <c r="F880" s="16"/>
-      <c r="G880" s="16"/>
+      <c r="D880" s="20"/>
+      <c r="E880" s="18"/>
+      <c r="F880" s="18"/>
+      <c r="G880" s="18"/>
       <c r="H880" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I880" s="17"/>
-      <c r="J880" s="17"/>
+      <c r="I880" s="19"/>
+      <c r="J880" s="19"/>
       <c r="K880" s="10" t="s">
         <v>20</v>
       </c>
@@ -39314,17 +39347,17 @@
     </row>
     <row r="881" ht="18.0" customHeight="1">
       <c r="A881" s="6"/>
-      <c r="B881" s="15"/>
+      <c r="B881" s="16"/>
       <c r="C881" s="14"/>
-      <c r="D881" s="19"/>
-      <c r="E881" s="16"/>
-      <c r="F881" s="16"/>
-      <c r="G881" s="16"/>
+      <c r="D881" s="20"/>
+      <c r="E881" s="18"/>
+      <c r="F881" s="18"/>
+      <c r="G881" s="18"/>
       <c r="H881" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I881" s="17"/>
-      <c r="J881" s="17"/>
+      <c r="I881" s="19"/>
+      <c r="J881" s="19"/>
       <c r="K881" s="10" t="s">
         <v>20</v>
       </c>
@@ -39340,17 +39373,17 @@
     </row>
     <row r="882" ht="18.0" customHeight="1">
       <c r="A882" s="6"/>
-      <c r="B882" s="15"/>
+      <c r="B882" s="16"/>
       <c r="C882" s="14"/>
-      <c r="D882" s="19"/>
-      <c r="E882" s="16"/>
-      <c r="F882" s="16"/>
-      <c r="G882" s="16"/>
+      <c r="D882" s="20"/>
+      <c r="E882" s="18"/>
+      <c r="F882" s="18"/>
+      <c r="G882" s="18"/>
       <c r="H882" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I882" s="17"/>
-      <c r="J882" s="17"/>
+      <c r="I882" s="19"/>
+      <c r="J882" s="19"/>
       <c r="K882" s="10" t="s">
         <v>20</v>
       </c>
@@ -39366,17 +39399,17 @@
     </row>
     <row r="883" ht="18.0" customHeight="1">
       <c r="A883" s="6"/>
-      <c r="B883" s="15"/>
+      <c r="B883" s="16"/>
       <c r="C883" s="14"/>
-      <c r="D883" s="19"/>
-      <c r="E883" s="16"/>
-      <c r="F883" s="16"/>
-      <c r="G883" s="16"/>
+      <c r="D883" s="20"/>
+      <c r="E883" s="18"/>
+      <c r="F883" s="18"/>
+      <c r="G883" s="18"/>
       <c r="H883" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I883" s="17"/>
-      <c r="J883" s="17"/>
+      <c r="I883" s="19"/>
+      <c r="J883" s="19"/>
       <c r="K883" s="10" t="s">
         <v>20</v>
       </c>
@@ -39392,17 +39425,17 @@
     </row>
     <row r="884" ht="18.0" customHeight="1">
       <c r="A884" s="6"/>
-      <c r="B884" s="15"/>
+      <c r="B884" s="16"/>
       <c r="C884" s="14"/>
-      <c r="D884" s="19"/>
-      <c r="E884" s="16"/>
-      <c r="F884" s="16"/>
-      <c r="G884" s="16"/>
+      <c r="D884" s="20"/>
+      <c r="E884" s="18"/>
+      <c r="F884" s="18"/>
+      <c r="G884" s="18"/>
       <c r="H884" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I884" s="17"/>
-      <c r="J884" s="17"/>
+      <c r="I884" s="19"/>
+      <c r="J884" s="19"/>
       <c r="K884" s="10" t="s">
         <v>20</v>
       </c>
@@ -39418,17 +39451,17 @@
     </row>
     <row r="885" ht="18.0" customHeight="1">
       <c r="A885" s="6"/>
-      <c r="B885" s="15"/>
+      <c r="B885" s="16"/>
       <c r="C885" s="14"/>
-      <c r="D885" s="19"/>
-      <c r="E885" s="16"/>
-      <c r="F885" s="16"/>
-      <c r="G885" s="16"/>
+      <c r="D885" s="20"/>
+      <c r="E885" s="18"/>
+      <c r="F885" s="18"/>
+      <c r="G885" s="18"/>
       <c r="H885" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I885" s="17"/>
-      <c r="J885" s="17"/>
+      <c r="I885" s="19"/>
+      <c r="J885" s="19"/>
       <c r="K885" s="10" t="s">
         <v>20</v>
       </c>
@@ -39444,17 +39477,17 @@
     </row>
     <row r="886" ht="18.0" customHeight="1">
       <c r="A886" s="6"/>
-      <c r="B886" s="15"/>
+      <c r="B886" s="16"/>
       <c r="C886" s="14"/>
-      <c r="D886" s="19"/>
-      <c r="E886" s="16"/>
-      <c r="F886" s="16"/>
-      <c r="G886" s="16"/>
+      <c r="D886" s="20"/>
+      <c r="E886" s="18"/>
+      <c r="F886" s="18"/>
+      <c r="G886" s="18"/>
       <c r="H886" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I886" s="17"/>
-      <c r="J886" s="17"/>
+      <c r="I886" s="19"/>
+      <c r="J886" s="19"/>
       <c r="K886" s="10" t="s">
         <v>20</v>
       </c>
@@ -39470,17 +39503,17 @@
     </row>
     <row r="887" ht="18.0" customHeight="1">
       <c r="A887" s="6"/>
-      <c r="B887" s="15"/>
+      <c r="B887" s="16"/>
       <c r="C887" s="14"/>
-      <c r="D887" s="19"/>
-      <c r="E887" s="16"/>
-      <c r="F887" s="16"/>
-      <c r="G887" s="16"/>
+      <c r="D887" s="20"/>
+      <c r="E887" s="18"/>
+      <c r="F887" s="18"/>
+      <c r="G887" s="18"/>
       <c r="H887" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I887" s="17"/>
-      <c r="J887" s="17"/>
+      <c r="I887" s="19"/>
+      <c r="J887" s="19"/>
       <c r="K887" s="10" t="s">
         <v>20</v>
       </c>
@@ -39496,17 +39529,17 @@
     </row>
     <row r="888" ht="18.0" customHeight="1">
       <c r="A888" s="6"/>
-      <c r="B888" s="15"/>
+      <c r="B888" s="16"/>
       <c r="C888" s="14"/>
-      <c r="D888" s="19"/>
-      <c r="E888" s="16"/>
-      <c r="F888" s="16"/>
-      <c r="G888" s="16"/>
+      <c r="D888" s="20"/>
+      <c r="E888" s="18"/>
+      <c r="F888" s="18"/>
+      <c r="G888" s="18"/>
       <c r="H888" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I888" s="17"/>
-      <c r="J888" s="17"/>
+      <c r="I888" s="19"/>
+      <c r="J888" s="19"/>
       <c r="K888" s="10" t="s">
         <v>20</v>
       </c>
@@ -39522,17 +39555,17 @@
     </row>
     <row r="889" ht="18.0" customHeight="1">
       <c r="A889" s="6"/>
-      <c r="B889" s="15"/>
+      <c r="B889" s="16"/>
       <c r="C889" s="14"/>
-      <c r="D889" s="19"/>
-      <c r="E889" s="16"/>
-      <c r="F889" s="16"/>
-      <c r="G889" s="16"/>
+      <c r="D889" s="20"/>
+      <c r="E889" s="18"/>
+      <c r="F889" s="18"/>
+      <c r="G889" s="18"/>
       <c r="H889" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I889" s="17"/>
-      <c r="J889" s="17"/>
+      <c r="I889" s="19"/>
+      <c r="J889" s="19"/>
       <c r="K889" s="10" t="s">
         <v>20</v>
       </c>
@@ -39548,17 +39581,17 @@
     </row>
     <row r="890" ht="18.0" customHeight="1">
       <c r="A890" s="6"/>
-      <c r="B890" s="15"/>
+      <c r="B890" s="16"/>
       <c r="C890" s="14"/>
-      <c r="D890" s="19"/>
-      <c r="E890" s="16"/>
-      <c r="F890" s="16"/>
-      <c r="G890" s="16"/>
+      <c r="D890" s="20"/>
+      <c r="E890" s="18"/>
+      <c r="F890" s="18"/>
+      <c r="G890" s="18"/>
       <c r="H890" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I890" s="17"/>
-      <c r="J890" s="17"/>
+      <c r="I890" s="19"/>
+      <c r="J890" s="19"/>
       <c r="K890" s="10" t="s">
         <v>20</v>
       </c>
@@ -39574,17 +39607,17 @@
     </row>
     <row r="891" ht="18.0" customHeight="1">
       <c r="A891" s="6"/>
-      <c r="B891" s="15"/>
+      <c r="B891" s="16"/>
       <c r="C891" s="14"/>
-      <c r="D891" s="19"/>
-      <c r="E891" s="16"/>
-      <c r="F891" s="16"/>
-      <c r="G891" s="16"/>
+      <c r="D891" s="20"/>
+      <c r="E891" s="18"/>
+      <c r="F891" s="18"/>
+      <c r="G891" s="18"/>
       <c r="H891" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I891" s="17"/>
-      <c r="J891" s="17"/>
+      <c r="I891" s="19"/>
+      <c r="J891" s="19"/>
       <c r="K891" s="10" t="s">
         <v>20</v>
       </c>
@@ -39600,17 +39633,17 @@
     </row>
     <row r="892" ht="18.0" customHeight="1">
       <c r="A892" s="6"/>
-      <c r="B892" s="15"/>
+      <c r="B892" s="16"/>
       <c r="C892" s="14"/>
-      <c r="D892" s="19"/>
-      <c r="E892" s="16"/>
-      <c r="F892" s="16"/>
-      <c r="G892" s="16"/>
+      <c r="D892" s="20"/>
+      <c r="E892" s="18"/>
+      <c r="F892" s="18"/>
+      <c r="G892" s="18"/>
       <c r="H892" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I892" s="17"/>
-      <c r="J892" s="17"/>
+      <c r="I892" s="19"/>
+      <c r="J892" s="19"/>
       <c r="K892" s="10" t="s">
         <v>20</v>
       </c>
@@ -39626,17 +39659,17 @@
     </row>
     <row r="893" ht="18.0" customHeight="1">
       <c r="A893" s="6"/>
-      <c r="B893" s="15"/>
+      <c r="B893" s="16"/>
       <c r="C893" s="14"/>
-      <c r="D893" s="19"/>
-      <c r="E893" s="16"/>
-      <c r="F893" s="16"/>
-      <c r="G893" s="16"/>
+      <c r="D893" s="20"/>
+      <c r="E893" s="18"/>
+      <c r="F893" s="18"/>
+      <c r="G893" s="18"/>
       <c r="H893" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I893" s="17"/>
-      <c r="J893" s="17"/>
+      <c r="I893" s="19"/>
+      <c r="J893" s="19"/>
       <c r="K893" s="10" t="s">
         <v>20</v>
       </c>
@@ -39652,17 +39685,17 @@
     </row>
     <row r="894" ht="18.0" customHeight="1">
       <c r="A894" s="6"/>
-      <c r="B894" s="15"/>
+      <c r="B894" s="16"/>
       <c r="C894" s="14"/>
-      <c r="D894" s="19"/>
-      <c r="E894" s="16"/>
-      <c r="F894" s="16"/>
-      <c r="G894" s="16"/>
+      <c r="D894" s="20"/>
+      <c r="E894" s="18"/>
+      <c r="F894" s="18"/>
+      <c r="G894" s="18"/>
       <c r="H894" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I894" s="17"/>
-      <c r="J894" s="17"/>
+      <c r="I894" s="19"/>
+      <c r="J894" s="19"/>
       <c r="K894" s="10" t="s">
         <v>20</v>
       </c>
@@ -39678,17 +39711,17 @@
     </row>
     <row r="895" ht="18.0" customHeight="1">
       <c r="A895" s="6"/>
-      <c r="B895" s="15"/>
+      <c r="B895" s="16"/>
       <c r="C895" s="14"/>
-      <c r="D895" s="19"/>
-      <c r="E895" s="16"/>
-      <c r="F895" s="16"/>
-      <c r="G895" s="16"/>
+      <c r="D895" s="20"/>
+      <c r="E895" s="18"/>
+      <c r="F895" s="18"/>
+      <c r="G895" s="18"/>
       <c r="H895" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I895" s="17"/>
-      <c r="J895" s="17"/>
+      <c r="I895" s="19"/>
+      <c r="J895" s="19"/>
       <c r="K895" s="10" t="s">
         <v>20</v>
       </c>
@@ -39704,17 +39737,17 @@
     </row>
     <row r="896" ht="18.0" customHeight="1">
       <c r="A896" s="6"/>
-      <c r="B896" s="15"/>
+      <c r="B896" s="16"/>
       <c r="C896" s="14"/>
-      <c r="D896" s="19"/>
-      <c r="E896" s="16"/>
-      <c r="F896" s="16"/>
-      <c r="G896" s="16"/>
+      <c r="D896" s="20"/>
+      <c r="E896" s="18"/>
+      <c r="F896" s="18"/>
+      <c r="G896" s="18"/>
       <c r="H896" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I896" s="17"/>
-      <c r="J896" s="17"/>
+      <c r="I896" s="19"/>
+      <c r="J896" s="19"/>
       <c r="K896" s="10" t="s">
         <v>20</v>
       </c>
@@ -39730,17 +39763,17 @@
     </row>
     <row r="897" ht="18.0" customHeight="1">
       <c r="A897" s="6"/>
-      <c r="B897" s="15"/>
+      <c r="B897" s="16"/>
       <c r="C897" s="14"/>
-      <c r="D897" s="19"/>
-      <c r="E897" s="16"/>
-      <c r="F897" s="16"/>
-      <c r="G897" s="16"/>
+      <c r="D897" s="20"/>
+      <c r="E897" s="18"/>
+      <c r="F897" s="18"/>
+      <c r="G897" s="18"/>
       <c r="H897" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I897" s="17"/>
-      <c r="J897" s="17"/>
+      <c r="I897" s="19"/>
+      <c r="J897" s="19"/>
       <c r="K897" s="10" t="s">
         <v>20</v>
       </c>
@@ -39756,17 +39789,17 @@
     </row>
     <row r="898" ht="18.0" customHeight="1">
       <c r="A898" s="6"/>
-      <c r="B898" s="15"/>
+      <c r="B898" s="16"/>
       <c r="C898" s="14"/>
-      <c r="D898" s="19"/>
-      <c r="E898" s="16"/>
-      <c r="F898" s="16"/>
-      <c r="G898" s="16"/>
+      <c r="D898" s="20"/>
+      <c r="E898" s="18"/>
+      <c r="F898" s="18"/>
+      <c r="G898" s="18"/>
       <c r="H898" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I898" s="17"/>
-      <c r="J898" s="17"/>
+      <c r="I898" s="19"/>
+      <c r="J898" s="19"/>
       <c r="K898" s="10" t="s">
         <v>20</v>
       </c>
@@ -39782,17 +39815,17 @@
     </row>
     <row r="899" ht="18.0" customHeight="1">
       <c r="A899" s="6"/>
-      <c r="B899" s="15"/>
+      <c r="B899" s="16"/>
       <c r="C899" s="14"/>
-      <c r="D899" s="19"/>
-      <c r="E899" s="16"/>
-      <c r="F899" s="16"/>
-      <c r="G899" s="16"/>
+      <c r="D899" s="20"/>
+      <c r="E899" s="18"/>
+      <c r="F899" s="18"/>
+      <c r="G899" s="18"/>
       <c r="H899" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I899" s="17"/>
-      <c r="J899" s="17"/>
+      <c r="I899" s="19"/>
+      <c r="J899" s="19"/>
       <c r="K899" s="10" t="s">
         <v>20</v>
       </c>
@@ -39808,17 +39841,17 @@
     </row>
     <row r="900" ht="18.0" customHeight="1">
       <c r="A900" s="6"/>
-      <c r="B900" s="15"/>
+      <c r="B900" s="16"/>
       <c r="C900" s="14"/>
-      <c r="D900" s="19"/>
-      <c r="E900" s="16"/>
-      <c r="F900" s="16"/>
-      <c r="G900" s="16"/>
+      <c r="D900" s="20"/>
+      <c r="E900" s="18"/>
+      <c r="F900" s="18"/>
+      <c r="G900" s="18"/>
       <c r="H900" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I900" s="17"/>
-      <c r="J900" s="17"/>
+      <c r="I900" s="19"/>
+      <c r="J900" s="19"/>
       <c r="K900" s="10" t="s">
         <v>20</v>
       </c>
@@ -39834,17 +39867,17 @@
     </row>
     <row r="901" ht="18.0" customHeight="1">
       <c r="A901" s="6"/>
-      <c r="B901" s="15"/>
+      <c r="B901" s="16"/>
       <c r="C901" s="14"/>
-      <c r="D901" s="19"/>
-      <c r="E901" s="16"/>
-      <c r="F901" s="16"/>
-      <c r="G901" s="16"/>
+      <c r="D901" s="20"/>
+      <c r="E901" s="18"/>
+      <c r="F901" s="18"/>
+      <c r="G901" s="18"/>
       <c r="H901" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I901" s="17"/>
-      <c r="J901" s="17"/>
+      <c r="I901" s="19"/>
+      <c r="J901" s="19"/>
       <c r="K901" s="10" t="s">
         <v>20</v>
       </c>
@@ -39860,17 +39893,17 @@
     </row>
     <row r="902" ht="18.0" customHeight="1">
       <c r="A902" s="6"/>
-      <c r="B902" s="15"/>
+      <c r="B902" s="16"/>
       <c r="C902" s="14"/>
-      <c r="D902" s="19"/>
-      <c r="E902" s="16"/>
-      <c r="F902" s="16"/>
-      <c r="G902" s="16"/>
+      <c r="D902" s="20"/>
+      <c r="E902" s="18"/>
+      <c r="F902" s="18"/>
+      <c r="G902" s="18"/>
       <c r="H902" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I902" s="17"/>
-      <c r="J902" s="17"/>
+      <c r="I902" s="19"/>
+      <c r="J902" s="19"/>
       <c r="K902" s="10" t="s">
         <v>20</v>
       </c>
@@ -39886,17 +39919,17 @@
     </row>
     <row r="903" ht="18.0" customHeight="1">
       <c r="A903" s="6"/>
-      <c r="B903" s="15"/>
+      <c r="B903" s="16"/>
       <c r="C903" s="14"/>
-      <c r="D903" s="19"/>
-      <c r="E903" s="16"/>
-      <c r="F903" s="16"/>
-      <c r="G903" s="16"/>
+      <c r="D903" s="20"/>
+      <c r="E903" s="18"/>
+      <c r="F903" s="18"/>
+      <c r="G903" s="18"/>
       <c r="H903" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I903" s="17"/>
-      <c r="J903" s="17"/>
+      <c r="I903" s="19"/>
+      <c r="J903" s="19"/>
       <c r="K903" s="10" t="s">
         <v>20</v>
       </c>
@@ -39912,17 +39945,17 @@
     </row>
     <row r="904" ht="18.0" customHeight="1">
       <c r="A904" s="6"/>
-      <c r="B904" s="15"/>
+      <c r="B904" s="16"/>
       <c r="C904" s="14"/>
-      <c r="D904" s="19"/>
-      <c r="E904" s="16"/>
-      <c r="F904" s="16"/>
-      <c r="G904" s="16"/>
+      <c r="D904" s="20"/>
+      <c r="E904" s="18"/>
+      <c r="F904" s="18"/>
+      <c r="G904" s="18"/>
       <c r="H904" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I904" s="17"/>
-      <c r="J904" s="17"/>
+      <c r="I904" s="19"/>
+      <c r="J904" s="19"/>
       <c r="K904" s="10" t="s">
         <v>20</v>
       </c>
@@ -39938,17 +39971,17 @@
     </row>
     <row r="905" ht="18.0" customHeight="1">
       <c r="A905" s="6"/>
-      <c r="B905" s="15"/>
+      <c r="B905" s="16"/>
       <c r="C905" s="14"/>
-      <c r="D905" s="19"/>
-      <c r="E905" s="16"/>
-      <c r="F905" s="16"/>
-      <c r="G905" s="16"/>
+      <c r="D905" s="20"/>
+      <c r="E905" s="18"/>
+      <c r="F905" s="18"/>
+      <c r="G905" s="18"/>
       <c r="H905" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I905" s="17"/>
-      <c r="J905" s="17"/>
+      <c r="I905" s="19"/>
+      <c r="J905" s="19"/>
       <c r="K905" s="10" t="s">
         <v>20</v>
       </c>
@@ -39964,17 +39997,17 @@
     </row>
     <row r="906" ht="18.0" customHeight="1">
       <c r="A906" s="6"/>
-      <c r="B906" s="15"/>
+      <c r="B906" s="16"/>
       <c r="C906" s="14"/>
-      <c r="D906" s="19"/>
-      <c r="E906" s="16"/>
-      <c r="F906" s="16"/>
-      <c r="G906" s="16"/>
+      <c r="D906" s="20"/>
+      <c r="E906" s="18"/>
+      <c r="F906" s="18"/>
+      <c r="G906" s="18"/>
       <c r="H906" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I906" s="17"/>
-      <c r="J906" s="17"/>
+      <c r="I906" s="19"/>
+      <c r="J906" s="19"/>
       <c r="K906" s="10" t="s">
         <v>20</v>
       </c>
@@ -39990,17 +40023,17 @@
     </row>
     <row r="907" ht="18.0" customHeight="1">
       <c r="A907" s="6"/>
-      <c r="B907" s="15"/>
+      <c r="B907" s="16"/>
       <c r="C907" s="14"/>
-      <c r="D907" s="19"/>
-      <c r="E907" s="16"/>
-      <c r="F907" s="16"/>
-      <c r="G907" s="16"/>
+      <c r="D907" s="20"/>
+      <c r="E907" s="18"/>
+      <c r="F907" s="18"/>
+      <c r="G907" s="18"/>
       <c r="H907" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I907" s="17"/>
-      <c r="J907" s="17"/>
+      <c r="I907" s="19"/>
+      <c r="J907" s="19"/>
       <c r="K907" s="10" t="s">
         <v>20</v>
       </c>
@@ -40016,17 +40049,17 @@
     </row>
     <row r="908" ht="18.0" customHeight="1">
       <c r="A908" s="6"/>
-      <c r="B908" s="15"/>
+      <c r="B908" s="16"/>
       <c r="C908" s="14"/>
-      <c r="D908" s="19"/>
-      <c r="E908" s="16"/>
-      <c r="F908" s="16"/>
-      <c r="G908" s="16"/>
+      <c r="D908" s="20"/>
+      <c r="E908" s="18"/>
+      <c r="F908" s="18"/>
+      <c r="G908" s="18"/>
       <c r="H908" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I908" s="17"/>
-      <c r="J908" s="17"/>
+      <c r="I908" s="19"/>
+      <c r="J908" s="19"/>
       <c r="K908" s="10" t="s">
         <v>20</v>
       </c>
@@ -40042,17 +40075,17 @@
     </row>
     <row r="909" ht="18.0" customHeight="1">
       <c r="A909" s="6"/>
-      <c r="B909" s="15"/>
+      <c r="B909" s="16"/>
       <c r="C909" s="14"/>
-      <c r="D909" s="19"/>
-      <c r="E909" s="16"/>
-      <c r="F909" s="16"/>
-      <c r="G909" s="16"/>
+      <c r="D909" s="20"/>
+      <c r="E909" s="18"/>
+      <c r="F909" s="18"/>
+      <c r="G909" s="18"/>
       <c r="H909" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I909" s="17"/>
-      <c r="J909" s="17"/>
+      <c r="I909" s="19"/>
+      <c r="J909" s="19"/>
       <c r="K909" s="10" t="s">
         <v>20</v>
       </c>
@@ -40068,17 +40101,17 @@
     </row>
     <row r="910" ht="18.0" customHeight="1">
       <c r="A910" s="6"/>
-      <c r="B910" s="15"/>
+      <c r="B910" s="16"/>
       <c r="C910" s="14"/>
-      <c r="D910" s="19"/>
-      <c r="E910" s="16"/>
-      <c r="F910" s="16"/>
-      <c r="G910" s="16"/>
+      <c r="D910" s="20"/>
+      <c r="E910" s="18"/>
+      <c r="F910" s="18"/>
+      <c r="G910" s="18"/>
       <c r="H910" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I910" s="17"/>
-      <c r="J910" s="17"/>
+      <c r="I910" s="19"/>
+      <c r="J910" s="19"/>
       <c r="K910" s="10" t="s">
         <v>20</v>
       </c>
@@ -40094,17 +40127,17 @@
     </row>
     <row r="911" ht="18.0" customHeight="1">
       <c r="A911" s="6"/>
-      <c r="B911" s="15"/>
+      <c r="B911" s="16"/>
       <c r="C911" s="14"/>
-      <c r="D911" s="19"/>
-      <c r="E911" s="16"/>
-      <c r="F911" s="16"/>
-      <c r="G911" s="16"/>
+      <c r="D911" s="20"/>
+      <c r="E911" s="18"/>
+      <c r="F911" s="18"/>
+      <c r="G911" s="18"/>
       <c r="H911" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I911" s="17"/>
-      <c r="J911" s="17"/>
+      <c r="I911" s="19"/>
+      <c r="J911" s="19"/>
       <c r="K911" s="10" t="s">
         <v>20</v>
       </c>
@@ -40120,17 +40153,17 @@
     </row>
     <row r="912" ht="18.0" customHeight="1">
       <c r="A912" s="6"/>
-      <c r="B912" s="15"/>
+      <c r="B912" s="16"/>
       <c r="C912" s="14"/>
-      <c r="D912" s="19"/>
-      <c r="E912" s="16"/>
-      <c r="F912" s="16"/>
-      <c r="G912" s="16"/>
+      <c r="D912" s="20"/>
+      <c r="E912" s="18"/>
+      <c r="F912" s="18"/>
+      <c r="G912" s="18"/>
       <c r="H912" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I912" s="17"/>
-      <c r="J912" s="17"/>
+      <c r="I912" s="19"/>
+      <c r="J912" s="19"/>
       <c r="K912" s="10" t="s">
         <v>20</v>
       </c>
@@ -40146,17 +40179,17 @@
     </row>
     <row r="913" ht="18.0" customHeight="1">
       <c r="A913" s="6"/>
-      <c r="B913" s="15"/>
+      <c r="B913" s="16"/>
       <c r="C913" s="14"/>
-      <c r="D913" s="19"/>
-      <c r="E913" s="16"/>
-      <c r="F913" s="16"/>
-      <c r="G913" s="16"/>
+      <c r="D913" s="20"/>
+      <c r="E913" s="18"/>
+      <c r="F913" s="18"/>
+      <c r="G913" s="18"/>
       <c r="H913" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I913" s="17"/>
-      <c r="J913" s="17"/>
+      <c r="I913" s="19"/>
+      <c r="J913" s="19"/>
       <c r="K913" s="10" t="s">
         <v>20</v>
       </c>
@@ -40172,17 +40205,17 @@
     </row>
     <row r="914" ht="18.0" customHeight="1">
       <c r="A914" s="6"/>
-      <c r="B914" s="15"/>
+      <c r="B914" s="16"/>
       <c r="C914" s="14"/>
-      <c r="D914" s="19"/>
-      <c r="E914" s="16"/>
-      <c r="F914" s="16"/>
-      <c r="G914" s="16"/>
+      <c r="D914" s="20"/>
+      <c r="E914" s="18"/>
+      <c r="F914" s="18"/>
+      <c r="G914" s="18"/>
       <c r="H914" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I914" s="17"/>
-      <c r="J914" s="17"/>
+      <c r="I914" s="19"/>
+      <c r="J914" s="19"/>
       <c r="K914" s="10" t="s">
         <v>20</v>
       </c>
@@ -40198,17 +40231,17 @@
     </row>
     <row r="915" ht="18.0" customHeight="1">
       <c r="A915" s="6"/>
-      <c r="B915" s="15"/>
+      <c r="B915" s="16"/>
       <c r="C915" s="14"/>
-      <c r="D915" s="19"/>
-      <c r="E915" s="16"/>
-      <c r="F915" s="16"/>
-      <c r="G915" s="16"/>
+      <c r="D915" s="20"/>
+      <c r="E915" s="18"/>
+      <c r="F915" s="18"/>
+      <c r="G915" s="18"/>
       <c r="H915" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I915" s="17"/>
-      <c r="J915" s="17"/>
+      <c r="I915" s="19"/>
+      <c r="J915" s="19"/>
       <c r="K915" s="10" t="s">
         <v>20</v>
       </c>
@@ -40224,17 +40257,17 @@
     </row>
     <row r="916" ht="18.0" customHeight="1">
       <c r="A916" s="6"/>
-      <c r="B916" s="15"/>
+      <c r="B916" s="16"/>
       <c r="C916" s="14"/>
-      <c r="D916" s="19"/>
-      <c r="E916" s="16"/>
-      <c r="F916" s="16"/>
-      <c r="G916" s="16"/>
+      <c r="D916" s="20"/>
+      <c r="E916" s="18"/>
+      <c r="F916" s="18"/>
+      <c r="G916" s="18"/>
       <c r="H916" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I916" s="17"/>
-      <c r="J916" s="17"/>
+      <c r="I916" s="19"/>
+      <c r="J916" s="19"/>
       <c r="K916" s="10" t="s">
         <v>20</v>
       </c>
@@ -40250,17 +40283,17 @@
     </row>
     <row r="917" ht="18.0" customHeight="1">
       <c r="A917" s="6"/>
-      <c r="B917" s="15"/>
+      <c r="B917" s="16"/>
       <c r="C917" s="14"/>
-      <c r="D917" s="19"/>
-      <c r="E917" s="16"/>
-      <c r="F917" s="16"/>
-      <c r="G917" s="16"/>
+      <c r="D917" s="20"/>
+      <c r="E917" s="18"/>
+      <c r="F917" s="18"/>
+      <c r="G917" s="18"/>
       <c r="H917" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I917" s="17"/>
-      <c r="J917" s="17"/>
+      <c r="I917" s="19"/>
+      <c r="J917" s="19"/>
       <c r="K917" s="10" t="s">
         <v>20</v>
       </c>
@@ -40276,17 +40309,17 @@
     </row>
     <row r="918" ht="18.0" customHeight="1">
       <c r="A918" s="6"/>
-      <c r="B918" s="15"/>
+      <c r="B918" s="16"/>
       <c r="C918" s="14"/>
-      <c r="D918" s="19"/>
-      <c r="E918" s="16"/>
-      <c r="F918" s="16"/>
-      <c r="G918" s="16"/>
+      <c r="D918" s="20"/>
+      <c r="E918" s="18"/>
+      <c r="F918" s="18"/>
+      <c r="G918" s="18"/>
       <c r="H918" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I918" s="17"/>
-      <c r="J918" s="17"/>
+      <c r="I918" s="19"/>
+      <c r="J918" s="19"/>
       <c r="K918" s="10" t="s">
         <v>20</v>
       </c>
@@ -40302,17 +40335,17 @@
     </row>
     <row r="919" ht="18.0" customHeight="1">
       <c r="A919" s="6"/>
-      <c r="B919" s="15"/>
+      <c r="B919" s="16"/>
       <c r="C919" s="14"/>
-      <c r="D919" s="19"/>
-      <c r="E919" s="16"/>
-      <c r="F919" s="16"/>
-      <c r="G919" s="16"/>
+      <c r="D919" s="20"/>
+      <c r="E919" s="18"/>
+      <c r="F919" s="18"/>
+      <c r="G919" s="18"/>
       <c r="H919" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I919" s="17"/>
-      <c r="J919" s="17"/>
+      <c r="I919" s="19"/>
+      <c r="J919" s="19"/>
       <c r="K919" s="10" t="s">
         <v>20</v>
       </c>
@@ -40328,17 +40361,17 @@
     </row>
     <row r="920" ht="18.0" customHeight="1">
       <c r="A920" s="6"/>
-      <c r="B920" s="15"/>
+      <c r="B920" s="16"/>
       <c r="C920" s="14"/>
-      <c r="D920" s="19"/>
-      <c r="E920" s="16"/>
-      <c r="F920" s="16"/>
-      <c r="G920" s="16"/>
+      <c r="D920" s="20"/>
+      <c r="E920" s="18"/>
+      <c r="F920" s="18"/>
+      <c r="G920" s="18"/>
       <c r="H920" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I920" s="17"/>
-      <c r="J920" s="17"/>
+      <c r="I920" s="19"/>
+      <c r="J920" s="19"/>
       <c r="K920" s="10" t="s">
         <v>20</v>
       </c>
@@ -40354,17 +40387,17 @@
     </row>
     <row r="921" ht="18.0" customHeight="1">
       <c r="A921" s="6"/>
-      <c r="B921" s="15"/>
+      <c r="B921" s="16"/>
       <c r="C921" s="14"/>
-      <c r="D921" s="19"/>
-      <c r="E921" s="16"/>
-      <c r="F921" s="16"/>
-      <c r="G921" s="16"/>
+      <c r="D921" s="20"/>
+      <c r="E921" s="18"/>
+      <c r="F921" s="18"/>
+      <c r="G921" s="18"/>
       <c r="H921" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I921" s="17"/>
-      <c r="J921" s="17"/>
+      <c r="I921" s="19"/>
+      <c r="J921" s="19"/>
       <c r="K921" s="10" t="s">
         <v>20</v>
       </c>
@@ -40380,17 +40413,17 @@
     </row>
     <row r="922" ht="18.0" customHeight="1">
       <c r="A922" s="6"/>
-      <c r="B922" s="15"/>
+      <c r="B922" s="16"/>
       <c r="C922" s="14"/>
-      <c r="D922" s="19"/>
-      <c r="E922" s="16"/>
-      <c r="F922" s="16"/>
-      <c r="G922" s="16"/>
+      <c r="D922" s="20"/>
+      <c r="E922" s="18"/>
+      <c r="F922" s="18"/>
+      <c r="G922" s="18"/>
       <c r="H922" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I922" s="17"/>
-      <c r="J922" s="17"/>
+      <c r="I922" s="19"/>
+      <c r="J922" s="19"/>
       <c r="K922" s="10" t="s">
         <v>20</v>
       </c>
@@ -40406,17 +40439,17 @@
     </row>
     <row r="923" ht="18.0" customHeight="1">
       <c r="A923" s="6"/>
-      <c r="B923" s="15"/>
+      <c r="B923" s="16"/>
       <c r="C923" s="14"/>
-      <c r="D923" s="19"/>
-      <c r="E923" s="16"/>
-      <c r="F923" s="16"/>
-      <c r="G923" s="16"/>
+      <c r="D923" s="20"/>
+      <c r="E923" s="18"/>
+      <c r="F923" s="18"/>
+      <c r="G923" s="18"/>
       <c r="H923" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I923" s="17"/>
-      <c r="J923" s="17"/>
+      <c r="I923" s="19"/>
+      <c r="J923" s="19"/>
       <c r="K923" s="10" t="s">
         <v>20</v>
       </c>
@@ -40432,17 +40465,17 @@
     </row>
     <row r="924" ht="18.0" customHeight="1">
       <c r="A924" s="6"/>
-      <c r="B924" s="15"/>
+      <c r="B924" s="16"/>
       <c r="C924" s="14"/>
-      <c r="D924" s="19"/>
-      <c r="E924" s="16"/>
-      <c r="F924" s="16"/>
-      <c r="G924" s="16"/>
+      <c r="D924" s="20"/>
+      <c r="E924" s="18"/>
+      <c r="F924" s="18"/>
+      <c r="G924" s="18"/>
       <c r="H924" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I924" s="17"/>
-      <c r="J924" s="17"/>
+      <c r="I924" s="19"/>
+      <c r="J924" s="19"/>
       <c r="K924" s="10" t="s">
         <v>20</v>
       </c>
@@ -40458,17 +40491,17 @@
     </row>
     <row r="925" ht="18.0" customHeight="1">
       <c r="A925" s="6"/>
-      <c r="B925" s="15"/>
+      <c r="B925" s="16"/>
       <c r="C925" s="14"/>
-      <c r="D925" s="19"/>
-      <c r="E925" s="16"/>
-      <c r="F925" s="16"/>
-      <c r="G925" s="16"/>
+      <c r="D925" s="20"/>
+      <c r="E925" s="18"/>
+      <c r="F925" s="18"/>
+      <c r="G925" s="18"/>
       <c r="H925" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I925" s="17"/>
-      <c r="J925" s="17"/>
+      <c r="I925" s="19"/>
+      <c r="J925" s="19"/>
       <c r="K925" s="10" t="s">
         <v>20</v>
       </c>
@@ -40484,17 +40517,17 @@
     </row>
     <row r="926" ht="18.0" customHeight="1">
       <c r="A926" s="6"/>
-      <c r="B926" s="15"/>
+      <c r="B926" s="16"/>
       <c r="C926" s="14"/>
-      <c r="D926" s="19"/>
-      <c r="E926" s="16"/>
-      <c r="F926" s="16"/>
-      <c r="G926" s="16"/>
+      <c r="D926" s="20"/>
+      <c r="E926" s="18"/>
+      <c r="F926" s="18"/>
+      <c r="G926" s="18"/>
       <c r="H926" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I926" s="17"/>
-      <c r="J926" s="17"/>
+      <c r="I926" s="19"/>
+      <c r="J926" s="19"/>
       <c r="K926" s="10" t="s">
         <v>20</v>
       </c>
@@ -40510,17 +40543,17 @@
     </row>
     <row r="927" ht="18.0" customHeight="1">
       <c r="A927" s="6"/>
-      <c r="B927" s="15"/>
+      <c r="B927" s="16"/>
       <c r="C927" s="14"/>
-      <c r="D927" s="19"/>
-      <c r="E927" s="16"/>
-      <c r="F927" s="16"/>
-      <c r="G927" s="16"/>
+      <c r="D927" s="20"/>
+      <c r="E927" s="18"/>
+      <c r="F927" s="18"/>
+      <c r="G927" s="18"/>
       <c r="H927" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I927" s="17"/>
-      <c r="J927" s="17"/>
+      <c r="I927" s="19"/>
+      <c r="J927" s="19"/>
       <c r="K927" s="10" t="s">
         <v>20</v>
       </c>
@@ -40536,17 +40569,17 @@
     </row>
     <row r="928" ht="18.0" customHeight="1">
       <c r="A928" s="6"/>
-      <c r="B928" s="15"/>
+      <c r="B928" s="16"/>
       <c r="C928" s="14"/>
-      <c r="D928" s="19"/>
-      <c r="E928" s="16"/>
-      <c r="F928" s="16"/>
-      <c r="G928" s="16"/>
+      <c r="D928" s="20"/>
+      <c r="E928" s="18"/>
+      <c r="F928" s="18"/>
+      <c r="G928" s="18"/>
       <c r="H928" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I928" s="17"/>
-      <c r="J928" s="17"/>
+      <c r="I928" s="19"/>
+      <c r="J928" s="19"/>
       <c r="K928" s="10" t="s">
         <v>20</v>
       </c>
@@ -40562,17 +40595,17 @@
     </row>
     <row r="929" ht="18.0" customHeight="1">
       <c r="A929" s="6"/>
-      <c r="B929" s="15"/>
+      <c r="B929" s="16"/>
       <c r="C929" s="14"/>
-      <c r="D929" s="19"/>
-      <c r="E929" s="16"/>
-      <c r="F929" s="16"/>
-      <c r="G929" s="16"/>
+      <c r="D929" s="20"/>
+      <c r="E929" s="18"/>
+      <c r="F929" s="18"/>
+      <c r="G929" s="18"/>
       <c r="H929" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I929" s="17"/>
-      <c r="J929" s="17"/>
+      <c r="I929" s="19"/>
+      <c r="J929" s="19"/>
       <c r="K929" s="10" t="s">
         <v>20</v>
       </c>
@@ -40588,17 +40621,17 @@
     </row>
     <row r="930" ht="18.0" customHeight="1">
       <c r="A930" s="6"/>
-      <c r="B930" s="15"/>
+      <c r="B930" s="16"/>
       <c r="C930" s="14"/>
-      <c r="D930" s="19"/>
-      <c r="E930" s="16"/>
-      <c r="F930" s="16"/>
-      <c r="G930" s="16"/>
+      <c r="D930" s="20"/>
+      <c r="E930" s="18"/>
+      <c r="F930" s="18"/>
+      <c r="G930" s="18"/>
       <c r="H930" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I930" s="17"/>
-      <c r="J930" s="17"/>
+      <c r="I930" s="19"/>
+      <c r="J930" s="19"/>
       <c r="K930" s="10" t="s">
         <v>20</v>
       </c>
@@ -40614,17 +40647,17 @@
     </row>
     <row r="931" ht="18.0" customHeight="1">
       <c r="A931" s="6"/>
-      <c r="B931" s="15"/>
+      <c r="B931" s="16"/>
       <c r="C931" s="14"/>
-      <c r="D931" s="19"/>
-      <c r="E931" s="16"/>
-      <c r="F931" s="16"/>
-      <c r="G931" s="16"/>
+      <c r="D931" s="20"/>
+      <c r="E931" s="18"/>
+      <c r="F931" s="18"/>
+      <c r="G931" s="18"/>
       <c r="H931" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I931" s="17"/>
-      <c r="J931" s="17"/>
+      <c r="I931" s="19"/>
+      <c r="J931" s="19"/>
       <c r="K931" s="10" t="s">
         <v>20</v>
       </c>
@@ -40640,17 +40673,17 @@
     </row>
     <row r="932" ht="18.0" customHeight="1">
       <c r="A932" s="6"/>
-      <c r="B932" s="15"/>
+      <c r="B932" s="16"/>
       <c r="C932" s="14"/>
-      <c r="D932" s="19"/>
-      <c r="E932" s="16"/>
-      <c r="F932" s="16"/>
-      <c r="G932" s="16"/>
+      <c r="D932" s="20"/>
+      <c r="E932" s="18"/>
+      <c r="F932" s="18"/>
+      <c r="G932" s="18"/>
       <c r="H932" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I932" s="17"/>
-      <c r="J932" s="17"/>
+      <c r="I932" s="19"/>
+      <c r="J932" s="19"/>
       <c r="K932" s="10" t="s">
         <v>20</v>
       </c>
@@ -40666,17 +40699,17 @@
     </row>
     <row r="933" ht="18.0" customHeight="1">
       <c r="A933" s="6"/>
-      <c r="B933" s="15"/>
+      <c r="B933" s="16"/>
       <c r="C933" s="14"/>
-      <c r="D933" s="19"/>
-      <c r="E933" s="16"/>
-      <c r="F933" s="16"/>
-      <c r="G933" s="16"/>
+      <c r="D933" s="20"/>
+      <c r="E933" s="18"/>
+      <c r="F933" s="18"/>
+      <c r="G933" s="18"/>
       <c r="H933" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I933" s="17"/>
-      <c r="J933" s="17"/>
+      <c r="I933" s="19"/>
+      <c r="J933" s="19"/>
       <c r="K933" s="10" t="s">
         <v>20</v>
       </c>
@@ -40692,17 +40725,17 @@
     </row>
     <row r="934" ht="18.0" customHeight="1">
       <c r="A934" s="6"/>
-      <c r="B934" s="15"/>
+      <c r="B934" s="16"/>
       <c r="C934" s="14"/>
-      <c r="D934" s="19"/>
-      <c r="E934" s="16"/>
-      <c r="F934" s="16"/>
-      <c r="G934" s="16"/>
+      <c r="D934" s="20"/>
+      <c r="E934" s="18"/>
+      <c r="F934" s="18"/>
+      <c r="G934" s="18"/>
       <c r="H934" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I934" s="17"/>
-      <c r="J934" s="17"/>
+      <c r="I934" s="19"/>
+      <c r="J934" s="19"/>
       <c r="K934" s="10" t="s">
         <v>20</v>
       </c>
@@ -40718,17 +40751,17 @@
     </row>
     <row r="935" ht="18.0" customHeight="1">
       <c r="A935" s="6"/>
-      <c r="B935" s="15"/>
+      <c r="B935" s="16"/>
       <c r="C935" s="14"/>
-      <c r="D935" s="19"/>
-      <c r="E935" s="16"/>
-      <c r="F935" s="16"/>
-      <c r="G935" s="16"/>
+      <c r="D935" s="20"/>
+      <c r="E935" s="18"/>
+      <c r="F935" s="18"/>
+      <c r="G935" s="18"/>
       <c r="H935" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I935" s="17"/>
-      <c r="J935" s="17"/>
+      <c r="I935" s="19"/>
+      <c r="J935" s="19"/>
       <c r="K935" s="10" t="s">
         <v>20</v>
       </c>
@@ -40744,17 +40777,17 @@
     </row>
     <row r="936" ht="18.0" customHeight="1">
       <c r="A936" s="6"/>
-      <c r="B936" s="15"/>
+      <c r="B936" s="16"/>
       <c r="C936" s="14"/>
-      <c r="D936" s="19"/>
-      <c r="E936" s="16"/>
-      <c r="F936" s="16"/>
-      <c r="G936" s="16"/>
+      <c r="D936" s="20"/>
+      <c r="E936" s="18"/>
+      <c r="F936" s="18"/>
+      <c r="G936" s="18"/>
       <c r="H936" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I936" s="17"/>
-      <c r="J936" s="17"/>
+      <c r="I936" s="19"/>
+      <c r="J936" s="19"/>
       <c r="K936" s="10" t="s">
         <v>20</v>
       </c>
@@ -40770,17 +40803,17 @@
     </row>
     <row r="937" ht="18.0" customHeight="1">
       <c r="A937" s="6"/>
-      <c r="B937" s="15"/>
+      <c r="B937" s="16"/>
       <c r="C937" s="14"/>
-      <c r="D937" s="19"/>
-      <c r="E937" s="16"/>
-      <c r="F937" s="16"/>
-      <c r="G937" s="16"/>
+      <c r="D937" s="20"/>
+      <c r="E937" s="18"/>
+      <c r="F937" s="18"/>
+      <c r="G937" s="18"/>
       <c r="H937" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I937" s="17"/>
-      <c r="J937" s="17"/>
+      <c r="I937" s="19"/>
+      <c r="J937" s="19"/>
       <c r="K937" s="10" t="s">
         <v>20</v>
       </c>
@@ -40796,17 +40829,17 @@
     </row>
     <row r="938" ht="18.0" customHeight="1">
       <c r="A938" s="6"/>
-      <c r="B938" s="15"/>
+      <c r="B938" s="16"/>
       <c r="C938" s="14"/>
-      <c r="D938" s="19"/>
-      <c r="E938" s="16"/>
-      <c r="F938" s="16"/>
-      <c r="G938" s="16"/>
+      <c r="D938" s="20"/>
+      <c r="E938" s="18"/>
+      <c r="F938" s="18"/>
+      <c r="G938" s="18"/>
       <c r="H938" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I938" s="17"/>
-      <c r="J938" s="17"/>
+      <c r="I938" s="19"/>
+      <c r="J938" s="19"/>
       <c r="K938" s="10" t="s">
         <v>20</v>
       </c>
@@ -40822,17 +40855,17 @@
     </row>
     <row r="939" ht="18.0" customHeight="1">
       <c r="A939" s="6"/>
-      <c r="B939" s="15"/>
+      <c r="B939" s="16"/>
       <c r="C939" s="14"/>
-      <c r="D939" s="19"/>
-      <c r="E939" s="16"/>
-      <c r="F939" s="16"/>
-      <c r="G939" s="16"/>
+      <c r="D939" s="20"/>
+      <c r="E939" s="18"/>
+      <c r="F939" s="18"/>
+      <c r="G939" s="18"/>
       <c r="H939" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I939" s="17"/>
-      <c r="J939" s="17"/>
+      <c r="I939" s="19"/>
+      <c r="J939" s="19"/>
       <c r="K939" s="10" t="s">
         <v>20</v>
       </c>
@@ -40848,17 +40881,17 @@
     </row>
     <row r="940" ht="18.0" customHeight="1">
       <c r="A940" s="6"/>
-      <c r="B940" s="15"/>
+      <c r="B940" s="16"/>
       <c r="C940" s="14"/>
-      <c r="D940" s="19"/>
-      <c r="E940" s="16"/>
-      <c r="F940" s="16"/>
-      <c r="G940" s="16"/>
+      <c r="D940" s="20"/>
+      <c r="E940" s="18"/>
+      <c r="F940" s="18"/>
+      <c r="G940" s="18"/>
       <c r="H940" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I940" s="17"/>
-      <c r="J940" s="17"/>
+      <c r="I940" s="19"/>
+      <c r="J940" s="19"/>
       <c r="K940" s="10" t="s">
         <v>20</v>
       </c>
@@ -40874,17 +40907,17 @@
     </row>
     <row r="941" ht="18.0" customHeight="1">
       <c r="A941" s="6"/>
-      <c r="B941" s="15"/>
+      <c r="B941" s="16"/>
       <c r="C941" s="14"/>
-      <c r="D941" s="19"/>
-      <c r="E941" s="16"/>
-      <c r="F941" s="16"/>
-      <c r="G941" s="16"/>
+      <c r="D941" s="20"/>
+      <c r="E941" s="18"/>
+      <c r="F941" s="18"/>
+      <c r="G941" s="18"/>
       <c r="H941" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I941" s="17"/>
-      <c r="J941" s="17"/>
+      <c r="I941" s="19"/>
+      <c r="J941" s="19"/>
       <c r="K941" s="10" t="s">
         <v>20</v>
       </c>
@@ -40900,17 +40933,17 @@
     </row>
     <row r="942" ht="18.0" customHeight="1">
       <c r="A942" s="6"/>
-      <c r="B942" s="15"/>
+      <c r="B942" s="16"/>
       <c r="C942" s="14"/>
-      <c r="D942" s="19"/>
-      <c r="E942" s="16"/>
-      <c r="F942" s="16"/>
-      <c r="G942" s="16"/>
+      <c r="D942" s="20"/>
+      <c r="E942" s="18"/>
+      <c r="F942" s="18"/>
+      <c r="G942" s="18"/>
       <c r="H942" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I942" s="17"/>
-      <c r="J942" s="17"/>
+      <c r="I942" s="19"/>
+      <c r="J942" s="19"/>
       <c r="K942" s="10" t="s">
         <v>20</v>
       </c>
@@ -40926,17 +40959,17 @@
     </row>
     <row r="943" ht="18.0" customHeight="1">
       <c r="A943" s="6"/>
-      <c r="B943" s="15"/>
+      <c r="B943" s="16"/>
       <c r="C943" s="14"/>
-      <c r="D943" s="19"/>
-      <c r="E943" s="16"/>
-      <c r="F943" s="16"/>
-      <c r="G943" s="16"/>
+      <c r="D943" s="20"/>
+      <c r="E943" s="18"/>
+      <c r="F943" s="18"/>
+      <c r="G943" s="18"/>
       <c r="H943" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I943" s="17"/>
-      <c r="J943" s="17"/>
+      <c r="I943" s="19"/>
+      <c r="J943" s="19"/>
       <c r="K943" s="10" t="s">
         <v>20</v>
       </c>
@@ -40952,17 +40985,17 @@
     </row>
     <row r="944" ht="18.0" customHeight="1">
       <c r="A944" s="6"/>
-      <c r="B944" s="15"/>
+      <c r="B944" s="16"/>
       <c r="C944" s="14"/>
-      <c r="D944" s="19"/>
-      <c r="E944" s="16"/>
-      <c r="F944" s="16"/>
-      <c r="G944" s="16"/>
+      <c r="D944" s="20"/>
+      <c r="E944" s="18"/>
+      <c r="F944" s="18"/>
+      <c r="G944" s="18"/>
       <c r="H944" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I944" s="17"/>
-      <c r="J944" s="17"/>
+      <c r="I944" s="19"/>
+      <c r="J944" s="19"/>
       <c r="K944" s="10" t="s">
         <v>20</v>
       </c>
@@ -40978,17 +41011,17 @@
     </row>
     <row r="945" ht="18.0" customHeight="1">
       <c r="A945" s="6"/>
-      <c r="B945" s="15"/>
+      <c r="B945" s="16"/>
       <c r="C945" s="14"/>
-      <c r="D945" s="19"/>
-      <c r="E945" s="16"/>
-      <c r="F945" s="16"/>
-      <c r="G945" s="16"/>
+      <c r="D945" s="20"/>
+      <c r="E945" s="18"/>
+      <c r="F945" s="18"/>
+      <c r="G945" s="18"/>
       <c r="H945" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I945" s="17"/>
-      <c r="J945" s="17"/>
+      <c r="I945" s="19"/>
+      <c r="J945" s="19"/>
       <c r="K945" s="10" t="s">
         <v>20</v>
       </c>
@@ -41004,17 +41037,17 @@
     </row>
     <row r="946" ht="18.0" customHeight="1">
       <c r="A946" s="6"/>
-      <c r="B946" s="15"/>
+      <c r="B946" s="16"/>
       <c r="C946" s="14"/>
-      <c r="D946" s="19"/>
-      <c r="E946" s="16"/>
-      <c r="F946" s="16"/>
-      <c r="G946" s="16"/>
+      <c r="D946" s="20"/>
+      <c r="E946" s="18"/>
+      <c r="F946" s="18"/>
+      <c r="G946" s="18"/>
       <c r="H946" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I946" s="17"/>
-      <c r="J946" s="17"/>
+      <c r="I946" s="19"/>
+      <c r="J946" s="19"/>
       <c r="K946" s="10" t="s">
         <v>20</v>
       </c>
@@ -41030,17 +41063,17 @@
     </row>
     <row r="947" ht="18.0" customHeight="1">
       <c r="A947" s="6"/>
-      <c r="B947" s="15"/>
+      <c r="B947" s="16"/>
       <c r="C947" s="14"/>
-      <c r="D947" s="19"/>
-      <c r="E947" s="16"/>
-      <c r="F947" s="16"/>
-      <c r="G947" s="16"/>
+      <c r="D947" s="20"/>
+      <c r="E947" s="18"/>
+      <c r="F947" s="18"/>
+      <c r="G947" s="18"/>
       <c r="H947" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I947" s="17"/>
-      <c r="J947" s="17"/>
+      <c r="I947" s="19"/>
+      <c r="J947" s="19"/>
       <c r="K947" s="10" t="s">
         <v>20</v>
       </c>
@@ -41056,17 +41089,17 @@
     </row>
     <row r="948" ht="18.0" customHeight="1">
       <c r="A948" s="6"/>
-      <c r="B948" s="15"/>
+      <c r="B948" s="16"/>
       <c r="C948" s="14"/>
-      <c r="D948" s="19"/>
-      <c r="E948" s="16"/>
-      <c r="F948" s="16"/>
-      <c r="G948" s="16"/>
+      <c r="D948" s="20"/>
+      <c r="E948" s="18"/>
+      <c r="F948" s="18"/>
+      <c r="G948" s="18"/>
       <c r="H948" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I948" s="17"/>
-      <c r="J948" s="17"/>
+      <c r="I948" s="19"/>
+      <c r="J948" s="19"/>
       <c r="K948" s="10" t="s">
         <v>20</v>
       </c>
@@ -41082,17 +41115,17 @@
     </row>
     <row r="949" ht="18.0" customHeight="1">
       <c r="A949" s="6"/>
-      <c r="B949" s="15"/>
+      <c r="B949" s="16"/>
       <c r="C949" s="14"/>
-      <c r="D949" s="19"/>
-      <c r="E949" s="16"/>
-      <c r="F949" s="16"/>
-      <c r="G949" s="16"/>
+      <c r="D949" s="20"/>
+      <c r="E949" s="18"/>
+      <c r="F949" s="18"/>
+      <c r="G949" s="18"/>
       <c r="H949" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I949" s="17"/>
-      <c r="J949" s="17"/>
+      <c r="I949" s="19"/>
+      <c r="J949" s="19"/>
       <c r="K949" s="10" t="s">
         <v>20</v>
       </c>
@@ -41108,17 +41141,17 @@
     </row>
     <row r="950" ht="18.0" customHeight="1">
       <c r="A950" s="6"/>
-      <c r="B950" s="15"/>
+      <c r="B950" s="16"/>
       <c r="C950" s="14"/>
-      <c r="D950" s="19"/>
-      <c r="E950" s="16"/>
-      <c r="F950" s="16"/>
-      <c r="G950" s="16"/>
+      <c r="D950" s="20"/>
+      <c r="E950" s="18"/>
+      <c r="F950" s="18"/>
+      <c r="G950" s="18"/>
       <c r="H950" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I950" s="17"/>
-      <c r="J950" s="17"/>
+      <c r="I950" s="19"/>
+      <c r="J950" s="19"/>
       <c r="K950" s="10" t="s">
         <v>20</v>
       </c>
@@ -41134,17 +41167,17 @@
     </row>
     <row r="951" ht="18.0" customHeight="1">
       <c r="A951" s="6"/>
-      <c r="B951" s="15"/>
+      <c r="B951" s="16"/>
       <c r="C951" s="14"/>
-      <c r="D951" s="19"/>
-      <c r="E951" s="16"/>
-      <c r="F951" s="16"/>
-      <c r="G951" s="16"/>
+      <c r="D951" s="20"/>
+      <c r="E951" s="18"/>
+      <c r="F951" s="18"/>
+      <c r="G951" s="18"/>
       <c r="H951" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I951" s="17"/>
-      <c r="J951" s="17"/>
+      <c r="I951" s="19"/>
+      <c r="J951" s="19"/>
       <c r="K951" s="10" t="s">
         <v>20</v>
       </c>
@@ -41160,17 +41193,17 @@
     </row>
     <row r="952" ht="18.0" customHeight="1">
       <c r="A952" s="6"/>
-      <c r="B952" s="15"/>
+      <c r="B952" s="16"/>
       <c r="C952" s="14"/>
-      <c r="D952" s="19"/>
-      <c r="E952" s="16"/>
-      <c r="F952" s="16"/>
-      <c r="G952" s="16"/>
+      <c r="D952" s="20"/>
+      <c r="E952" s="18"/>
+      <c r="F952" s="18"/>
+      <c r="G952" s="18"/>
       <c r="H952" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I952" s="17"/>
-      <c r="J952" s="17"/>
+      <c r="I952" s="19"/>
+      <c r="J952" s="19"/>
       <c r="K952" s="10" t="s">
         <v>20</v>
       </c>
@@ -41186,17 +41219,17 @@
     </row>
     <row r="953" ht="18.0" customHeight="1">
       <c r="A953" s="6"/>
-      <c r="B953" s="15"/>
+      <c r="B953" s="16"/>
       <c r="C953" s="14"/>
-      <c r="D953" s="19"/>
-      <c r="E953" s="16"/>
-      <c r="F953" s="16"/>
-      <c r="G953" s="16"/>
+      <c r="D953" s="20"/>
+      <c r="E953" s="18"/>
+      <c r="F953" s="18"/>
+      <c r="G953" s="18"/>
       <c r="H953" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I953" s="17"/>
-      <c r="J953" s="17"/>
+      <c r="I953" s="19"/>
+      <c r="J953" s="19"/>
       <c r="K953" s="10" t="s">
         <v>20</v>
       </c>
@@ -41212,17 +41245,17 @@
     </row>
     <row r="954" ht="18.0" customHeight="1">
       <c r="A954" s="6"/>
-      <c r="B954" s="15"/>
+      <c r="B954" s="16"/>
       <c r="C954" s="14"/>
-      <c r="D954" s="19"/>
-      <c r="E954" s="16"/>
-      <c r="F954" s="16"/>
-      <c r="G954" s="16"/>
+      <c r="D954" s="20"/>
+      <c r="E954" s="18"/>
+      <c r="F954" s="18"/>
+      <c r="G954" s="18"/>
       <c r="H954" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I954" s="17"/>
-      <c r="J954" s="17"/>
+      <c r="I954" s="19"/>
+      <c r="J954" s="19"/>
       <c r="K954" s="10" t="s">
         <v>20</v>
       </c>
@@ -41238,17 +41271,17 @@
     </row>
     <row r="955" ht="18.0" customHeight="1">
       <c r="A955" s="6"/>
-      <c r="B955" s="15"/>
+      <c r="B955" s="16"/>
       <c r="C955" s="14"/>
-      <c r="D955" s="19"/>
-      <c r="E955" s="16"/>
-      <c r="F955" s="16"/>
-      <c r="G955" s="16"/>
+      <c r="D955" s="20"/>
+      <c r="E955" s="18"/>
+      <c r="F955" s="18"/>
+      <c r="G955" s="18"/>
       <c r="H955" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I955" s="17"/>
-      <c r="J955" s="17"/>
+      <c r="I955" s="19"/>
+      <c r="J955" s="19"/>
       <c r="K955" s="10" t="s">
         <v>20</v>
       </c>
@@ -41264,17 +41297,17 @@
     </row>
     <row r="956" ht="18.0" customHeight="1">
       <c r="A956" s="6"/>
-      <c r="B956" s="15"/>
+      <c r="B956" s="16"/>
       <c r="C956" s="14"/>
-      <c r="D956" s="19"/>
-      <c r="E956" s="16"/>
-      <c r="F956" s="16"/>
-      <c r="G956" s="16"/>
+      <c r="D956" s="20"/>
+      <c r="E956" s="18"/>
+      <c r="F956" s="18"/>
+      <c r="G956" s="18"/>
       <c r="H956" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I956" s="17"/>
-      <c r="J956" s="17"/>
+      <c r="I956" s="19"/>
+      <c r="J956" s="19"/>
       <c r="K956" s="10" t="s">
         <v>20</v>
       </c>
@@ -41290,17 +41323,17 @@
     </row>
     <row r="957" ht="18.0" customHeight="1">
       <c r="A957" s="6"/>
-      <c r="B957" s="15"/>
+      <c r="B957" s="16"/>
       <c r="C957" s="14"/>
-      <c r="D957" s="19"/>
-      <c r="E957" s="16"/>
-      <c r="F957" s="16"/>
-      <c r="G957" s="16"/>
+      <c r="D957" s="20"/>
+      <c r="E957" s="18"/>
+      <c r="F957" s="18"/>
+      <c r="G957" s="18"/>
       <c r="H957" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I957" s="17"/>
-      <c r="J957" s="17"/>
+      <c r="I957" s="19"/>
+      <c r="J957" s="19"/>
       <c r="K957" s="10" t="s">
         <v>20</v>
       </c>
@@ -41316,17 +41349,17 @@
     </row>
     <row r="958" ht="18.0" customHeight="1">
       <c r="A958" s="6"/>
-      <c r="B958" s="15"/>
+      <c r="B958" s="16"/>
       <c r="C958" s="14"/>
-      <c r="D958" s="19"/>
-      <c r="E958" s="16"/>
-      <c r="F958" s="16"/>
-      <c r="G958" s="16"/>
+      <c r="D958" s="20"/>
+      <c r="E958" s="18"/>
+      <c r="F958" s="18"/>
+      <c r="G958" s="18"/>
       <c r="H958" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I958" s="17"/>
-      <c r="J958" s="17"/>
+      <c r="I958" s="19"/>
+      <c r="J958" s="19"/>
       <c r="K958" s="10" t="s">
         <v>20</v>
       </c>
@@ -41342,17 +41375,17 @@
     </row>
     <row r="959" ht="18.0" customHeight="1">
       <c r="A959" s="6"/>
-      <c r="B959" s="15"/>
+      <c r="B959" s="16"/>
       <c r="C959" s="14"/>
-      <c r="D959" s="19"/>
-      <c r="E959" s="16"/>
-      <c r="F959" s="16"/>
-      <c r="G959" s="16"/>
+      <c r="D959" s="20"/>
+      <c r="E959" s="18"/>
+      <c r="F959" s="18"/>
+      <c r="G959" s="18"/>
       <c r="H959" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I959" s="17"/>
-      <c r="J959" s="17"/>
+      <c r="I959" s="19"/>
+      <c r="J959" s="19"/>
       <c r="K959" s="10" t="s">
         <v>20</v>
       </c>
@@ -41368,17 +41401,17 @@
     </row>
     <row r="960" ht="18.0" customHeight="1">
       <c r="A960" s="6"/>
-      <c r="B960" s="15"/>
+      <c r="B960" s="16"/>
       <c r="C960" s="14"/>
-      <c r="D960" s="19"/>
-      <c r="E960" s="16"/>
-      <c r="F960" s="16"/>
-      <c r="G960" s="16"/>
+      <c r="D960" s="20"/>
+      <c r="E960" s="18"/>
+      <c r="F960" s="18"/>
+      <c r="G960" s="18"/>
       <c r="H960" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I960" s="17"/>
-      <c r="J960" s="17"/>
+      <c r="I960" s="19"/>
+      <c r="J960" s="19"/>
       <c r="K960" s="10" t="s">
         <v>20</v>
       </c>
@@ -41394,17 +41427,17 @@
     </row>
     <row r="961" ht="18.0" customHeight="1">
       <c r="A961" s="6"/>
-      <c r="B961" s="15"/>
+      <c r="B961" s="16"/>
       <c r="C961" s="14"/>
-      <c r="D961" s="19"/>
-      <c r="E961" s="16"/>
-      <c r="F961" s="16"/>
-      <c r="G961" s="16"/>
+      <c r="D961" s="20"/>
+      <c r="E961" s="18"/>
+      <c r="F961" s="18"/>
+      <c r="G961" s="18"/>
       <c r="H961" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I961" s="17"/>
-      <c r="J961" s="17"/>
+      <c r="I961" s="19"/>
+      <c r="J961" s="19"/>
       <c r="K961" s="10" t="s">
         <v>20</v>
       </c>
@@ -41420,17 +41453,17 @@
     </row>
     <row r="962" ht="18.0" customHeight="1">
       <c r="A962" s="6"/>
-      <c r="B962" s="15"/>
+      <c r="B962" s="16"/>
       <c r="C962" s="14"/>
-      <c r="D962" s="19"/>
-      <c r="E962" s="16"/>
-      <c r="F962" s="16"/>
-      <c r="G962" s="16"/>
+      <c r="D962" s="20"/>
+      <c r="E962" s="18"/>
+      <c r="F962" s="18"/>
+      <c r="G962" s="18"/>
       <c r="H962" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I962" s="17"/>
-      <c r="J962" s="17"/>
+      <c r="I962" s="19"/>
+      <c r="J962" s="19"/>
       <c r="K962" s="10" t="s">
         <v>20</v>
       </c>
@@ -41446,17 +41479,17 @@
     </row>
     <row r="963" ht="18.0" customHeight="1">
       <c r="A963" s="6"/>
-      <c r="B963" s="15"/>
+      <c r="B963" s="16"/>
       <c r="C963" s="14"/>
-      <c r="D963" s="19"/>
-      <c r="E963" s="16"/>
-      <c r="F963" s="16"/>
-      <c r="G963" s="16"/>
+      <c r="D963" s="20"/>
+      <c r="E963" s="18"/>
+      <c r="F963" s="18"/>
+      <c r="G963" s="18"/>
       <c r="H963" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I963" s="17"/>
-      <c r="J963" s="17"/>
+      <c r="I963" s="19"/>
+      <c r="J963" s="19"/>
       <c r="K963" s="10" t="s">
         <v>20</v>
       </c>
@@ -41472,17 +41505,17 @@
     </row>
     <row r="964" ht="18.0" customHeight="1">
       <c r="A964" s="6"/>
-      <c r="B964" s="15"/>
+      <c r="B964" s="16"/>
       <c r="C964" s="14"/>
-      <c r="D964" s="19"/>
-      <c r="E964" s="16"/>
-      <c r="F964" s="16"/>
-      <c r="G964" s="16"/>
+      <c r="D964" s="20"/>
+      <c r="E964" s="18"/>
+      <c r="F964" s="18"/>
+      <c r="G964" s="18"/>
       <c r="H964" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I964" s="17"/>
-      <c r="J964" s="17"/>
+      <c r="I964" s="19"/>
+      <c r="J964" s="19"/>
       <c r="K964" s="10" t="s">
         <v>20</v>
       </c>
@@ -41498,17 +41531,17 @@
     </row>
     <row r="965" ht="18.0" customHeight="1">
       <c r="A965" s="6"/>
-      <c r="B965" s="15"/>
+      <c r="B965" s="16"/>
       <c r="C965" s="14"/>
-      <c r="D965" s="19"/>
-      <c r="E965" s="16"/>
-      <c r="F965" s="16"/>
-      <c r="G965" s="16"/>
+      <c r="D965" s="20"/>
+      <c r="E965" s="18"/>
+      <c r="F965" s="18"/>
+      <c r="G965" s="18"/>
       <c r="H965" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I965" s="17"/>
-      <c r="J965" s="17"/>
+      <c r="I965" s="19"/>
+      <c r="J965" s="19"/>
       <c r="K965" s="10" t="s">
         <v>20</v>
       </c>
@@ -41524,17 +41557,17 @@
     </row>
     <row r="966" ht="18.0" customHeight="1">
       <c r="A966" s="6"/>
-      <c r="B966" s="15"/>
+      <c r="B966" s="16"/>
       <c r="C966" s="14"/>
-      <c r="D966" s="19"/>
-      <c r="E966" s="16"/>
-      <c r="F966" s="16"/>
-      <c r="G966" s="16"/>
+      <c r="D966" s="20"/>
+      <c r="E966" s="18"/>
+      <c r="F966" s="18"/>
+      <c r="G966" s="18"/>
       <c r="H966" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I966" s="17"/>
-      <c r="J966" s="17"/>
+      <c r="I966" s="19"/>
+      <c r="J966" s="19"/>
       <c r="K966" s="10" t="s">
         <v>20</v>
       </c>
@@ -41550,17 +41583,17 @@
     </row>
     <row r="967" ht="18.0" customHeight="1">
       <c r="A967" s="6"/>
-      <c r="B967" s="15"/>
+      <c r="B967" s="16"/>
       <c r="C967" s="14"/>
-      <c r="D967" s="19"/>
-      <c r="E967" s="16"/>
-      <c r="F967" s="16"/>
-      <c r="G967" s="16"/>
+      <c r="D967" s="20"/>
+      <c r="E967" s="18"/>
+      <c r="F967" s="18"/>
+      <c r="G967" s="18"/>
       <c r="H967" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I967" s="17"/>
-      <c r="J967" s="17"/>
+      <c r="I967" s="19"/>
+      <c r="J967" s="19"/>
       <c r="K967" s="10" t="s">
         <v>20</v>
       </c>
@@ -41576,17 +41609,17 @@
     </row>
     <row r="968" ht="18.0" customHeight="1">
       <c r="A968" s="6"/>
-      <c r="B968" s="15"/>
+      <c r="B968" s="16"/>
       <c r="C968" s="14"/>
-      <c r="D968" s="19"/>
-      <c r="E968" s="16"/>
-      <c r="F968" s="16"/>
-      <c r="G968" s="16"/>
+      <c r="D968" s="20"/>
+      <c r="E968" s="18"/>
+      <c r="F968" s="18"/>
+      <c r="G968" s="18"/>
       <c r="H968" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I968" s="17"/>
-      <c r="J968" s="17"/>
+      <c r="I968" s="19"/>
+      <c r="J968" s="19"/>
       <c r="K968" s="10" t="s">
         <v>20</v>
       </c>
@@ -41602,17 +41635,17 @@
     </row>
     <row r="969" ht="18.0" customHeight="1">
       <c r="A969" s="6"/>
-      <c r="B969" s="15"/>
+      <c r="B969" s="16"/>
       <c r="C969" s="14"/>
-      <c r="D969" s="19"/>
-      <c r="E969" s="16"/>
-      <c r="F969" s="16"/>
-      <c r="G969" s="16"/>
+      <c r="D969" s="20"/>
+      <c r="E969" s="18"/>
+      <c r="F969" s="18"/>
+      <c r="G969" s="18"/>
       <c r="H969" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I969" s="17"/>
-      <c r="J969" s="17"/>
+      <c r="I969" s="19"/>
+      <c r="J969" s="19"/>
       <c r="K969" s="10" t="s">
         <v>20</v>
       </c>
@@ -41628,17 +41661,17 @@
     </row>
     <row r="970" ht="18.0" customHeight="1">
       <c r="A970" s="6"/>
-      <c r="B970" s="15"/>
+      <c r="B970" s="16"/>
       <c r="C970" s="14"/>
-      <c r="D970" s="19"/>
-      <c r="E970" s="16"/>
-      <c r="F970" s="16"/>
-      <c r="G970" s="16"/>
+      <c r="D970" s="20"/>
+      <c r="E970" s="18"/>
+      <c r="F970" s="18"/>
+      <c r="G970" s="18"/>
       <c r="H970" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I970" s="17"/>
-      <c r="J970" s="17"/>
+      <c r="I970" s="19"/>
+      <c r="J970" s="19"/>
       <c r="K970" s="10" t="s">
         <v>20</v>
       </c>
@@ -41654,17 +41687,17 @@
     </row>
     <row r="971" ht="18.0" customHeight="1">
       <c r="A971" s="6"/>
-      <c r="B971" s="15"/>
+      <c r="B971" s="16"/>
       <c r="C971" s="14"/>
-      <c r="D971" s="19"/>
-      <c r="E971" s="16"/>
-      <c r="F971" s="16"/>
-      <c r="G971" s="16"/>
+      <c r="D971" s="20"/>
+      <c r="E971" s="18"/>
+      <c r="F971" s="18"/>
+      <c r="G971" s="18"/>
       <c r="H971" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I971" s="17"/>
-      <c r="J971" s="17"/>
+      <c r="I971" s="19"/>
+      <c r="J971" s="19"/>
       <c r="K971" s="10" t="s">
         <v>20</v>
       </c>
@@ -41680,17 +41713,17 @@
     </row>
     <row r="972" ht="18.0" customHeight="1">
       <c r="A972" s="6"/>
-      <c r="B972" s="15"/>
+      <c r="B972" s="16"/>
       <c r="C972" s="14"/>
-      <c r="D972" s="19"/>
-      <c r="E972" s="16"/>
-      <c r="F972" s="16"/>
-      <c r="G972" s="16"/>
+      <c r="D972" s="20"/>
+      <c r="E972" s="18"/>
+      <c r="F972" s="18"/>
+      <c r="G972" s="18"/>
       <c r="H972" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I972" s="17"/>
-      <c r="J972" s="17"/>
+      <c r="I972" s="19"/>
+      <c r="J972" s="19"/>
       <c r="K972" s="10" t="s">
         <v>20</v>
       </c>
@@ -41706,17 +41739,17 @@
     </row>
     <row r="973" ht="18.0" customHeight="1">
       <c r="A973" s="6"/>
-      <c r="B973" s="15"/>
+      <c r="B973" s="16"/>
       <c r="C973" s="14"/>
-      <c r="D973" s="19"/>
-      <c r="E973" s="16"/>
-      <c r="F973" s="16"/>
-      <c r="G973" s="16"/>
+      <c r="D973" s="20"/>
+      <c r="E973" s="18"/>
+      <c r="F973" s="18"/>
+      <c r="G973" s="18"/>
       <c r="H973" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I973" s="17"/>
-      <c r="J973" s="17"/>
+      <c r="I973" s="19"/>
+      <c r="J973" s="19"/>
       <c r="K973" s="10" t="s">
         <v>20</v>
       </c>
@@ -41732,17 +41765,17 @@
     </row>
     <row r="974" ht="18.0" customHeight="1">
       <c r="A974" s="6"/>
-      <c r="B974" s="15"/>
+      <c r="B974" s="16"/>
       <c r="C974" s="14"/>
-      <c r="D974" s="19"/>
-      <c r="E974" s="16"/>
-      <c r="F974" s="16"/>
-      <c r="G974" s="16"/>
+      <c r="D974" s="20"/>
+      <c r="E974" s="18"/>
+      <c r="F974" s="18"/>
+      <c r="G974" s="18"/>
       <c r="H974" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I974" s="17"/>
-      <c r="J974" s="17"/>
+      <c r="I974" s="19"/>
+      <c r="J974" s="19"/>
       <c r="K974" s="10" t="s">
         <v>20</v>
       </c>
@@ -41758,17 +41791,17 @@
     </row>
     <row r="975" ht="18.0" customHeight="1">
       <c r="A975" s="6"/>
-      <c r="B975" s="15"/>
+      <c r="B975" s="16"/>
       <c r="C975" s="14"/>
-      <c r="D975" s="19"/>
-      <c r="E975" s="16"/>
-      <c r="F975" s="16"/>
-      <c r="G975" s="16"/>
+      <c r="D975" s="20"/>
+      <c r="E975" s="18"/>
+      <c r="F975" s="18"/>
+      <c r="G975" s="18"/>
       <c r="H975" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I975" s="17"/>
-      <c r="J975" s="17"/>
+      <c r="I975" s="19"/>
+      <c r="J975" s="19"/>
       <c r="K975" s="10" t="s">
         <v>20</v>
       </c>
@@ -41784,17 +41817,17 @@
     </row>
     <row r="976" ht="18.0" customHeight="1">
       <c r="A976" s="6"/>
-      <c r="B976" s="15"/>
+      <c r="B976" s="16"/>
       <c r="C976" s="14"/>
-      <c r="D976" s="19"/>
-      <c r="E976" s="16"/>
-      <c r="F976" s="16"/>
-      <c r="G976" s="16"/>
+      <c r="D976" s="20"/>
+      <c r="E976" s="18"/>
+      <c r="F976" s="18"/>
+      <c r="G976" s="18"/>
       <c r="H976" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I976" s="17"/>
-      <c r="J976" s="17"/>
+      <c r="I976" s="19"/>
+      <c r="J976" s="19"/>
       <c r="K976" s="10" t="s">
         <v>20</v>
       </c>
@@ -41810,17 +41843,17 @@
     </row>
     <row r="977" ht="18.0" customHeight="1">
       <c r="A977" s="6"/>
-      <c r="B977" s="15"/>
+      <c r="B977" s="16"/>
       <c r="C977" s="14"/>
-      <c r="D977" s="19"/>
-      <c r="E977" s="16"/>
-      <c r="F977" s="16"/>
-      <c r="G977" s="16"/>
+      <c r="D977" s="20"/>
+      <c r="E977" s="18"/>
+      <c r="F977" s="18"/>
+      <c r="G977" s="18"/>
       <c r="H977" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I977" s="17"/>
-      <c r="J977" s="17"/>
+      <c r="I977" s="19"/>
+      <c r="J977" s="19"/>
       <c r="K977" s="10" t="s">
         <v>20</v>
       </c>
@@ -41836,17 +41869,17 @@
     </row>
     <row r="978" ht="18.0" customHeight="1">
       <c r="A978" s="6"/>
-      <c r="B978" s="15"/>
+      <c r="B978" s="16"/>
       <c r="C978" s="14"/>
-      <c r="D978" s="19"/>
-      <c r="E978" s="16"/>
-      <c r="F978" s="16"/>
-      <c r="G978" s="16"/>
+      <c r="D978" s="20"/>
+      <c r="E978" s="18"/>
+      <c r="F978" s="18"/>
+      <c r="G978" s="18"/>
       <c r="H978" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I978" s="17"/>
-      <c r="J978" s="17"/>
+      <c r="I978" s="19"/>
+      <c r="J978" s="19"/>
       <c r="K978" s="10" t="s">
         <v>20</v>
       </c>
@@ -41862,17 +41895,17 @@
     </row>
     <row r="979" ht="18.0" customHeight="1">
       <c r="A979" s="6"/>
-      <c r="B979" s="15"/>
+      <c r="B979" s="16"/>
       <c r="C979" s="14"/>
-      <c r="D979" s="19"/>
-      <c r="E979" s="16"/>
-      <c r="F979" s="16"/>
-      <c r="G979" s="16"/>
+      <c r="D979" s="20"/>
+      <c r="E979" s="18"/>
+      <c r="F979" s="18"/>
+      <c r="G979" s="18"/>
       <c r="H979" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I979" s="17"/>
-      <c r="J979" s="17"/>
+      <c r="I979" s="19"/>
+      <c r="J979" s="19"/>
       <c r="K979" s="10" t="s">
         <v>20</v>
       </c>
@@ -41888,17 +41921,17 @@
     </row>
     <row r="980" ht="18.0" customHeight="1">
       <c r="A980" s="6"/>
-      <c r="B980" s="15"/>
+      <c r="B980" s="16"/>
       <c r="C980" s="14"/>
-      <c r="D980" s="19"/>
-      <c r="E980" s="16"/>
-      <c r="F980" s="16"/>
-      <c r="G980" s="16"/>
+      <c r="D980" s="20"/>
+      <c r="E980" s="18"/>
+      <c r="F980" s="18"/>
+      <c r="G980" s="18"/>
       <c r="H980" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I980" s="17"/>
-      <c r="J980" s="17"/>
+      <c r="I980" s="19"/>
+      <c r="J980" s="19"/>
       <c r="K980" s="10" t="s">
         <v>20</v>
       </c>
@@ -41914,17 +41947,17 @@
     </row>
     <row r="981" ht="18.0" customHeight="1">
       <c r="A981" s="6"/>
-      <c r="B981" s="15"/>
+      <c r="B981" s="16"/>
       <c r="C981" s="14"/>
-      <c r="D981" s="19"/>
-      <c r="E981" s="16"/>
-      <c r="F981" s="16"/>
-      <c r="G981" s="16"/>
+      <c r="D981" s="20"/>
+      <c r="E981" s="18"/>
+      <c r="F981" s="18"/>
+      <c r="G981" s="18"/>
       <c r="H981" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I981" s="17"/>
-      <c r="J981" s="17"/>
+      <c r="I981" s="19"/>
+      <c r="J981" s="19"/>
       <c r="K981" s="10" t="s">
         <v>20</v>
       </c>
@@ -41940,17 +41973,17 @@
     </row>
     <row r="982" ht="18.0" customHeight="1">
       <c r="A982" s="6"/>
-      <c r="B982" s="15"/>
+      <c r="B982" s="16"/>
       <c r="C982" s="14"/>
-      <c r="D982" s="19"/>
-      <c r="E982" s="16"/>
-      <c r="F982" s="16"/>
-      <c r="G982" s="16"/>
+      <c r="D982" s="20"/>
+      <c r="E982" s="18"/>
+      <c r="F982" s="18"/>
+      <c r="G982" s="18"/>
       <c r="H982" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I982" s="17"/>
-      <c r="J982" s="17"/>
+      <c r="I982" s="19"/>
+      <c r="J982" s="19"/>
       <c r="K982" s="10" t="s">
         <v>20</v>
       </c>
@@ -41966,17 +41999,17 @@
     </row>
     <row r="983" ht="18.0" customHeight="1">
       <c r="A983" s="6"/>
-      <c r="B983" s="15"/>
+      <c r="B983" s="16"/>
       <c r="C983" s="14"/>
-      <c r="D983" s="19"/>
-      <c r="E983" s="16"/>
-      <c r="F983" s="16"/>
-      <c r="G983" s="16"/>
+      <c r="D983" s="20"/>
+      <c r="E983" s="18"/>
+      <c r="F983" s="18"/>
+      <c r="G983" s="18"/>
       <c r="H983" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I983" s="17"/>
-      <c r="J983" s="17"/>
+      <c r="I983" s="19"/>
+      <c r="J983" s="19"/>
       <c r="K983" s="10" t="s">
         <v>20</v>
       </c>
@@ -41992,17 +42025,17 @@
     </row>
     <row r="984" ht="18.0" customHeight="1">
       <c r="A984" s="6"/>
-      <c r="B984" s="15"/>
+      <c r="B984" s="16"/>
       <c r="C984" s="14"/>
-      <c r="D984" s="19"/>
-      <c r="E984" s="16"/>
-      <c r="F984" s="16"/>
-      <c r="G984" s="16"/>
+      <c r="D984" s="20"/>
+      <c r="E984" s="18"/>
+      <c r="F984" s="18"/>
+      <c r="G984" s="18"/>
       <c r="H984" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I984" s="17"/>
-      <c r="J984" s="17"/>
+      <c r="I984" s="19"/>
+      <c r="J984" s="19"/>
       <c r="K984" s="10" t="s">
         <v>20</v>
       </c>
@@ -42018,17 +42051,17 @@
     </row>
     <row r="985" ht="18.0" customHeight="1">
       <c r="A985" s="6"/>
-      <c r="B985" s="15"/>
+      <c r="B985" s="16"/>
       <c r="C985" s="14"/>
-      <c r="D985" s="19"/>
-      <c r="E985" s="16"/>
-      <c r="F985" s="16"/>
-      <c r="G985" s="16"/>
+      <c r="D985" s="20"/>
+      <c r="E985" s="18"/>
+      <c r="F985" s="18"/>
+      <c r="G985" s="18"/>
       <c r="H985" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I985" s="17"/>
-      <c r="J985" s="17"/>
+      <c r="I985" s="19"/>
+      <c r="J985" s="19"/>
       <c r="K985" s="10" t="s">
         <v>20</v>
       </c>
@@ -42044,17 +42077,17 @@
     </row>
     <row r="986" ht="18.0" customHeight="1">
       <c r="A986" s="6"/>
-      <c r="B986" s="15"/>
+      <c r="B986" s="16"/>
       <c r="C986" s="14"/>
-      <c r="D986" s="19"/>
-      <c r="E986" s="16"/>
-      <c r="F986" s="16"/>
-      <c r="G986" s="16"/>
+      <c r="D986" s="20"/>
+      <c r="E986" s="18"/>
+      <c r="F986" s="18"/>
+      <c r="G986" s="18"/>
       <c r="H986" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I986" s="17"/>
-      <c r="J986" s="17"/>
+      <c r="I986" s="19"/>
+      <c r="J986" s="19"/>
       <c r="K986" s="10" t="s">
         <v>20</v>
       </c>
@@ -42070,17 +42103,17 @@
     </row>
     <row r="987" ht="18.0" customHeight="1">
       <c r="A987" s="6"/>
-      <c r="B987" s="15"/>
+      <c r="B987" s="16"/>
       <c r="C987" s="14"/>
-      <c r="D987" s="19"/>
-      <c r="E987" s="16"/>
-      <c r="F987" s="16"/>
-      <c r="G987" s="16"/>
+      <c r="D987" s="20"/>
+      <c r="E987" s="18"/>
+      <c r="F987" s="18"/>
+      <c r="G987" s="18"/>
       <c r="H987" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I987" s="17"/>
-      <c r="J987" s="17"/>
+      <c r="I987" s="19"/>
+      <c r="J987" s="19"/>
       <c r="K987" s="10" t="s">
         <v>20</v>
       </c>
@@ -42096,17 +42129,17 @@
     </row>
     <row r="988" ht="18.0" customHeight="1">
       <c r="A988" s="6"/>
-      <c r="B988" s="15"/>
+      <c r="B988" s="16"/>
       <c r="C988" s="14"/>
-      <c r="D988" s="19"/>
-      <c r="E988" s="16"/>
-      <c r="F988" s="16"/>
-      <c r="G988" s="16"/>
+      <c r="D988" s="20"/>
+      <c r="E988" s="18"/>
+      <c r="F988" s="18"/>
+      <c r="G988" s="18"/>
       <c r="H988" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I988" s="17"/>
-      <c r="J988" s="17"/>
+      <c r="I988" s="19"/>
+      <c r="J988" s="19"/>
       <c r="K988" s="10" t="s">
         <v>20</v>
       </c>
@@ -42122,17 +42155,17 @@
     </row>
     <row r="989" ht="18.0" customHeight="1">
       <c r="A989" s="6"/>
-      <c r="B989" s="15"/>
+      <c r="B989" s="16"/>
       <c r="C989" s="14"/>
-      <c r="D989" s="19"/>
-      <c r="E989" s="16"/>
-      <c r="F989" s="16"/>
-      <c r="G989" s="16"/>
+      <c r="D989" s="20"/>
+      <c r="E989" s="18"/>
+      <c r="F989" s="18"/>
+      <c r="G989" s="18"/>
       <c r="H989" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I989" s="17"/>
-      <c r="J989" s="17"/>
+      <c r="I989" s="19"/>
+      <c r="J989" s="19"/>
       <c r="K989" s="10" t="s">
         <v>20</v>
       </c>
@@ -42148,17 +42181,17 @@
     </row>
     <row r="990" ht="18.0" customHeight="1">
       <c r="A990" s="6"/>
-      <c r="B990" s="15"/>
+      <c r="B990" s="16"/>
       <c r="C990" s="14"/>
-      <c r="D990" s="19"/>
-      <c r="E990" s="16"/>
-      <c r="F990" s="16"/>
-      <c r="G990" s="16"/>
+      <c r="D990" s="20"/>
+      <c r="E990" s="18"/>
+      <c r="F990" s="18"/>
+      <c r="G990" s="18"/>
       <c r="H990" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I990" s="17"/>
-      <c r="J990" s="17"/>
+      <c r="I990" s="19"/>
+      <c r="J990" s="19"/>
       <c r="K990" s="10" t="s">
         <v>20</v>
       </c>
@@ -42174,17 +42207,17 @@
     </row>
     <row r="991" ht="18.0" customHeight="1">
       <c r="A991" s="6"/>
-      <c r="B991" s="15"/>
+      <c r="B991" s="16"/>
       <c r="C991" s="14"/>
-      <c r="D991" s="19"/>
-      <c r="E991" s="16"/>
-      <c r="F991" s="16"/>
-      <c r="G991" s="16"/>
+      <c r="D991" s="20"/>
+      <c r="E991" s="18"/>
+      <c r="F991" s="18"/>
+      <c r="G991" s="18"/>
       <c r="H991" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I991" s="17"/>
-      <c r="J991" s="17"/>
+      <c r="I991" s="19"/>
+      <c r="J991" s="19"/>
       <c r="K991" s="10" t="s">
         <v>20</v>
       </c>
@@ -42200,17 +42233,17 @@
     </row>
     <row r="992" ht="18.0" customHeight="1">
       <c r="A992" s="6"/>
-      <c r="B992" s="15"/>
+      <c r="B992" s="16"/>
       <c r="C992" s="14"/>
-      <c r="D992" s="19"/>
-      <c r="E992" s="16"/>
-      <c r="F992" s="16"/>
-      <c r="G992" s="16"/>
+      <c r="D992" s="20"/>
+      <c r="E992" s="18"/>
+      <c r="F992" s="18"/>
+      <c r="G992" s="18"/>
       <c r="H992" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I992" s="17"/>
-      <c r="J992" s="17"/>
+      <c r="I992" s="19"/>
+      <c r="J992" s="19"/>
       <c r="K992" s="10" t="s">
         <v>20</v>
       </c>
@@ -42226,17 +42259,17 @@
     </row>
     <row r="993" ht="18.0" customHeight="1">
       <c r="A993" s="6"/>
-      <c r="B993" s="15"/>
+      <c r="B993" s="16"/>
       <c r="C993" s="14"/>
-      <c r="D993" s="19"/>
-      <c r="E993" s="16"/>
-      <c r="F993" s="16"/>
-      <c r="G993" s="16"/>
+      <c r="D993" s="20"/>
+      <c r="E993" s="18"/>
+      <c r="F993" s="18"/>
+      <c r="G993" s="18"/>
       <c r="H993" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I993" s="17"/>
-      <c r="J993" s="17"/>
+      <c r="I993" s="19"/>
+      <c r="J993" s="19"/>
       <c r="K993" s="10" t="s">
         <v>20</v>
       </c>
@@ -42252,17 +42285,17 @@
     </row>
     <row r="994" ht="18.0" customHeight="1">
       <c r="A994" s="6"/>
-      <c r="B994" s="15"/>
+      <c r="B994" s="16"/>
       <c r="C994" s="14"/>
-      <c r="D994" s="19"/>
-      <c r="E994" s="16"/>
-      <c r="F994" s="16"/>
-      <c r="G994" s="16"/>
+      <c r="D994" s="20"/>
+      <c r="E994" s="18"/>
+      <c r="F994" s="18"/>
+      <c r="G994" s="18"/>
       <c r="H994" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I994" s="17"/>
-      <c r="J994" s="17"/>
+      <c r="I994" s="19"/>
+      <c r="J994" s="19"/>
       <c r="K994" s="10" t="s">
         <v>20</v>
       </c>
@@ -42278,17 +42311,17 @@
     </row>
     <row r="995" ht="18.0" customHeight="1">
       <c r="A995" s="6"/>
-      <c r="B995" s="15"/>
+      <c r="B995" s="16"/>
       <c r="C995" s="14"/>
-      <c r="D995" s="19"/>
-      <c r="E995" s="16"/>
-      <c r="F995" s="16"/>
-      <c r="G995" s="16"/>
+      <c r="D995" s="20"/>
+      <c r="E995" s="18"/>
+      <c r="F995" s="18"/>
+      <c r="G995" s="18"/>
       <c r="H995" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I995" s="17"/>
-      <c r="J995" s="17"/>
+      <c r="I995" s="19"/>
+      <c r="J995" s="19"/>
       <c r="K995" s="10" t="s">
         <v>20</v>
       </c>
@@ -42304,17 +42337,17 @@
     </row>
     <row r="996" ht="18.0" customHeight="1">
       <c r="A996" s="6"/>
-      <c r="B996" s="15"/>
+      <c r="B996" s="16"/>
       <c r="C996" s="14"/>
-      <c r="D996" s="19"/>
-      <c r="E996" s="16"/>
-      <c r="F996" s="16"/>
-      <c r="G996" s="16"/>
+      <c r="D996" s="20"/>
+      <c r="E996" s="18"/>
+      <c r="F996" s="18"/>
+      <c r="G996" s="18"/>
       <c r="H996" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I996" s="17"/>
-      <c r="J996" s="17"/>
+      <c r="I996" s="19"/>
+      <c r="J996" s="19"/>
       <c r="K996" s="10" t="s">
         <v>20</v>
       </c>
@@ -42330,17 +42363,17 @@
     </row>
     <row r="997" ht="18.0" customHeight="1">
       <c r="A997" s="6"/>
-      <c r="B997" s="15"/>
+      <c r="B997" s="16"/>
       <c r="C997" s="14"/>
-      <c r="D997" s="19"/>
-      <c r="E997" s="16"/>
-      <c r="F997" s="16"/>
-      <c r="G997" s="16"/>
+      <c r="D997" s="20"/>
+      <c r="E997" s="18"/>
+      <c r="F997" s="18"/>
+      <c r="G997" s="18"/>
       <c r="H997" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I997" s="17"/>
-      <c r="J997" s="17"/>
+      <c r="I997" s="19"/>
+      <c r="J997" s="19"/>
       <c r="K997" s="10" t="s">
         <v>20</v>
       </c>
@@ -42356,17 +42389,17 @@
     </row>
     <row r="998" ht="18.0" customHeight="1">
       <c r="A998" s="6"/>
-      <c r="B998" s="15"/>
+      <c r="B998" s="16"/>
       <c r="C998" s="14"/>
-      <c r="D998" s="19"/>
-      <c r="E998" s="16"/>
-      <c r="F998" s="16"/>
-      <c r="G998" s="16"/>
+      <c r="D998" s="20"/>
+      <c r="E998" s="18"/>
+      <c r="F998" s="18"/>
+      <c r="G998" s="18"/>
       <c r="H998" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I998" s="17"/>
-      <c r="J998" s="17"/>
+      <c r="I998" s="19"/>
+      <c r="J998" s="19"/>
       <c r="K998" s="10" t="s">
         <v>20</v>
       </c>
@@ -42382,17 +42415,17 @@
     </row>
     <row r="999" ht="18.0" customHeight="1">
       <c r="A999" s="6"/>
-      <c r="B999" s="15"/>
+      <c r="B999" s="16"/>
       <c r="C999" s="14"/>
-      <c r="D999" s="19"/>
-      <c r="E999" s="16"/>
-      <c r="F999" s="16"/>
-      <c r="G999" s="16"/>
+      <c r="D999" s="20"/>
+      <c r="E999" s="18"/>
+      <c r="F999" s="18"/>
+      <c r="G999" s="18"/>
       <c r="H999" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I999" s="17"/>
-      <c r="J999" s="17"/>
+      <c r="I999" s="19"/>
+      <c r="J999" s="19"/>
       <c r="K999" s="10" t="s">
         <v>20</v>
       </c>
@@ -42408,17 +42441,17 @@
     </row>
     <row r="1000" ht="18.0" customHeight="1">
       <c r="A1000" s="6"/>
-      <c r="B1000" s="15"/>
+      <c r="B1000" s="16"/>
       <c r="C1000" s="14"/>
-      <c r="D1000" s="19"/>
-      <c r="E1000" s="16"/>
-      <c r="F1000" s="16"/>
-      <c r="G1000" s="16"/>
+      <c r="D1000" s="20"/>
+      <c r="E1000" s="18"/>
+      <c r="F1000" s="18"/>
+      <c r="G1000" s="18"/>
       <c r="H1000" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I1000" s="17"/>
-      <c r="J1000" s="17"/>
+      <c r="I1000" s="19"/>
+      <c r="J1000" s="19"/>
       <c r="K1000" s="10" t="s">
         <v>20</v>
       </c>
